--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G69">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G78">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G134">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G145">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G174">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU184"/>
+  <dimension ref="A1:AU186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G41">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-28 19:30:00</t>
+          <t>2026-08-28 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-28 20:00:00</t>
+          <t>2026-08-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G120">
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-28 20:30:00</t>
+          <t>2026-08-28 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G142">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,22 +25206,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G169">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G175">
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G182">
@@ -30091,27 +30091,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G183">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-28 22:00:00</t>
+          <t>2026-08-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -30254,156 +30254,482 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Teleoptik</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Voždovac</t>
+        </is>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>0</v>
+      </c>
+      <c r="Q184">
+        <v>0</v>
+      </c>
+      <c r="R184">
+        <v>0</v>
+      </c>
+      <c r="S184">
+        <v>0</v>
+      </c>
+      <c r="T184">
+        <v>0</v>
+      </c>
+      <c r="U184">
+        <v>0</v>
+      </c>
+      <c r="V184">
+        <v>0</v>
+      </c>
+      <c r="W184">
+        <v>0</v>
+      </c>
+      <c r="X184">
+        <v>0</v>
+      </c>
+      <c r="Y184">
+        <v>0</v>
+      </c>
+      <c r="Z184">
+        <v>0</v>
+      </c>
+      <c r="AA184">
+        <v>0</v>
+      </c>
+      <c r="AB184">
+        <v>0</v>
+      </c>
+      <c r="AC184">
+        <v>0</v>
+      </c>
+      <c r="AD184">
+        <v>0</v>
+      </c>
+      <c r="AE184">
+        <v>0</v>
+      </c>
+      <c r="AF184">
+        <v>0</v>
+      </c>
+      <c r="AG184">
+        <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ184">
+        <v>0</v>
+      </c>
+      <c r="AK184">
+        <v>0</v>
+      </c>
+      <c r="AL184">
+        <v>0</v>
+      </c>
+      <c r="AM184">
+        <v>-1</v>
+      </c>
+      <c r="AN184">
+        <v>-1</v>
+      </c>
+      <c r="AO184">
+        <v>-1</v>
+      </c>
+      <c r="AP184">
+        <v>-1</v>
+      </c>
+      <c r="AQ184">
+        <v>0</v>
+      </c>
+      <c r="AR184">
+        <v>0</v>
+      </c>
+      <c r="AS184">
+        <v>0</v>
+      </c>
+      <c r="AT184">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>2026-08-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors</t>
+        </is>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>0</v>
+      </c>
+      <c r="Q185">
+        <v>0</v>
+      </c>
+      <c r="R185">
+        <v>0</v>
+      </c>
+      <c r="S185">
+        <v>0</v>
+      </c>
+      <c r="T185">
+        <v>0</v>
+      </c>
+      <c r="U185">
+        <v>0</v>
+      </c>
+      <c r="V185">
+        <v>0</v>
+      </c>
+      <c r="W185">
+        <v>0</v>
+      </c>
+      <c r="X185">
+        <v>0</v>
+      </c>
+      <c r="Y185">
+        <v>0</v>
+      </c>
+      <c r="Z185">
+        <v>0</v>
+      </c>
+      <c r="AA185">
+        <v>0</v>
+      </c>
+      <c r="AB185">
+        <v>0</v>
+      </c>
+      <c r="AC185">
+        <v>0</v>
+      </c>
+      <c r="AD185">
+        <v>0</v>
+      </c>
+      <c r="AE185">
+        <v>0</v>
+      </c>
+      <c r="AF185">
+        <v>0</v>
+      </c>
+      <c r="AG185">
+        <v>0</v>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ185">
+        <v>0</v>
+      </c>
+      <c r="AK185">
+        <v>0</v>
+      </c>
+      <c r="AL185">
+        <v>0</v>
+      </c>
+      <c r="AM185">
+        <v>-1</v>
+      </c>
+      <c r="AN185">
+        <v>-1</v>
+      </c>
+      <c r="AO185">
+        <v>-1</v>
+      </c>
+      <c r="AP185">
+        <v>-1</v>
+      </c>
+      <c r="AQ185">
+        <v>0</v>
+      </c>
+      <c r="AR185">
+        <v>0</v>
+      </c>
+      <c r="AS185">
+        <v>0</v>
+      </c>
+      <c r="AT185">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Racing Louisville</t>
         </is>
       </c>
-      <c r="G184">
-        <v>0</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-      <c r="I184">
-        <v>0</v>
-      </c>
-      <c r="J184">
-        <v>0</v>
-      </c>
-      <c r="K184">
-        <v>0</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
-      <c r="M184" t="inlineStr">
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N184">
-        <v>0</v>
-      </c>
-      <c r="O184">
-        <v>0</v>
-      </c>
-      <c r="P184">
-        <v>0</v>
-      </c>
-      <c r="Q184">
-        <v>0</v>
-      </c>
-      <c r="R184">
-        <v>0</v>
-      </c>
-      <c r="S184">
-        <v>0</v>
-      </c>
-      <c r="T184">
-        <v>0</v>
-      </c>
-      <c r="U184">
-        <v>0</v>
-      </c>
-      <c r="V184">
-        <v>0</v>
-      </c>
-      <c r="W184">
-        <v>0</v>
-      </c>
-      <c r="X184">
-        <v>0</v>
-      </c>
-      <c r="Y184">
-        <v>0</v>
-      </c>
-      <c r="Z184">
-        <v>0</v>
-      </c>
-      <c r="AA184">
-        <v>0</v>
-      </c>
-      <c r="AB184">
-        <v>0</v>
-      </c>
-      <c r="AC184">
-        <v>0</v>
-      </c>
-      <c r="AD184">
-        <v>0</v>
-      </c>
-      <c r="AE184">
-        <v>0</v>
-      </c>
-      <c r="AF184">
-        <v>0</v>
-      </c>
-      <c r="AG184">
-        <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ184">
-        <v>0</v>
-      </c>
-      <c r="AK184">
-        <v>0</v>
-      </c>
-      <c r="AL184">
-        <v>0</v>
-      </c>
-      <c r="AM184">
-        <v>-1</v>
-      </c>
-      <c r="AN184">
-        <v>-1</v>
-      </c>
-      <c r="AO184">
-        <v>-1</v>
-      </c>
-      <c r="AP184">
-        <v>-1</v>
-      </c>
-      <c r="AQ184">
-        <v>0</v>
-      </c>
-      <c r="AR184">
-        <v>0</v>
-      </c>
-      <c r="AS184">
-        <v>0</v>
-      </c>
-      <c r="AT184">
-        <v>0</v>
-      </c>
-      <c r="AU184" t="inlineStr">
+      <c r="N186">
+        <v>0</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+      <c r="P186">
+        <v>0</v>
+      </c>
+      <c r="Q186">
+        <v>0</v>
+      </c>
+      <c r="R186">
+        <v>0</v>
+      </c>
+      <c r="S186">
+        <v>0</v>
+      </c>
+      <c r="T186">
+        <v>0</v>
+      </c>
+      <c r="U186">
+        <v>0</v>
+      </c>
+      <c r="V186">
+        <v>0</v>
+      </c>
+      <c r="W186">
+        <v>0</v>
+      </c>
+      <c r="X186">
+        <v>0</v>
+      </c>
+      <c r="Y186">
+        <v>0</v>
+      </c>
+      <c r="Z186">
+        <v>0</v>
+      </c>
+      <c r="AA186">
+        <v>0</v>
+      </c>
+      <c r="AB186">
+        <v>0</v>
+      </c>
+      <c r="AC186">
+        <v>0</v>
+      </c>
+      <c r="AD186">
+        <v>0</v>
+      </c>
+      <c r="AE186">
+        <v>0</v>
+      </c>
+      <c r="AF186">
+        <v>0</v>
+      </c>
+      <c r="AG186">
+        <v>0</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ186">
+        <v>0</v>
+      </c>
+      <c r="AK186">
+        <v>0</v>
+      </c>
+      <c r="AL186">
+        <v>0</v>
+      </c>
+      <c r="AM186">
+        <v>-1</v>
+      </c>
+      <c r="AN186">
+        <v>-1</v>
+      </c>
+      <c r="AO186">
+        <v>-1</v>
+      </c>
+      <c r="AP186">
+        <v>-1</v>
+      </c>
+      <c r="AQ186">
+        <v>0</v>
+      </c>
+      <c r="AR186">
+        <v>0</v>
+      </c>
+      <c r="AS186">
+        <v>0</v>
+      </c>
+      <c r="AT186">
+        <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
         <is>
           <t>2026-08-28 23:00:00</t>
         </is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G39">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G135">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G146">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G183">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G184">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G101">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G112">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G140">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G153">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G168">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G94">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G111">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G121">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G128">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G121">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G135">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G140">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G153">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G171">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G174">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G176">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="G146">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="G32">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-28 13:00:00</t>
+          <t>2026-08-28 13:15:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-28 13:15:00</t>
+          <t>2026-08-28 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G42">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-28 13:30:00</t>
+          <t>2026-08-28 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="G51">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-08-28 14:00:00</t>
+          <t>2026-08-28 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G57">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-28 14:30:00</t>
+          <t>2026-08-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G77">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-08-28 15:00:00</t>
+          <t>2026-08-28 15:15:00</t>
         </is>
       </c>
     </row>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Aluminij</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>Koper</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Aluminij</t>
         </is>
       </c>
       <c r="G79">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G89">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G101">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G123">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G128">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G56">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU186"/>
+  <dimension ref="A1:AU160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-08-28 12:30:00</t>
+          <t>2026-08-28 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G20">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G77">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:00</t>
+          <t>2026-08-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:00</t>
+          <t>2026-08-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G82">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-28 15:30:00</t>
+          <t>2026-08-28 15:15:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-28 15:30:00</t>
+          <t>2026-08-28 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G90">
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-28 15:45:00</t>
+          <t>2026-08-28 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-28 15:45:00</t>
+          <t>2026-08-28 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G103">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-08-28 16:00:00</t>
+          <t>2026-08-28 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-08-28 16:00:00</t>
+          <t>2026-08-28 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G112">
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-08-28 16:15:00</t>
+          <t>2026-08-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-08-28 16:15:00</t>
+          <t>2026-08-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-08-28 16:30:00</t>
+          <t>2026-08-28 16:15:00</t>
         </is>
       </c>
     </row>
@@ -19170,12 +19170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-28 17:00:00</t>
+          <t>2026-08-28 16:15:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-28 17:30:00</t>
+          <t>2026-08-28 16:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-08-28 19:30:00</t>
+          <t>2026-08-28 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-28 19:30:00</t>
+          <t>2026-08-28 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-28 20:00:00</t>
+          <t>2026-08-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-28 20:00:00</t>
+          <t>2026-08-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,12 +20148,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G122">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-28 20:30:00</t>
+          <t>2026-08-28 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20311,12 +20311,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-28 20:30:00</t>
+          <t>2026-08-28 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 20:30:00</t>
         </is>
       </c>
     </row>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G142">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G143">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G158">
@@ -26179,27 +26179,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G159">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 22:00:00</t>
         </is>
       </c>
     </row>
@@ -26342,27 +26342,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G160">
@@ -26492,4244 +26492,6 @@
         <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>CS Sfaxien</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Zarzis</t>
-        </is>
-      </c>
-      <c r="G161">
-        <v>0</v>
-      </c>
-      <c r="H161">
-        <v>0</v>
-      </c>
-      <c r="I161">
-        <v>0</v>
-      </c>
-      <c r="J161">
-        <v>0</v>
-      </c>
-      <c r="K161">
-        <v>0</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N161">
-        <v>0</v>
-      </c>
-      <c r="O161">
-        <v>0</v>
-      </c>
-      <c r="P161">
-        <v>0</v>
-      </c>
-      <c r="Q161">
-        <v>0</v>
-      </c>
-      <c r="R161">
-        <v>0</v>
-      </c>
-      <c r="S161">
-        <v>0</v>
-      </c>
-      <c r="T161">
-        <v>0</v>
-      </c>
-      <c r="U161">
-        <v>0</v>
-      </c>
-      <c r="V161">
-        <v>0</v>
-      </c>
-      <c r="W161">
-        <v>0</v>
-      </c>
-      <c r="X161">
-        <v>0</v>
-      </c>
-      <c r="Y161">
-        <v>0</v>
-      </c>
-      <c r="Z161">
-        <v>0</v>
-      </c>
-      <c r="AA161">
-        <v>0</v>
-      </c>
-      <c r="AB161">
-        <v>0</v>
-      </c>
-      <c r="AC161">
-        <v>0</v>
-      </c>
-      <c r="AD161">
-        <v>0</v>
-      </c>
-      <c r="AE161">
-        <v>0</v>
-      </c>
-      <c r="AF161">
-        <v>0</v>
-      </c>
-      <c r="AG161">
-        <v>0</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ161">
-        <v>0</v>
-      </c>
-      <c r="AK161">
-        <v>0</v>
-      </c>
-      <c r="AL161">
-        <v>0</v>
-      </c>
-      <c r="AM161">
-        <v>-1</v>
-      </c>
-      <c r="AN161">
-        <v>-1</v>
-      </c>
-      <c r="AO161">
-        <v>-1</v>
-      </c>
-      <c r="AP161">
-        <v>-1</v>
-      </c>
-      <c r="AQ161">
-        <v>0</v>
-      </c>
-      <c r="AR161">
-        <v>0</v>
-      </c>
-      <c r="AS161">
-        <v>0</v>
-      </c>
-      <c r="AT161">
-        <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Etoile du Sahel</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Métlaoui</t>
-        </is>
-      </c>
-      <c r="G162">
-        <v>0</v>
-      </c>
-      <c r="H162">
-        <v>0</v>
-      </c>
-      <c r="I162">
-        <v>0</v>
-      </c>
-      <c r="J162">
-        <v>0</v>
-      </c>
-      <c r="K162">
-        <v>0</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
-      <c r="O162">
-        <v>0</v>
-      </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <v>0</v>
-      </c>
-      <c r="R162">
-        <v>0</v>
-      </c>
-      <c r="S162">
-        <v>0</v>
-      </c>
-      <c r="T162">
-        <v>0</v>
-      </c>
-      <c r="U162">
-        <v>0</v>
-      </c>
-      <c r="V162">
-        <v>0</v>
-      </c>
-      <c r="W162">
-        <v>0</v>
-      </c>
-      <c r="X162">
-        <v>0</v>
-      </c>
-      <c r="Y162">
-        <v>0</v>
-      </c>
-      <c r="Z162">
-        <v>0</v>
-      </c>
-      <c r="AA162">
-        <v>0</v>
-      </c>
-      <c r="AB162">
-        <v>0</v>
-      </c>
-      <c r="AC162">
-        <v>0</v>
-      </c>
-      <c r="AD162">
-        <v>0</v>
-      </c>
-      <c r="AE162">
-        <v>0</v>
-      </c>
-      <c r="AF162">
-        <v>0</v>
-      </c>
-      <c r="AG162">
-        <v>0</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>0</v>
-      </c>
-      <c r="AK162">
-        <v>0</v>
-      </c>
-      <c r="AL162">
-        <v>0</v>
-      </c>
-      <c r="AM162">
-        <v>-1</v>
-      </c>
-      <c r="AN162">
-        <v>-1</v>
-      </c>
-      <c r="AO162">
-        <v>-1</v>
-      </c>
-      <c r="AP162">
-        <v>-1</v>
-      </c>
-      <c r="AQ162">
-        <v>0</v>
-      </c>
-      <c r="AR162">
-        <v>0</v>
-      </c>
-      <c r="AS162">
-        <v>0</v>
-      </c>
-      <c r="AT162">
-        <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Marsa</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Progrès Sakiet Eddaïer</t>
-        </is>
-      </c>
-      <c r="G163">
-        <v>0</v>
-      </c>
-      <c r="H163">
-        <v>0</v>
-      </c>
-      <c r="I163">
-        <v>0</v>
-      </c>
-      <c r="J163">
-        <v>0</v>
-      </c>
-      <c r="K163">
-        <v>0</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N163">
-        <v>0</v>
-      </c>
-      <c r="O163">
-        <v>0</v>
-      </c>
-      <c r="P163">
-        <v>0</v>
-      </c>
-      <c r="Q163">
-        <v>0</v>
-      </c>
-      <c r="R163">
-        <v>0</v>
-      </c>
-      <c r="S163">
-        <v>0</v>
-      </c>
-      <c r="T163">
-        <v>0</v>
-      </c>
-      <c r="U163">
-        <v>0</v>
-      </c>
-      <c r="V163">
-        <v>0</v>
-      </c>
-      <c r="W163">
-        <v>0</v>
-      </c>
-      <c r="X163">
-        <v>0</v>
-      </c>
-      <c r="Y163">
-        <v>0</v>
-      </c>
-      <c r="Z163">
-        <v>0</v>
-      </c>
-      <c r="AA163">
-        <v>0</v>
-      </c>
-      <c r="AB163">
-        <v>0</v>
-      </c>
-      <c r="AC163">
-        <v>0</v>
-      </c>
-      <c r="AD163">
-        <v>0</v>
-      </c>
-      <c r="AE163">
-        <v>0</v>
-      </c>
-      <c r="AF163">
-        <v>0</v>
-      </c>
-      <c r="AG163">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ163">
-        <v>0</v>
-      </c>
-      <c r="AK163">
-        <v>0</v>
-      </c>
-      <c r="AL163">
-        <v>0</v>
-      </c>
-      <c r="AM163">
-        <v>-1</v>
-      </c>
-      <c r="AN163">
-        <v>-1</v>
-      </c>
-      <c r="AO163">
-        <v>-1</v>
-      </c>
-      <c r="AP163">
-        <v>-1</v>
-      </c>
-      <c r="AQ163">
-        <v>0</v>
-      </c>
-      <c r="AR163">
-        <v>0</v>
-      </c>
-      <c r="AS163">
-        <v>0</v>
-      </c>
-      <c r="AT163">
-        <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Istra 1961</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Dinamo Zagreb</t>
-        </is>
-      </c>
-      <c r="G164">
-        <v>0</v>
-      </c>
-      <c r="H164">
-        <v>0</v>
-      </c>
-      <c r="I164">
-        <v>0</v>
-      </c>
-      <c r="J164">
-        <v>0</v>
-      </c>
-      <c r="K164">
-        <v>0</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N164">
-        <v>0</v>
-      </c>
-      <c r="O164">
-        <v>0</v>
-      </c>
-      <c r="P164">
-        <v>0</v>
-      </c>
-      <c r="Q164">
-        <v>0</v>
-      </c>
-      <c r="R164">
-        <v>0</v>
-      </c>
-      <c r="S164">
-        <v>0</v>
-      </c>
-      <c r="T164">
-        <v>0</v>
-      </c>
-      <c r="U164">
-        <v>0</v>
-      </c>
-      <c r="V164">
-        <v>0</v>
-      </c>
-      <c r="W164">
-        <v>0</v>
-      </c>
-      <c r="X164">
-        <v>0</v>
-      </c>
-      <c r="Y164">
-        <v>0</v>
-      </c>
-      <c r="Z164">
-        <v>0</v>
-      </c>
-      <c r="AA164">
-        <v>0</v>
-      </c>
-      <c r="AB164">
-        <v>0</v>
-      </c>
-      <c r="AC164">
-        <v>0</v>
-      </c>
-      <c r="AD164">
-        <v>0</v>
-      </c>
-      <c r="AE164">
-        <v>0</v>
-      </c>
-      <c r="AF164">
-        <v>0</v>
-      </c>
-      <c r="AG164">
-        <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ164">
-        <v>0</v>
-      </c>
-      <c r="AK164">
-        <v>0</v>
-      </c>
-      <c r="AL164">
-        <v>0</v>
-      </c>
-      <c r="AM164">
-        <v>-1</v>
-      </c>
-      <c r="AN164">
-        <v>-1</v>
-      </c>
-      <c r="AO164">
-        <v>-1</v>
-      </c>
-      <c r="AP164">
-        <v>-1</v>
-      </c>
-      <c r="AQ164">
-        <v>0</v>
-      </c>
-      <c r="AR164">
-        <v>0</v>
-      </c>
-      <c r="AS164">
-        <v>0</v>
-      </c>
-      <c r="AT164">
-        <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Lokomotiva Zagreb</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Hajduk Split</t>
-        </is>
-      </c>
-      <c r="G165">
-        <v>0</v>
-      </c>
-      <c r="H165">
-        <v>0</v>
-      </c>
-      <c r="I165">
-        <v>0</v>
-      </c>
-      <c r="J165">
-        <v>0</v>
-      </c>
-      <c r="K165">
-        <v>0</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N165">
-        <v>0</v>
-      </c>
-      <c r="O165">
-        <v>0</v>
-      </c>
-      <c r="P165">
-        <v>0</v>
-      </c>
-      <c r="Q165">
-        <v>0</v>
-      </c>
-      <c r="R165">
-        <v>0</v>
-      </c>
-      <c r="S165">
-        <v>0</v>
-      </c>
-      <c r="T165">
-        <v>0</v>
-      </c>
-      <c r="U165">
-        <v>0</v>
-      </c>
-      <c r="V165">
-        <v>0</v>
-      </c>
-      <c r="W165">
-        <v>0</v>
-      </c>
-      <c r="X165">
-        <v>0</v>
-      </c>
-      <c r="Y165">
-        <v>0</v>
-      </c>
-      <c r="Z165">
-        <v>0</v>
-      </c>
-      <c r="AA165">
-        <v>0</v>
-      </c>
-      <c r="AB165">
-        <v>0</v>
-      </c>
-      <c r="AC165">
-        <v>0</v>
-      </c>
-      <c r="AD165">
-        <v>0</v>
-      </c>
-      <c r="AE165">
-        <v>0</v>
-      </c>
-      <c r="AF165">
-        <v>0</v>
-      </c>
-      <c r="AG165">
-        <v>0</v>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ165">
-        <v>0</v>
-      </c>
-      <c r="AK165">
-        <v>0</v>
-      </c>
-      <c r="AL165">
-        <v>0</v>
-      </c>
-      <c r="AM165">
-        <v>-1</v>
-      </c>
-      <c r="AN165">
-        <v>-1</v>
-      </c>
-      <c r="AO165">
-        <v>-1</v>
-      </c>
-      <c r="AP165">
-        <v>-1</v>
-      </c>
-      <c r="AQ165">
-        <v>0</v>
-      </c>
-      <c r="AR165">
-        <v>0</v>
-      </c>
-      <c r="AS165">
-        <v>0</v>
-      </c>
-      <c r="AT165">
-        <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Gorica</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Rijeka</t>
-        </is>
-      </c>
-      <c r="G166">
-        <v>0</v>
-      </c>
-      <c r="H166">
-        <v>0</v>
-      </c>
-      <c r="I166">
-        <v>0</v>
-      </c>
-      <c r="J166">
-        <v>0</v>
-      </c>
-      <c r="K166">
-        <v>0</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N166">
-        <v>0</v>
-      </c>
-      <c r="O166">
-        <v>0</v>
-      </c>
-      <c r="P166">
-        <v>0</v>
-      </c>
-      <c r="Q166">
-        <v>0</v>
-      </c>
-      <c r="R166">
-        <v>0</v>
-      </c>
-      <c r="S166">
-        <v>0</v>
-      </c>
-      <c r="T166">
-        <v>0</v>
-      </c>
-      <c r="U166">
-        <v>0</v>
-      </c>
-      <c r="V166">
-        <v>0</v>
-      </c>
-      <c r="W166">
-        <v>0</v>
-      </c>
-      <c r="X166">
-        <v>0</v>
-      </c>
-      <c r="Y166">
-        <v>0</v>
-      </c>
-      <c r="Z166">
-        <v>0</v>
-      </c>
-      <c r="AA166">
-        <v>0</v>
-      </c>
-      <c r="AB166">
-        <v>0</v>
-      </c>
-      <c r="AC166">
-        <v>0</v>
-      </c>
-      <c r="AD166">
-        <v>0</v>
-      </c>
-      <c r="AE166">
-        <v>0</v>
-      </c>
-      <c r="AF166">
-        <v>0</v>
-      </c>
-      <c r="AG166">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ166">
-        <v>0</v>
-      </c>
-      <c r="AK166">
-        <v>0</v>
-      </c>
-      <c r="AL166">
-        <v>0</v>
-      </c>
-      <c r="AM166">
-        <v>-1</v>
-      </c>
-      <c r="AN166">
-        <v>-1</v>
-      </c>
-      <c r="AO166">
-        <v>-1</v>
-      </c>
-      <c r="AP166">
-        <v>-1</v>
-      </c>
-      <c r="AQ166">
-        <v>0</v>
-      </c>
-      <c r="AR166">
-        <v>0</v>
-      </c>
-      <c r="AS166">
-        <v>0</v>
-      </c>
-      <c r="AT166">
-        <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Osijek</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Slaven Koprivnica</t>
-        </is>
-      </c>
-      <c r="G167">
-        <v>0</v>
-      </c>
-      <c r="H167">
-        <v>0</v>
-      </c>
-      <c r="I167">
-        <v>0</v>
-      </c>
-      <c r="J167">
-        <v>0</v>
-      </c>
-      <c r="K167">
-        <v>0</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N167">
-        <v>0</v>
-      </c>
-      <c r="O167">
-        <v>0</v>
-      </c>
-      <c r="P167">
-        <v>0</v>
-      </c>
-      <c r="Q167">
-        <v>0</v>
-      </c>
-      <c r="R167">
-        <v>0</v>
-      </c>
-      <c r="S167">
-        <v>0</v>
-      </c>
-      <c r="T167">
-        <v>0</v>
-      </c>
-      <c r="U167">
-        <v>0</v>
-      </c>
-      <c r="V167">
-        <v>0</v>
-      </c>
-      <c r="W167">
-        <v>0</v>
-      </c>
-      <c r="X167">
-        <v>0</v>
-      </c>
-      <c r="Y167">
-        <v>0</v>
-      </c>
-      <c r="Z167">
-        <v>0</v>
-      </c>
-      <c r="AA167">
-        <v>0</v>
-      </c>
-      <c r="AB167">
-        <v>0</v>
-      </c>
-      <c r="AC167">
-        <v>0</v>
-      </c>
-      <c r="AD167">
-        <v>0</v>
-      </c>
-      <c r="AE167">
-        <v>0</v>
-      </c>
-      <c r="AF167">
-        <v>0</v>
-      </c>
-      <c r="AG167">
-        <v>0</v>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ167">
-        <v>0</v>
-      </c>
-      <c r="AK167">
-        <v>0</v>
-      </c>
-      <c r="AL167">
-        <v>0</v>
-      </c>
-      <c r="AM167">
-        <v>-1</v>
-      </c>
-      <c r="AN167">
-        <v>-1</v>
-      </c>
-      <c r="AO167">
-        <v>-1</v>
-      </c>
-      <c r="AP167">
-        <v>-1</v>
-      </c>
-      <c r="AQ167">
-        <v>0</v>
-      </c>
-      <c r="AR167">
-        <v>0</v>
-      </c>
-      <c r="AS167">
-        <v>0</v>
-      </c>
-      <c r="AT167">
-        <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Croatia Prva HNL</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Varaždin</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Rudeš</t>
-        </is>
-      </c>
-      <c r="G168">
-        <v>0</v>
-      </c>
-      <c r="H168">
-        <v>0</v>
-      </c>
-      <c r="I168">
-        <v>0</v>
-      </c>
-      <c r="J168">
-        <v>0</v>
-      </c>
-      <c r="K168">
-        <v>0</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N168">
-        <v>0</v>
-      </c>
-      <c r="O168">
-        <v>0</v>
-      </c>
-      <c r="P168">
-        <v>0</v>
-      </c>
-      <c r="Q168">
-        <v>0</v>
-      </c>
-      <c r="R168">
-        <v>0</v>
-      </c>
-      <c r="S168">
-        <v>0</v>
-      </c>
-      <c r="T168">
-        <v>0</v>
-      </c>
-      <c r="U168">
-        <v>0</v>
-      </c>
-      <c r="V168">
-        <v>0</v>
-      </c>
-      <c r="W168">
-        <v>0</v>
-      </c>
-      <c r="X168">
-        <v>0</v>
-      </c>
-      <c r="Y168">
-        <v>0</v>
-      </c>
-      <c r="Z168">
-        <v>0</v>
-      </c>
-      <c r="AA168">
-        <v>0</v>
-      </c>
-      <c r="AB168">
-        <v>0</v>
-      </c>
-      <c r="AC168">
-        <v>0</v>
-      </c>
-      <c r="AD168">
-        <v>0</v>
-      </c>
-      <c r="AE168">
-        <v>0</v>
-      </c>
-      <c r="AF168">
-        <v>0</v>
-      </c>
-      <c r="AG168">
-        <v>0</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>0</v>
-      </c>
-      <c r="AK168">
-        <v>0</v>
-      </c>
-      <c r="AL168">
-        <v>0</v>
-      </c>
-      <c r="AM168">
-        <v>-1</v>
-      </c>
-      <c r="AN168">
-        <v>-1</v>
-      </c>
-      <c r="AO168">
-        <v>-1</v>
-      </c>
-      <c r="AP168">
-        <v>-1</v>
-      </c>
-      <c r="AQ168">
-        <v>0</v>
-      </c>
-      <c r="AR168">
-        <v>0</v>
-      </c>
-      <c r="AS168">
-        <v>0</v>
-      </c>
-      <c r="AT168">
-        <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Universitatea Cluj</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Petrolul 52</t>
-        </is>
-      </c>
-      <c r="G169">
-        <v>0</v>
-      </c>
-      <c r="H169">
-        <v>0</v>
-      </c>
-      <c r="I169">
-        <v>0</v>
-      </c>
-      <c r="J169">
-        <v>0</v>
-      </c>
-      <c r="K169">
-        <v>0</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N169">
-        <v>0</v>
-      </c>
-      <c r="O169">
-        <v>0</v>
-      </c>
-      <c r="P169">
-        <v>0</v>
-      </c>
-      <c r="Q169">
-        <v>0</v>
-      </c>
-      <c r="R169">
-        <v>0</v>
-      </c>
-      <c r="S169">
-        <v>0</v>
-      </c>
-      <c r="T169">
-        <v>0</v>
-      </c>
-      <c r="U169">
-        <v>0</v>
-      </c>
-      <c r="V169">
-        <v>0</v>
-      </c>
-      <c r="W169">
-        <v>0</v>
-      </c>
-      <c r="X169">
-        <v>0</v>
-      </c>
-      <c r="Y169">
-        <v>0</v>
-      </c>
-      <c r="Z169">
-        <v>0</v>
-      </c>
-      <c r="AA169">
-        <v>0</v>
-      </c>
-      <c r="AB169">
-        <v>0</v>
-      </c>
-      <c r="AC169">
-        <v>0</v>
-      </c>
-      <c r="AD169">
-        <v>0</v>
-      </c>
-      <c r="AE169">
-        <v>0</v>
-      </c>
-      <c r="AF169">
-        <v>0</v>
-      </c>
-      <c r="AG169">
-        <v>0</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ169">
-        <v>0</v>
-      </c>
-      <c r="AK169">
-        <v>0</v>
-      </c>
-      <c r="AL169">
-        <v>0</v>
-      </c>
-      <c r="AM169">
-        <v>-1</v>
-      </c>
-      <c r="AN169">
-        <v>-1</v>
-      </c>
-      <c r="AO169">
-        <v>-1</v>
-      </c>
-      <c r="AP169">
-        <v>-1</v>
-      </c>
-      <c r="AQ169">
-        <v>0</v>
-      </c>
-      <c r="AR169">
-        <v>0</v>
-      </c>
-      <c r="AS169">
-        <v>0</v>
-      </c>
-      <c r="AT169">
-        <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>SSC Farul</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Botoşani</t>
-        </is>
-      </c>
-      <c r="G170">
-        <v>0</v>
-      </c>
-      <c r="H170">
-        <v>0</v>
-      </c>
-      <c r="I170">
-        <v>0</v>
-      </c>
-      <c r="J170">
-        <v>0</v>
-      </c>
-      <c r="K170">
-        <v>0</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N170">
-        <v>0</v>
-      </c>
-      <c r="O170">
-        <v>0</v>
-      </c>
-      <c r="P170">
-        <v>0</v>
-      </c>
-      <c r="Q170">
-        <v>0</v>
-      </c>
-      <c r="R170">
-        <v>0</v>
-      </c>
-      <c r="S170">
-        <v>0</v>
-      </c>
-      <c r="T170">
-        <v>0</v>
-      </c>
-      <c r="U170">
-        <v>0</v>
-      </c>
-      <c r="V170">
-        <v>0</v>
-      </c>
-      <c r="W170">
-        <v>0</v>
-      </c>
-      <c r="X170">
-        <v>0</v>
-      </c>
-      <c r="Y170">
-        <v>0</v>
-      </c>
-      <c r="Z170">
-        <v>0</v>
-      </c>
-      <c r="AA170">
-        <v>0</v>
-      </c>
-      <c r="AB170">
-        <v>0</v>
-      </c>
-      <c r="AC170">
-        <v>0</v>
-      </c>
-      <c r="AD170">
-        <v>0</v>
-      </c>
-      <c r="AE170">
-        <v>0</v>
-      </c>
-      <c r="AF170">
-        <v>0</v>
-      </c>
-      <c r="AG170">
-        <v>0</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ170">
-        <v>0</v>
-      </c>
-      <c r="AK170">
-        <v>0</v>
-      </c>
-      <c r="AL170">
-        <v>0</v>
-      </c>
-      <c r="AM170">
-        <v>-1</v>
-      </c>
-      <c r="AN170">
-        <v>-1</v>
-      </c>
-      <c r="AO170">
-        <v>-1</v>
-      </c>
-      <c r="AP170">
-        <v>-1</v>
-      </c>
-      <c r="AQ170">
-        <v>0</v>
-      </c>
-      <c r="AR170">
-        <v>0</v>
-      </c>
-      <c r="AS170">
-        <v>0</v>
-      </c>
-      <c r="AT170">
-        <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>FCSB</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>UTA Arad</t>
-        </is>
-      </c>
-      <c r="G171">
-        <v>0</v>
-      </c>
-      <c r="H171">
-        <v>0</v>
-      </c>
-      <c r="I171">
-        <v>0</v>
-      </c>
-      <c r="J171">
-        <v>0</v>
-      </c>
-      <c r="K171">
-        <v>0</v>
-      </c>
-      <c r="L171">
-        <v>0</v>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N171">
-        <v>0</v>
-      </c>
-      <c r="O171">
-        <v>0</v>
-      </c>
-      <c r="P171">
-        <v>0</v>
-      </c>
-      <c r="Q171">
-        <v>0</v>
-      </c>
-      <c r="R171">
-        <v>0</v>
-      </c>
-      <c r="S171">
-        <v>0</v>
-      </c>
-      <c r="T171">
-        <v>0</v>
-      </c>
-      <c r="U171">
-        <v>0</v>
-      </c>
-      <c r="V171">
-        <v>0</v>
-      </c>
-      <c r="W171">
-        <v>0</v>
-      </c>
-      <c r="X171">
-        <v>0</v>
-      </c>
-      <c r="Y171">
-        <v>0</v>
-      </c>
-      <c r="Z171">
-        <v>0</v>
-      </c>
-      <c r="AA171">
-        <v>0</v>
-      </c>
-      <c r="AB171">
-        <v>0</v>
-      </c>
-      <c r="AC171">
-        <v>0</v>
-      </c>
-      <c r="AD171">
-        <v>0</v>
-      </c>
-      <c r="AE171">
-        <v>0</v>
-      </c>
-      <c r="AF171">
-        <v>0</v>
-      </c>
-      <c r="AG171">
-        <v>0</v>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ171">
-        <v>0</v>
-      </c>
-      <c r="AK171">
-        <v>0</v>
-      </c>
-      <c r="AL171">
-        <v>0</v>
-      </c>
-      <c r="AM171">
-        <v>-1</v>
-      </c>
-      <c r="AN171">
-        <v>-1</v>
-      </c>
-      <c r="AO171">
-        <v>-1</v>
-      </c>
-      <c r="AP171">
-        <v>-1</v>
-      </c>
-      <c r="AQ171">
-        <v>0</v>
-      </c>
-      <c r="AR171">
-        <v>0</v>
-      </c>
-      <c r="AS171">
-        <v>0</v>
-      </c>
-      <c r="AT171">
-        <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Voluntari</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Oţelul Galaţi</t>
-        </is>
-      </c>
-      <c r="G172">
-        <v>0</v>
-      </c>
-      <c r="H172">
-        <v>0</v>
-      </c>
-      <c r="I172">
-        <v>0</v>
-      </c>
-      <c r="J172">
-        <v>0</v>
-      </c>
-      <c r="K172">
-        <v>0</v>
-      </c>
-      <c r="L172">
-        <v>0</v>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N172">
-        <v>0</v>
-      </c>
-      <c r="O172">
-        <v>0</v>
-      </c>
-      <c r="P172">
-        <v>0</v>
-      </c>
-      <c r="Q172">
-        <v>0</v>
-      </c>
-      <c r="R172">
-        <v>0</v>
-      </c>
-      <c r="S172">
-        <v>0</v>
-      </c>
-      <c r="T172">
-        <v>0</v>
-      </c>
-      <c r="U172">
-        <v>0</v>
-      </c>
-      <c r="V172">
-        <v>0</v>
-      </c>
-      <c r="W172">
-        <v>0</v>
-      </c>
-      <c r="X172">
-        <v>0</v>
-      </c>
-      <c r="Y172">
-        <v>0</v>
-      </c>
-      <c r="Z172">
-        <v>0</v>
-      </c>
-      <c r="AA172">
-        <v>0</v>
-      </c>
-      <c r="AB172">
-        <v>0</v>
-      </c>
-      <c r="AC172">
-        <v>0</v>
-      </c>
-      <c r="AD172">
-        <v>0</v>
-      </c>
-      <c r="AE172">
-        <v>0</v>
-      </c>
-      <c r="AF172">
-        <v>0</v>
-      </c>
-      <c r="AG172">
-        <v>0</v>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ172">
-        <v>0</v>
-      </c>
-      <c r="AK172">
-        <v>0</v>
-      </c>
-      <c r="AL172">
-        <v>0</v>
-      </c>
-      <c r="AM172">
-        <v>-1</v>
-      </c>
-      <c r="AN172">
-        <v>-1</v>
-      </c>
-      <c r="AO172">
-        <v>-1</v>
-      </c>
-      <c r="AP172">
-        <v>-1</v>
-      </c>
-      <c r="AQ172">
-        <v>0</v>
-      </c>
-      <c r="AR172">
-        <v>0</v>
-      </c>
-      <c r="AS172">
-        <v>0</v>
-      </c>
-      <c r="AT172">
-        <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Rapid Bucureşti</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>CS U Craiova</t>
-        </is>
-      </c>
-      <c r="G173">
-        <v>0</v>
-      </c>
-      <c r="H173">
-        <v>0</v>
-      </c>
-      <c r="I173">
-        <v>0</v>
-      </c>
-      <c r="J173">
-        <v>0</v>
-      </c>
-      <c r="K173">
-        <v>0</v>
-      </c>
-      <c r="L173">
-        <v>0</v>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N173">
-        <v>0</v>
-      </c>
-      <c r="O173">
-        <v>0</v>
-      </c>
-      <c r="P173">
-        <v>0</v>
-      </c>
-      <c r="Q173">
-        <v>0</v>
-      </c>
-      <c r="R173">
-        <v>0</v>
-      </c>
-      <c r="S173">
-        <v>0</v>
-      </c>
-      <c r="T173">
-        <v>0</v>
-      </c>
-      <c r="U173">
-        <v>0</v>
-      </c>
-      <c r="V173">
-        <v>0</v>
-      </c>
-      <c r="W173">
-        <v>0</v>
-      </c>
-      <c r="X173">
-        <v>0</v>
-      </c>
-      <c r="Y173">
-        <v>0</v>
-      </c>
-      <c r="Z173">
-        <v>0</v>
-      </c>
-      <c r="AA173">
-        <v>0</v>
-      </c>
-      <c r="AB173">
-        <v>0</v>
-      </c>
-      <c r="AC173">
-        <v>0</v>
-      </c>
-      <c r="AD173">
-        <v>0</v>
-      </c>
-      <c r="AE173">
-        <v>0</v>
-      </c>
-      <c r="AF173">
-        <v>0</v>
-      </c>
-      <c r="AG173">
-        <v>0</v>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ173">
-        <v>0</v>
-      </c>
-      <c r="AK173">
-        <v>0</v>
-      </c>
-      <c r="AL173">
-        <v>0</v>
-      </c>
-      <c r="AM173">
-        <v>-1</v>
-      </c>
-      <c r="AN173">
-        <v>-1</v>
-      </c>
-      <c r="AO173">
-        <v>-1</v>
-      </c>
-      <c r="AP173">
-        <v>-1</v>
-      </c>
-      <c r="AQ173">
-        <v>0</v>
-      </c>
-      <c r="AR173">
-        <v>0</v>
-      </c>
-      <c r="AS173">
-        <v>0</v>
-      </c>
-      <c r="AT173">
-        <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Corvinul Hunedoara</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Dinamo Bucureşti</t>
-        </is>
-      </c>
-      <c r="G174">
-        <v>0</v>
-      </c>
-      <c r="H174">
-        <v>0</v>
-      </c>
-      <c r="I174">
-        <v>0</v>
-      </c>
-      <c r="J174">
-        <v>0</v>
-      </c>
-      <c r="K174">
-        <v>0</v>
-      </c>
-      <c r="L174">
-        <v>0</v>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N174">
-        <v>0</v>
-      </c>
-      <c r="O174">
-        <v>0</v>
-      </c>
-      <c r="P174">
-        <v>0</v>
-      </c>
-      <c r="Q174">
-        <v>0</v>
-      </c>
-      <c r="R174">
-        <v>0</v>
-      </c>
-      <c r="S174">
-        <v>0</v>
-      </c>
-      <c r="T174">
-        <v>0</v>
-      </c>
-      <c r="U174">
-        <v>0</v>
-      </c>
-      <c r="V174">
-        <v>0</v>
-      </c>
-      <c r="W174">
-        <v>0</v>
-      </c>
-      <c r="X174">
-        <v>0</v>
-      </c>
-      <c r="Y174">
-        <v>0</v>
-      </c>
-      <c r="Z174">
-        <v>0</v>
-      </c>
-      <c r="AA174">
-        <v>0</v>
-      </c>
-      <c r="AB174">
-        <v>0</v>
-      </c>
-      <c r="AC174">
-        <v>0</v>
-      </c>
-      <c r="AD174">
-        <v>0</v>
-      </c>
-      <c r="AE174">
-        <v>0</v>
-      </c>
-      <c r="AF174">
-        <v>0</v>
-      </c>
-      <c r="AG174">
-        <v>0</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ174">
-        <v>0</v>
-      </c>
-      <c r="AK174">
-        <v>0</v>
-      </c>
-      <c r="AL174">
-        <v>0</v>
-      </c>
-      <c r="AM174">
-        <v>-1</v>
-      </c>
-      <c r="AN174">
-        <v>-1</v>
-      </c>
-      <c r="AO174">
-        <v>-1</v>
-      </c>
-      <c r="AP174">
-        <v>-1</v>
-      </c>
-      <c r="AQ174">
-        <v>0</v>
-      </c>
-      <c r="AR174">
-        <v>0</v>
-      </c>
-      <c r="AS174">
-        <v>0</v>
-      </c>
-      <c r="AT174">
-        <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Argeș</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Sepsi</t>
-        </is>
-      </c>
-      <c r="G175">
-        <v>0</v>
-      </c>
-      <c r="H175">
-        <v>0</v>
-      </c>
-      <c r="I175">
-        <v>0</v>
-      </c>
-      <c r="J175">
-        <v>0</v>
-      </c>
-      <c r="K175">
-        <v>0</v>
-      </c>
-      <c r="L175">
-        <v>0</v>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N175">
-        <v>0</v>
-      </c>
-      <c r="O175">
-        <v>0</v>
-      </c>
-      <c r="P175">
-        <v>0</v>
-      </c>
-      <c r="Q175">
-        <v>0</v>
-      </c>
-      <c r="R175">
-        <v>0</v>
-      </c>
-      <c r="S175">
-        <v>0</v>
-      </c>
-      <c r="T175">
-        <v>0</v>
-      </c>
-      <c r="U175">
-        <v>0</v>
-      </c>
-      <c r="V175">
-        <v>0</v>
-      </c>
-      <c r="W175">
-        <v>0</v>
-      </c>
-      <c r="X175">
-        <v>0</v>
-      </c>
-      <c r="Y175">
-        <v>0</v>
-      </c>
-      <c r="Z175">
-        <v>0</v>
-      </c>
-      <c r="AA175">
-        <v>0</v>
-      </c>
-      <c r="AB175">
-        <v>0</v>
-      </c>
-      <c r="AC175">
-        <v>0</v>
-      </c>
-      <c r="AD175">
-        <v>0</v>
-      </c>
-      <c r="AE175">
-        <v>0</v>
-      </c>
-      <c r="AF175">
-        <v>0</v>
-      </c>
-      <c r="AG175">
-        <v>0</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>0</v>
-      </c>
-      <c r="AK175">
-        <v>0</v>
-      </c>
-      <c r="AL175">
-        <v>0</v>
-      </c>
-      <c r="AM175">
-        <v>-1</v>
-      </c>
-      <c r="AN175">
-        <v>-1</v>
-      </c>
-      <c r="AO175">
-        <v>-1</v>
-      </c>
-      <c r="AP175">
-        <v>-1</v>
-      </c>
-      <c r="AQ175">
-        <v>0</v>
-      </c>
-      <c r="AR175">
-        <v>0</v>
-      </c>
-      <c r="AS175">
-        <v>0</v>
-      </c>
-      <c r="AT175">
-        <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Csikszereda</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>CFR Cluj</t>
-        </is>
-      </c>
-      <c r="G176">
-        <v>0</v>
-      </c>
-      <c r="H176">
-        <v>0</v>
-      </c>
-      <c r="I176">
-        <v>0</v>
-      </c>
-      <c r="J176">
-        <v>0</v>
-      </c>
-      <c r="K176">
-        <v>0</v>
-      </c>
-      <c r="L176">
-        <v>0</v>
-      </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N176">
-        <v>0</v>
-      </c>
-      <c r="O176">
-        <v>0</v>
-      </c>
-      <c r="P176">
-        <v>0</v>
-      </c>
-      <c r="Q176">
-        <v>0</v>
-      </c>
-      <c r="R176">
-        <v>0</v>
-      </c>
-      <c r="S176">
-        <v>0</v>
-      </c>
-      <c r="T176">
-        <v>0</v>
-      </c>
-      <c r="U176">
-        <v>0</v>
-      </c>
-      <c r="V176">
-        <v>0</v>
-      </c>
-      <c r="W176">
-        <v>0</v>
-      </c>
-      <c r="X176">
-        <v>0</v>
-      </c>
-      <c r="Y176">
-        <v>0</v>
-      </c>
-      <c r="Z176">
-        <v>0</v>
-      </c>
-      <c r="AA176">
-        <v>0</v>
-      </c>
-      <c r="AB176">
-        <v>0</v>
-      </c>
-      <c r="AC176">
-        <v>0</v>
-      </c>
-      <c r="AD176">
-        <v>0</v>
-      </c>
-      <c r="AE176">
-        <v>0</v>
-      </c>
-      <c r="AF176">
-        <v>0</v>
-      </c>
-      <c r="AG176">
-        <v>0</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>0</v>
-      </c>
-      <c r="AK176">
-        <v>0</v>
-      </c>
-      <c r="AL176">
-        <v>0</v>
-      </c>
-      <c r="AM176">
-        <v>-1</v>
-      </c>
-      <c r="AN176">
-        <v>-1</v>
-      </c>
-      <c r="AO176">
-        <v>-1</v>
-      </c>
-      <c r="AP176">
-        <v>-1</v>
-      </c>
-      <c r="AQ176">
-        <v>0</v>
-      </c>
-      <c r="AR176">
-        <v>0</v>
-      </c>
-      <c r="AS176">
-        <v>0</v>
-      </c>
-      <c r="AT176">
-        <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G177">
-        <v>0</v>
-      </c>
-      <c r="H177">
-        <v>0</v>
-      </c>
-      <c r="I177">
-        <v>0</v>
-      </c>
-      <c r="J177">
-        <v>0</v>
-      </c>
-      <c r="K177">
-        <v>0</v>
-      </c>
-      <c r="L177">
-        <v>0</v>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N177">
-        <v>0</v>
-      </c>
-      <c r="O177">
-        <v>0</v>
-      </c>
-      <c r="P177">
-        <v>0</v>
-      </c>
-      <c r="Q177">
-        <v>0</v>
-      </c>
-      <c r="R177">
-        <v>0</v>
-      </c>
-      <c r="S177">
-        <v>0</v>
-      </c>
-      <c r="T177">
-        <v>0</v>
-      </c>
-      <c r="U177">
-        <v>0</v>
-      </c>
-      <c r="V177">
-        <v>0</v>
-      </c>
-      <c r="W177">
-        <v>0</v>
-      </c>
-      <c r="X177">
-        <v>0</v>
-      </c>
-      <c r="Y177">
-        <v>0</v>
-      </c>
-      <c r="Z177">
-        <v>0</v>
-      </c>
-      <c r="AA177">
-        <v>0</v>
-      </c>
-      <c r="AB177">
-        <v>0</v>
-      </c>
-      <c r="AC177">
-        <v>0</v>
-      </c>
-      <c r="AD177">
-        <v>0</v>
-      </c>
-      <c r="AE177">
-        <v>0</v>
-      </c>
-      <c r="AF177">
-        <v>0</v>
-      </c>
-      <c r="AG177">
-        <v>0</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ177">
-        <v>0</v>
-      </c>
-      <c r="AK177">
-        <v>0</v>
-      </c>
-      <c r="AL177">
-        <v>0</v>
-      </c>
-      <c r="AM177">
-        <v>-1</v>
-      </c>
-      <c r="AN177">
-        <v>-1</v>
-      </c>
-      <c r="AO177">
-        <v>-1</v>
-      </c>
-      <c r="AP177">
-        <v>-1</v>
-      </c>
-      <c r="AQ177">
-        <v>0</v>
-      </c>
-      <c r="AR177">
-        <v>0</v>
-      </c>
-      <c r="AS177">
-        <v>0</v>
-      </c>
-      <c r="AT177">
-        <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G178">
-        <v>0</v>
-      </c>
-      <c r="H178">
-        <v>0</v>
-      </c>
-      <c r="I178">
-        <v>0</v>
-      </c>
-      <c r="J178">
-        <v>0</v>
-      </c>
-      <c r="K178">
-        <v>0</v>
-      </c>
-      <c r="L178">
-        <v>0</v>
-      </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N178">
-        <v>0</v>
-      </c>
-      <c r="O178">
-        <v>0</v>
-      </c>
-      <c r="P178">
-        <v>0</v>
-      </c>
-      <c r="Q178">
-        <v>0</v>
-      </c>
-      <c r="R178">
-        <v>0</v>
-      </c>
-      <c r="S178">
-        <v>0</v>
-      </c>
-      <c r="T178">
-        <v>0</v>
-      </c>
-      <c r="U178">
-        <v>0</v>
-      </c>
-      <c r="V178">
-        <v>0</v>
-      </c>
-      <c r="W178">
-        <v>0</v>
-      </c>
-      <c r="X178">
-        <v>0</v>
-      </c>
-      <c r="Y178">
-        <v>0</v>
-      </c>
-      <c r="Z178">
-        <v>0</v>
-      </c>
-      <c r="AA178">
-        <v>0</v>
-      </c>
-      <c r="AB178">
-        <v>0</v>
-      </c>
-      <c r="AC178">
-        <v>0</v>
-      </c>
-      <c r="AD178">
-        <v>0</v>
-      </c>
-      <c r="AE178">
-        <v>0</v>
-      </c>
-      <c r="AF178">
-        <v>0</v>
-      </c>
-      <c r="AG178">
-        <v>0</v>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ178">
-        <v>0</v>
-      </c>
-      <c r="AK178">
-        <v>0</v>
-      </c>
-      <c r="AL178">
-        <v>0</v>
-      </c>
-      <c r="AM178">
-        <v>-1</v>
-      </c>
-      <c r="AN178">
-        <v>-1</v>
-      </c>
-      <c r="AO178">
-        <v>-1</v>
-      </c>
-      <c r="AP178">
-        <v>-1</v>
-      </c>
-      <c r="AQ178">
-        <v>0</v>
-      </c>
-      <c r="AR178">
-        <v>0</v>
-      </c>
-      <c r="AS178">
-        <v>0</v>
-      </c>
-      <c r="AT178">
-        <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G179">
-        <v>0</v>
-      </c>
-      <c r="H179">
-        <v>0</v>
-      </c>
-      <c r="I179">
-        <v>0</v>
-      </c>
-      <c r="J179">
-        <v>0</v>
-      </c>
-      <c r="K179">
-        <v>0</v>
-      </c>
-      <c r="L179">
-        <v>0</v>
-      </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N179">
-        <v>0</v>
-      </c>
-      <c r="O179">
-        <v>0</v>
-      </c>
-      <c r="P179">
-        <v>0</v>
-      </c>
-      <c r="Q179">
-        <v>0</v>
-      </c>
-      <c r="R179">
-        <v>0</v>
-      </c>
-      <c r="S179">
-        <v>0</v>
-      </c>
-      <c r="T179">
-        <v>0</v>
-      </c>
-      <c r="U179">
-        <v>0</v>
-      </c>
-      <c r="V179">
-        <v>0</v>
-      </c>
-      <c r="W179">
-        <v>0</v>
-      </c>
-      <c r="X179">
-        <v>0</v>
-      </c>
-      <c r="Y179">
-        <v>0</v>
-      </c>
-      <c r="Z179">
-        <v>0</v>
-      </c>
-      <c r="AA179">
-        <v>0</v>
-      </c>
-      <c r="AB179">
-        <v>0</v>
-      </c>
-      <c r="AC179">
-        <v>0</v>
-      </c>
-      <c r="AD179">
-        <v>0</v>
-      </c>
-      <c r="AE179">
-        <v>0</v>
-      </c>
-      <c r="AF179">
-        <v>0</v>
-      </c>
-      <c r="AG179">
-        <v>0</v>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ179">
-        <v>0</v>
-      </c>
-      <c r="AK179">
-        <v>0</v>
-      </c>
-      <c r="AL179">
-        <v>0</v>
-      </c>
-      <c r="AM179">
-        <v>-1</v>
-      </c>
-      <c r="AN179">
-        <v>-1</v>
-      </c>
-      <c r="AO179">
-        <v>-1</v>
-      </c>
-      <c r="AP179">
-        <v>-1</v>
-      </c>
-      <c r="AQ179">
-        <v>0</v>
-      </c>
-      <c r="AR179">
-        <v>0</v>
-      </c>
-      <c r="AS179">
-        <v>0</v>
-      </c>
-      <c r="AT179">
-        <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G180">
-        <v>0</v>
-      </c>
-      <c r="H180">
-        <v>0</v>
-      </c>
-      <c r="I180">
-        <v>0</v>
-      </c>
-      <c r="J180">
-        <v>0</v>
-      </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N180">
-        <v>0</v>
-      </c>
-      <c r="O180">
-        <v>0</v>
-      </c>
-      <c r="P180">
-        <v>0</v>
-      </c>
-      <c r="Q180">
-        <v>0</v>
-      </c>
-      <c r="R180">
-        <v>0</v>
-      </c>
-      <c r="S180">
-        <v>0</v>
-      </c>
-      <c r="T180">
-        <v>0</v>
-      </c>
-      <c r="U180">
-        <v>0</v>
-      </c>
-      <c r="V180">
-        <v>0</v>
-      </c>
-      <c r="W180">
-        <v>0</v>
-      </c>
-      <c r="X180">
-        <v>0</v>
-      </c>
-      <c r="Y180">
-        <v>0</v>
-      </c>
-      <c r="Z180">
-        <v>0</v>
-      </c>
-      <c r="AA180">
-        <v>0</v>
-      </c>
-      <c r="AB180">
-        <v>0</v>
-      </c>
-      <c r="AC180">
-        <v>0</v>
-      </c>
-      <c r="AD180">
-        <v>0</v>
-      </c>
-      <c r="AE180">
-        <v>0</v>
-      </c>
-      <c r="AF180">
-        <v>0</v>
-      </c>
-      <c r="AG180">
-        <v>0</v>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ180">
-        <v>0</v>
-      </c>
-      <c r="AK180">
-        <v>0</v>
-      </c>
-      <c r="AL180">
-        <v>0</v>
-      </c>
-      <c r="AM180">
-        <v>-1</v>
-      </c>
-      <c r="AN180">
-        <v>-1</v>
-      </c>
-      <c r="AO180">
-        <v>-1</v>
-      </c>
-      <c r="AP180">
-        <v>-1</v>
-      </c>
-      <c r="AQ180">
-        <v>0</v>
-      </c>
-      <c r="AR180">
-        <v>0</v>
-      </c>
-      <c r="AS180">
-        <v>0</v>
-      </c>
-      <c r="AT180">
-        <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G181">
-        <v>0</v>
-      </c>
-      <c r="H181">
-        <v>0</v>
-      </c>
-      <c r="I181">
-        <v>0</v>
-      </c>
-      <c r="J181">
-        <v>0</v>
-      </c>
-      <c r="K181">
-        <v>0</v>
-      </c>
-      <c r="L181">
-        <v>0</v>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N181">
-        <v>0</v>
-      </c>
-      <c r="O181">
-        <v>0</v>
-      </c>
-      <c r="P181">
-        <v>0</v>
-      </c>
-      <c r="Q181">
-        <v>0</v>
-      </c>
-      <c r="R181">
-        <v>0</v>
-      </c>
-      <c r="S181">
-        <v>0</v>
-      </c>
-      <c r="T181">
-        <v>0</v>
-      </c>
-      <c r="U181">
-        <v>0</v>
-      </c>
-      <c r="V181">
-        <v>0</v>
-      </c>
-      <c r="W181">
-        <v>0</v>
-      </c>
-      <c r="X181">
-        <v>0</v>
-      </c>
-      <c r="Y181">
-        <v>0</v>
-      </c>
-      <c r="Z181">
-        <v>0</v>
-      </c>
-      <c r="AA181">
-        <v>0</v>
-      </c>
-      <c r="AB181">
-        <v>0</v>
-      </c>
-      <c r="AC181">
-        <v>0</v>
-      </c>
-      <c r="AD181">
-        <v>0</v>
-      </c>
-      <c r="AE181">
-        <v>0</v>
-      </c>
-      <c r="AF181">
-        <v>0</v>
-      </c>
-      <c r="AG181">
-        <v>0</v>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ181">
-        <v>0</v>
-      </c>
-      <c r="AK181">
-        <v>0</v>
-      </c>
-      <c r="AL181">
-        <v>0</v>
-      </c>
-      <c r="AM181">
-        <v>-1</v>
-      </c>
-      <c r="AN181">
-        <v>-1</v>
-      </c>
-      <c r="AO181">
-        <v>-1</v>
-      </c>
-      <c r="AP181">
-        <v>-1</v>
-      </c>
-      <c r="AQ181">
-        <v>0</v>
-      </c>
-      <c r="AR181">
-        <v>0</v>
-      </c>
-      <c r="AS181">
-        <v>0</v>
-      </c>
-      <c r="AT181">
-        <v>0</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="G182">
-        <v>0</v>
-      </c>
-      <c r="H182">
-        <v>0</v>
-      </c>
-      <c r="I182">
-        <v>0</v>
-      </c>
-      <c r="J182">
-        <v>0</v>
-      </c>
-      <c r="K182">
-        <v>0</v>
-      </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N182">
-        <v>0</v>
-      </c>
-      <c r="O182">
-        <v>0</v>
-      </c>
-      <c r="P182">
-        <v>0</v>
-      </c>
-      <c r="Q182">
-        <v>0</v>
-      </c>
-      <c r="R182">
-        <v>0</v>
-      </c>
-      <c r="S182">
-        <v>0</v>
-      </c>
-      <c r="T182">
-        <v>0</v>
-      </c>
-      <c r="U182">
-        <v>0</v>
-      </c>
-      <c r="V182">
-        <v>0</v>
-      </c>
-      <c r="W182">
-        <v>0</v>
-      </c>
-      <c r="X182">
-        <v>0</v>
-      </c>
-      <c r="Y182">
-        <v>0</v>
-      </c>
-      <c r="Z182">
-        <v>0</v>
-      </c>
-      <c r="AA182">
-        <v>0</v>
-      </c>
-      <c r="AB182">
-        <v>0</v>
-      </c>
-      <c r="AC182">
-        <v>0</v>
-      </c>
-      <c r="AD182">
-        <v>0</v>
-      </c>
-      <c r="AE182">
-        <v>0</v>
-      </c>
-      <c r="AF182">
-        <v>0</v>
-      </c>
-      <c r="AG182">
-        <v>0</v>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ182">
-        <v>0</v>
-      </c>
-      <c r="AK182">
-        <v>0</v>
-      </c>
-      <c r="AL182">
-        <v>0</v>
-      </c>
-      <c r="AM182">
-        <v>-1</v>
-      </c>
-      <c r="AN182">
-        <v>-1</v>
-      </c>
-      <c r="AO182">
-        <v>-1</v>
-      </c>
-      <c r="AP182">
-        <v>-1</v>
-      </c>
-      <c r="AQ182">
-        <v>0</v>
-      </c>
-      <c r="AR182">
-        <v>0</v>
-      </c>
-      <c r="AS182">
-        <v>0</v>
-      </c>
-      <c r="AT182">
-        <v>0</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="G183">
-        <v>0</v>
-      </c>
-      <c r="H183">
-        <v>0</v>
-      </c>
-      <c r="I183">
-        <v>0</v>
-      </c>
-      <c r="J183">
-        <v>0</v>
-      </c>
-      <c r="K183">
-        <v>0</v>
-      </c>
-      <c r="L183">
-        <v>0</v>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N183">
-        <v>0</v>
-      </c>
-      <c r="O183">
-        <v>0</v>
-      </c>
-      <c r="P183">
-        <v>0</v>
-      </c>
-      <c r="Q183">
-        <v>0</v>
-      </c>
-      <c r="R183">
-        <v>0</v>
-      </c>
-      <c r="S183">
-        <v>0</v>
-      </c>
-      <c r="T183">
-        <v>0</v>
-      </c>
-      <c r="U183">
-        <v>0</v>
-      </c>
-      <c r="V183">
-        <v>0</v>
-      </c>
-      <c r="W183">
-        <v>0</v>
-      </c>
-      <c r="X183">
-        <v>0</v>
-      </c>
-      <c r="Y183">
-        <v>0</v>
-      </c>
-      <c r="Z183">
-        <v>0</v>
-      </c>
-      <c r="AA183">
-        <v>0</v>
-      </c>
-      <c r="AB183">
-        <v>0</v>
-      </c>
-      <c r="AC183">
-        <v>0</v>
-      </c>
-      <c r="AD183">
-        <v>0</v>
-      </c>
-      <c r="AE183">
-        <v>0</v>
-      </c>
-      <c r="AF183">
-        <v>0</v>
-      </c>
-      <c r="AG183">
-        <v>0</v>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ183">
-        <v>0</v>
-      </c>
-      <c r="AK183">
-        <v>0</v>
-      </c>
-      <c r="AL183">
-        <v>0</v>
-      </c>
-      <c r="AM183">
-        <v>-1</v>
-      </c>
-      <c r="AN183">
-        <v>-1</v>
-      </c>
-      <c r="AO183">
-        <v>-1</v>
-      </c>
-      <c r="AP183">
-        <v>-1</v>
-      </c>
-      <c r="AQ183">
-        <v>0</v>
-      </c>
-      <c r="AR183">
-        <v>0</v>
-      </c>
-      <c r="AS183">
-        <v>0</v>
-      </c>
-      <c r="AT183">
-        <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="G184">
-        <v>0</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-      <c r="I184">
-        <v>0</v>
-      </c>
-      <c r="J184">
-        <v>0</v>
-      </c>
-      <c r="K184">
-        <v>0</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N184">
-        <v>0</v>
-      </c>
-      <c r="O184">
-        <v>0</v>
-      </c>
-      <c r="P184">
-        <v>0</v>
-      </c>
-      <c r="Q184">
-        <v>0</v>
-      </c>
-      <c r="R184">
-        <v>0</v>
-      </c>
-      <c r="S184">
-        <v>0</v>
-      </c>
-      <c r="T184">
-        <v>0</v>
-      </c>
-      <c r="U184">
-        <v>0</v>
-      </c>
-      <c r="V184">
-        <v>0</v>
-      </c>
-      <c r="W184">
-        <v>0</v>
-      </c>
-      <c r="X184">
-        <v>0</v>
-      </c>
-      <c r="Y184">
-        <v>0</v>
-      </c>
-      <c r="Z184">
-        <v>0</v>
-      </c>
-      <c r="AA184">
-        <v>0</v>
-      </c>
-      <c r="AB184">
-        <v>0</v>
-      </c>
-      <c r="AC184">
-        <v>0</v>
-      </c>
-      <c r="AD184">
-        <v>0</v>
-      </c>
-      <c r="AE184">
-        <v>0</v>
-      </c>
-      <c r="AF184">
-        <v>0</v>
-      </c>
-      <c r="AG184">
-        <v>0</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ184">
-        <v>0</v>
-      </c>
-      <c r="AK184">
-        <v>0</v>
-      </c>
-      <c r="AL184">
-        <v>0</v>
-      </c>
-      <c r="AM184">
-        <v>-1</v>
-      </c>
-      <c r="AN184">
-        <v>-1</v>
-      </c>
-      <c r="AO184">
-        <v>-1</v>
-      </c>
-      <c r="AP184">
-        <v>-1</v>
-      </c>
-      <c r="AQ184">
-        <v>0</v>
-      </c>
-      <c r="AR184">
-        <v>0</v>
-      </c>
-      <c r="AS184">
-        <v>0</v>
-      </c>
-      <c r="AT184">
-        <v>0</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Chacarita Juniors</t>
-        </is>
-      </c>
-      <c r="G185">
-        <v>0</v>
-      </c>
-      <c r="H185">
-        <v>0</v>
-      </c>
-      <c r="I185">
-        <v>0</v>
-      </c>
-      <c r="J185">
-        <v>0</v>
-      </c>
-      <c r="K185">
-        <v>0</v>
-      </c>
-      <c r="L185">
-        <v>0</v>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N185">
-        <v>0</v>
-      </c>
-      <c r="O185">
-        <v>0</v>
-      </c>
-      <c r="P185">
-        <v>0</v>
-      </c>
-      <c r="Q185">
-        <v>0</v>
-      </c>
-      <c r="R185">
-        <v>0</v>
-      </c>
-      <c r="S185">
-        <v>0</v>
-      </c>
-      <c r="T185">
-        <v>0</v>
-      </c>
-      <c r="U185">
-        <v>0</v>
-      </c>
-      <c r="V185">
-        <v>0</v>
-      </c>
-      <c r="W185">
-        <v>0</v>
-      </c>
-      <c r="X185">
-        <v>0</v>
-      </c>
-      <c r="Y185">
-        <v>0</v>
-      </c>
-      <c r="Z185">
-        <v>0</v>
-      </c>
-      <c r="AA185">
-        <v>0</v>
-      </c>
-      <c r="AB185">
-        <v>0</v>
-      </c>
-      <c r="AC185">
-        <v>0</v>
-      </c>
-      <c r="AD185">
-        <v>0</v>
-      </c>
-      <c r="AE185">
-        <v>0</v>
-      </c>
-      <c r="AF185">
-        <v>0</v>
-      </c>
-      <c r="AG185">
-        <v>0</v>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ185">
-        <v>0</v>
-      </c>
-      <c r="AK185">
-        <v>0</v>
-      </c>
-      <c r="AL185">
-        <v>0</v>
-      </c>
-      <c r="AM185">
-        <v>-1</v>
-      </c>
-      <c r="AN185">
-        <v>-1</v>
-      </c>
-      <c r="AO185">
-        <v>-1</v>
-      </c>
-      <c r="AP185">
-        <v>-1</v>
-      </c>
-      <c r="AQ185">
-        <v>0</v>
-      </c>
-      <c r="AR185">
-        <v>0</v>
-      </c>
-      <c r="AS185">
-        <v>0</v>
-      </c>
-      <c r="AT185">
-        <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G186">
-        <v>0</v>
-      </c>
-      <c r="H186">
-        <v>0</v>
-      </c>
-      <c r="I186">
-        <v>0</v>
-      </c>
-      <c r="J186">
-        <v>0</v>
-      </c>
-      <c r="K186">
-        <v>0</v>
-      </c>
-      <c r="L186">
-        <v>0</v>
-      </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N186">
-        <v>0</v>
-      </c>
-      <c r="O186">
-        <v>0</v>
-      </c>
-      <c r="P186">
-        <v>0</v>
-      </c>
-      <c r="Q186">
-        <v>0</v>
-      </c>
-      <c r="R186">
-        <v>0</v>
-      </c>
-      <c r="S186">
-        <v>0</v>
-      </c>
-      <c r="T186">
-        <v>0</v>
-      </c>
-      <c r="U186">
-        <v>0</v>
-      </c>
-      <c r="V186">
-        <v>0</v>
-      </c>
-      <c r="W186">
-        <v>0</v>
-      </c>
-      <c r="X186">
-        <v>0</v>
-      </c>
-      <c r="Y186">
-        <v>0</v>
-      </c>
-      <c r="Z186">
-        <v>0</v>
-      </c>
-      <c r="AA186">
-        <v>0</v>
-      </c>
-      <c r="AB186">
-        <v>0</v>
-      </c>
-      <c r="AC186">
-        <v>0</v>
-      </c>
-      <c r="AD186">
-        <v>0</v>
-      </c>
-      <c r="AE186">
-        <v>0</v>
-      </c>
-      <c r="AF186">
-        <v>0</v>
-      </c>
-      <c r="AG186">
-        <v>0</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ186">
-        <v>0</v>
-      </c>
-      <c r="AK186">
-        <v>0</v>
-      </c>
-      <c r="AL186">
-        <v>0</v>
-      </c>
-      <c r="AM186">
-        <v>-1</v>
-      </c>
-      <c r="AN186">
-        <v>-1</v>
-      </c>
-      <c r="AO186">
-        <v>-1</v>
-      </c>
-      <c r="AP186">
-        <v>-1</v>
-      </c>
-      <c r="AQ186">
-        <v>0</v>
-      </c>
-      <c r="AR186">
-        <v>0</v>
-      </c>
-      <c r="AS186">
-        <v>0</v>
-      </c>
-      <c r="AT186">
-        <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
         <is>
           <t>2026-08-28 23:00:00</t>
         </is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G146">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G20">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -8969,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -8981,31 +8981,31 @@
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE53">
         <v>0</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G147">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU160"/>
+  <dimension ref="A1:AU149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>6.15</v>
+        <v>5.75</v>
       </c>
       <c r="O2">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="P2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q2">
         <v>6.07</v>
@@ -656,7 +656,7 @@
         <v>3.58</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="V2">
         <v>1.67</v>
@@ -677,7 +677,7 @@
         <v>1.5</v>
       </c>
       <c r="AB2">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC2">
         <v>2.21</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,16 +807,16 @@
         <v>2.7</v>
       </c>
       <c r="Q3">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="R3">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U3">
         <v>2.56</v>
@@ -846,7 +846,7 @@
         <v>2.75</v>
       </c>
       <c r="AD3">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE3">
         <v>1.12</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>3.85</v>
+        <v>2.09</v>
       </c>
       <c r="Q5">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="R5">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>5.5</v>
+        <v>3.68</v>
       </c>
       <c r="U5">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="V5">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA5">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="AC5">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="AK5">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
-        <v>2.09</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
+        <v>1.96</v>
+      </c>
+      <c r="R6">
+        <v>2.64</v>
+      </c>
+      <c r="S6">
+        <v>1.17</v>
+      </c>
+      <c r="T6">
+        <v>5.5</v>
+      </c>
+      <c r="U6">
+        <v>1.83</v>
+      </c>
+      <c r="V6">
+        <v>1.93</v>
+      </c>
+      <c r="W6">
+        <v>1.22</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.09</v>
+      </c>
+      <c r="Z6">
+        <v>6.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.3</v>
+      </c>
+      <c r="AB6">
         <v>3.25</v>
       </c>
-      <c r="R6">
-        <v>2.5</v>
-      </c>
-      <c r="S6">
-        <v>1.2</v>
-      </c>
-      <c r="T6">
-        <v>3.68</v>
-      </c>
-      <c r="U6">
-        <v>2.09</v>
-      </c>
-      <c r="V6">
-        <v>1.68</v>
-      </c>
-      <c r="W6">
-        <v>1.16</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.13</v>
-      </c>
-      <c r="Z6">
-        <v>5.3</v>
-      </c>
-      <c r="AA6">
-        <v>1.4</v>
-      </c>
-      <c r="AB6">
-        <v>2.67</v>
-      </c>
       <c r="AC6">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AD6">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AE6">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AF6">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG6">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.22</v>
+        <v>2.99</v>
       </c>
       <c r="R27">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="V27">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z27">
-        <v>3.82</v>
+        <v>2.92</v>
       </c>
       <c r="AA27">
+        <v>2.04</v>
+      </c>
+      <c r="AB27">
         <v>1.69</v>
       </c>
-      <c r="AB27">
-        <v>2.04</v>
-      </c>
       <c r="AC27">
-        <v>2.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG27">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>2.01</v>
+        <v>1.49</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G28">
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.99</v>
+        <v>2.22</v>
       </c>
       <c r="R28">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>2.92</v>
+        <v>3.82</v>
       </c>
       <c r="AA28">
+        <v>1.69</v>
+      </c>
+      <c r="AB28">
         <v>2.04</v>
       </c>
-      <c r="AB28">
-        <v>1.69</v>
-      </c>
       <c r="AC28">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK28">
-        <v>1.49</v>
+        <v>2.01</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="R39">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U39">
         <v>2.5</v>
@@ -6693,53 +6693,53 @@
         <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>3.92</v>
+      </c>
+      <c r="AA39">
+        <v>1.72</v>
+      </c>
+      <c r="AB39">
+        <v>2.07</v>
+      </c>
+      <c r="AC39">
+        <v>2.68</v>
+      </c>
+      <c r="AD39">
+        <v>1.37</v>
+      </c>
+      <c r="AE39">
+        <v>1.16</v>
+      </c>
+      <c r="AF39">
+        <v>1.71</v>
+      </c>
+      <c r="AG39">
+        <v>2.02</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.22</v>
       </c>
-      <c r="Z39">
-        <v>4.29</v>
-      </c>
-      <c r="AA39">
-        <v>1.74</v>
-      </c>
-      <c r="AB39">
-        <v>2.12</v>
-      </c>
-      <c r="AC39">
-        <v>2.64</v>
-      </c>
-      <c r="AD39">
-        <v>1.38</v>
-      </c>
-      <c r="AE39">
-        <v>1.17</v>
-      </c>
-      <c r="AF39">
-        <v>1.57</v>
-      </c>
-      <c r="AG39">
-        <v>2.3</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.26</v>
-      </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q40">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
         <v>2.5</v>
@@ -6856,37 +6856,37 @@
         <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.92</v>
+        <v>4.29</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB40">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC40">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE40">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>7.21</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,16 +7816,16 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U46">
         <v>0</v>
@@ -7840,31 +7840,31 @@
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -12392,10 +12392,10 @@
         <v>0</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -12404,31 +12404,31 @@
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -12718,10 +12718,10 @@
         <v>0</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -12730,31 +12730,31 @@
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="P99">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q99">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S99">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T99">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U99">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V99">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W99">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y99">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z99">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD99">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE99">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF99">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG99">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK99">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="O100">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="P100">
-        <v>2.75</v>
+        <v>7.85</v>
       </c>
       <c r="Q100">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="R100">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="S100">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="T100">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="U100">
-        <v>2.66</v>
+        <v>2.17</v>
       </c>
       <c r="V100">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="W100">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X100">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z100">
-        <v>3.45</v>
+        <v>5.05</v>
       </c>
       <c r="AA100">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB100">
-        <v>1.88</v>
+        <v>2.49</v>
       </c>
       <c r="AC100">
-        <v>3.04</v>
+        <v>2.18</v>
       </c>
       <c r="AD100">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AE100">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF100">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG100">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK100">
-        <v>1.49</v>
+        <v>3.12</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="O102">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="O103">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>7.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q103">
-        <v>1.67</v>
+        <v>3.43</v>
       </c>
       <c r="R103">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="S103">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U103">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="V103">
+        <v>1.5</v>
+      </c>
+      <c r="W103">
+        <v>1.11</v>
+      </c>
+      <c r="X103">
+        <v>1.03</v>
+      </c>
+      <c r="Y103">
+        <v>1.16</v>
+      </c>
+      <c r="Z103">
+        <v>4.15</v>
+      </c>
+      <c r="AA103">
         <v>1.65</v>
       </c>
-      <c r="W103">
-        <v>1.14</v>
-      </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
-        <v>1.14</v>
-      </c>
-      <c r="Z103">
-        <v>5.05</v>
-      </c>
-      <c r="AA103">
-        <v>1.44</v>
-      </c>
       <c r="AB103">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="AC103">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="AD103">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AE103">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF103">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>3.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G111">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G113">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19715,55 +19715,55 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G136">
@@ -22486,55 +22486,55 @@
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G137">
@@ -22649,55 +22649,55 @@
         <v>0</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G144">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G147">
@@ -24386,27 +24386,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V148">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y148">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z148">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF148">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG148">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK148">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 22:00:00</t>
         </is>
       </c>
     </row>
@@ -24549,27 +24549,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G149">
@@ -24605,55 +24605,55 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24699,1799 +24699,6 @@
         <v>0</v>
       </c>
       <c r="AU149" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Romania Liga I</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Rapid Bucureşti</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>CS U Craiova</t>
-        </is>
-      </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>0</v>
-      </c>
-      <c r="R150">
-        <v>0</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150">
-        <v>0</v>
-      </c>
-      <c r="U150">
-        <v>0</v>
-      </c>
-      <c r="V150">
-        <v>0</v>
-      </c>
-      <c r="W150">
-        <v>0</v>
-      </c>
-      <c r="X150">
-        <v>0</v>
-      </c>
-      <c r="Y150">
-        <v>0</v>
-      </c>
-      <c r="Z150">
-        <v>0</v>
-      </c>
-      <c r="AA150">
-        <v>0</v>
-      </c>
-      <c r="AB150">
-        <v>0</v>
-      </c>
-      <c r="AC150">
-        <v>0</v>
-      </c>
-      <c r="AD150">
-        <v>0</v>
-      </c>
-      <c r="AE150">
-        <v>0</v>
-      </c>
-      <c r="AF150">
-        <v>0</v>
-      </c>
-      <c r="AG150">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>0</v>
-      </c>
-      <c r="AK150">
-        <v>0</v>
-      </c>
-      <c r="AL150">
-        <v>0</v>
-      </c>
-      <c r="AM150">
-        <v>-1</v>
-      </c>
-      <c r="AN150">
-        <v>-1</v>
-      </c>
-      <c r="AO150">
-        <v>-1</v>
-      </c>
-      <c r="AP150">
-        <v>-1</v>
-      </c>
-      <c r="AQ150">
-        <v>0</v>
-      </c>
-      <c r="AR150">
-        <v>0</v>
-      </c>
-      <c r="AS150">
-        <v>0</v>
-      </c>
-      <c r="AT150">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>0</v>
-      </c>
-      <c r="R151">
-        <v>0</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151">
-        <v>0</v>
-      </c>
-      <c r="U151">
-        <v>0</v>
-      </c>
-      <c r="V151">
-        <v>0</v>
-      </c>
-      <c r="W151">
-        <v>0</v>
-      </c>
-      <c r="X151">
-        <v>0</v>
-      </c>
-      <c r="Y151">
-        <v>0</v>
-      </c>
-      <c r="Z151">
-        <v>0</v>
-      </c>
-      <c r="AA151">
-        <v>0</v>
-      </c>
-      <c r="AB151">
-        <v>0</v>
-      </c>
-      <c r="AC151">
-        <v>0</v>
-      </c>
-      <c r="AD151">
-        <v>0</v>
-      </c>
-      <c r="AE151">
-        <v>0</v>
-      </c>
-      <c r="AF151">
-        <v>0</v>
-      </c>
-      <c r="AG151">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ151">
-        <v>0</v>
-      </c>
-      <c r="AK151">
-        <v>0</v>
-      </c>
-      <c r="AL151">
-        <v>0</v>
-      </c>
-      <c r="AM151">
-        <v>-1</v>
-      </c>
-      <c r="AN151">
-        <v>-1</v>
-      </c>
-      <c r="AO151">
-        <v>-1</v>
-      </c>
-      <c r="AP151">
-        <v>-1</v>
-      </c>
-      <c r="AQ151">
-        <v>0</v>
-      </c>
-      <c r="AR151">
-        <v>0</v>
-      </c>
-      <c r="AS151">
-        <v>0</v>
-      </c>
-      <c r="AT151">
-        <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152">
-        <v>0</v>
-      </c>
-      <c r="R152">
-        <v>0</v>
-      </c>
-      <c r="S152">
-        <v>0</v>
-      </c>
-      <c r="T152">
-        <v>0</v>
-      </c>
-      <c r="U152">
-        <v>0</v>
-      </c>
-      <c r="V152">
-        <v>0</v>
-      </c>
-      <c r="W152">
-        <v>0</v>
-      </c>
-      <c r="X152">
-        <v>0</v>
-      </c>
-      <c r="Y152">
-        <v>0</v>
-      </c>
-      <c r="Z152">
-        <v>0</v>
-      </c>
-      <c r="AA152">
-        <v>0</v>
-      </c>
-      <c r="AB152">
-        <v>0</v>
-      </c>
-      <c r="AC152">
-        <v>0</v>
-      </c>
-      <c r="AD152">
-        <v>0</v>
-      </c>
-      <c r="AE152">
-        <v>0</v>
-      </c>
-      <c r="AF152">
-        <v>0</v>
-      </c>
-      <c r="AG152">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>0</v>
-      </c>
-      <c r="AK152">
-        <v>0</v>
-      </c>
-      <c r="AL152">
-        <v>0</v>
-      </c>
-      <c r="AM152">
-        <v>-1</v>
-      </c>
-      <c r="AN152">
-        <v>-1</v>
-      </c>
-      <c r="AO152">
-        <v>-1</v>
-      </c>
-      <c r="AP152">
-        <v>-1</v>
-      </c>
-      <c r="AQ152">
-        <v>0</v>
-      </c>
-      <c r="AR152">
-        <v>0</v>
-      </c>
-      <c r="AS152">
-        <v>0</v>
-      </c>
-      <c r="AT152">
-        <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G153">
-        <v>0</v>
-      </c>
-      <c r="H153">
-        <v>0</v>
-      </c>
-      <c r="I153">
-        <v>0</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <v>0</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>0</v>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="T153">
-        <v>0</v>
-      </c>
-      <c r="U153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>0</v>
-      </c>
-      <c r="W153">
-        <v>0</v>
-      </c>
-      <c r="X153">
-        <v>0</v>
-      </c>
-      <c r="Y153">
-        <v>0</v>
-      </c>
-      <c r="Z153">
-        <v>0</v>
-      </c>
-      <c r="AA153">
-        <v>0</v>
-      </c>
-      <c r="AB153">
-        <v>0</v>
-      </c>
-      <c r="AC153">
-        <v>0</v>
-      </c>
-      <c r="AD153">
-        <v>0</v>
-      </c>
-      <c r="AE153">
-        <v>0</v>
-      </c>
-      <c r="AF153">
-        <v>0</v>
-      </c>
-      <c r="AG153">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ153">
-        <v>0</v>
-      </c>
-      <c r="AK153">
-        <v>0</v>
-      </c>
-      <c r="AL153">
-        <v>0</v>
-      </c>
-      <c r="AM153">
-        <v>-1</v>
-      </c>
-      <c r="AN153">
-        <v>-1</v>
-      </c>
-      <c r="AO153">
-        <v>-1</v>
-      </c>
-      <c r="AP153">
-        <v>-1</v>
-      </c>
-      <c r="AQ153">
-        <v>0</v>
-      </c>
-      <c r="AR153">
-        <v>0</v>
-      </c>
-      <c r="AS153">
-        <v>0</v>
-      </c>
-      <c r="AT153">
-        <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G154">
-        <v>0</v>
-      </c>
-      <c r="H154">
-        <v>0</v>
-      </c>
-      <c r="I154">
-        <v>0</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <v>0</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>0</v>
-      </c>
-      <c r="R154">
-        <v>0</v>
-      </c>
-      <c r="S154">
-        <v>0</v>
-      </c>
-      <c r="T154">
-        <v>0</v>
-      </c>
-      <c r="U154">
-        <v>0</v>
-      </c>
-      <c r="V154">
-        <v>0</v>
-      </c>
-      <c r="W154">
-        <v>0</v>
-      </c>
-      <c r="X154">
-        <v>0</v>
-      </c>
-      <c r="Y154">
-        <v>0</v>
-      </c>
-      <c r="Z154">
-        <v>0</v>
-      </c>
-      <c r="AA154">
-        <v>0</v>
-      </c>
-      <c r="AB154">
-        <v>0</v>
-      </c>
-      <c r="AC154">
-        <v>0</v>
-      </c>
-      <c r="AD154">
-        <v>0</v>
-      </c>
-      <c r="AE154">
-        <v>0</v>
-      </c>
-      <c r="AF154">
-        <v>0</v>
-      </c>
-      <c r="AG154">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
-      <c r="AK154">
-        <v>0</v>
-      </c>
-      <c r="AL154">
-        <v>0</v>
-      </c>
-      <c r="AM154">
-        <v>-1</v>
-      </c>
-      <c r="AN154">
-        <v>-1</v>
-      </c>
-      <c r="AO154">
-        <v>-1</v>
-      </c>
-      <c r="AP154">
-        <v>-1</v>
-      </c>
-      <c r="AQ154">
-        <v>0</v>
-      </c>
-      <c r="AR154">
-        <v>0</v>
-      </c>
-      <c r="AS154">
-        <v>0</v>
-      </c>
-      <c r="AT154">
-        <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
-        <v>0</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
-      <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <v>0</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
-        <v>0</v>
-      </c>
-      <c r="Q155">
-        <v>0</v>
-      </c>
-      <c r="R155">
-        <v>0</v>
-      </c>
-      <c r="S155">
-        <v>0</v>
-      </c>
-      <c r="T155">
-        <v>0</v>
-      </c>
-      <c r="U155">
-        <v>0</v>
-      </c>
-      <c r="V155">
-        <v>0</v>
-      </c>
-      <c r="W155">
-        <v>0</v>
-      </c>
-      <c r="X155">
-        <v>0</v>
-      </c>
-      <c r="Y155">
-        <v>0</v>
-      </c>
-      <c r="Z155">
-        <v>0</v>
-      </c>
-      <c r="AA155">
-        <v>0</v>
-      </c>
-      <c r="AB155">
-        <v>0</v>
-      </c>
-      <c r="AC155">
-        <v>0</v>
-      </c>
-      <c r="AD155">
-        <v>0</v>
-      </c>
-      <c r="AE155">
-        <v>0</v>
-      </c>
-      <c r="AF155">
-        <v>0</v>
-      </c>
-      <c r="AG155">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>0</v>
-      </c>
-      <c r="AK155">
-        <v>0</v>
-      </c>
-      <c r="AL155">
-        <v>0</v>
-      </c>
-      <c r="AM155">
-        <v>-1</v>
-      </c>
-      <c r="AN155">
-        <v>-1</v>
-      </c>
-      <c r="AO155">
-        <v>-1</v>
-      </c>
-      <c r="AP155">
-        <v>-1</v>
-      </c>
-      <c r="AQ155">
-        <v>0</v>
-      </c>
-      <c r="AR155">
-        <v>0</v>
-      </c>
-      <c r="AS155">
-        <v>0</v>
-      </c>
-      <c r="AT155">
-        <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
-        <v>0</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>0</v>
-      </c>
-      <c r="P156">
-        <v>0</v>
-      </c>
-      <c r="Q156">
-        <v>0</v>
-      </c>
-      <c r="R156">
-        <v>0</v>
-      </c>
-      <c r="S156">
-        <v>0</v>
-      </c>
-      <c r="T156">
-        <v>0</v>
-      </c>
-      <c r="U156">
-        <v>0</v>
-      </c>
-      <c r="V156">
-        <v>0</v>
-      </c>
-      <c r="W156">
-        <v>0</v>
-      </c>
-      <c r="X156">
-        <v>0</v>
-      </c>
-      <c r="Y156">
-        <v>0</v>
-      </c>
-      <c r="Z156">
-        <v>0</v>
-      </c>
-      <c r="AA156">
-        <v>0</v>
-      </c>
-      <c r="AB156">
-        <v>0</v>
-      </c>
-      <c r="AC156">
-        <v>0</v>
-      </c>
-      <c r="AD156">
-        <v>0</v>
-      </c>
-      <c r="AE156">
-        <v>0</v>
-      </c>
-      <c r="AF156">
-        <v>0</v>
-      </c>
-      <c r="AG156">
-        <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>0</v>
-      </c>
-      <c r="AK156">
-        <v>0</v>
-      </c>
-      <c r="AL156">
-        <v>0</v>
-      </c>
-      <c r="AM156">
-        <v>-1</v>
-      </c>
-      <c r="AN156">
-        <v>-1</v>
-      </c>
-      <c r="AO156">
-        <v>-1</v>
-      </c>
-      <c r="AP156">
-        <v>-1</v>
-      </c>
-      <c r="AQ156">
-        <v>0</v>
-      </c>
-      <c r="AR156">
-        <v>0</v>
-      </c>
-      <c r="AS156">
-        <v>0</v>
-      </c>
-      <c r="AT156">
-        <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="G157">
-        <v>0</v>
-      </c>
-      <c r="H157">
-        <v>0</v>
-      </c>
-      <c r="I157">
-        <v>0</v>
-      </c>
-      <c r="J157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <v>0</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
-      <c r="O157">
-        <v>0</v>
-      </c>
-      <c r="P157">
-        <v>0</v>
-      </c>
-      <c r="Q157">
-        <v>0</v>
-      </c>
-      <c r="R157">
-        <v>0</v>
-      </c>
-      <c r="S157">
-        <v>0</v>
-      </c>
-      <c r="T157">
-        <v>0</v>
-      </c>
-      <c r="U157">
-        <v>0</v>
-      </c>
-      <c r="V157">
-        <v>0</v>
-      </c>
-      <c r="W157">
-        <v>0</v>
-      </c>
-      <c r="X157">
-        <v>0</v>
-      </c>
-      <c r="Y157">
-        <v>0</v>
-      </c>
-      <c r="Z157">
-        <v>0</v>
-      </c>
-      <c r="AA157">
-        <v>0</v>
-      </c>
-      <c r="AB157">
-        <v>0</v>
-      </c>
-      <c r="AC157">
-        <v>0</v>
-      </c>
-      <c r="AD157">
-        <v>0</v>
-      </c>
-      <c r="AE157">
-        <v>0</v>
-      </c>
-      <c r="AF157">
-        <v>0</v>
-      </c>
-      <c r="AG157">
-        <v>0</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>0</v>
-      </c>
-      <c r="AK157">
-        <v>0</v>
-      </c>
-      <c r="AL157">
-        <v>0</v>
-      </c>
-      <c r="AM157">
-        <v>-1</v>
-      </c>
-      <c r="AN157">
-        <v>-1</v>
-      </c>
-      <c r="AO157">
-        <v>-1</v>
-      </c>
-      <c r="AP157">
-        <v>-1</v>
-      </c>
-      <c r="AQ157">
-        <v>0</v>
-      </c>
-      <c r="AR157">
-        <v>0</v>
-      </c>
-      <c r="AS157">
-        <v>0</v>
-      </c>
-      <c r="AT157">
-        <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="G158">
-        <v>0</v>
-      </c>
-      <c r="H158">
-        <v>0</v>
-      </c>
-      <c r="I158">
-        <v>0</v>
-      </c>
-      <c r="J158">
-        <v>0</v>
-      </c>
-      <c r="K158">
-        <v>0</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N158">
-        <v>0</v>
-      </c>
-      <c r="O158">
-        <v>0</v>
-      </c>
-      <c r="P158">
-        <v>0</v>
-      </c>
-      <c r="Q158">
-        <v>0</v>
-      </c>
-      <c r="R158">
-        <v>0</v>
-      </c>
-      <c r="S158">
-        <v>0</v>
-      </c>
-      <c r="T158">
-        <v>0</v>
-      </c>
-      <c r="U158">
-        <v>0</v>
-      </c>
-      <c r="V158">
-        <v>0</v>
-      </c>
-      <c r="W158">
-        <v>0</v>
-      </c>
-      <c r="X158">
-        <v>0</v>
-      </c>
-      <c r="Y158">
-        <v>0</v>
-      </c>
-      <c r="Z158">
-        <v>0</v>
-      </c>
-      <c r="AA158">
-        <v>0</v>
-      </c>
-      <c r="AB158">
-        <v>0</v>
-      </c>
-      <c r="AC158">
-        <v>0</v>
-      </c>
-      <c r="AD158">
-        <v>0</v>
-      </c>
-      <c r="AE158">
-        <v>0</v>
-      </c>
-      <c r="AF158">
-        <v>0</v>
-      </c>
-      <c r="AG158">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>0</v>
-      </c>
-      <c r="AK158">
-        <v>0</v>
-      </c>
-      <c r="AL158">
-        <v>0</v>
-      </c>
-      <c r="AM158">
-        <v>-1</v>
-      </c>
-      <c r="AN158">
-        <v>-1</v>
-      </c>
-      <c r="AO158">
-        <v>-1</v>
-      </c>
-      <c r="AP158">
-        <v>-1</v>
-      </c>
-      <c r="AQ158">
-        <v>0</v>
-      </c>
-      <c r="AR158">
-        <v>0</v>
-      </c>
-      <c r="AS158">
-        <v>0</v>
-      </c>
-      <c r="AT158">
-        <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>2026-08-28 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Chacarita Juniors</t>
-        </is>
-      </c>
-      <c r="G159">
-        <v>0</v>
-      </c>
-      <c r="H159">
-        <v>0</v>
-      </c>
-      <c r="I159">
-        <v>0</v>
-      </c>
-      <c r="J159">
-        <v>0</v>
-      </c>
-      <c r="K159">
-        <v>0</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N159">
-        <v>0</v>
-      </c>
-      <c r="O159">
-        <v>0</v>
-      </c>
-      <c r="P159">
-        <v>0</v>
-      </c>
-      <c r="Q159">
-        <v>0</v>
-      </c>
-      <c r="R159">
-        <v>0</v>
-      </c>
-      <c r="S159">
-        <v>0</v>
-      </c>
-      <c r="T159">
-        <v>0</v>
-      </c>
-      <c r="U159">
-        <v>0</v>
-      </c>
-      <c r="V159">
-        <v>0</v>
-      </c>
-      <c r="W159">
-        <v>0</v>
-      </c>
-      <c r="X159">
-        <v>0</v>
-      </c>
-      <c r="Y159">
-        <v>0</v>
-      </c>
-      <c r="Z159">
-        <v>0</v>
-      </c>
-      <c r="AA159">
-        <v>0</v>
-      </c>
-      <c r="AB159">
-        <v>0</v>
-      </c>
-      <c r="AC159">
-        <v>0</v>
-      </c>
-      <c r="AD159">
-        <v>0</v>
-      </c>
-      <c r="AE159">
-        <v>0</v>
-      </c>
-      <c r="AF159">
-        <v>0</v>
-      </c>
-      <c r="AG159">
-        <v>0</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>0</v>
-      </c>
-      <c r="AK159">
-        <v>0</v>
-      </c>
-      <c r="AL159">
-        <v>0</v>
-      </c>
-      <c r="AM159">
-        <v>-1</v>
-      </c>
-      <c r="AN159">
-        <v>-1</v>
-      </c>
-      <c r="AO159">
-        <v>-1</v>
-      </c>
-      <c r="AP159">
-        <v>-1</v>
-      </c>
-      <c r="AQ159">
-        <v>0</v>
-      </c>
-      <c r="AR159">
-        <v>0</v>
-      </c>
-      <c r="AS159">
-        <v>0</v>
-      </c>
-      <c r="AT159">
-        <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G160">
-        <v>0</v>
-      </c>
-      <c r="H160">
-        <v>0</v>
-      </c>
-      <c r="I160">
-        <v>0</v>
-      </c>
-      <c r="J160">
-        <v>0</v>
-      </c>
-      <c r="K160">
-        <v>0</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N160">
-        <v>0</v>
-      </c>
-      <c r="O160">
-        <v>0</v>
-      </c>
-      <c r="P160">
-        <v>0</v>
-      </c>
-      <c r="Q160">
-        <v>0</v>
-      </c>
-      <c r="R160">
-        <v>0</v>
-      </c>
-      <c r="S160">
-        <v>0</v>
-      </c>
-      <c r="T160">
-        <v>0</v>
-      </c>
-      <c r="U160">
-        <v>0</v>
-      </c>
-      <c r="V160">
-        <v>0</v>
-      </c>
-      <c r="W160">
-        <v>0</v>
-      </c>
-      <c r="X160">
-        <v>0</v>
-      </c>
-      <c r="Y160">
-        <v>0</v>
-      </c>
-      <c r="Z160">
-        <v>0</v>
-      </c>
-      <c r="AA160">
-        <v>0</v>
-      </c>
-      <c r="AB160">
-        <v>0</v>
-      </c>
-      <c r="AC160">
-        <v>0</v>
-      </c>
-      <c r="AD160">
-        <v>0</v>
-      </c>
-      <c r="AE160">
-        <v>0</v>
-      </c>
-      <c r="AF160">
-        <v>0</v>
-      </c>
-      <c r="AG160">
-        <v>0</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ160">
-        <v>0</v>
-      </c>
-      <c r="AK160">
-        <v>0</v>
-      </c>
-      <c r="AL160">
-        <v>0</v>
-      </c>
-      <c r="AM160">
-        <v>-1</v>
-      </c>
-      <c r="AN160">
-        <v>-1</v>
-      </c>
-      <c r="AO160">
-        <v>-1</v>
-      </c>
-      <c r="AP160">
-        <v>-1</v>
-      </c>
-      <c r="AQ160">
-        <v>0</v>
-      </c>
-      <c r="AR160">
-        <v>0</v>
-      </c>
-      <c r="AS160">
-        <v>0</v>
-      </c>
-      <c r="AT160">
-        <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
         <is>
           <t>2026-08-28 23:00:00</t>
         </is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -1945,58 +1945,58 @@
         <v>2.65</v>
       </c>
       <c r="P10">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="R10">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S10">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="U10">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.07</v>
+      </c>
+      <c r="Y10">
+        <v>1.54</v>
+      </c>
+      <c r="Z10">
+        <v>2.28</v>
+      </c>
+      <c r="AA10">
+        <v>2.48</v>
+      </c>
+      <c r="AB10">
+        <v>1.38</v>
+      </c>
+      <c r="AC10">
+        <v>4.8</v>
+      </c>
+      <c r="AD10">
+        <v>1.11</v>
+      </c>
+      <c r="AE10">
         <v>1.01</v>
       </c>
-      <c r="X10">
-        <v>1.09</v>
-      </c>
-      <c r="Y10">
-        <v>1.53</v>
-      </c>
-      <c r="Z10">
-        <v>2.33</v>
-      </c>
-      <c r="AA10">
-        <v>2.59</v>
-      </c>
-      <c r="AB10">
-        <v>1.39</v>
-      </c>
-      <c r="AC10">
-        <v>5.5</v>
-      </c>
-      <c r="AD10">
-        <v>1.14</v>
-      </c>
-      <c r="AE10">
-        <v>1.03</v>
-      </c>
       <c r="AF10">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
         <v>1.5</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="O13">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="P13">
         <v>1.65</v>
       </c>
       <c r="Q13">
-        <v>4.8</v>
+        <v>4.04</v>
       </c>
       <c r="R13">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="S13">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T13">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W13">
         <v>1.12</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC13">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD13">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE13">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
         <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q14">
         <v>3.52</v>
@@ -2609,10 +2609,10 @@
         <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
         <v>1.28</v>
@@ -2624,7 +2624,7 @@
         <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z14">
         <v>2.62</v>
@@ -2639,7 +2639,7 @@
         <v>4.05</v>
       </c>
       <c r="AD14">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
@@ -2648,7 +2648,7 @@
         <v>1.92</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G38">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="O102">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q102">
-        <v>2.95</v>
+        <v>3.43</v>
       </c>
       <c r="R102">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S102">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U102">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V102">
+        <v>1.5</v>
+      </c>
+      <c r="W102">
+        <v>1.11</v>
+      </c>
+      <c r="X102">
+        <v>1.03</v>
+      </c>
+      <c r="Y102">
+        <v>1.16</v>
+      </c>
+      <c r="Z102">
+        <v>4.15</v>
+      </c>
+      <c r="AA102">
+        <v>1.65</v>
+      </c>
+      <c r="AB102">
+        <v>2.11</v>
+      </c>
+      <c r="AC102">
+        <v>2.59</v>
+      </c>
+      <c r="AD102">
+        <v>1.39</v>
+      </c>
+      <c r="AE102">
+        <v>1.17</v>
+      </c>
+      <c r="AF102">
+        <v>1.53</v>
+      </c>
+      <c r="AG102">
+        <v>2.3</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.22</v>
+      </c>
+      <c r="AK102">
         <v>1.4</v>
-      </c>
-      <c r="W102">
-        <v>1.1</v>
-      </c>
-      <c r="X102">
-        <v>1.06</v>
-      </c>
-      <c r="Y102">
-        <v>1.25</v>
-      </c>
-      <c r="Z102">
-        <v>3.45</v>
-      </c>
-      <c r="AA102">
-        <v>1.9</v>
-      </c>
-      <c r="AB102">
-        <v>1.88</v>
-      </c>
-      <c r="AC102">
-        <v>3.04</v>
-      </c>
-      <c r="AD102">
-        <v>1.29</v>
-      </c>
-      <c r="AE102">
-        <v>1.11</v>
-      </c>
-      <c r="AF102">
-        <v>1.65</v>
-      </c>
-      <c r="AG102">
-        <v>2.1</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.24</v>
-      </c>
-      <c r="AK102">
-        <v>1.49</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P103">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q103">
-        <v>3.43</v>
+        <v>2.95</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
+        <v>1.34</v>
+      </c>
+      <c r="T103">
+        <v>2.88</v>
+      </c>
+      <c r="U103">
+        <v>2.66</v>
+      </c>
+      <c r="V103">
+        <v>1.4</v>
+      </c>
+      <c r="W103">
+        <v>1.1</v>
+      </c>
+      <c r="X103">
+        <v>1.06</v>
+      </c>
+      <c r="Y103">
+        <v>1.25</v>
+      </c>
+      <c r="Z103">
+        <v>3.45</v>
+      </c>
+      <c r="AA103">
+        <v>1.9</v>
+      </c>
+      <c r="AB103">
+        <v>1.88</v>
+      </c>
+      <c r="AC103">
+        <v>3.04</v>
+      </c>
+      <c r="AD103">
         <v>1.29</v>
       </c>
-      <c r="T103">
-        <v>3.3</v>
-      </c>
-      <c r="U103">
-        <v>2.5</v>
-      </c>
-      <c r="V103">
-        <v>1.5</v>
-      </c>
-      <c r="W103">
+      <c r="AE103">
         <v>1.11</v>
       </c>
-      <c r="X103">
-        <v>1.03</v>
-      </c>
-      <c r="Y103">
-        <v>1.16</v>
-      </c>
-      <c r="Z103">
-        <v>4.15</v>
-      </c>
-      <c r="AA103">
+      <c r="AF103">
         <v>1.65</v>
       </c>
-      <c r="AB103">
-        <v>2.11</v>
-      </c>
-      <c r="AC103">
-        <v>2.59</v>
-      </c>
-      <c r="AD103">
-        <v>1.39</v>
-      </c>
-      <c r="AE103">
-        <v>1.17</v>
-      </c>
-      <c r="AF103">
-        <v>1.53</v>
-      </c>
       <c r="AG103">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL103">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -638,28 +638,28 @@
         <v>5.75</v>
       </c>
       <c r="O2">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="P2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q2">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="R2">
         <v>2.5</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T2">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,7 +668,7 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z2">
         <v>5.15</v>
@@ -683,7 +683,7 @@
         <v>2.21</v>
       </c>
       <c r="AD2">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE2">
         <v>1.19</v>
@@ -692,7 +692,7 @@
         <v>1.64</v>
       </c>
       <c r="AG2">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK2">
         <v>1.06</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -816,7 +816,7 @@
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
         <v>2.56</v>
@@ -834,7 +834,7 @@
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA3">
         <v>1.65</v>
@@ -846,7 +846,7 @@
         <v>2.75</v>
       </c>
       <c r="AD3">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE3">
         <v>1.12</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S5">
         <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U5">
         <v>2.09</v>
@@ -1157,31 +1157,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
         <v>5.3</v>
       </c>
       <c r="AA5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB5">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE5">
         <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG5">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,31 +1296,31 @@
         <v>3.85</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="S6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
         <v>5.5</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="V6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Z6">
         <v>6.5</v>
@@ -1329,19 +1329,19 @@
         <v>1.3</v>
       </c>
       <c r="AB6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AC6">
         <v>1.75</v>
       </c>
       <c r="AD6">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AE6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AF6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG6">
         <v>3.14</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
         <v>3.65</v>
       </c>
       <c r="P7">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="S7">
         <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="U7">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="V7">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="AA7">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB7">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="AD7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE7">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
         <v>2.99</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q28">
         <v>2.22</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>7.25</v>
+        <v>3.42</v>
       </c>
       <c r="O44">
-        <v>3.96</v>
+        <v>2.59</v>
       </c>
       <c r="P44">
-        <v>1.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q44">
-        <v>7.21</v>
+        <v>4.72</v>
       </c>
       <c r="R44">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="S44">
-        <v>1.39</v>
+        <v>1.69</v>
       </c>
       <c r="T44">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="U44">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="Z44">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="AA44">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AB44">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AC44">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AD44">
+        <v>1.09</v>
+      </c>
+      <c r="AE44">
+        <v>1.03</v>
+      </c>
+      <c r="AF44">
+        <v>2.23</v>
+      </c>
+      <c r="AG44">
+        <v>1.57</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.4</v>
+      </c>
+      <c r="AK44">
         <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.05</v>
-      </c>
-      <c r="AF44">
-        <v>2.09</v>
-      </c>
-      <c r="AG44">
-        <v>1.65</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.17</v>
-      </c>
-      <c r="AK44">
-        <v>1.04</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.42</v>
+        <v>7.25</v>
       </c>
       <c r="O45">
-        <v>2.59</v>
+        <v>3.96</v>
       </c>
       <c r="P45">
-        <v>2.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q45">
-        <v>4.72</v>
+        <v>7.21</v>
       </c>
       <c r="R45">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="S45">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="T45">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="U45">
-        <v>3.84</v>
+        <v>2.88</v>
       </c>
       <c r="V45">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="W45">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="Z45">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="AB45">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AC45">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD45">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AE45">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AG45">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7828,16 +7828,16 @@
         <v>2.63</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
         <v>1.3</v>
@@ -7858,7 +7858,7 @@
         <v>1.25</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
         <v>1.73</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="O64">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="P64">
-        <v>4.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q64">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V64">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AB64">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AC64">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF64">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK64">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O66">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="P66">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="O67">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
-        <v>3.71</v>
+        <v>4.85</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T67">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="U67">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="V67">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>2.89</v>
+        <v>3.7</v>
       </c>
       <c r="AA67">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AB67">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AC67">
-        <v>3.77</v>
+        <v>3.03</v>
       </c>
       <c r="AD67">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,37 +12371,37 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="O74">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P74">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="Q74">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="R74">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U74">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V74">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
         <v>1.15</v>
@@ -12410,25 +12410,25 @@
         <v>4.6</v>
       </c>
       <c r="AA74">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AB74">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AC74">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="AD74">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O76">
         <v>3.7</v>
       </c>
       <c r="P76">
-        <v>3.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q76">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="R76">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U76">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="V76">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="AA76">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB76">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC76">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AD76">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF76">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="O77">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
-        <v>3.92</v>
+        <v>2.3</v>
       </c>
       <c r="Q77">
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="R77">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T77">
-        <v>4.8</v>
+        <v>3.68</v>
       </c>
       <c r="U77">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="V77">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="W77">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z77">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA77">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AB77">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC77">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD77">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AE77">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF77">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG77">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK77">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,34 +13023,34 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O78">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="Q78">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="R78">
         <v>2.34</v>
       </c>
       <c r="S78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
         <v>3.44</v>
       </c>
       <c r="U78">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V78">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W78">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X78">
         <v>1.02</v>
@@ -13059,13 +13059,13 @@
         <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA78">
         <v>1.49</v>
       </c>
       <c r="AB78">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC78">
         <v>2.33</v>
@@ -13074,10 +13074,10 @@
         <v>1.57</v>
       </c>
       <c r="AE78">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF78">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG78">
         <v>2.53</v>
@@ -13096,7 +13096,7 @@
         <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,61 +13186,61 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.56</v>
+        <v>1.73</v>
       </c>
       <c r="O79">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q79">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R79">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="S79">
+        <v>1.16</v>
+      </c>
+      <c r="T79">
+        <v>4.2</v>
+      </c>
+      <c r="U79">
+        <v>1.95</v>
+      </c>
+      <c r="V79">
+        <v>1.75</v>
+      </c>
+      <c r="W79">
         <v>1.2</v>
-      </c>
-      <c r="T79">
-        <v>3.8</v>
-      </c>
-      <c r="U79">
-        <v>2</v>
-      </c>
-      <c r="V79">
-        <v>1.7</v>
-      </c>
-      <c r="W79">
-        <v>1.16</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z79">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AA79">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB79">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AC79">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD79">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE79">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG79">
         <v>2.86</v>
@@ -13259,7 +13259,7 @@
         <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>1.44</v>
+        <v>2.01</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="O82">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q82">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R82">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="S82">
+        <v>1.24</v>
+      </c>
+      <c r="T82">
+        <v>3.8</v>
+      </c>
+      <c r="U82">
+        <v>2.2</v>
+      </c>
+      <c r="V82">
+        <v>1.59</v>
+      </c>
+      <c r="W82">
+        <v>1.13</v>
+      </c>
+      <c r="X82">
+        <v>1.01</v>
+      </c>
+      <c r="Y82">
+        <v>1.15</v>
+      </c>
+      <c r="Z82">
+        <v>4.65</v>
+      </c>
+      <c r="AA82">
+        <v>1.48</v>
+      </c>
+      <c r="AB82">
+        <v>2.33</v>
+      </c>
+      <c r="AC82">
+        <v>2.25</v>
+      </c>
+      <c r="AD82">
+        <v>1.57</v>
+      </c>
+      <c r="AE82">
         <v>1.2</v>
       </c>
-      <c r="T82">
-        <v>4</v>
-      </c>
-      <c r="U82">
-        <v>2.15</v>
-      </c>
-      <c r="V82">
-        <v>1.67</v>
-      </c>
-      <c r="W82">
-        <v>1.14</v>
-      </c>
-      <c r="X82">
-        <v>1.02</v>
-      </c>
-      <c r="Y82">
-        <v>1.1</v>
-      </c>
-      <c r="Z82">
-        <v>5.05</v>
-      </c>
-      <c r="AA82">
-        <v>1.42</v>
-      </c>
-      <c r="AB82">
-        <v>2.6</v>
-      </c>
-      <c r="AC82">
-        <v>2.16</v>
-      </c>
-      <c r="AD82">
-        <v>1.67</v>
-      </c>
-      <c r="AE82">
-        <v>1.24</v>
-      </c>
       <c r="AF82">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG82">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R83">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="S83">
+        <v>1.2</v>
+      </c>
+      <c r="T83">
+        <v>4</v>
+      </c>
+      <c r="U83">
+        <v>2.15</v>
+      </c>
+      <c r="V83">
+        <v>1.67</v>
+      </c>
+      <c r="W83">
+        <v>1.14</v>
+      </c>
+      <c r="X83">
+        <v>1.02</v>
+      </c>
+      <c r="Y83">
+        <v>1.1</v>
+      </c>
+      <c r="Z83">
+        <v>5.05</v>
+      </c>
+      <c r="AA83">
+        <v>1.42</v>
+      </c>
+      <c r="AB83">
+        <v>2.6</v>
+      </c>
+      <c r="AC83">
+        <v>2.16</v>
+      </c>
+      <c r="AD83">
+        <v>1.67</v>
+      </c>
+      <c r="AE83">
         <v>1.24</v>
       </c>
-      <c r="T83">
-        <v>3.8</v>
-      </c>
-      <c r="U83">
-        <v>2.2</v>
-      </c>
-      <c r="V83">
-        <v>1.59</v>
-      </c>
-      <c r="W83">
-        <v>1.13</v>
-      </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.15</v>
-      </c>
-      <c r="Z83">
-        <v>4.65</v>
-      </c>
-      <c r="AA83">
-        <v>1.48</v>
-      </c>
-      <c r="AB83">
-        <v>2.33</v>
-      </c>
-      <c r="AC83">
-        <v>2.25</v>
-      </c>
-      <c r="AD83">
-        <v>1.57</v>
-      </c>
-      <c r="AE83">
+      <c r="AF83">
+        <v>1.42</v>
+      </c>
+      <c r="AG83">
+        <v>2.62</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.2</v>
       </c>
-      <c r="AF83">
-        <v>1.44</v>
-      </c>
-      <c r="AG83">
-        <v>2.55</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.22</v>
-      </c>
       <c r="AK83">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O99">
         <v>3.39</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="O100">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>7.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q100">
-        <v>1.67</v>
+        <v>2.99</v>
       </c>
       <c r="R100">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="S100">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="U100">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="V100">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="W100">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z100">
-        <v>5.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA100">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AB100">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AC100">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="AD100">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AE100">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF100">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AG100">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>3.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,61 +16772,61 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="O101">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="P101">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="Q101">
+        <v>1.65</v>
+      </c>
+      <c r="R101">
+        <v>2.7</v>
+      </c>
+      <c r="S101">
+        <v>1.22</v>
+      </c>
+      <c r="T101">
+        <v>3.9</v>
+      </c>
+      <c r="U101">
         <v>1.93</v>
       </c>
-      <c r="R101">
-        <v>2.4</v>
-      </c>
-      <c r="S101">
-        <v>1.26</v>
-      </c>
-      <c r="T101">
-        <v>3.4</v>
-      </c>
-      <c r="U101">
-        <v>2.3</v>
-      </c>
       <c r="V101">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="W101">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="Z101">
-        <v>4.42</v>
+        <v>5.3</v>
       </c>
       <c r="AA101">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AB101">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="AC101">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AD101">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE101">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF101">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG101">
         <v>1.95</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK101">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="P102">
-        <v>2.2</v>
+        <v>6.75</v>
       </c>
       <c r="Q102">
-        <v>3.43</v>
+        <v>1.79</v>
       </c>
       <c r="R102">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="S102">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T102">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U102">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V102">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
+        <v>1.17</v>
+      </c>
+      <c r="Z102">
+        <v>4.45</v>
+      </c>
+      <c r="AA102">
+        <v>1.57</v>
+      </c>
+      <c r="AB102">
+        <v>2.1</v>
+      </c>
+      <c r="AC102">
+        <v>2.38</v>
+      </c>
+      <c r="AD102">
+        <v>1.46</v>
+      </c>
+      <c r="AE102">
         <v>1.16</v>
       </c>
-      <c r="Z102">
-        <v>4.15</v>
-      </c>
-      <c r="AA102">
-        <v>1.65</v>
-      </c>
-      <c r="AB102">
-        <v>2.11</v>
-      </c>
-      <c r="AC102">
-        <v>2.59</v>
-      </c>
-      <c r="AD102">
-        <v>1.39</v>
-      </c>
-      <c r="AE102">
-        <v>1.17</v>
-      </c>
       <c r="AF102">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK102">
-        <v>1.4</v>
+        <v>2.68</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,49 +17107,49 @@
         <v>2.75</v>
       </c>
       <c r="Q103">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S103">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T103">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U103">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
         <v>1.25</v>
       </c>
       <c r="Z103">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA103">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB103">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC103">
         <v>3.04</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF103">
         <v>1.65</v>
@@ -17171,7 +17171,7 @@
         <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G114">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G130">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
+        <v>4.7</v>
+      </c>
+      <c r="O13">
+        <v>4.2</v>
+      </c>
+      <c r="P13">
+        <v>1.66</v>
+      </c>
+      <c r="Q13">
         <v>4.75</v>
-      </c>
-      <c r="O13">
-        <v>4.1</v>
-      </c>
-      <c r="P13">
-        <v>1.65</v>
-      </c>
-      <c r="Q13">
-        <v>4.04</v>
       </c>
       <c r="R13">
         <v>2.33</v>
@@ -2461,7 +2461,7 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
         <v>4.8</v>
@@ -2470,13 +2470,13 @@
         <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AC13">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AD13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE13">
         <v>1.21</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
+        <v>3.05</v>
+      </c>
+      <c r="P14">
+        <v>2.8</v>
+      </c>
+      <c r="Q14">
+        <v>3.07</v>
+      </c>
+      <c r="R14">
+        <v>2.13</v>
+      </c>
+      <c r="S14">
+        <v>1.36</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
         <v>3</v>
       </c>
-      <c r="P14">
-        <v>2.45</v>
-      </c>
-      <c r="Q14">
-        <v>3.52</v>
-      </c>
-      <c r="R14">
-        <v>1.95</v>
-      </c>
-      <c r="S14">
-        <v>1.47</v>
-      </c>
-      <c r="T14">
-        <v>2.6</v>
-      </c>
-      <c r="U14">
-        <v>3.3</v>
-      </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
         <v>1.02</v>
       </c>
-      <c r="X14">
-        <v>1.04</v>
-      </c>
       <c r="Y14">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z14">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="AA14">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AC14">
-        <v>4.05</v>
+        <v>3.57</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AG14">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AK14">
         <v>1.4</v>
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q26">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R26">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA26">
+        <v>2.04</v>
+      </c>
+      <c r="AB26">
+        <v>1.76</v>
+      </c>
+      <c r="AC26">
+        <v>3.6</v>
+      </c>
+      <c r="AD26">
+        <v>1.25</v>
+      </c>
+      <c r="AE26">
+        <v>1.07</v>
+      </c>
+      <c r="AF26">
+        <v>1.75</v>
+      </c>
+      <c r="AG26">
         <v>1.97</v>
       </c>
-      <c r="AB26">
-        <v>1.79</v>
-      </c>
-      <c r="AC26">
-        <v>3.34</v>
-      </c>
-      <c r="AD26">
-        <v>1.24</v>
-      </c>
-      <c r="AE26">
-        <v>1.04</v>
-      </c>
-      <c r="AF26">
-        <v>1.7</v>
-      </c>
-      <c r="AG26">
-        <v>2</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,46 +4719,46 @@
         <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="R27">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U27">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA27">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC27">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD27">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE27">
         <v>1.05</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>4.4</v>
       </c>
       <c r="Q28">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="U28">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="V28">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="AA28">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AB28">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="AD28">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5371,71 +5371,71 @@
         <v>4.35</v>
       </c>
       <c r="Q31">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R31">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="S31">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T31">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="U31">
-        <v>3.24</v>
+        <v>2.86</v>
       </c>
       <c r="V31">
+        <v>1.33</v>
+      </c>
+      <c r="W31">
+        <v>1.02</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
+        <v>3</v>
+      </c>
+      <c r="AA31">
+        <v>1.98</v>
+      </c>
+      <c r="AB31">
+        <v>1.65</v>
+      </c>
+      <c r="AC31">
+        <v>3.74</v>
+      </c>
+      <c r="AD31">
+        <v>1.19</v>
+      </c>
+      <c r="AE31">
+        <v>1.05</v>
+      </c>
+      <c r="AF31">
+        <v>1.77</v>
+      </c>
+      <c r="AG31">
+        <v>1.88</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.3</v>
       </c>
-      <c r="W31">
-        <v>1.01</v>
-      </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.35</v>
-      </c>
-      <c r="Z31">
-        <v>2.97</v>
-      </c>
-      <c r="AA31">
-        <v>2.1</v>
-      </c>
-      <c r="AB31">
-        <v>1.7</v>
-      </c>
-      <c r="AC31">
-        <v>3.92</v>
-      </c>
-      <c r="AD31">
-        <v>1.22</v>
-      </c>
-      <c r="AE31">
-        <v>1.01</v>
-      </c>
-      <c r="AF31">
-        <v>1.93</v>
-      </c>
-      <c r="AG31">
-        <v>1.76</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.29</v>
-      </c>
       <c r="AK31">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q39">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U39">
         <v>2.5</v>
@@ -6693,37 +6693,37 @@
         <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.92</v>
+        <v>4.29</v>
       </c>
       <c r="AA39">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB39">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC39">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD39">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE39">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="R40">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U40">
         <v>2.5</v>
@@ -6856,53 +6856,53 @@
         <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
+        <v>1.18</v>
+      </c>
+      <c r="Z40">
+        <v>3.92</v>
+      </c>
+      <c r="AA40">
+        <v>1.72</v>
+      </c>
+      <c r="AB40">
+        <v>2.07</v>
+      </c>
+      <c r="AC40">
+        <v>2.68</v>
+      </c>
+      <c r="AD40">
+        <v>1.37</v>
+      </c>
+      <c r="AE40">
+        <v>1.16</v>
+      </c>
+      <c r="AF40">
+        <v>1.71</v>
+      </c>
+      <c r="AG40">
+        <v>2.02</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.22</v>
       </c>
-      <c r="Z40">
-        <v>4.29</v>
-      </c>
-      <c r="AA40">
-        <v>1.74</v>
-      </c>
-      <c r="AB40">
-        <v>2.12</v>
-      </c>
-      <c r="AC40">
-        <v>2.64</v>
-      </c>
-      <c r="AD40">
-        <v>1.38</v>
-      </c>
-      <c r="AE40">
-        <v>1.17</v>
-      </c>
-      <c r="AF40">
-        <v>1.57</v>
-      </c>
-      <c r="AG40">
-        <v>2.3</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.26</v>
-      </c>
       <c r="AK40">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7807,61 +7807,61 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q46">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R46">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="U46">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V46">
         <v>1.33</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA46">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB46">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE46">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG46">
         <v>1.92</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q49">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="R49">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S49">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="U49">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AB49">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC49">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AD49">
         <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG49">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10578,31 +10578,31 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="O63">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P63">
-        <v>4.02</v>
+        <v>4.5</v>
       </c>
       <c r="Q63">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R63">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="S63">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="U63">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V63">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
         <v>1.07</v>
@@ -10611,31 +10611,31 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA63">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AB63">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AC63">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD63">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK63">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
+        <v>2.37</v>
+      </c>
+      <c r="O64">
+        <v>3.25</v>
+      </c>
+      <c r="P64">
         <v>2.6</v>
-      </c>
-      <c r="O64">
-        <v>3.52</v>
-      </c>
-      <c r="P64">
-        <v>2.7</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="P65">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="Q65">
         <v>2.7</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T65">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V65">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
         <v>1.34</v>
       </c>
       <c r="Z65">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA65">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AB65">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="AD65">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE65">
         <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG65">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="O66">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Q66">
         <v>3.66</v>
@@ -11109,7 +11109,7 @@
         <v>2.28</v>
       </c>
       <c r="AB66">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC66">
         <v>4.2</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK66">
         <v>1.4</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="Q67">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="R67">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="U67">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W67">
+        <v>1.05</v>
+      </c>
+      <c r="X67">
+        <v>1.05</v>
+      </c>
+      <c r="Y67">
+        <v>1.27</v>
+      </c>
+      <c r="Z67">
+        <v>3.4</v>
+      </c>
+      <c r="AA67">
+        <v>1.88</v>
+      </c>
+      <c r="AB67">
+        <v>1.85</v>
+      </c>
+      <c r="AC67">
+        <v>3.35</v>
+      </c>
+      <c r="AD67">
+        <v>1.3</v>
+      </c>
+      <c r="AE67">
         <v>1.06</v>
       </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>1.25</v>
-      </c>
-      <c r="Z67">
-        <v>3.7</v>
-      </c>
-      <c r="AA67">
-        <v>1.76</v>
-      </c>
-      <c r="AB67">
-        <v>2.01</v>
-      </c>
-      <c r="AC67">
-        <v>3.03</v>
-      </c>
-      <c r="AD67">
-        <v>1.37</v>
-      </c>
-      <c r="AE67">
-        <v>1.13</v>
-      </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG67">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK67">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O70">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q70">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R70">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
         <v>1.35</v>
       </c>
       <c r="T70">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U70">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V70">
         <v>1.4</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA70">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB70">
         <v>1.88</v>
       </c>
       <c r="AC70">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD70">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF70">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG70">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.24</v>
       </c>
       <c r="AK70">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="Q78">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="R78">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T78">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="U78">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V78">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W78">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z78">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AA78">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AC78">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AD78">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AE78">
+        <v>1.3</v>
+      </c>
+      <c r="AF78">
+        <v>1.4</v>
+      </c>
+      <c r="AG78">
+        <v>2.86</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.23</v>
       </c>
-      <c r="AF78">
-        <v>1.44</v>
-      </c>
-      <c r="AG78">
-        <v>2.53</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.24</v>
-      </c>
       <c r="AK78">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="Q79">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="R79">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="S79">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T79">
+        <v>3.44</v>
+      </c>
+      <c r="U79">
+        <v>2.2</v>
+      </c>
+      <c r="V79">
+        <v>1.62</v>
+      </c>
+      <c r="W79">
+        <v>1.12</v>
+      </c>
+      <c r="X79">
+        <v>1.02</v>
+      </c>
+      <c r="Y79">
+        <v>1.12</v>
+      </c>
+      <c r="Z79">
         <v>4.2</v>
       </c>
-      <c r="U79">
-        <v>1.95</v>
-      </c>
-      <c r="V79">
-        <v>1.75</v>
-      </c>
-      <c r="W79">
-        <v>1.2</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.05</v>
-      </c>
-      <c r="Z79">
-        <v>6</v>
-      </c>
       <c r="AA79">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AB79">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC79">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AD79">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AE79">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF79">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG79">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13533,10 +13533,10 @@
         <v>3.7</v>
       </c>
       <c r="U81">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="V81">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W81">
         <v>1.12</v>
@@ -13545,7 +13545,7 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z81">
         <v>4.75</v>
@@ -13557,13 +13557,13 @@
         <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD81">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE81">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF81">
         <v>1.5</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="AK81">
         <v>1.25</v>
@@ -14010,22 +14010,22 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R84">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S84">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U84">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V84">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W84">
         <v>1.08</v>
@@ -14040,25 +14040,25 @@
         <v>3.4</v>
       </c>
       <c r="AA84">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB84">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AD84">
         <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF84">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AG84">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK84">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14342,19 +14342,19 @@
         <v>2.09</v>
       </c>
       <c r="S86">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T86">
         <v>3.18</v>
       </c>
       <c r="U86">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V86">
         <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
         <v>1.05</v>
@@ -14369,7 +14369,7 @@
         <v>1.8</v>
       </c>
       <c r="AB86">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC86">
         <v>3.01</v>
@@ -14378,7 +14378,7 @@
         <v>1.33</v>
       </c>
       <c r="AE86">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF86">
         <v>1.65</v>
@@ -14834,46 +14834,46 @@
         <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U89">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="V89">
         <v>1.51</v>
       </c>
       <c r="W89">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z89">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA89">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB89">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC89">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="AD89">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE89">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
         <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15794,61 +15794,61 @@
         </is>
       </c>
       <c r="N95">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O95">
         <v>3.9</v>
       </c>
       <c r="P95">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q95">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S95">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T95">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U95">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V95">
         <v>1.5</v>
       </c>
       <c r="W95">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X95">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
         <v>1.2</v>
       </c>
       <c r="Z95">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="AA95">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB95">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC95">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AD95">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE95">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG95">
         <v>2.1</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK95">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O96">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="P96">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="Q96">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="R96">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T96">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U96">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W96">
         <v>1.13</v>
@@ -15990,13 +15990,13 @@
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z96">
         <v>4.4</v>
       </c>
       <c r="AA96">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AB96">
         <v>2.39</v>
@@ -16011,10 +16011,10 @@
         <v>1.2</v>
       </c>
       <c r="AF96">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG96">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.14</v>
       </c>
       <c r="AK96">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O97">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P97">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Q97">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R97">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T97">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="V97">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W97">
         <v>1.13</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA97">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AB97">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="AC97">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD97">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE97">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF97">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG97">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK97">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16286,13 +16286,13 @@
         <v>2.55</v>
       </c>
       <c r="O98">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
         <v>2.4</v>
       </c>
       <c r="Q98">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R98">
         <v>2.2</v>
@@ -16304,43 +16304,43 @@
         <v>3.04</v>
       </c>
       <c r="U98">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V98">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y98">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z98">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA98">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB98">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC98">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG98">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.5</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,65 +16935,65 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="O102">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>6.75</v>
+        <v>2.75</v>
       </c>
       <c r="Q102">
-        <v>1.79</v>
+        <v>2.77</v>
       </c>
       <c r="R102">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="S102">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T102">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="U102">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="V102">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA102">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AB102">
+        <v>1.94</v>
+      </c>
+      <c r="AC102">
+        <v>3.04</v>
+      </c>
+      <c r="AD102">
+        <v>1.34</v>
+      </c>
+      <c r="AE102">
+        <v>1.07</v>
+      </c>
+      <c r="AF102">
+        <v>1.65</v>
+      </c>
+      <c r="AG102">
         <v>2.1</v>
       </c>
-      <c r="AC102">
-        <v>2.38</v>
-      </c>
-      <c r="AD102">
-        <v>1.46</v>
-      </c>
-      <c r="AE102">
-        <v>1.16</v>
-      </c>
-      <c r="AF102">
-        <v>1.73</v>
-      </c>
-      <c r="AG102">
-        <v>1.98</v>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O103">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="P103">
-        <v>2.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q103">
-        <v>2.77</v>
+        <v>1.79</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="S103">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="U103">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="V103">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W103">
+        <v>1.1</v>
+      </c>
+      <c r="X103">
         <v>1.04</v>
       </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
       <c r="Y103">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA103">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AB103">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC103">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AD103">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE103">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF103">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK103">
-        <v>1.47</v>
+        <v>2.68</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="O104">
-        <v>4.92</v>
+        <v>4.7</v>
       </c>
       <c r="P104">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q104">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="R104">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S104">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T104">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="U104">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="V104">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z104">
-        <v>3.6</v>
+        <v>3.81</v>
       </c>
       <c r="AA104">
         <v>1.9</v>
       </c>
       <c r="AB104">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC104">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="AD104">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE104">
         <v>1.08</v>
       </c>
       <c r="AF104">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG104">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17750,52 +17750,52 @@
         </is>
       </c>
       <c r="N107">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O107">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="P107">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q107">
-        <v>5</v>
+        <v>5.48</v>
       </c>
       <c r="R107">
         <v>2.53</v>
       </c>
       <c r="S107">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U107">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="V107">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W107">
         <v>1.11</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y107">
         <v>1.18</v>
       </c>
       <c r="Z107">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA107">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AB107">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AC107">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AD107">
         <v>1.44</v>
@@ -17807,7 +17807,7 @@
         <v>1.68</v>
       </c>
       <c r="AG107">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O108">
         <v>3.5</v>
       </c>
       <c r="P108">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="Q108">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S108">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T108">
         <v>3.3</v>
       </c>
       <c r="U108">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V108">
         <v>1.45</v>
       </c>
       <c r="W108">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z108">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA108">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB108">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC108">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AD108">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE108">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF108">
         <v>1.59</v>
       </c>
       <c r="AG108">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AK108">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18082,58 +18082,58 @@
         <v>3.1</v>
       </c>
       <c r="P109">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q109">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="R109">
         <v>1.98</v>
       </c>
       <c r="S109">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T109">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="U109">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V109">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W109">
         <v>1.01</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z109">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AA109">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AB109">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AC109">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="AD109">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE109">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AG109">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G145">

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,80 +12371,80 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.65</v>
+        <v>1.65</v>
       </c>
       <c r="O74">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P74">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="Q74">
-        <v>3.48</v>
+        <v>2</v>
       </c>
       <c r="R74">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T74">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="U74">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="V74">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="W74">
+        <v>1.16</v>
+      </c>
+      <c r="X74">
+        <v>1.01</v>
+      </c>
+      <c r="Y74">
         <v>1.12</v>
       </c>
-      <c r="X74">
-        <v>1.02</v>
-      </c>
-      <c r="Y74">
-        <v>1.15</v>
-      </c>
       <c r="Z74">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA74">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AC74">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="AD74">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AE74">
+        <v>1.29</v>
+      </c>
+      <c r="AF74">
+        <v>1.43</v>
+      </c>
+      <c r="AG74">
+        <v>2.63</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
         <v>1.17</v>
       </c>
-      <c r="AF74">
-        <v>1.5</v>
-      </c>
-      <c r="AG74">
-        <v>2.4</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>1.25</v>
-      </c>
       <c r="AK74">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P75">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q75">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="R75">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T75">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="U75">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V75">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W75">
         <v>1.16</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z75">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB75">
         <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD75">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AE75">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF75">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AG75">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
         <v>3.7</v>
       </c>
       <c r="P76">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q76">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="R76">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T76">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="U76">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="V76">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z76">
-        <v>4.94</v>
+        <v>6</v>
       </c>
       <c r="AA76">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AB76">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="AC76">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AE76">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF76">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG76">
-        <v>2.35</v>
+        <v>2.86</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O77">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P77">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q77">
-        <v>2.92</v>
+        <v>3.48</v>
       </c>
       <c r="R77">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S77">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T77">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U77">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="V77">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="W77">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z77">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA77">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AB77">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="AC77">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="AD77">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AE77">
+        <v>1.17</v>
+      </c>
+      <c r="AF77">
+        <v>1.5</v>
+      </c>
+      <c r="AG77">
+        <v>2.4</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
         <v>1.25</v>
       </c>
-      <c r="AF77">
-        <v>1.38</v>
-      </c>
-      <c r="AG77">
-        <v>2.76</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.23</v>
-      </c>
       <c r="AK77">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="Q78">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="R78">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="S78">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
+        <v>3.44</v>
+      </c>
+      <c r="U78">
+        <v>2.2</v>
+      </c>
+      <c r="V78">
+        <v>1.62</v>
+      </c>
+      <c r="W78">
+        <v>1.12</v>
+      </c>
+      <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.12</v>
+      </c>
+      <c r="Z78">
         <v>4.2</v>
       </c>
-      <c r="U78">
-        <v>1.95</v>
-      </c>
-      <c r="V78">
-        <v>1.75</v>
-      </c>
-      <c r="W78">
-        <v>1.2</v>
-      </c>
-      <c r="X78">
-        <v>1.01</v>
-      </c>
-      <c r="Y78">
-        <v>1.05</v>
-      </c>
-      <c r="Z78">
-        <v>6</v>
-      </c>
       <c r="AA78">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AB78">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC78">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AD78">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AE78">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF78">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG78">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="O79">
+        <v>3.7</v>
+      </c>
+      <c r="P79">
         <v>3.6</v>
       </c>
-      <c r="P79">
-        <v>2.97</v>
-      </c>
       <c r="Q79">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="R79">
         <v>2.34</v>
       </c>
       <c r="S79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="U79">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V79">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W79">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z79">
-        <v>4.2</v>
+        <v>4.94</v>
       </c>
       <c r="AA79">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AB79">
+        <v>2.15</v>
+      </c>
+      <c r="AC79">
         <v>2.35</v>
-      </c>
-      <c r="AC79">
-        <v>2.33</v>
       </c>
       <c r="AD79">
         <v>1.57</v>
       </c>
       <c r="AE79">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG79">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O96">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="P96">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q96">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R96">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="S96">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T96">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U96">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V96">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W96">
         <v>1.13</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA96">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AB96">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="AC96">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD96">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE96">
         <v>1.2</v>
       </c>
       <c r="AF96">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG96">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK96">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.3</v>
+        <v>2.55</v>
       </c>
       <c r="O97">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="Q97">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="R97">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T97">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U97">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="V97">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y97">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA97">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AB97">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="AC97">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="AD97">
+        <v>1.4</v>
+      </c>
+      <c r="AE97">
+        <v>1.14</v>
+      </c>
+      <c r="AF97">
         <v>1.59</v>
       </c>
-      <c r="AE97">
-        <v>1.2</v>
-      </c>
-      <c r="AF97">
-        <v>1.85</v>
-      </c>
       <c r="AG97">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="AK97">
-        <v>3.22</v>
+        <v>1.45</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.55</v>
+        <v>1.33</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="P98">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q98">
-        <v>3.1</v>
+        <v>1.68</v>
       </c>
       <c r="R98">
+        <v>2.61</v>
+      </c>
+      <c r="S98">
+        <v>1.2</v>
+      </c>
+      <c r="T98">
+        <v>4</v>
+      </c>
+      <c r="U98">
         <v>2.2</v>
       </c>
-      <c r="S98">
-        <v>1.33</v>
-      </c>
-      <c r="T98">
-        <v>3.04</v>
-      </c>
-      <c r="U98">
-        <v>2.53</v>
-      </c>
       <c r="V98">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W98">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X98">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA98">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="AB98">
-        <v>2.07</v>
+        <v>2.39</v>
       </c>
       <c r="AC98">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="AD98">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE98">
+        <v>1.2</v>
+      </c>
+      <c r="AF98">
+        <v>1.77</v>
+      </c>
+      <c r="AG98">
+        <v>1.94</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.14</v>
       </c>
-      <c r="AF98">
-        <v>1.59</v>
-      </c>
-      <c r="AG98">
-        <v>2.21</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.5</v>
-      </c>
       <c r="AK98">
-        <v>1.45</v>
+        <v>2.94</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="O101">
-        <v>5.75</v>
+        <v>4.7</v>
       </c>
       <c r="P101">
-        <v>8.4</v>
+        <v>6.75</v>
       </c>
       <c r="Q101">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="R101">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="S101">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T101">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="U101">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="V101">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="W101">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>5.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA101">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AB101">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC101">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD101">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE101">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AF101">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK101">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="O103">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="P103">
-        <v>6.75</v>
+        <v>8.4</v>
       </c>
       <c r="Q103">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="R103">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="S103">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="U103">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="V103">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z103">
-        <v>4.45</v>
+        <v>5.3</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AB103">
+        <v>2.65</v>
+      </c>
+      <c r="AC103">
         <v>2.1</v>
       </c>
-      <c r="AC103">
-        <v>2.38</v>
-      </c>
       <c r="AD103">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AE103">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG103">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK103">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -19715,46 +19715,46 @@
         <v>0</v>
       </c>
       <c r="Q119">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R119">
         <v>2.2</v>
       </c>
       <c r="S119">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T119">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U119">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V119">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W119">
         <v>1.06</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y119">
         <v>1.3</v>
       </c>
       <c r="Z119">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AA119">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB119">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC119">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="AD119">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE119">
         <v>1.1</v>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK119">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19872,28 +19872,28 @@
         <v>2.6</v>
       </c>
       <c r="O120">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P120">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q120">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R120">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T120">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U120">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="V120">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W120">
         <v>1.11</v>
@@ -19905,28 +19905,28 @@
         <v>1.19</v>
       </c>
       <c r="Z120">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AA120">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB120">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC120">
         <v>2.6</v>
       </c>
       <c r="AD120">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE120">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF120">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG120">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK120">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20044,13 +20044,13 @@
         <v>2.4</v>
       </c>
       <c r="R121">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S121">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T121">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U121">
         <v>3.16</v>
@@ -20059,37 +20059,37 @@
         <v>1.3</v>
       </c>
       <c r="W121">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
         <v>1.36</v>
       </c>
       <c r="Z121">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA121">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AB121">
         <v>1.62</v>
       </c>
       <c r="AC121">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="AD121">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE121">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF121">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AG121">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU149"/>
+  <dimension ref="A1:AU148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O11">
         <v>2.65</v>
       </c>
       <c r="P11">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S11">
         <v>1.57</v>
       </c>
       <c r="T11">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
         <v>3.8</v>
@@ -2132,25 +2132,25 @@
         <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y11">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z11">
         <v>2.28</v>
       </c>
       <c r="AA11">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB11">
         <v>1.38</v>
       </c>
       <c r="AC11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE11">
         <v>1.01</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
         <v>1.5</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7004,31 +7004,31 @@
         <v>3.42</v>
       </c>
       <c r="R41">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
         <v>1.24</v>
       </c>
       <c r="T41">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>4.98</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
         <v>1.49</v>
@@ -7043,7 +7043,7 @@
         <v>1.55</v>
       </c>
       <c r="AE41">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF41">
         <v>1.46</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7170,16 +7170,16 @@
         <v>2.7</v>
       </c>
       <c r="S42">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T42">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U42">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V42">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W42">
         <v>1.22</v>
@@ -7188,16 +7188,16 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z42">
-        <v>6.45</v>
+        <v>6.3</v>
       </c>
       <c r="AA42">
         <v>1.33</v>
       </c>
       <c r="AB42">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="AC42">
         <v>1.82</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK42">
         <v>1.07</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="O44">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="P44">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>4.72</v>
+        <v>4.1</v>
       </c>
       <c r="R44">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="S44">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="T44">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="U44">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="V44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W44">
         <v>1.01</v>
@@ -7517,22 +7517,22 @@
         <v>1.62</v>
       </c>
       <c r="Z44">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AA44">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AB44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC44">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD44">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF44">
         <v>2.23</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="O45">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="P45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q45">
-        <v>7.21</v>
+        <v>6.5</v>
       </c>
       <c r="R45">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S45">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U45">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V45">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
         <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z45">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA45">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB45">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG45">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.17</v>
+        <v>2.63</v>
       </c>
       <c r="AK45">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8631,22 +8631,22 @@
         <v>3.23</v>
       </c>
       <c r="Q51">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R51">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
         <v>1.07</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA51">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB51">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
         <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK51">
         <v>1.64</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G69">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O75">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P75">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q75">
-        <v>2.92</v>
+        <v>2.15</v>
       </c>
       <c r="R75">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S75">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="T75">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="U75">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V75">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W75">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z75">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA75">
         <v>1.4</v>
       </c>
       <c r="AB75">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC75">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AD75">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AE75">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF75">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG75">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>1.46</v>
+        <v>2.01</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="O76">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P76">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="Q76">
-        <v>2.15</v>
+        <v>3.48</v>
       </c>
       <c r="R76">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="S76">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="U76">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="V76">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="W76">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z76">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA76">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AB76">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="AC76">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="AD76">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AE76">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF76">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>2.01</v>
+        <v>1.37</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="O77">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q77">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="R77">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
+        <v>1.21</v>
+      </c>
+      <c r="T77">
+        <v>3.68</v>
+      </c>
+      <c r="U77">
+        <v>2.09</v>
+      </c>
+      <c r="V77">
+        <v>1.68</v>
+      </c>
+      <c r="W77">
+        <v>1.16</v>
+      </c>
+      <c r="X77">
+        <v>1.03</v>
+      </c>
+      <c r="Y77">
+        <v>1.09</v>
+      </c>
+      <c r="Z77">
+        <v>5.25</v>
+      </c>
+      <c r="AA77">
+        <v>1.4</v>
+      </c>
+      <c r="AB77">
+        <v>2.7</v>
+      </c>
+      <c r="AC77">
+        <v>2.09</v>
+      </c>
+      <c r="AD77">
+        <v>1.7</v>
+      </c>
+      <c r="AE77">
         <v>1.25</v>
       </c>
-      <c r="T77">
-        <v>3.6</v>
-      </c>
-      <c r="U77">
-        <v>2.42</v>
-      </c>
-      <c r="V77">
-        <v>1.51</v>
-      </c>
-      <c r="W77">
-        <v>1.12</v>
-      </c>
-      <c r="X77">
-        <v>1.02</v>
-      </c>
-      <c r="Y77">
-        <v>1.15</v>
-      </c>
-      <c r="Z77">
-        <v>4.6</v>
-      </c>
-      <c r="AA77">
-        <v>1.64</v>
-      </c>
-      <c r="AB77">
-        <v>2.18</v>
-      </c>
-      <c r="AC77">
-        <v>2.49</v>
-      </c>
-      <c r="AD77">
-        <v>1.42</v>
-      </c>
-      <c r="AE77">
-        <v>1.17</v>
-      </c>
       <c r="AF77">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AG77">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK77">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="O78">
+        <v>3.7</v>
+      </c>
+      <c r="P78">
         <v>3.6</v>
       </c>
-      <c r="P78">
-        <v>2.97</v>
-      </c>
       <c r="Q78">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="R78">
         <v>2.34</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T78">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="U78">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V78">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W78">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z78">
-        <v>4.2</v>
+        <v>4.94</v>
       </c>
       <c r="AA78">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AB78">
+        <v>2.15</v>
+      </c>
+      <c r="AC78">
         <v>2.35</v>
-      </c>
-      <c r="AC78">
-        <v>2.33</v>
       </c>
       <c r="AD78">
         <v>1.57</v>
       </c>
       <c r="AE78">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF78">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG78">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="Q79">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="R79">
         <v>2.34</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T79">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="U79">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V79">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z79">
-        <v>4.94</v>
+        <v>4.2</v>
       </c>
       <c r="AA79">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AB79">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC79">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD79">
         <v>1.57</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF79">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG79">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -24223,27 +24223,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 22:00:00</t>
         </is>
       </c>
     </row>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q148">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="R148">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="S148">
+        <v>1.24</v>
+      </c>
+      <c r="T148">
+        <v>3.6</v>
+      </c>
+      <c r="U148">
+        <v>2.22</v>
+      </c>
+      <c r="V148">
+        <v>1.58</v>
+      </c>
+      <c r="W148">
+        <v>1.14</v>
+      </c>
+      <c r="X148">
+        <v>1.02</v>
+      </c>
+      <c r="Y148">
+        <v>1.14</v>
+      </c>
+      <c r="Z148">
+        <v>4.8</v>
+      </c>
+      <c r="AA148">
         <v>1.53</v>
       </c>
-      <c r="T148">
-        <v>2.3</v>
-      </c>
-      <c r="U148">
-        <v>3.5</v>
-      </c>
-      <c r="V148">
-        <v>1.21</v>
-      </c>
-      <c r="W148">
-        <v>1.01</v>
-      </c>
-      <c r="X148">
-        <v>1.07</v>
-      </c>
-      <c r="Y148">
-        <v>1.5</v>
-      </c>
-      <c r="Z148">
-        <v>2.35</v>
-      </c>
-      <c r="AA148">
-        <v>2.55</v>
-      </c>
       <c r="AB148">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC148">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="AD148">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="AE148">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF148">
-        <v>2.38</v>
+        <v>1.66</v>
       </c>
       <c r="AG148">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK148">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24536,169 +24536,6 @@
         <v>0</v>
       </c>
       <c r="AU148" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>1.99</v>
-      </c>
-      <c r="R149">
-        <v>2.6</v>
-      </c>
-      <c r="S149">
-        <v>1.24</v>
-      </c>
-      <c r="T149">
-        <v>3.6</v>
-      </c>
-      <c r="U149">
-        <v>2.22</v>
-      </c>
-      <c r="V149">
-        <v>1.58</v>
-      </c>
-      <c r="W149">
-        <v>1.14</v>
-      </c>
-      <c r="X149">
-        <v>1.02</v>
-      </c>
-      <c r="Y149">
-        <v>1.14</v>
-      </c>
-      <c r="Z149">
-        <v>4.8</v>
-      </c>
-      <c r="AA149">
-        <v>1.53</v>
-      </c>
-      <c r="AB149">
-        <v>2.38</v>
-      </c>
-      <c r="AC149">
-        <v>2.2</v>
-      </c>
-      <c r="AD149">
-        <v>1.54</v>
-      </c>
-      <c r="AE149">
-        <v>1.18</v>
-      </c>
-      <c r="AF149">
-        <v>1.66</v>
-      </c>
-      <c r="AG149">
-        <v>2.05</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>1.15</v>
-      </c>
-      <c r="AK149">
-        <v>2.27</v>
-      </c>
-      <c r="AL149">
-        <v>0</v>
-      </c>
-      <c r="AM149">
-        <v>-1</v>
-      </c>
-      <c r="AN149">
-        <v>-1</v>
-      </c>
-      <c r="AO149">
-        <v>-1</v>
-      </c>
-      <c r="AP149">
-        <v>-1</v>
-      </c>
-      <c r="AQ149">
-        <v>0</v>
-      </c>
-      <c r="AR149">
-        <v>0</v>
-      </c>
-      <c r="AS149">
-        <v>0</v>
-      </c>
-      <c r="AT149">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
         <is>
           <t>2026-08-28 23:00:00</t>
         </is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="O2">
-        <v>5.05</v>
+        <v>4.2</v>
       </c>
       <c r="P2">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
         <v>6</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S2">
         <v>1.21</v>
       </c>
       <c r="T2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,13 +668,13 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
         <v>5.15</v>
       </c>
       <c r="AA2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB2">
         <v>2.55</v>
@@ -692,7 +692,7 @@
         <v>1.64</v>
       </c>
       <c r="AG2">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK2">
         <v>1.06</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -816,40 +816,40 @@
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC3">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AD3">
         <v>1.37</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF3">
         <v>1.57</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1130,19 +1130,19 @@
         <v>3.85</v>
       </c>
       <c r="P5">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
       </c>
       <c r="R5">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
         <v>2.09</v>
@@ -1157,31 +1157,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
         <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AD5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE5">
         <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.73</v>
       </c>
       <c r="AK5">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="O6">
+        <v>4.25</v>
+      </c>
+      <c r="P6">
         <v>4.1</v>
       </c>
-      <c r="P6">
-        <v>3.85</v>
-      </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="R6">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="T6">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="U6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W6">
         <v>1.23</v>
@@ -1332,19 +1332,19 @@
         <v>3.3</v>
       </c>
       <c r="AC6">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AD6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AE6">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AF6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG6">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
         <v>1.79</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R7">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
         <v>1.22</v>
@@ -1480,34 +1480,34 @@
         <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
         <v>5.1</v>
       </c>
       <c r="AA7">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD7">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE7">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
         <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>4.7</v>
       </c>
       <c r="O13">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
         <v>1.66</v>
@@ -2440,7 +2440,7 @@
         <v>4.75</v>
       </c>
       <c r="R13">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="S13">
         <v>1.27</v>
@@ -2449,10 +2449,10 @@
         <v>3.45</v>
       </c>
       <c r="U13">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
         <v>1.12</v>
@@ -2461,7 +2461,7 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
         <v>4.8</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q14">
         <v>3.07</v>
       </c>
       <c r="R14">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2624,22 +2624,22 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="AA14">
         <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC14">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="AD14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
         <v>1.05</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="R24">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z24">
-        <v>4.65</v>
+        <v>5.35</v>
       </c>
       <c r="AA24">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AB24">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AC24">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AD24">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG24">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>2.47</v>
       </c>
       <c r="Q26">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z26">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AB26">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,13 +4719,13 @@
         <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R27">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
         <v>2.53</v>
@@ -4749,7 +4749,7 @@
         <v>2.97</v>
       </c>
       <c r="AA27">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB27">
         <v>1.72</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
         <v>1.61</v>
@@ -4882,46 +4882,46 @@
         <v>4.4</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="U28">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AA28">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC28">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -4930,7 +4930,7 @@
         <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5371,56 +5371,56 @@
         <v>4.35</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="S31">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="U31">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="V31">
         <v>1.33</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA31">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC31">
         <v>3.74</v>
       </c>
       <c r="AD31">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
+        <v>1.94</v>
+      </c>
+      <c r="AG31">
         <v>1.77</v>
       </c>
-      <c r="AG31">
-        <v>1.88</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,40 +5688,40 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
+        <v>2.35</v>
+      </c>
+      <c r="Q33">
+        <v>3.12</v>
+      </c>
+      <c r="R33">
         <v>2.25</v>
       </c>
-      <c r="Q33">
-        <v>3.4</v>
-      </c>
-      <c r="R33">
-        <v>2.22</v>
-      </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U33">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="V33">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
         <v>3.84</v>
@@ -5745,7 +5745,7 @@
         <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AK33">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6343,31 +6343,31 @@
         <v>2.25</v>
       </c>
       <c r="O37">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
         <v>2.75</v>
       </c>
       <c r="Q37">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U37">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,7 +6376,7 @@
         <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA37">
         <v>1.69</v>
@@ -6388,16 +6388,16 @@
         <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.56</v>
       </c>
       <c r="AG37">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK37">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6672,22 +6672,22 @@
         <v>3.3</v>
       </c>
       <c r="P39">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="R39">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V39">
         <v>1.5</v>
@@ -6696,31 +6696,31 @@
         <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="AA39">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AD39">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG39">
         <v>2.3</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O40">
         <v>4</v>
       </c>
       <c r="P40">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q40">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
         <v>1.31</v>
@@ -6850,43 +6850,43 @@
         <v>3.15</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
         <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB40">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD40">
         <v>1.37</v>
       </c>
       <c r="AE40">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG40">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7816,40 +7816,40 @@
         <v>2.7</v>
       </c>
       <c r="Q46">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R46">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U46">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V46">
         <v>1.33</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
         <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA46">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB46">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC46">
         <v>3.5</v>
@@ -7861,7 +7861,7 @@
         <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
         <v>1.92</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O47">
         <v>4.4</v>
@@ -7979,16 +7979,16 @@
         <v>4.6</v>
       </c>
       <c r="Q47">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R47">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="S47">
         <v>1.2</v>
       </c>
       <c r="T47">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U47">
         <v>2.08</v>
@@ -7997,7 +7997,7 @@
         <v>1.66</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8012,13 +8012,13 @@
         <v>1.39</v>
       </c>
       <c r="AB47">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC47">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD47">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE47">
         <v>1.25</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8299,61 +8299,61 @@
         <v>2.2</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>3.05</v>
       </c>
       <c r="Q49">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S49">
         <v>1.38</v>
       </c>
       <c r="T49">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA49">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC49">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AD49">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
         <v>1.63</v>
       </c>
       <c r="AG49">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK49">
         <v>1.66</v>
@@ -8462,77 +8462,77 @@
         <v>4.2</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q50">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S50">
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U50">
         <v>2.3</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>4.47</v>
       </c>
       <c r="AA50">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC50">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AD50">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE50">
+        <v>1.19</v>
+      </c>
+      <c r="AF50">
+        <v>1.6</v>
+      </c>
+      <c r="AG50">
+        <v>2.2</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.22</v>
+      </c>
+      <c r="AK50">
         <v>1.18</v>
-      </c>
-      <c r="AF50">
-        <v>1.67</v>
-      </c>
-      <c r="AG50">
-        <v>2.05</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.19</v>
-      </c>
-      <c r="AK50">
-        <v>1.16</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,25 +8785,25 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q52">
         <v>2.88</v>
       </c>
       <c r="R52">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
         <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U52">
         <v>2.4</v>
@@ -8812,37 +8812,37 @@
         <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z52">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
         <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC52">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD52">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>4.2</v>
       </c>
       <c r="Q55">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="R55">
         <v>2.5</v>
@@ -9295,13 +9295,13 @@
         <v>3.5</v>
       </c>
       <c r="U55">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V55">
         <v>1.62</v>
       </c>
       <c r="W55">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X55">
         <v>1.02</v>
@@ -9310,7 +9310,7 @@
         <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>5.13</v>
+        <v>4.95</v>
       </c>
       <c r="AA55">
         <v>1.45</v>
@@ -9319,10 +9319,10 @@
         <v>2.41</v>
       </c>
       <c r="AC55">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AD55">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE55">
         <v>1.2</v>
@@ -9331,7 +9331,7 @@
         <v>1.5</v>
       </c>
       <c r="AG55">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O63">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q63">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R63">
         <v>2.25</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T63">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V63">
         <v>1.5</v>
@@ -10608,7 +10608,7 @@
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y63">
         <v>1.2</v>
@@ -10617,10 +10617,10 @@
         <v>4.1</v>
       </c>
       <c r="AA63">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB63">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC63">
         <v>2.75</v>
@@ -10632,10 +10632,10 @@
         <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG63">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O64">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="P64">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10904,22 +10904,22 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O65">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q65">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="R65">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
         <v>2.75</v>
@@ -10928,40 +10928,40 @@
         <v>3.15</v>
       </c>
       <c r="V65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
         <v>3.1</v>
       </c>
       <c r="AA65">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB65">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC65">
         <v>3.9</v>
       </c>
       <c r="AD65">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE65">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG65">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
         <v>3</v>
       </c>
       <c r="P66">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R66">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="S66">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T66">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="U66">
         <v>3.3</v>
       </c>
       <c r="V66">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.38</v>
+      </c>
+      <c r="Z66">
+        <v>2.8</v>
+      </c>
+      <c r="AA66">
+        <v>2.15</v>
+      </c>
+      <c r="AB66">
+        <v>1.6</v>
+      </c>
+      <c r="AC66">
+        <v>4.15</v>
+      </c>
+      <c r="AD66">
+        <v>1.2</v>
+      </c>
+      <c r="AE66">
         <v>1.01</v>
-      </c>
-      <c r="X66">
-        <v>1.05</v>
-      </c>
-      <c r="Y66">
-        <v>1.4</v>
-      </c>
-      <c r="Z66">
-        <v>2.98</v>
-      </c>
-      <c r="AA66">
-        <v>2.28</v>
-      </c>
-      <c r="AB66">
-        <v>1.63</v>
-      </c>
-      <c r="AC66">
-        <v>4.2</v>
-      </c>
-      <c r="AD66">
-        <v>1.22</v>
-      </c>
-      <c r="AE66">
-        <v>1.04</v>
       </c>
       <c r="AF66">
         <v>1.89</v>
       </c>
       <c r="AG66">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
         <v>1.4</v>
@@ -11236,58 +11236,58 @@
         <v>3.6</v>
       </c>
       <c r="P67">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q67">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R67">
         <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="U67">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="V67">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z67">
         <v>3.4</v>
       </c>
       <c r="AA67">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC67">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
         <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG67">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11719,28 +11719,28 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q70">
         <v>2.28</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S70">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T70">
+        <v>2.93</v>
+      </c>
+      <c r="U70">
         <v>2.75</v>
-      </c>
-      <c r="U70">
-        <v>2.66</v>
       </c>
       <c r="V70">
         <v>1.4</v>
@@ -11755,19 +11755,19 @@
         <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA70">
         <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC70">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="AD70">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE70">
         <v>1.08</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O71">
-        <v>4.84</v>
+        <v>4.6</v>
       </c>
       <c r="P71">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="Q71">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R71">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T71">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U71">
         <v>2.04</v>
       </c>
       <c r="V71">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W71">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA71">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC71">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD71">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF71">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG71">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.12</v>
       </c>
       <c r="AK71">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,31 +12208,31 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O73">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="P73">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q73">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="R73">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S73">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
         <v>2.2</v>
       </c>
       <c r="V73">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W73">
         <v>1.11</v>
@@ -12253,10 +12253,10 @@
         <v>2.35</v>
       </c>
       <c r="AC73">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD73">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE73">
         <v>1.18</v>
@@ -12265,7 +12265,7 @@
         <v>1.45</v>
       </c>
       <c r="AG73">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
         <v>1.67</v>
@@ -12377,28 +12377,28 @@
         <v>4</v>
       </c>
       <c r="P74">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="R74">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S74">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
         <v>4.5</v>
       </c>
       <c r="U74">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V74">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12413,7 +12413,7 @@
         <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC74">
         <v>2.04</v>
@@ -12422,7 +12422,7 @@
         <v>1.74</v>
       </c>
       <c r="AE74">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF74">
         <v>1.43</v>
@@ -12534,22 +12534,22 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O75">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="P75">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q75">
         <v>2.15</v>
       </c>
       <c r="R75">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S75">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
         <v>4.2</v>
@@ -12561,7 +12561,7 @@
         <v>1.75</v>
       </c>
       <c r="W75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12573,19 +12573,19 @@
         <v>6</v>
       </c>
       <c r="AA75">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB75">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AC75">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD75">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE75">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF75">
         <v>1.4</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="O76">
         <v>3.6</v>
       </c>
       <c r="P76">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q76">
-        <v>3.48</v>
+        <v>2.99</v>
       </c>
       <c r="R76">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T76">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U76">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="V76">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="W76">
+        <v>1.16</v>
+      </c>
+      <c r="X76">
+        <v>1.03</v>
+      </c>
+      <c r="Y76">
         <v>1.12</v>
       </c>
-      <c r="X76">
-        <v>1.02</v>
-      </c>
-      <c r="Y76">
-        <v>1.15</v>
-      </c>
       <c r="Z76">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA76">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AB76">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="AC76">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="AD76">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AE76">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF76">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AG76">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="O77">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
+        <v>3.83</v>
+      </c>
+      <c r="Q77">
         <v>2.3</v>
-      </c>
-      <c r="Q77">
-        <v>2.92</v>
       </c>
       <c r="R77">
         <v>2.5</v>
       </c>
       <c r="S77">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T77">
-        <v>3.68</v>
+        <v>3.36</v>
       </c>
       <c r="U77">
-        <v>2.09</v>
+        <v>2.29</v>
       </c>
       <c r="V77">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="W77">
+        <v>1.11</v>
+      </c>
+      <c r="X77">
+        <v>1.04</v>
+      </c>
+      <c r="Y77">
+        <v>1.2</v>
+      </c>
+      <c r="Z77">
+        <v>4.55</v>
+      </c>
+      <c r="AA77">
+        <v>1.62</v>
+      </c>
+      <c r="AB77">
+        <v>2.1</v>
+      </c>
+      <c r="AC77">
+        <v>2.55</v>
+      </c>
+      <c r="AD77">
+        <v>1.43</v>
+      </c>
+      <c r="AE77">
         <v>1.16</v>
       </c>
-      <c r="X77">
-        <v>1.03</v>
-      </c>
-      <c r="Y77">
-        <v>1.09</v>
-      </c>
-      <c r="Z77">
-        <v>5.25</v>
-      </c>
-      <c r="AA77">
-        <v>1.4</v>
-      </c>
-      <c r="AB77">
-        <v>2.7</v>
-      </c>
-      <c r="AC77">
-        <v>2.09</v>
-      </c>
-      <c r="AD77">
-        <v>1.7</v>
-      </c>
-      <c r="AE77">
-        <v>1.25</v>
-      </c>
       <c r="AF77">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG77">
-        <v>2.76</v>
+        <v>2.35</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.23</v>
       </c>
       <c r="AK77">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P78">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q78">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="R78">
         <v>2.34</v>
       </c>
       <c r="S78">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T78">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="U78">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V78">
+        <v>1.6</v>
+      </c>
+      <c r="W78">
+        <v>1.13</v>
+      </c>
+      <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.12</v>
+      </c>
+      <c r="Z78">
+        <v>5</v>
+      </c>
+      <c r="AA78">
         <v>1.57</v>
       </c>
-      <c r="W78">
-        <v>1.11</v>
-      </c>
-      <c r="X78">
-        <v>1.04</v>
-      </c>
-      <c r="Y78">
-        <v>1.16</v>
-      </c>
-      <c r="Z78">
-        <v>4.94</v>
-      </c>
-      <c r="AA78">
-        <v>1.66</v>
-      </c>
       <c r="AB78">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC78">
         <v>2.35</v>
       </c>
       <c r="AD78">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AE78">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF78">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AG78">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,65 +13186,65 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q79">
-        <v>2.45</v>
+        <v>3.41</v>
       </c>
       <c r="R79">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S79">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T79">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="U79">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="V79">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W79">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z79">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA79">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AB79">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
+        <v>2.49</v>
+      </c>
+      <c r="AD79">
+        <v>1.47</v>
+      </c>
+      <c r="AE79">
+        <v>1.13</v>
+      </c>
+      <c r="AF79">
+        <v>1.52</v>
+      </c>
+      <c r="AG79">
         <v>2.33</v>
       </c>
-      <c r="AD79">
-        <v>1.57</v>
-      </c>
-      <c r="AE79">
-        <v>1.23</v>
-      </c>
-      <c r="AF79">
-        <v>1.44</v>
-      </c>
-      <c r="AG79">
-        <v>2.53</v>
-      </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>4.75</v>
       </c>
       <c r="AA81">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AB81">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC81">
         <v>2.34</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="AK81">
         <v>1.25</v>
@@ -13684,16 +13684,16 @@
         <v>3</v>
       </c>
       <c r="Q82">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R82">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="S82">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U82">
         <v>2.2</v>
@@ -13702,7 +13702,7 @@
         <v>1.59</v>
       </c>
       <c r="W82">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13714,7 +13714,7 @@
         <v>4.65</v>
       </c>
       <c r="AA82">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AB82">
         <v>2.33</v>
@@ -13726,13 +13726,13 @@
         <v>1.57</v>
       </c>
       <c r="AE82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF82">
         <v>1.44</v>
       </c>
       <c r="AG82">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13847,19 +13847,19 @@
         <v>3.3</v>
       </c>
       <c r="Q83">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R83">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U83">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
         <v>1.67</v>
@@ -13880,19 +13880,19 @@
         <v>1.42</v>
       </c>
       <c r="AB83">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC83">
         <v>2.16</v>
       </c>
       <c r="AD83">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE83">
         <v>1.24</v>
       </c>
       <c r="AF83">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
         <v>2.62</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK83">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R84">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
+        <v>1.4</v>
+      </c>
+      <c r="T84">
+        <v>2.7</v>
+      </c>
+      <c r="U84">
+        <v>2.88</v>
+      </c>
+      <c r="V84">
         <v>1.36</v>
       </c>
-      <c r="T84">
-        <v>2.66</v>
-      </c>
-      <c r="U84">
-        <v>2.62</v>
-      </c>
-      <c r="V84">
-        <v>1.4</v>
-      </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z84">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA84">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB84">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC84">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="AD84">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AG84">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK84">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O85">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q85">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="R85">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S85">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T85">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="U85">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V85">
         <v>1.29</v>
       </c>
       <c r="W85">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X85">
         <v>1.09</v>
@@ -14203,16 +14203,16 @@
         <v>2.72</v>
       </c>
       <c r="AA85">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AB85">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC85">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AD85">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE85">
         <v>1.02</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14342,22 +14342,22 @@
         <v>2.09</v>
       </c>
       <c r="S86">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U86">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
         <v>1.25</v>
@@ -14366,25 +14366,25 @@
         <v>3.88</v>
       </c>
       <c r="AA86">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB86">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC86">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="AD86">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE86">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF86">
         <v>1.65</v>
       </c>
       <c r="AG86">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="O87">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q87">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="R87">
         <v>2.2</v>
       </c>
       <c r="S87">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U87">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="V87">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W87">
         <v>1.04</v>
@@ -14523,31 +14523,31 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
+        <v>1.26</v>
+      </c>
+      <c r="Z87">
+        <v>3.45</v>
+      </c>
+      <c r="AA87">
+        <v>1.87</v>
+      </c>
+      <c r="AB87">
+        <v>1.81</v>
+      </c>
+      <c r="AC87">
+        <v>3.3</v>
+      </c>
+      <c r="AD87">
         <v>1.28</v>
-      </c>
-      <c r="Z87">
-        <v>3.47</v>
-      </c>
-      <c r="AA87">
-        <v>1.88</v>
-      </c>
-      <c r="AB87">
-        <v>1.66</v>
-      </c>
-      <c r="AC87">
-        <v>3.2</v>
-      </c>
-      <c r="AD87">
-        <v>1.26</v>
       </c>
       <c r="AE87">
         <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>1.41</v>
       </c>
       <c r="AK87">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>5.74</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R89">
         <v>2.53</v>
@@ -14834,16 +14834,16 @@
         <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="U89">
         <v>2.49</v>
       </c>
       <c r="V89">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W89">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X89">
         <v>1.04</v>
@@ -14855,25 +14855,25 @@
         <v>4.33</v>
       </c>
       <c r="AA89">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB89">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC89">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD89">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE89">
         <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG89">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.15</v>
       </c>
       <c r="AK89">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="O92">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P92">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q92">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="R92">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="S92">
         <v>1.15</v>
@@ -15326,43 +15326,43 @@
         <v>5</v>
       </c>
       <c r="U92">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="V92">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="W92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z92">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA92">
         <v>1.18</v>
       </c>
       <c r="AB92">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC92">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AD92">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AE92">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF92">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK92">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>2.14</v>
       </c>
       <c r="Q93">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="R93">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S93">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
         <v>2.7</v>
       </c>
       <c r="U93">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="V93">
         <v>1.33</v>
       </c>
       <c r="W93">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
         <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z93">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA93">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AB93">
         <v>1.71</v>
       </c>
       <c r="AC93">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="AD93">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE93">
         <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AG93">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
         <v>1.3</v>
@@ -15631,34 +15631,34 @@
         </is>
       </c>
       <c r="N94">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="O94">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="P94">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q94">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="R94">
         <v>2.45</v>
       </c>
       <c r="S94">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T94">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U94">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V94">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X94">
         <v>1.02</v>
@@ -15667,28 +15667,28 @@
         <v>1.16</v>
       </c>
       <c r="Z94">
-        <v>4.15</v>
+        <v>4.08</v>
       </c>
       <c r="AA94">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB94">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC94">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AD94">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE94">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF94">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG94">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AK94">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15797,28 +15797,28 @@
         <v>4.33</v>
       </c>
       <c r="O95">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P95">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q95">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="R95">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W95">
         <v>1.09</v>
@@ -15833,13 +15833,13 @@
         <v>3.96</v>
       </c>
       <c r="AA95">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AB95">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC95">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD95">
         <v>1.39</v>
@@ -15851,7 +15851,7 @@
         <v>1.65</v>
       </c>
       <c r="AG95">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK95">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O96">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P96">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Q96">
         <v>1.7</v>
@@ -15999,7 +15999,7 @@
         <v>1.48</v>
       </c>
       <c r="AB96">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="AC96">
         <v>2.31</v>
@@ -16008,10 +16008,10 @@
         <v>1.59</v>
       </c>
       <c r="AE96">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF96">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG96">
         <v>1.85</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK96">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>2.55</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P97">
         <v>2.4</v>
@@ -16132,52 +16132,52 @@
         <v>3.1</v>
       </c>
       <c r="R97">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S97">
         <v>1.33</v>
       </c>
       <c r="T97">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="U97">
         <v>2.53</v>
       </c>
       <c r="V97">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X97">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
         <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA97">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB97">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC97">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD97">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE97">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF97">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG97">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AK97">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16286,16 +16286,16 @@
         <v>1.33</v>
       </c>
       <c r="O98">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q98">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="R98">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
         <v>1.2</v>
@@ -16304,10 +16304,10 @@
         <v>4</v>
       </c>
       <c r="U98">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V98">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W98">
         <v>1.13</v>
@@ -16322,10 +16322,10 @@
         <v>4.4</v>
       </c>
       <c r="AA98">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB98">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AC98">
         <v>2.29</v>
@@ -16356,7 +16356,7 @@
         <v>1.14</v>
       </c>
       <c r="AK98">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="O99">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="P99">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16618,22 +16618,22 @@
         <v>2.2</v>
       </c>
       <c r="Q100">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="R100">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S100">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="V100">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W100">
         <v>1.07</v>
@@ -16645,13 +16645,13 @@
         <v>1.16</v>
       </c>
       <c r="Z100">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="AA100">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB100">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC100">
         <v>2.59</v>
@@ -16660,7 +16660,7 @@
         <v>1.39</v>
       </c>
       <c r="AE100">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
         <v>1.55</v>
@@ -16682,7 +16682,7 @@
         <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,16 +16781,16 @@
         <v>6.75</v>
       </c>
       <c r="Q101">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R101">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S101">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T101">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U101">
         <v>2.3</v>
@@ -16802,31 +16802,31 @@
         <v>1.1</v>
       </c>
       <c r="X101">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
         <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AA101">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB101">
         <v>2.1</v>
       </c>
       <c r="AC101">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AD101">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE101">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG101">
         <v>1.98</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AK101">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.35</v>
+        <v>1.23</v>
       </c>
       <c r="O102">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="P102">
-        <v>2.75</v>
+        <v>8.4</v>
       </c>
       <c r="Q102">
-        <v>2.77</v>
+        <v>1.65</v>
       </c>
       <c r="R102">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S102">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T102">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="U102">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z102">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA102">
-        <v>1.84</v>
+        <v>1.48</v>
       </c>
       <c r="AB102">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="AC102">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD102">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="AE102">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AF102">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG102">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AK102">
-        <v>1.47</v>
+        <v>3.3</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,65 +17098,65 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="O103">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="P103">
-        <v>8.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q103">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="R103">
-        <v>2.7</v>
+        <v>2.09</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="T103">
-        <v>3.9</v>
+        <v>3.11</v>
       </c>
       <c r="U103">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="V103">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="W103">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z103">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA103">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="AB103">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="AC103">
+        <v>2.8</v>
+      </c>
+      <c r="AD103">
+        <v>1.29</v>
+      </c>
+      <c r="AE103">
+        <v>1.13</v>
+      </c>
+      <c r="AF103">
+        <v>1.64</v>
+      </c>
+      <c r="AG103">
         <v>2.1</v>
       </c>
-      <c r="AD103">
-        <v>1.7</v>
-      </c>
-      <c r="AE103">
-        <v>1.27</v>
-      </c>
-      <c r="AF103">
-        <v>1.77</v>
-      </c>
-      <c r="AG103">
-        <v>1.95</v>
-      </c>
       <c r="AH103" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,19 +17270,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q104">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R104">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S104">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="U104">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V104">
         <v>1.42</v>
@@ -17291,22 +17291,22 @@
         <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z104">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="AA104">
         <v>1.9</v>
       </c>
       <c r="AB104">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC104">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="AD104">
         <v>1.33</v>
@@ -17318,7 +17318,7 @@
         <v>2.18</v>
       </c>
       <c r="AG104">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK104">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O105">
         <v>3.76</v>
@@ -17756,46 +17756,46 @@
         <v>3.9</v>
       </c>
       <c r="P107">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q107">
         <v>5.48</v>
       </c>
       <c r="R107">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="S107">
         <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="V107">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z107">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA107">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB107">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AC107">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AD107">
         <v>1.44</v>
@@ -17804,10 +17804,10 @@
         <v>1.14</v>
       </c>
       <c r="AF107">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17913,61 +17913,61 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O108">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q108">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="R108">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T108">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U108">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="V108">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
         <v>1.18</v>
       </c>
       <c r="Z108">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA108">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB108">
         <v>1.95</v>
       </c>
       <c r="AC108">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AD108">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
         <v>1.13</v>
       </c>
       <c r="AF108">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG108">
         <v>2.21</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="AK108">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18082,46 +18082,46 @@
         <v>3.1</v>
       </c>
       <c r="P109">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q109">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R109">
         <v>1.98</v>
       </c>
       <c r="S109">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T109">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U109">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="V109">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W109">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z109">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA109">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AB109">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC109">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AD109">
         <v>1.21</v>
@@ -18130,10 +18130,10 @@
         <v>1.04</v>
       </c>
       <c r="AF109">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG109">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK109">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,19 +18239,19 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O110">
-        <v>3.18</v>
+        <v>3.27</v>
       </c>
       <c r="P110">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="Q110">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="R110">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S110">
         <v>1.36</v>
@@ -18260,43 +18260,43 @@
         <v>2.88</v>
       </c>
       <c r="U110">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V110">
         <v>1.39</v>
       </c>
       <c r="W110">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>3.47</v>
+        <v>2.98</v>
       </c>
       <c r="AA110">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB110">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC110">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="AD110">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE110">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF110">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG110">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK110">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19217,34 +19217,34 @@
         </is>
       </c>
       <c r="N116">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O116">
         <v>5.5</v>
       </c>
       <c r="P116">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q116">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="R116">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S116">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
         <v>3.75</v>
       </c>
       <c r="U116">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="V116">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W116">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X116">
         <v>1.02</v>
@@ -19253,28 +19253,28 @@
         <v>1.1</v>
       </c>
       <c r="Z116">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
       <c r="AA116">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB116">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AC116">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AD116">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE116">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG116">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK116">
         <v>1.04</v>
@@ -19380,61 +19380,61 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O117">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Q117">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R117">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S117">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T117">
         <v>3.02</v>
       </c>
       <c r="U117">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="V117">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W117">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X117">
         <v>1.05</v>
       </c>
       <c r="Y117">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="AA117">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB117">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AC117">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AD117">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE117">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG117">
         <v>2.15</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q119">
         <v>2</v>
@@ -19727,7 +19727,7 @@
         <v>2.7</v>
       </c>
       <c r="U119">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="V119">
         <v>1.4</v>
@@ -20086,10 +20086,10 @@
         <v>1.02</v>
       </c>
       <c r="AF121">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG121">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O122">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P122">
-        <v>3.51</v>
+        <v>3.65</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="O123">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="P123">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20530,55 +20530,55 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20693,55 +20693,55 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -22486,40 +22486,40 @@
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R136">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S136">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T136">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U136">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="V136">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W136">
         <v>1.04</v>
       </c>
       <c r="X136">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y136">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z136">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AA136">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AB136">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC136">
         <v>4.75</v>
@@ -22528,7 +22528,7 @@
         <v>1.18</v>
       </c>
       <c r="AE136">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
         <v>2.04</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK136">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL136">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G126">
@@ -20856,55 +20856,55 @@
         <v>0</v>
       </c>
       <c r="Q126">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R126">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S126">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T126">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="U126">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V126">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W126">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z126">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AA126">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB126">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC126">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="AD126">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE126">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG126">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G127">
@@ -21019,55 +21019,55 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R127">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S127">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T127">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="U127">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V127">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W127">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z127">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA127">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB127">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC127">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="AD127">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF127">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG127">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK127">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL127">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -2265,46 +2265,46 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O12">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R12">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="S12">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T12">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U12">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z12">
         <v>2.28</v>
       </c>
       <c r="AA12">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AB12">
         <v>1.38</v>
@@ -2313,16 +2313,16 @@
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE12">
         <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AG12">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2754,37 +2754,37 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q15">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
         <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.33</v>
@@ -2793,16 +2793,16 @@
         <v>3.21</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="AD15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.05</v>
@@ -2811,7 +2811,7 @@
         <v>1.79</v>
       </c>
       <c r="AG15">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4393,22 +4393,22 @@
         <v>3.4</v>
       </c>
       <c r="Q25">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U25">
         <v>2.16</v>
       </c>
       <c r="V25">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W25">
         <v>1.17</v>
@@ -4417,31 +4417,31 @@
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA25">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AB25">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD25">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF25">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG25">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R28">
         <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T28">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U28">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD28">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,49 +5045,49 @@
         <v>4.4</v>
       </c>
       <c r="Q29">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
         <v>2.29</v>
       </c>
       <c r="S29">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V29">
         <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
         <v>3.43</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB29">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC29">
         <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
         <v>1.85</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
         <v>2.05</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5525,43 +5525,43 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R32">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="AA32">
         <v>2.14</v>
@@ -5573,16 +5573,16 @@
         <v>3.74</v>
       </c>
       <c r="AD32">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG32">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
         <v>2.25</v>
@@ -5869,13 +5869,13 @@
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5884,7 +5884,7 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
         <v>3.84</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
         <v>1.4</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P40">
+        <v>4.4</v>
+      </c>
+      <c r="Q40">
+        <v>2.15</v>
+      </c>
+      <c r="R40">
+        <v>2.3</v>
+      </c>
+      <c r="S40">
+        <v>1.31</v>
+      </c>
+      <c r="T40">
+        <v>3.15</v>
+      </c>
+      <c r="U40">
         <v>2.55</v>
       </c>
-      <c r="Q40">
-        <v>3.14</v>
-      </c>
-      <c r="R40">
-        <v>2.38</v>
-      </c>
-      <c r="S40">
-        <v>1.29</v>
-      </c>
-      <c r="T40">
-        <v>3.25</v>
-      </c>
-      <c r="U40">
-        <v>2.45</v>
-      </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.04</v>
       </c>
       <c r="Y40">
+        <v>1.22</v>
+      </c>
+      <c r="Z40">
+        <v>4</v>
+      </c>
+      <c r="AA40">
+        <v>1.7</v>
+      </c>
+      <c r="AB40">
+        <v>2.1</v>
+      </c>
+      <c r="AC40">
+        <v>2.8</v>
+      </c>
+      <c r="AD40">
+        <v>1.37</v>
+      </c>
+      <c r="AE40">
+        <v>1.11</v>
+      </c>
+      <c r="AF40">
+        <v>1.7</v>
+      </c>
+      <c r="AG40">
+        <v>2.01</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.2</v>
       </c>
-      <c r="Z40">
-        <v>4.1</v>
-      </c>
-      <c r="AA40">
-        <v>1.69</v>
-      </c>
-      <c r="AB40">
-        <v>2.05</v>
-      </c>
-      <c r="AC40">
-        <v>2.56</v>
-      </c>
-      <c r="AD40">
-        <v>1.43</v>
-      </c>
-      <c r="AE40">
-        <v>1.13</v>
-      </c>
-      <c r="AF40">
-        <v>1.55</v>
-      </c>
-      <c r="AG40">
-        <v>2.3</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.48</v>
-      </c>
       <c r="AK40">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="O41">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>4.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA41">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AK41">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         <v>1.24</v>
       </c>
       <c r="T42">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
         <v>2.22</v>
@@ -7185,7 +7185,7 @@
         <v>1.15</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
         <v>1.13</v>
@@ -7200,16 +7200,16 @@
         <v>2.42</v>
       </c>
       <c r="AC42">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD42">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE42">
         <v>1.19</v>
       </c>
       <c r="AF42">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
         <v>2.4</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O43">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="P43">
         <v>1.4</v>
@@ -7333,34 +7333,34 @@
         <v>2.7</v>
       </c>
       <c r="S43">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T43">
         <v>4.5</v>
       </c>
       <c r="U43">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V43">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z43">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="AA43">
         <v>1.33</v>
       </c>
       <c r="AB43">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="AC43">
         <v>1.82</v>
@@ -7369,13 +7369,13 @@
         <v>1.93</v>
       </c>
       <c r="AE43">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
         <v>1.07</v>
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O45">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P45">
         <v>2.3</v>
       </c>
       <c r="Q45">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R45">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="S45">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T45">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U45">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V45">
         <v>1.2</v>
       </c>
       <c r="W45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
         <v>1.11</v>
@@ -7680,28 +7680,28 @@
         <v>1.62</v>
       </c>
       <c r="Z45">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA45">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB45">
         <v>1.36</v>
       </c>
       <c r="AC45">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD45">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG45">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AK45">
         <v>1.3</v>
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>7.35</v>
+        <v>7.4</v>
       </c>
       <c r="O46">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q46">
         <v>6.5</v>
       </c>
       <c r="R46">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
         <v>1.36</v>
       </c>
       <c r="T46">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="U46">
         <v>2.78</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
         <v>1.04</v>
@@ -7846,19 +7846,19 @@
         <v>3.34</v>
       </c>
       <c r="AA46">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB46">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC46">
         <v>3.35</v>
       </c>
       <c r="AD46">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF46">
         <v>2.05</v>
@@ -8622,55 +8622,55 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P51">
         <v>1.68</v>
       </c>
       <c r="Q51">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="R51">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
         <v>3.34</v>
       </c>
       <c r="U51">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>4.47</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.62</v>
       </c>
       <c r="AB51">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AC51">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="AD51">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE51">
         <v>1.19</v>
@@ -8679,7 +8679,7 @@
         <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>3.23</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S52">
         <v>1.36</v>
@@ -8806,10 +8806,10 @@
         <v>2.88</v>
       </c>
       <c r="U52">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V52">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
         <v>1.07</v>
@@ -8824,10 +8824,10 @@
         <v>3.14</v>
       </c>
       <c r="AA52">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB52">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC52">
         <v>3.28</v>
@@ -8842,7 +8842,7 @@
         <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.31</v>
       </c>
       <c r="AK52">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O56">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q56">
         <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U56">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W56">
         <v>1.12</v>
@@ -9470,25 +9470,25 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>4.95</v>
+        <v>5.13</v>
       </c>
       <c r="AA56">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB56">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AC56">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AD56">
         <v>1.59</v>
       </c>
       <c r="AE56">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF56">
         <v>1.5</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK56">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="P67">
+        <v>2.62</v>
+      </c>
+      <c r="Q67">
         <v>3.4</v>
       </c>
-      <c r="P67">
-        <v>3.6</v>
-      </c>
-      <c r="Q67">
-        <v>2.61</v>
-      </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S67">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T67">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U67">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V67">
         <v>1.33</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.38</v>
+      </c>
+      <c r="Z67">
+        <v>2.8</v>
+      </c>
+      <c r="AA67">
+        <v>2.15</v>
+      </c>
+      <c r="AB67">
+        <v>1.6</v>
+      </c>
+      <c r="AC67">
+        <v>4.15</v>
+      </c>
+      <c r="AD67">
+        <v>1.2</v>
+      </c>
+      <c r="AE67">
         <v>1.01</v>
       </c>
-      <c r="Y67">
+      <c r="AF67">
+        <v>1.89</v>
+      </c>
+      <c r="AG67">
+        <v>1.79</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.33</v>
       </c>
-      <c r="Z67">
-        <v>3.1</v>
-      </c>
-      <c r="AA67">
-        <v>2.02</v>
-      </c>
-      <c r="AB67">
-        <v>1.69</v>
-      </c>
-      <c r="AC67">
-        <v>3.9</v>
-      </c>
-      <c r="AD67">
-        <v>1.19</v>
-      </c>
-      <c r="AE67">
-        <v>1.02</v>
-      </c>
-      <c r="AF67">
-        <v>1.83</v>
-      </c>
-      <c r="AG67">
-        <v>1.83</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.3</v>
-      </c>
       <c r="AK67">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.62</v>
+        <v>4.33</v>
       </c>
       <c r="Q68">
+        <v>2.2</v>
+      </c>
+      <c r="R68">
+        <v>2.15</v>
+      </c>
+      <c r="S68">
+        <v>1.36</v>
+      </c>
+      <c r="T68">
+        <v>2.88</v>
+      </c>
+      <c r="U68">
+        <v>2.77</v>
+      </c>
+      <c r="V68">
+        <v>1.4</v>
+      </c>
+      <c r="W68">
+        <v>1.05</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
+        <v>1.29</v>
+      </c>
+      <c r="Z68">
         <v>3.4</v>
       </c>
-      <c r="R68">
-        <v>1.95</v>
-      </c>
-      <c r="S68">
-        <v>1.46</v>
-      </c>
-      <c r="T68">
-        <v>2.53</v>
-      </c>
-      <c r="U68">
-        <v>3.3</v>
-      </c>
-      <c r="V68">
-        <v>1.33</v>
-      </c>
-      <c r="W68">
+      <c r="AA68">
+        <v>1.9</v>
+      </c>
+      <c r="AB68">
+        <v>1.87</v>
+      </c>
+      <c r="AC68">
+        <v>3.12</v>
+      </c>
+      <c r="AD68">
+        <v>1.28</v>
+      </c>
+      <c r="AE68">
         <v>1.06</v>
       </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.38</v>
-      </c>
-      <c r="Z68">
-        <v>2.8</v>
-      </c>
-      <c r="AA68">
-        <v>2.15</v>
-      </c>
-      <c r="AB68">
-        <v>1.6</v>
-      </c>
-      <c r="AC68">
-        <v>4.15</v>
-      </c>
-      <c r="AD68">
+      <c r="AF68">
+        <v>1.84</v>
+      </c>
+      <c r="AG68">
+        <v>1.89</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.2</v>
       </c>
-      <c r="AE68">
-        <v>1.01</v>
-      </c>
-      <c r="AF68">
-        <v>1.89</v>
-      </c>
-      <c r="AG68">
-        <v>1.79</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.33</v>
-      </c>
       <c r="AK68">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="O69">
+        <v>3.4</v>
+      </c>
+      <c r="P69">
         <v>3.6</v>
       </c>
-      <c r="P69">
-        <v>4.33</v>
-      </c>
       <c r="Q69">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="R69">
         <v>2.15</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U69">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z69">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA69">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AB69">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AC69">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="AD69">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG69">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK69">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O72">
         <v>3.5</v>
       </c>
       <c r="P72">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q72">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R72">
         <v>2.15</v>
       </c>
       <c r="S72">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T72">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="U72">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="V72">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W72">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z72">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA72">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB72">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC72">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD72">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE72">
         <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG72">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O75">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P75">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q75">
         <v>2.59</v>
@@ -12552,16 +12552,16 @@
         <v>1.22</v>
       </c>
       <c r="T75">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U75">
         <v>2.2</v>
       </c>
       <c r="V75">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X75">
         <v>1.03</v>
@@ -12579,19 +12579,19 @@
         <v>2.35</v>
       </c>
       <c r="AC75">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD75">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE75">
         <v>1.18</v>
       </c>
       <c r="AF75">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O76">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P76">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q76">
         <v>2.13</v>
       </c>
       <c r="R76">
-        <v>2.51</v>
+        <v>2.68</v>
       </c>
       <c r="S76">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U76">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V76">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W76">
         <v>1.17</v>
@@ -12733,28 +12733,28 @@
         <v>1.12</v>
       </c>
       <c r="Z76">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="AA76">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB76">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AC76">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AD76">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE76">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF76">
         <v>1.43</v>
       </c>
       <c r="AG76">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.17</v>
       </c>
       <c r="AK76">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,34 +12860,34 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O77">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q77">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R77">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T77">
         <v>4.2</v>
       </c>
       <c r="U77">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V77">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W77">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -12896,28 +12896,28 @@
         <v>1.05</v>
       </c>
       <c r="Z77">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="AA77">
         <v>1.38</v>
       </c>
       <c r="AB77">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AC77">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AD77">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE77">
         <v>1.27</v>
       </c>
       <c r="AF77">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG77">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,31 +13026,31 @@
         <v>2.45</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q78">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="R78">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="S78">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T78">
         <v>3.68</v>
       </c>
       <c r="U78">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V78">
         <v>1.7</v>
       </c>
       <c r="W78">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
         <v>1.03</v>
@@ -13062,25 +13062,25 @@
         <v>5.75</v>
       </c>
       <c r="AA78">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AB78">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC78">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AD78">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE78">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF78">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG78">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AK78">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P79">
         <v>3.83</v>
@@ -13201,13 +13201,13 @@
         <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T79">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="U79">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V79">
         <v>1.59</v>
@@ -13216,34 +13216,34 @@
         <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z79">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA79">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AB79">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC79">
         <v>2.55</v>
       </c>
       <c r="AD79">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE79">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG79">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,25 +13349,25 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P80">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q80">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="R80">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S80">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T80">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="U80">
         <v>2.44</v>
@@ -13382,7 +13382,7 @@
         <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z80">
         <v>4.33</v>
@@ -13394,19 +13394,19 @@
         <v>2.2</v>
       </c>
       <c r="AC80">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AD80">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE80">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF80">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG80">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK80">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,34 +13512,34 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O81">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q81">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="R81">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="U81">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V81">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W81">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X81">
         <v>1.02</v>
@@ -13557,16 +13557,16 @@
         <v>2.3</v>
       </c>
       <c r="AC81">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AD81">
         <v>1.45</v>
       </c>
       <c r="AE81">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG81">
         <v>2.5</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AK81">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q84">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="R84">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T84">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V84">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>4.65</v>
+        <v>5.52</v>
       </c>
       <c r="AA84">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AB84">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AC84">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD84">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AE84">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,22 +14164,22 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O85">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="Q85">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R85">
         <v>2.56</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
         <v>3.5</v>
@@ -14197,7 +14197,7 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
         <v>5.05</v>
@@ -14209,7 +14209,7 @@
         <v>2.49</v>
       </c>
       <c r="AC85">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD85">
         <v>1.64</v>
@@ -14221,7 +14221,7 @@
         <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
         <v>1.74</v>
@@ -14327,43 +14327,43 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q86">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="R86">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S86">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T86">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U86">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V86">
         <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z86">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AA86">
         <v>2</v>
@@ -14375,16 +14375,16 @@
         <v>3.28</v>
       </c>
       <c r="AD86">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE86">
         <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG86">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK86">
         <v>2.4</v>
@@ -14493,61 +14493,61 @@
         <v>1.83</v>
       </c>
       <c r="O87">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="P87">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q87">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="R87">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="S87">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T87">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="U87">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V87">
         <v>1.29</v>
       </c>
       <c r="W87">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Z87">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AA87">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AB87">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC87">
-        <v>4.75</v>
+        <v>4.64</v>
       </c>
       <c r="AD87">
         <v>1.17</v>
       </c>
       <c r="AE87">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF87">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG87">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O94">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="P94">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="Q94">
         <v>1.57</v>
@@ -15646,49 +15646,49 @@
         <v>3.13</v>
       </c>
       <c r="S94">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T94">
         <v>5</v>
       </c>
       <c r="U94">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V94">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="W94">
         <v>1.3</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z94">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA94">
         <v>1.18</v>
       </c>
       <c r="AB94">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AC94">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD94">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE94">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF94">
         <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK94">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,22 +15803,22 @@
         <v>2.14</v>
       </c>
       <c r="Q95">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R95">
         <v>2.09</v>
       </c>
       <c r="S95">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T95">
         <v>2.7</v>
       </c>
       <c r="U95">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V95">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W95">
         <v>1.07</v>
@@ -15830,13 +15830,13 @@
         <v>1.31</v>
       </c>
       <c r="Z95">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="AA95">
         <v>2.04</v>
       </c>
       <c r="AB95">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC95">
         <v>3.58</v>
@@ -15848,10 +15848,10 @@
         <v>1.04</v>
       </c>
       <c r="AF95">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AG95">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -17587,34 +17587,34 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="O106">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="P106">
-        <v>8.300000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q106">
         <v>1.8</v>
       </c>
       <c r="R106">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U106">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17623,22 +17623,22 @@
         <v>1.28</v>
       </c>
       <c r="Z106">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="AA106">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB106">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AC106">
         <v>3.1</v>
       </c>
       <c r="AD106">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE106">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
         <v>2.18</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,49 +17750,49 @@
         </is>
       </c>
       <c r="N107">
+        <v>1.65</v>
+      </c>
+      <c r="O107">
+        <v>3.93</v>
+      </c>
+      <c r="P107">
+        <v>5.32</v>
+      </c>
+      <c r="Q107">
+        <v>0</v>
+      </c>
+      <c r="R107">
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+      <c r="U107">
+        <v>0</v>
+      </c>
+      <c r="V107">
+        <v>0</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107">
+        <v>0</v>
+      </c>
+      <c r="Z107">
+        <v>0</v>
+      </c>
+      <c r="AA107">
         <v>1.7</v>
       </c>
-      <c r="O107">
-        <v>3.76</v>
-      </c>
-      <c r="P107">
-        <v>4.95</v>
-      </c>
-      <c r="Q107">
-        <v>0</v>
-      </c>
-      <c r="R107">
-        <v>0</v>
-      </c>
-      <c r="S107">
-        <v>0</v>
-      </c>
-      <c r="T107">
-        <v>0</v>
-      </c>
-      <c r="U107">
-        <v>0</v>
-      </c>
-      <c r="V107">
-        <v>0</v>
-      </c>
-      <c r="W107">
-        <v>0</v>
-      </c>
-      <c r="X107">
-        <v>0</v>
-      </c>
-      <c r="Y107">
-        <v>0</v>
-      </c>
-      <c r="Z107">
-        <v>0</v>
-      </c>
-      <c r="AA107">
-        <v>0</v>
-      </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC107">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
         <v>2.76</v>
@@ -647,7 +647,7 @@
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
         <v>1.3</v>
@@ -656,10 +656,10 @@
         <v>3.08</v>
       </c>
       <c r="U2">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,10 +668,10 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z2">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA2">
         <v>1.72</v>
@@ -686,7 +686,7 @@
         <v>1.37</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
         <v>1.57</v>
@@ -708,7 +708,7 @@
         <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="O3">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P3">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>6</v>
+        <v>4.46</v>
       </c>
       <c r="R3">
         <v>2.63</v>
       </c>
       <c r="S3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
         <v>3.6</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V3">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
         <v>1.11</v>
@@ -840,16 +840,16 @@
         <v>1.44</v>
       </c>
       <c r="AB3">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC3">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AD3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF3">
         <v>1.64</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK3">
         <v>1.06</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O5">
         <v>3.85</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R5">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
         <v>1.22</v>
@@ -1145,10 +1145,10 @@
         <v>3.8</v>
       </c>
       <c r="U5">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W5">
         <v>1.16</v>
@@ -1166,19 +1166,19 @@
         <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC5">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AD5">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG5">
         <v>2.65</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
         <v>4.25</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="R6">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="S6">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="U6">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z6">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AB6">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AC6">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AD6">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE6">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AF6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S7">
         <v>1.22</v>
@@ -1471,43 +1471,43 @@
         <v>3.6</v>
       </c>
       <c r="U7">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB7">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC7">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AD7">
         <v>1.59</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG7">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="O14">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P14">
         <v>1.66</v>
@@ -2612,7 +2612,7 @@
         <v>3.45</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
         <v>1.56</v>
@@ -2624,31 +2624,31 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB14">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC14">
         <v>2.36</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>2.07</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
         <v>3.75</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.47</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>2.47</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R27">
         <v>2.05</v>
@@ -4728,13 +4728,13 @@
         <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
         <v>1.07</v>
@@ -4743,31 +4743,31 @@
         <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA27">
         <v>2.02</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AK27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="S29">
         <v>1.36</v>
@@ -5060,7 +5060,7 @@
         <v>2.86</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
         <v>1.08</v>
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q32">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="R32">
         <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U32">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="V32">
         <v>1.32</v>
@@ -5558,10 +5558,10 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z32">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AA32">
         <v>2.14</v>
@@ -5570,19 +5570,19 @@
         <v>1.67</v>
       </c>
       <c r="AC32">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="AD32">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AG32">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="P36">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
         <v>3.5</v>
       </c>
       <c r="P38">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q38">
         <v>2.76</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
         <v>1.3</v>
@@ -6536,28 +6536,28 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>3.9</v>
+        <v>4.19</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB38">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC38">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD38">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
         <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
         <v>2.2</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK38">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,28 +6829,28 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P40">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q40">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U40">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
         <v>1.47</v>
@@ -6862,31 +6862,31 @@
         <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="AA40">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC40">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AD40">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>3.3</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
         <v>3.14</v>
@@ -7010,40 +7010,40 @@
         <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W41">
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA41">
         <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC41">
         <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
         <v>1.55</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7979,25 +7979,25 @@
         <v>2.7</v>
       </c>
       <c r="Q47">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S47">
         <v>1.36</v>
       </c>
       <c r="T47">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U47">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V47">
         <v>1.33</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -8006,13 +8006,13 @@
         <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB47">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC47">
         <v>3.5</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O48">
+        <v>4.5</v>
+      </c>
+      <c r="P48">
         <v>4.4</v>
       </c>
-      <c r="P48">
-        <v>4.6</v>
-      </c>
       <c r="Q48">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R48">
         <v>2.52</v>
@@ -8157,10 +8157,10 @@
         <v>2.08</v>
       </c>
       <c r="V48">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8175,7 +8175,7 @@
         <v>1.39</v>
       </c>
       <c r="AB48">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC48">
         <v>2.06</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q50">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R50">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U50">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W50">
         <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA50">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AD50">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8951,16 +8951,16 @@
         <v>2.3</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P53">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q53">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S53">
         <v>1.3</v>
@@ -8975,7 +8975,7 @@
         <v>1.5</v>
       </c>
       <c r="W53">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.01</v>
@@ -8984,19 +8984,19 @@
         <v>1.16</v>
       </c>
       <c r="Z53">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA53">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB53">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC53">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AD53">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE53">
         <v>1.13</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK53">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q65">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S65">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U65">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AA65">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB65">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC65">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE65">
         <v>1.1</v>
       </c>
       <c r="AF65">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG65">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O66">
-        <v>3.52</v>
+        <v>1.48</v>
       </c>
       <c r="P66">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
+        <v>1.8</v>
+      </c>
+      <c r="AB66">
         <v>2</v>
-      </c>
-      <c r="AB66">
-        <v>1.8</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11230,28 +11230,28 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="P67">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
       </c>
       <c r="R67">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S67">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
         <v>2.53</v>
       </c>
       <c r="U67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V67">
         <v>1.33</v>
@@ -11260,25 +11260,25 @@
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z67">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AA67">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB67">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC67">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD67">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE67">
         <v>1.01</v>
@@ -11287,7 +11287,7 @@
         <v>1.89</v>
       </c>
       <c r="AG67">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AK67">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,10 +11396,10 @@
         <v>1.65</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
-        <v>4.33</v>
+        <v>4.79</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
@@ -11414,28 +11414,28 @@
         <v>2.88</v>
       </c>
       <c r="U68">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W68">
         <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA68">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC68">
         <v>3.12</v>
@@ -11450,7 +11450,7 @@
         <v>1.84</v>
       </c>
       <c r="AG68">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P69">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q69">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="R69">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T69">
         <v>2.75</v>
       </c>
       <c r="U69">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V69">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,25 +11592,25 @@
         <v>1.33</v>
       </c>
       <c r="Z69">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA69">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AB69">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC69">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="AD69">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE69">
         <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG69">
         <v>1.83</v>
@@ -11629,7 +11629,7 @@
         <v>1.3</v>
       </c>
       <c r="AK69">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12060,19 +12060,19 @@
         <v>2.15</v>
       </c>
       <c r="S72">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T72">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U72">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="V72">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
         <v>1.02</v>
@@ -12084,7 +12084,7 @@
         <v>3.3</v>
       </c>
       <c r="AA72">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB72">
         <v>1.83</v>
@@ -12211,16 +12211,16 @@
         <v>1.49</v>
       </c>
       <c r="O73">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="P73">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="Q73">
         <v>1.86</v>
       </c>
       <c r="R73">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="S73">
         <v>1.18</v>
@@ -12229,7 +12229,7 @@
         <v>4.05</v>
       </c>
       <c r="U73">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V73">
         <v>1.68</v>
@@ -12241,31 +12241,31 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z73">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AA73">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB73">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AC73">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AD73">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE73">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF73">
         <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.12</v>
       </c>
       <c r="AK73">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O75">
         <v>3.6</v>
@@ -12579,10 +12579,10 @@
         <v>2.35</v>
       </c>
       <c r="AC75">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD75">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE75">
         <v>1.18</v>
@@ -12607,7 +12607,7 @@
         <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O76">
         <v>4.25</v>
@@ -12712,10 +12712,10 @@
         <v>2.68</v>
       </c>
       <c r="S76">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T76">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="U76">
         <v>2.16</v>
@@ -12736,7 +12736,7 @@
         <v>5.88</v>
       </c>
       <c r="AA76">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB76">
         <v>2.83</v>
@@ -12748,10 +12748,10 @@
         <v>1.76</v>
       </c>
       <c r="AE76">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF76">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AG76">
         <v>2.55</v>
@@ -12869,10 +12869,10 @@
         <v>3.7</v>
       </c>
       <c r="Q77">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R77">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="S77">
         <v>1.22</v>
@@ -12905,19 +12905,19 @@
         <v>3</v>
       </c>
       <c r="AC77">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD77">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE77">
         <v>1.27</v>
       </c>
       <c r="AF77">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG77">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK77">
         <v>2.01</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
         <v>2.35</v>
@@ -13096,7 +13096,7 @@
         <v>1.53</v>
       </c>
       <c r="AK78">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="O79">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P79">
-        <v>3.83</v>
+        <v>2.22</v>
       </c>
       <c r="Q79">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S79">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T79">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="U79">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="V79">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="W79">
         <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z79">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA79">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB79">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD79">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
         <v>1.5</v>
       </c>
       <c r="AG79">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK79">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="O80">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>2.22</v>
+        <v>2.87</v>
       </c>
       <c r="Q80">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="R80">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S80">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="U80">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="V80">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X80">
         <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z80">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA80">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB80">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC80">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AD80">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE80">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF80">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG80">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AK80">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="P81">
-        <v>2.87</v>
+        <v>3.79</v>
       </c>
       <c r="Q81">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T81">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="U81">
         <v>2.2</v>
       </c>
       <c r="V81">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W81">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA81">
         <v>1.57</v>
       </c>
       <c r="AB81">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC81">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD81">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE81">
         <v>1.17</v>
       </c>
       <c r="AF81">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG81">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AK81">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R83">
         <v>2.3</v>
@@ -13859,10 +13859,10 @@
         <v>3.7</v>
       </c>
       <c r="U83">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V83">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W83">
         <v>1.12</v>
@@ -13877,25 +13877,25 @@
         <v>4.75</v>
       </c>
       <c r="AA83">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB83">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC83">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD83">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE83">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF83">
         <v>1.5</v>
       </c>
       <c r="AG83">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P86">
         <v>5.75</v>
@@ -14342,13 +14342,13 @@
         <v>2.28</v>
       </c>
       <c r="S86">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T86">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U86">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V86">
         <v>1.36</v>
@@ -14360,16 +14360,16 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z86">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA86">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB86">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC86">
         <v>3.28</v>
@@ -14384,7 +14384,7 @@
         <v>2.05</v>
       </c>
       <c r="AG86">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.23</v>
       </c>
       <c r="AK86">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14662,25 +14662,25 @@
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R88">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T88">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U88">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V88">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14689,28 +14689,28 @@
         <v>1.25</v>
       </c>
       <c r="Z88">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AA88">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB88">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC88">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="AD88">
         <v>1.38</v>
       </c>
       <c r="AE88">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF88">
         <v>1.65</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,49 +14816,49 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q89">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="R89">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="U89">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V89">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z89">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA89">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB89">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC89">
         <v>3.3</v>
@@ -14873,7 +14873,7 @@
         <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK89">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15142,37 +15142,37 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O91">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P91">
-        <v>5.74</v>
+        <v>5</v>
       </c>
       <c r="Q91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R91">
         <v>2.53</v>
       </c>
       <c r="S91">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T91">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U91">
         <v>2.49</v>
       </c>
       <c r="V91">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W91">
         <v>1.09</v>
       </c>
       <c r="X91">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
         <v>1.18</v>
@@ -15193,13 +15193,13 @@
         <v>1.41</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15966,10 +15966,10 @@
         <v>1.35</v>
       </c>
       <c r="Q96">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R96">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S96">
         <v>1.28</v>
@@ -15978,10 +15978,10 @@
         <v>3.18</v>
       </c>
       <c r="U96">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V96">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W96">
         <v>1.1</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>3.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK96">
         <v>1.05</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="O97">
         <v>3.8</v>
@@ -16132,19 +16132,19 @@
         <v>4.85</v>
       </c>
       <c r="R97">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S97">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T97">
         <v>3.25</v>
       </c>
       <c r="U97">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V97">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W97">
         <v>1.09</v>
@@ -16159,10 +16159,10 @@
         <v>3.96</v>
       </c>
       <c r="AA97">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB97">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AC97">
         <v>2.72</v>
@@ -16171,13 +16171,13 @@
         <v>1.39</v>
       </c>
       <c r="AE97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF97">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG97">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O98">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q98">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R98">
         <v>2.6</v>
@@ -16307,40 +16307,40 @@
         <v>2.2</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W98">
         <v>1.13</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA98">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB98">
         <v>2.5</v>
       </c>
       <c r="AC98">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD98">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE98">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG98">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK98">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,28 +16446,28 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O99">
         <v>3.3</v>
       </c>
       <c r="P99">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q99">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R99">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S99">
         <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="U99">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V99">
         <v>1.45</v>
@@ -16482,7 +16482,7 @@
         <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>4.07</v>
+        <v>3.62</v>
       </c>
       <c r="AA99">
         <v>1.76</v>
@@ -16497,13 +16497,13 @@
         <v>1.36</v>
       </c>
       <c r="AE99">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF99">
         <v>1.6</v>
       </c>
       <c r="AG99">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,40 +16609,40 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O100">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P100">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="Q100">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R100">
         <v>2.5</v>
       </c>
       <c r="S100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U100">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V100">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W100">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X100">
         <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z100">
         <v>4.4</v>
@@ -16651,16 +16651,16 @@
         <v>1.46</v>
       </c>
       <c r="AB100">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AC100">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD100">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF100">
         <v>1.77</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK100">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O101">
-        <v>3.38</v>
+        <v>3.13</v>
       </c>
       <c r="P101">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16935,34 +16935,34 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
         <v>2.2</v>
       </c>
       <c r="Q102">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S102">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U102">
         <v>2.38</v>
       </c>
       <c r="V102">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
         <v>1.03</v>
@@ -16971,10 +16971,10 @@
         <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="AA102">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB102">
         <v>2.1</v>
@@ -16986,10 +16986,10 @@
         <v>1.39</v>
       </c>
       <c r="AE102">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF102">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG102">
         <v>2.29</v>
@@ -17008,7 +17008,7 @@
         <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,16 +17098,16 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O103">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P103">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="Q103">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="R103">
         <v>2.5</v>
@@ -17116,7 +17116,7 @@
         <v>1.28</v>
       </c>
       <c r="T103">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U103">
         <v>2.3</v>
@@ -17125,37 +17125,37 @@
         <v>1.55</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA103">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB103">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC103">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AD103">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE103">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF103">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG103">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK103">
-        <v>2.42</v>
+        <v>2.79</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O104">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="P104">
-        <v>8.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q104">
         <v>1.65</v>
@@ -17279,7 +17279,7 @@
         <v>1.2</v>
       </c>
       <c r="T104">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U104">
         <v>1.93</v>
@@ -17288,7 +17288,7 @@
         <v>1.68</v>
       </c>
       <c r="W104">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X104">
         <v>1.01</v>
@@ -17300,25 +17300,25 @@
         <v>5.3</v>
       </c>
       <c r="AA104">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AB104">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AC104">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AD104">
         <v>1.68</v>
       </c>
       <c r="AE104">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF104">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK104">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,31 +17424,31 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P105">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q105">
         <v>2.95</v>
       </c>
       <c r="R105">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S105">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>3.11</v>
+        <v>2.91</v>
       </c>
       <c r="U105">
         <v>2.73</v>
       </c>
       <c r="V105">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W105">
         <v>1.04</v>
@@ -17466,19 +17466,19 @@
         <v>1.81</v>
       </c>
       <c r="AB105">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC105">
         <v>2.8</v>
       </c>
       <c r="AD105">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
         <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG105">
         <v>2.1</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AK105">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17608,7 +17608,7 @@
         <v>3.1</v>
       </c>
       <c r="U106">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V106">
         <v>1.48</v>
@@ -17641,10 +17641,10 @@
         <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AG106">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK106">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18076,22 +18076,22 @@
         </is>
       </c>
       <c r="N109">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O109">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P109">
         <v>1.62</v>
       </c>
       <c r="Q109">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="R109">
         <v>2.36</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T109">
         <v>3.3</v>
@@ -18100,25 +18100,25 @@
         <v>2.4</v>
       </c>
       <c r="V109">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W109">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z109">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA109">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB109">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AC109">
         <v>2.47</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AG109">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AK109">
         <v>1.18</v>
@@ -18239,58 +18239,58 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O110">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S110">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U110">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="V110">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W110">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y110">
         <v>1.18</v>
       </c>
       <c r="Z110">
-        <v>4.17</v>
+        <v>3.94</v>
       </c>
       <c r="AA110">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB110">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AC110">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AD110">
         <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF110">
         <v>1.54</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P111">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q111">
         <v>2.8</v>
@@ -18423,19 +18423,19 @@
         <v>2.75</v>
       </c>
       <c r="U111">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V111">
         <v>1.31</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
         <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
         <v>2.88</v>
@@ -18453,13 +18453,13 @@
         <v>1.21</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AG111">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.28</v>
       </c>
       <c r="AK111">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,16 +18565,16 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O112">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="Q112">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R112">
         <v>2.05</v>
@@ -18583,19 +18583,19 @@
         <v>1.36</v>
       </c>
       <c r="T112">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U112">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="V112">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W112">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
         <v>1.3</v>
@@ -18604,19 +18604,19 @@
         <v>3.47</v>
       </c>
       <c r="AA112">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB112">
         <v>1.8</v>
       </c>
       <c r="AC112">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="AD112">
         <v>1.29</v>
       </c>
       <c r="AE112">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF112">
         <v>1.73</v>
@@ -18638,7 +18638,7 @@
         <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19546,28 +19546,28 @@
         <v>7.5</v>
       </c>
       <c r="O118">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P118">
         <v>1.35</v>
       </c>
       <c r="Q118">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R118">
         <v>2.63</v>
       </c>
       <c r="S118">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T118">
         <v>3.75</v>
       </c>
       <c r="U118">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="V118">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W118">
         <v>1.12</v>
@@ -19576,31 +19576,31 @@
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z118">
-        <v>5.02</v>
+        <v>5.15</v>
       </c>
       <c r="AA118">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB118">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AC118">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD118">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE118">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF118">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG118">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK118">
         <v>1.04</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="O119">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P119">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q119">
         <v>3.9</v>
@@ -19727,7 +19727,7 @@
         <v>3.02</v>
       </c>
       <c r="U119">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V119">
         <v>1.46</v>
@@ -19736,34 +19736,34 @@
         <v>1.08</v>
       </c>
       <c r="X119">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z119">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="AA119">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB119">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC119">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AD119">
         <v>1.35</v>
       </c>
       <c r="AE119">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG119">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AK119">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20032,16 +20032,16 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="O121">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P121">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Q121">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R121">
         <v>2.2</v>
@@ -20053,40 +20053,40 @@
         <v>2.7</v>
       </c>
       <c r="U121">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W121">
         <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y121">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z121">
         <v>3.31</v>
       </c>
       <c r="AA121">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB121">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC121">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="AD121">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE121">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF121">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG121">
         <v>1.72</v>
@@ -20105,7 +20105,7 @@
         <v>1.08</v>
       </c>
       <c r="AK121">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,31 +20195,31 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q122">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R122">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U122">
         <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
         <v>1.11</v>
@@ -20228,31 +20228,31 @@
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z122">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA122">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB122">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD122">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE122">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG122">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AK122">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,52 +20358,52 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q123">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R123">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S123">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T123">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U123">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="V123">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W123">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z123">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AA123">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AB123">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC123">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD123">
         <v>1.17</v>
@@ -20412,10 +20412,10 @@
         <v>1.02</v>
       </c>
       <c r="AF123">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG123">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK123">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="O124">
+        <v>1.9</v>
+      </c>
+      <c r="P124">
         <v>3.75</v>
-      </c>
-      <c r="P124">
-        <v>3.65</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20684,10 +20684,10 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O125">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P125">
         <v>1.81</v>
@@ -20847,61 +20847,61 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q126">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R126">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S126">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T126">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U126">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V126">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z126">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="AA126">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB126">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC126">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AD126">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF126">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG126">
         <v>1.81</v>
@@ -20920,7 +20920,7 @@
         <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
       </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S127">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="T127">
+        <v>2.79</v>
+      </c>
+      <c r="U127">
         <v>2.95</v>
       </c>
-      <c r="U127">
-        <v>2.9</v>
-      </c>
       <c r="V127">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W127">
         <v>1.04</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y127">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z127">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA127">
         <v>2.1</v>
       </c>
       <c r="AB127">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC127">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="AD127">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE127">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG127">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK127">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q133">
         <v>2.9</v>
@@ -22006,13 +22006,13 @@
         <v>1.53</v>
       </c>
       <c r="T133">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U133">
         <v>3.25</v>
       </c>
       <c r="V133">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W133">
         <v>1.04</v>
@@ -22021,31 +22021,31 @@
         <v>1.06</v>
       </c>
       <c r="Y133">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z133">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="AA133">
         <v>2.55</v>
       </c>
       <c r="AB133">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AC133">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="AD133">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE133">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF133">
         <v>2.04</v>
       </c>
       <c r="AG133">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22160,55 +22160,55 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="R134">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S134">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T134">
-        <v>2.39</v>
+        <v>2.97</v>
       </c>
       <c r="U134">
         <v>2.13</v>
       </c>
       <c r="V134">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z134">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA134">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AB134">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC134">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD134">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE134">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG134">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AK134">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O136">
         <v>3.05</v>
@@ -22498,7 +22498,7 @@
         <v>2.4</v>
       </c>
       <c r="U136">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V136">
         <v>1.21</v>
@@ -22510,7 +22510,7 @@
         <v>1.09</v>
       </c>
       <c r="Y136">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="Z136">
         <v>2.32</v>
@@ -22522,16 +22522,16 @@
         <v>1.4</v>
       </c>
       <c r="AC136">
-        <v>4.8</v>
+        <v>5.39</v>
       </c>
       <c r="AD136">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE136">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF136">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG136">
         <v>1.53</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK136">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22658,13 +22658,13 @@
         <v>1.25</v>
       </c>
       <c r="T137">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U137">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V137">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W137">
         <v>1.14</v>
@@ -22685,19 +22685,19 @@
         <v>2.26</v>
       </c>
       <c r="AC137">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD137">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE137">
         <v>1.18</v>
       </c>
       <c r="AF137">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG137">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK137">
         <v>2.27</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>9.199999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="O60">
-        <v>6.14</v>
+        <v>5.5</v>
       </c>
       <c r="P60">
-        <v>1.25</v>
+        <v>7.1</v>
       </c>
       <c r="Q60">
-        <v>7.68</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O61">
+        <v>6.14</v>
+      </c>
+      <c r="P61">
+        <v>1.25</v>
+      </c>
+      <c r="Q61">
+        <v>7.68</v>
+      </c>
+      <c r="R61">
+        <v>2.83</v>
+      </c>
+      <c r="S61">
+        <v>1.18</v>
+      </c>
+      <c r="T61">
+        <v>3.9</v>
+      </c>
+      <c r="U61">
+        <v>2.09</v>
+      </c>
+      <c r="V61">
+        <v>1.67</v>
+      </c>
+      <c r="W61">
+        <v>1.16</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>1.13</v>
+      </c>
+      <c r="Z61">
+        <v>5.3</v>
+      </c>
+      <c r="AA61">
+        <v>1.39</v>
+      </c>
+      <c r="AB61">
+        <v>2.59</v>
+      </c>
+      <c r="AC61">
+        <v>2.08</v>
+      </c>
+      <c r="AD61">
+        <v>1.7</v>
+      </c>
+      <c r="AE61">
         <v>1.28</v>
       </c>
-      <c r="O61">
-        <v>5.5</v>
-      </c>
-      <c r="P61">
-        <v>7.1</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>0</v>
-      </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>0</v>
-      </c>
-      <c r="AB61">
-        <v>0</v>
-      </c>
-      <c r="AC61">
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
-      <c r="AE61">
-        <v>0</v>
-      </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="O79">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
-        <v>2.22</v>
+        <v>2.87</v>
       </c>
       <c r="Q79">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="R79">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S79">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="U79">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="V79">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z79">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA79">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB79">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AD79">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE79">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG79">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AK79">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,65 +13349,65 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P80">
-        <v>2.87</v>
+        <v>2.22</v>
       </c>
       <c r="Q80">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="R80">
+        <v>2.26</v>
+      </c>
+      <c r="S80">
+        <v>1.27</v>
+      </c>
+      <c r="T80">
+        <v>3.35</v>
+      </c>
+      <c r="U80">
+        <v>2.44</v>
+      </c>
+      <c r="V80">
+        <v>1.51</v>
+      </c>
+      <c r="W80">
+        <v>1.11</v>
+      </c>
+      <c r="X80">
+        <v>1.04</v>
+      </c>
+      <c r="Y80">
+        <v>1.15</v>
+      </c>
+      <c r="Z80">
+        <v>4.33</v>
+      </c>
+      <c r="AA80">
+        <v>1.65</v>
+      </c>
+      <c r="AB80">
+        <v>2.2</v>
+      </c>
+      <c r="AC80">
+        <v>2.6</v>
+      </c>
+      <c r="AD80">
+        <v>1.48</v>
+      </c>
+      <c r="AE80">
+        <v>1.14</v>
+      </c>
+      <c r="AF80">
+        <v>1.5</v>
+      </c>
+      <c r="AG80">
         <v>2.38</v>
       </c>
-      <c r="S80">
-        <v>1.25</v>
-      </c>
-      <c r="T80">
-        <v>3.7</v>
-      </c>
-      <c r="U80">
-        <v>2.2</v>
-      </c>
-      <c r="V80">
-        <v>1.53</v>
-      </c>
-      <c r="W80">
-        <v>1.15</v>
-      </c>
-      <c r="X80">
-        <v>1.02</v>
-      </c>
-      <c r="Y80">
-        <v>1.12</v>
-      </c>
-      <c r="Z80">
-        <v>5</v>
-      </c>
-      <c r="AA80">
-        <v>1.53</v>
-      </c>
-      <c r="AB80">
-        <v>2.3</v>
-      </c>
-      <c r="AC80">
-        <v>2.35</v>
-      </c>
-      <c r="AD80">
-        <v>1.45</v>
-      </c>
-      <c r="AE80">
-        <v>1.17</v>
-      </c>
-      <c r="AF80">
-        <v>1.44</v>
-      </c>
-      <c r="AG80">
-        <v>2.5</v>
-      </c>
       <c r="AH80" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AK80">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -20361,13 +20361,13 @@
         <v>1.75</v>
       </c>
       <c r="O123">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q123">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="R123">
         <v>2.1</v>
@@ -20376,7 +20376,7 @@
         <v>1.44</v>
       </c>
       <c r="T123">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U123">
         <v>3.15</v>
@@ -20391,31 +20391,31 @@
         <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z123">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA123">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="AB123">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC123">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD123">
         <v>1.17</v>
       </c>
       <c r="AE123">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF123">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG123">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK123">
         <v>1.95</v>
@@ -21022,49 +21022,49 @@
         <v>2.3</v>
       </c>
       <c r="R127">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S127">
         <v>1.46</v>
       </c>
       <c r="T127">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="U127">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="V127">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W127">
         <v>1.04</v>
       </c>
       <c r="X127">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y127">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z127">
         <v>3</v>
       </c>
       <c r="AA127">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB127">
         <v>1.7</v>
       </c>
       <c r="AC127">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD127">
         <v>1.25</v>
       </c>
       <c r="AE127">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF127">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG127">
         <v>1.73</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -5534,19 +5534,19 @@
         <v>3.9</v>
       </c>
       <c r="Q32">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
         <v>2.56</v>
       </c>
       <c r="U32">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="V32">
         <v>1.32</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
         <v>1.84</v>
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O86">
         <v>3.9</v>
@@ -14342,19 +14342,19 @@
         <v>2.28</v>
       </c>
       <c r="S86">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T86">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V86">
         <v>1.36</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
         <v>1.02</v>
@@ -14363,7 +14363,7 @@
         <v>1.29</v>
       </c>
       <c r="Z86">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA86">
         <v>2.05</v>
@@ -20044,7 +20044,7 @@
         <v>2.1</v>
       </c>
       <c r="R121">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S121">
         <v>1.38</v>
@@ -20053,10 +20053,10 @@
         <v>2.7</v>
       </c>
       <c r="U121">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="V121">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W121">
         <v>1.06</v>
@@ -20068,19 +20068,19 @@
         <v>1.27</v>
       </c>
       <c r="Z121">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="AA121">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB121">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC121">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="AD121">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE121">
         <v>1.09</v>
@@ -20105,7 +20105,7 @@
         <v>1.08</v>
       </c>
       <c r="AK121">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20198,22 +20198,22 @@
         <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
         <v>2.45</v>
       </c>
       <c r="Q122">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R122">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S122">
         <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U122">
         <v>2.5</v>
@@ -20228,10 +20228,10 @@
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z122">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA122">
         <v>1.76</v>
@@ -20243,7 +20243,7 @@
         <v>2.75</v>
       </c>
       <c r="AD122">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE122">
         <v>1.1</v>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
         <v>1.4</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O123">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q123">
         <v>2.49</v>
@@ -20400,10 +20400,10 @@
         <v>2.24</v>
       </c>
       <c r="AB123">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC123">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD123">
         <v>1.17</v>
@@ -20431,7 +20431,7 @@
         <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20865,7 +20865,7 @@
         <v>1.45</v>
       </c>
       <c r="T126">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U126">
         <v>3.1</v>
@@ -20880,7 +20880,7 @@
         <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z126">
         <v>3.01</v>
@@ -21013,25 +21013,25 @@
         <v>1.67</v>
       </c>
       <c r="O127">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
       </c>
       <c r="R127">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S127">
         <v>1.46</v>
       </c>
       <c r="T127">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="U127">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="V127">
         <v>1.33</v>
@@ -21046,25 +21046,25 @@
         <v>1.29</v>
       </c>
       <c r="Z127">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA127">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB127">
         <v>1.7</v>
       </c>
       <c r="AC127">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="AD127">
         <v>1.25</v>
       </c>
       <c r="AE127">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF127">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG127">
         <v>1.73</v>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK127">
         <v>2.05</v>
@@ -22021,25 +22021,25 @@
         <v>1.06</v>
       </c>
       <c r="Y133">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z133">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="AA133">
         <v>2.55</v>
       </c>
       <c r="AB133">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC133">
         <v>4.67</v>
       </c>
       <c r="AD133">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE133">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
         <v>2.04</v>
@@ -22495,10 +22495,10 @@
         <v>1.57</v>
       </c>
       <c r="T136">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="U136">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V136">
         <v>1.21</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O12">
         <v>2.75</v>
@@ -2274,7 +2274,7 @@
         <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R12">
         <v>1.93</v>
@@ -2283,10 +2283,10 @@
         <v>1.62</v>
       </c>
       <c r="T12">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="U12">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="V12">
         <v>1.21</v>
@@ -2298,13 +2298,13 @@
         <v>1.08</v>
       </c>
       <c r="Y12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z12">
         <v>2.28</v>
       </c>
       <c r="AA12">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AB12">
         <v>1.38</v>
@@ -2319,7 +2319,7 @@
         <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
         <v>1.64</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2769,22 +2769,22 @@
         <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
         <v>2.8</v>
       </c>
       <c r="U15">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.33</v>
@@ -2799,7 +2799,7 @@
         <v>1.7</v>
       </c>
       <c r="AC15">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
@@ -4224,61 +4224,61 @@
         <v>3.7</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="P24">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>3.4</v>
       </c>
       <c r="Q25">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S25">
         <v>1.2</v>
@@ -4432,13 +4432,13 @@
         <v>2.16</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE25">
         <v>1.21</v>
       </c>
       <c r="AF25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
         <v>2.43</v>
@@ -4457,7 +4457,7 @@
         <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4882,22 +4882,22 @@
         <v>3.2</v>
       </c>
       <c r="Q28">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
         <v>1.42</v>
       </c>
       <c r="T28">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="U28">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
         <v>1.06</v>
@@ -4906,19 +4906,19 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AA28">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB28">
         <v>1.75</v>
       </c>
       <c r="AC28">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD28">
         <v>1.25</v>
@@ -4927,10 +4927,10 @@
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
@@ -5054,19 +5054,19 @@
         <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
         <v>1.26</v>
@@ -5078,10 +5078,10 @@
         <v>1.93</v>
       </c>
       <c r="AB29">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD29">
         <v>1.31</v>
@@ -5093,7 +5093,7 @@
         <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5540,13 +5540,13 @@
         <v>2.01</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T32">
         <v>2.56</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="V32">
         <v>1.32</v>
@@ -5558,10 +5558,10 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA32">
         <v>2.14</v>
@@ -5570,19 +5570,19 @@
         <v>1.67</v>
       </c>
       <c r="AC32">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="AD32">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE32">
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG32">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,22 +5860,22 @@
         <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U34">
         <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5893,7 +5893,7 @@
         <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AC34">
         <v>2.62</v>
@@ -5908,7 +5908,7 @@
         <v>1.56</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AK34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O42">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="Q42">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="R42">
         <v>2.25</v>
@@ -7182,10 +7182,10 @@
         <v>1.58</v>
       </c>
       <c r="W42">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
         <v>1.13</v>
@@ -7197,7 +7197,7 @@
         <v>1.49</v>
       </c>
       <c r="AB42">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AC42">
         <v>2.27</v>
@@ -7212,7 +7212,7 @@
         <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O43">
         <v>4.4</v>
@@ -7327,10 +7327,10 @@
         <v>1.4</v>
       </c>
       <c r="Q43">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="R43">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="S43">
         <v>1.16</v>
@@ -7339,7 +7339,7 @@
         <v>4.5</v>
       </c>
       <c r="U43">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V43">
         <v>1.85</v>
@@ -7354,7 +7354,7 @@
         <v>1.06</v>
       </c>
       <c r="Z43">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="AA43">
         <v>1.33</v>
@@ -7369,7 +7369,7 @@
         <v>1.93</v>
       </c>
       <c r="AE43">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF43">
         <v>1.45</v>
@@ -7647,37 +7647,37 @@
         <v>3.2</v>
       </c>
       <c r="O45">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P45">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R45">
         <v>1.72</v>
       </c>
       <c r="S45">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="T45">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U45">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="V45">
         <v>1.2</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X45">
         <v>1.11</v>
       </c>
       <c r="Y45">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z45">
         <v>2.15</v>
@@ -7689,16 +7689,16 @@
         <v>1.36</v>
       </c>
       <c r="AC45">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD45">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE45">
         <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG45">
         <v>1.55</v>
@@ -7807,58 +7807,58 @@
         </is>
       </c>
       <c r="N46">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="P46">
         <v>1.44</v>
       </c>
       <c r="Q46">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="U46">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="V46">
         <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
         <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA46">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AB46">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC46">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
         <v>2.05</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AK46">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O48">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S48">
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="U48">
         <v>2.08</v>
       </c>
       <c r="V48">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="W48">
         <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AA48">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB48">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC48">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AD48">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF48">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8628,46 +8628,46 @@
         <v>4.05</v>
       </c>
       <c r="P51">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q51">
-        <v>4.33</v>
+        <v>4.72</v>
       </c>
       <c r="R51">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
         <v>3.34</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
         <v>4.33</v>
       </c>
       <c r="AA51">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD51">
         <v>1.42</v>
@@ -8676,10 +8676,10 @@
         <v>1.19</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,7 +8794,7 @@
         <v>3.23</v>
       </c>
       <c r="Q52">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
         <v>2.07</v>
@@ -8806,7 +8806,7 @@
         <v>2.88</v>
       </c>
       <c r="U52">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V52">
         <v>1.36</v>
@@ -8827,7 +8827,7 @@
         <v>1.97</v>
       </c>
       <c r="AB52">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC52">
         <v>3.28</v>
@@ -8842,7 +8842,7 @@
         <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>1.66</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P56">
         <v>3.95</v>
@@ -9449,13 +9449,13 @@
         <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U56">
         <v>2.2</v>
@@ -9476,16 +9476,16 @@
         <v>5.13</v>
       </c>
       <c r="AA56">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB56">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
         <v>2.21</v>
       </c>
       <c r="AD56">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE56">
         <v>1.21</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
         <v>2.1</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O60">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="P60">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,25 +10252,25 @@
         </is>
       </c>
       <c r="N61">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O61">
-        <v>6.14</v>
+        <v>5.5</v>
       </c>
       <c r="P61">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q61">
-        <v>7.68</v>
+        <v>6.5</v>
       </c>
       <c r="R61">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S61">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U61">
         <v>2.09</v>
@@ -10282,25 +10282,25 @@
         <v>1.16</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>5.3</v>
+        <v>5.46</v>
       </c>
       <c r="AA61">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AB61">
         <v>2.59</v>
       </c>
       <c r="AC61">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE61">
         <v>1.28</v>
@@ -10309,7 +10309,7 @@
         <v>1.76</v>
       </c>
       <c r="AG61">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="AK61">
         <v>1.06</v>
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O72">
         <v>3.5</v>
       </c>
       <c r="P72">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q72">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="R72">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S72">
         <v>1.37</v>
       </c>
       <c r="T72">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U72">
         <v>2.81</v>
@@ -12078,7 +12078,7 @@
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z72">
         <v>3.3</v>
@@ -12090,13 +12090,13 @@
         <v>1.83</v>
       </c>
       <c r="AC72">
-        <v>3.3</v>
+        <v>3.57</v>
       </c>
       <c r="AD72">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE72">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
         <v>1.84</v>
@@ -12214,58 +12214,58 @@
         <v>4.65</v>
       </c>
       <c r="P73">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="Q73">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="R73">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="S73">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T73">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="U73">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z73">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA73">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AB73">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AC73">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AD73">
         <v>1.7</v>
       </c>
       <c r="AE73">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF73">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG73">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.12</v>
       </c>
       <c r="AK73">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="O75">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="P75">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="Q75">
         <v>2.59</v>
@@ -12549,25 +12549,25 @@
         <v>2.35</v>
       </c>
       <c r="S75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U75">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V75">
         <v>1.6</v>
       </c>
       <c r="W75">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z75">
         <v>4.95</v>
@@ -12582,7 +12582,7 @@
         <v>2.25</v>
       </c>
       <c r="AD75">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE75">
         <v>1.18</v>
@@ -12591,7 +12591,7 @@
         <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12700,16 +12700,16 @@
         <v>1.65</v>
       </c>
       <c r="O76">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="Q76">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="R76">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="S76">
         <v>1.17</v>
@@ -12730,16 +12730,16 @@
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z76">
-        <v>5.88</v>
+        <v>5.75</v>
       </c>
       <c r="AA76">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB76">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
         <v>2.03</v>
@@ -12748,13 +12748,13 @@
         <v>1.76</v>
       </c>
       <c r="AE76">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF76">
         <v>1.42</v>
       </c>
       <c r="AG76">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12860,19 +12860,19 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O77">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P77">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="Q77">
         <v>2.15</v>
       </c>
       <c r="R77">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="S77">
         <v>1.22</v>
@@ -12884,7 +12884,7 @@
         <v>1.98</v>
       </c>
       <c r="V77">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="W77">
         <v>1.17</v>
@@ -12896,10 +12896,10 @@
         <v>1.05</v>
       </c>
       <c r="Z77">
-        <v>6.21</v>
+        <v>6</v>
       </c>
       <c r="AA77">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AB77">
         <v>3</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O78">
         <v>3.6</v>
@@ -13032,10 +13032,10 @@
         <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R78">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="S78">
         <v>1.17</v>
@@ -13044,16 +13044,16 @@
         <v>3.68</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V78">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W78">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
         <v>1.12</v>
@@ -13065,13 +13065,13 @@
         <v>1.42</v>
       </c>
       <c r="AB78">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC78">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD78">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE78">
         <v>1.29</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AK78">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13198,22 +13198,22 @@
         <v>2.58</v>
       </c>
       <c r="R79">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T79">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="U79">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W79">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X79">
         <v>1.02</v>
@@ -13222,7 +13222,7 @@
         <v>1.12</v>
       </c>
       <c r="Z79">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA79">
         <v>1.53</v>
@@ -13231,19 +13231,19 @@
         <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD79">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF79">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG79">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.34</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="O80">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q80">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R80">
         <v>2.26</v>
@@ -13370,22 +13370,22 @@
         <v>3.35</v>
       </c>
       <c r="U80">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V80">
         <v>1.51</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z80">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="AA80">
         <v>1.65</v>
@@ -13394,19 +13394,19 @@
         <v>2.2</v>
       </c>
       <c r="AC80">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AD80">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE80">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
         <v>1.5</v>
       </c>
       <c r="AG80">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13518,13 +13518,13 @@
         <v>3.88</v>
       </c>
       <c r="P81">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="Q81">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R81">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S81">
         <v>1.24</v>
@@ -13533,40 +13533,40 @@
         <v>3.44</v>
       </c>
       <c r="U81">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V81">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W81">
         <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z81">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="AA81">
         <v>1.57</v>
       </c>
       <c r="AB81">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC81">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD81">
         <v>1.49</v>
       </c>
       <c r="AE81">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF81">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG81">
         <v>2.4</v>
@@ -13585,7 +13585,7 @@
         <v>1.23</v>
       </c>
       <c r="AK81">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="O84">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P84">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="Q84">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R84">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S84">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U84">
         <v>2.1</v>
       </c>
       <c r="V84">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14037,28 +14037,28 @@
         <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>5.52</v>
+        <v>5.05</v>
       </c>
       <c r="AA84">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AB84">
         <v>2.6</v>
       </c>
       <c r="AC84">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AD84">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE84">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG84">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,28 +14164,28 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P85">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
       </c>
       <c r="R85">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="S85">
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
         <v>1.67</v>
@@ -14200,28 +14200,28 @@
         <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA85">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AB85">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AC85">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AD85">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
         <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O87">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="P87">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q87">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="R87">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S87">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T87">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U87">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="V87">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W87">
         <v>1.06</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y87">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z87">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AA87">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AB87">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC87">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="AD87">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE87">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF87">
         <v>2.05</v>
       </c>
       <c r="AG87">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
         <v>1.92</v>
@@ -14689,10 +14689,10 @@
         <v>1.25</v>
       </c>
       <c r="Z88">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA88">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB88">
         <v>1.97</v>
@@ -14701,7 +14701,7 @@
         <v>3.01</v>
       </c>
       <c r="AD88">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE88">
         <v>1.09</v>
@@ -14710,7 +14710,7 @@
         <v>1.65</v>
       </c>
       <c r="AG88">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O94">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="P94">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q94">
         <v>1.57</v>
@@ -15646,49 +15646,49 @@
         <v>3.13</v>
       </c>
       <c r="S94">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T94">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U94">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V94">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="W94">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X94">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
         <v>1.07</v>
       </c>
       <c r="Z94">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA94">
         <v>1.18</v>
       </c>
       <c r="AB94">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AC94">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD94">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AE94">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF94">
         <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK94">
         <v>3.8</v>
@@ -15803,10 +15803,10 @@
         <v>2.14</v>
       </c>
       <c r="Q95">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R95">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="S95">
         <v>1.38</v>
@@ -15836,7 +15836,7 @@
         <v>2.04</v>
       </c>
       <c r="AB95">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC95">
         <v>3.58</v>
@@ -15848,10 +15848,10 @@
         <v>1.04</v>
       </c>
       <c r="AF95">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AG95">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK95">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O106">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P106">
-        <v>9.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U106">
         <v>2.68</v>
       </c>
       <c r="V106">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
         <v>3.68</v>
       </c>
       <c r="AA106">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB106">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AC106">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AD106">
         <v>1.35</v>
       </c>
       <c r="AE106">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF106">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG106">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK106">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O107">
-        <v>3.93</v>
+        <v>4.1</v>
       </c>
       <c r="P107">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>2.88</v>
       </c>
       <c r="AA111">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB111">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC111">
         <v>3.85</v>
@@ -18456,7 +18456,7 @@
         <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
         <v>1.8</v>
@@ -19878,55 +19878,55 @@
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL120">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU137"/>
+  <dimension ref="A1:AU136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S2">
         <v>1.3</v>
@@ -656,7 +656,7 @@
         <v>3.08</v>
       </c>
       <c r="U2">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V2">
         <v>1.45</v>
@@ -674,7 +674,7 @@
         <v>3.95</v>
       </c>
       <c r="AA2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB2">
         <v>2.03</v>
@@ -692,7 +692,7 @@
         <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
         <v>1.48</v>
@@ -807,10 +807,10 @@
         <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>4.46</v>
+        <v>5.6</v>
       </c>
       <c r="R3">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S3">
         <v>1.22</v>
@@ -819,34 +819,34 @@
         <v>3.6</v>
       </c>
       <c r="U3">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
         <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>5.15</v>
+        <v>5.01</v>
       </c>
       <c r="AA3">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB3">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC3">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AD3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE3">
         <v>1.23</v>
@@ -871,7 +871,7 @@
         <v>1.12</v>
       </c>
       <c r="AK3">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="O5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>3.44</v>
+      </c>
+      <c r="R5">
+        <v>2.61</v>
+      </c>
+      <c r="S5">
+        <v>1.21</v>
+      </c>
+      <c r="T5">
+        <v>3.68</v>
+      </c>
+      <c r="U5">
         <v>2.01</v>
       </c>
-      <c r="Q5">
-        <v>3.3</v>
-      </c>
-      <c r="R5">
-        <v>2.5</v>
-      </c>
-      <c r="S5">
-        <v>1.22</v>
-      </c>
-      <c r="T5">
-        <v>3.8</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
       <c r="V5">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W5">
         <v>1.16</v>
@@ -1160,28 +1160,28 @@
         <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC5">
         <v>2.12</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF5">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG5">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,28 +1290,28 @@
         <v>1.72</v>
       </c>
       <c r="O6">
-        <v>4.25</v>
+        <v>3.77</v>
       </c>
       <c r="P6">
-        <v>4.05</v>
+        <v>3.02</v>
       </c>
       <c r="Q6">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T6">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W6">
         <v>1.24</v>
@@ -1320,10 +1320,10 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA6">
         <v>1.21</v>
@@ -1332,19 +1332,19 @@
         <v>3.58</v>
       </c>
       <c r="AC6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AD6">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AE6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF6">
         <v>1.28</v>
       </c>
       <c r="AG6">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>3.05</v>
       </c>
       <c r="O7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
         <v>3.54</v>
@@ -1477,7 +1477,7 @@
         <v>1.65</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1492,22 +1492,22 @@
         <v>1.49</v>
       </c>
       <c r="AB7">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AC7">
         <v>2.28</v>
       </c>
       <c r="AD7">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE7">
         <v>1.21</v>
       </c>
       <c r="AF7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>2.38</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W14">
         <v>1.12</v>
@@ -2630,7 +2630,7 @@
         <v>4.75</v>
       </c>
       <c r="AA14">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB14">
         <v>2.38</v>
@@ -2639,10 +2639,10 @@
         <v>2.36</v>
       </c>
       <c r="AD14">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
         <v>1.58</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
         <v>2.05</v>
@@ -4728,7 +4728,7 @@
         <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="U27">
         <v>2.95</v>
@@ -4767,7 +4767,7 @@
         <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O35">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P35">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="R35">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="S35">
         <v>1.52</v>
       </c>
       <c r="T35">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U35">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="V35">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W35">
         <v>1.02</v>
@@ -6047,22 +6047,22 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Z35">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="AA35">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AB35">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AC35">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD35">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE35">
         <v>1.01</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O36">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6503,52 +6503,52 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
         <v>3.5</v>
       </c>
       <c r="P38">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q38">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R38">
         <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="U38">
         <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.19</v>
+        <v>3.92</v>
       </c>
       <c r="AA38">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC38">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AD38">
         <v>1.43</v>
@@ -6557,7 +6557,7 @@
         <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG38">
         <v>2.2</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q40">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="R40">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="S40">
         <v>1.3</v>
@@ -6865,25 +6865,25 @@
         <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AA40">
         <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC40">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="AD40">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG40">
         <v>2.05</v>
@@ -6902,7 +6902,7 @@
         <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>2.5</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q41">
         <v>3.14</v>
@@ -7007,28 +7007,28 @@
         <v>2.38</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
         <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="V41">
         <v>1.52</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AA41">
         <v>1.69</v>
@@ -7040,13 +7040,13 @@
         <v>2.56</v>
       </c>
       <c r="AD41">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
         <v>2.3</v>
@@ -7976,28 +7976,28 @@
         <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R47">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="S47">
         <v>1.36</v>
       </c>
       <c r="T47">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V47">
         <v>1.33</v>
       </c>
       <c r="W47">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -8009,10 +8009,10 @@
         <v>3.08</v>
       </c>
       <c r="AA47">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB47">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC47">
         <v>3.5</v>
@@ -8024,10 +8024,10 @@
         <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG47">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK47">
         <v>1.51</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O50">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q50">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R50">
         <v>2.13</v>
@@ -8480,10 +8480,10 @@
         <v>3.02</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V50">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W50">
         <v>1.07</v>
@@ -8492,16 +8492,16 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AA50">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
         <v>2.84</v>
@@ -8513,10 +8513,10 @@
         <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK50">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O53">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P53">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="Q53">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R53">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S53">
         <v>1.3</v>
       </c>
       <c r="T53">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U53">
         <v>2.4</v>
@@ -8975,13 +8975,13 @@
         <v>1.5</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
         <v>4.1</v>
@@ -8990,13 +8990,13 @@
         <v>1.7</v>
       </c>
       <c r="AB53">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC53">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AD53">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE53">
         <v>1.13</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK53">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10919,16 +10919,16 @@
         <v>2.24</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U65">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V65">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W65">
         <v>1.08</v>
@@ -10937,19 +10937,19 @@
         <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
         <v>3.78</v>
       </c>
       <c r="AA65">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC65">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AD65">
         <v>1.36</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="O66">
-        <v>1.48</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11230,37 +11230,37 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O67">
         <v>3.18</v>
       </c>
       <c r="P67">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q67">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="R67">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T67">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U67">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V67">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W67">
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y67">
         <v>1.37</v>
@@ -11278,16 +11278,16 @@
         <v>4.2</v>
       </c>
       <c r="AD67">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE67">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
         <v>1.89</v>
       </c>
       <c r="AG67">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.49</v>
       </c>
       <c r="AK67">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P68">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="Q68">
         <v>2.2</v>
       </c>
       <c r="R68">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S68">
         <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U68">
         <v>2.75</v>
@@ -11420,7 +11420,7 @@
         <v>1.39</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
         <v>1</v>
@@ -11432,7 +11432,7 @@
         <v>3.3</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB68">
         <v>1.83</v>
@@ -11441,16 +11441,16 @@
         <v>3.12</v>
       </c>
       <c r="AD68">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF68">
         <v>1.84</v>
       </c>
       <c r="AG68">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,7 +11559,7 @@
         <v>2.11</v>
       </c>
       <c r="O69">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P69">
         <v>4</v>
@@ -11574,43 +11574,43 @@
         <v>1.43</v>
       </c>
       <c r="T69">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U69">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V69">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z69">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AA69">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AB69">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC69">
-        <v>3.77</v>
+        <v>3.9</v>
       </c>
       <c r="AD69">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF69">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG69">
         <v>1.83</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O73">
         <v>4.65</v>
       </c>
       <c r="P73">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q73">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="R73">
         <v>2.59</v>
@@ -12229,10 +12229,10 @@
         <v>3.94</v>
       </c>
       <c r="U73">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V73">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W73">
         <v>1.14</v>
@@ -12247,16 +12247,16 @@
         <v>5.7</v>
       </c>
       <c r="AA73">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB73">
         <v>2.68</v>
       </c>
       <c r="AC73">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD73">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE73">
         <v>1.3</v>
@@ -12281,7 +12281,7 @@
         <v>1.12</v>
       </c>
       <c r="AK73">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13847,22 +13847,22 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S83">
         <v>1.23</v>
       </c>
       <c r="T83">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="U83">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V83">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W83">
         <v>1.12</v>
@@ -13871,31 +13871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
         <v>4.75</v>
       </c>
       <c r="AA83">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AB83">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC83">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AD83">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE83">
         <v>1.19</v>
       </c>
       <c r="AF83">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG83">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AK83">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14819,61 +14819,61 @@
         <v>2.45</v>
       </c>
       <c r="O89">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q89">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R89">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U89">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
         <v>1.07</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA89">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC89">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD89">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK89">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15148,10 +15148,10 @@
         <v>3.9</v>
       </c>
       <c r="P91">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Q91">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R91">
         <v>2.53</v>
@@ -15160,13 +15160,13 @@
         <v>1.28</v>
       </c>
       <c r="T91">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U91">
         <v>2.49</v>
       </c>
       <c r="V91">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W91">
         <v>1.09</v>
@@ -15175,10 +15175,10 @@
         <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z91">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="AA91">
         <v>1.66</v>
@@ -15193,13 +15193,13 @@
         <v>1.41</v>
       </c>
       <c r="AE91">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF91">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15957,16 +15957,16 @@
         </is>
       </c>
       <c r="N96">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O96">
-        <v>4.55</v>
+        <v>5.05</v>
       </c>
       <c r="P96">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Q96">
-        <v>7</v>
+        <v>7.74</v>
       </c>
       <c r="R96">
         <v>2.43</v>
@@ -15984,7 +15984,7 @@
         <v>1.5</v>
       </c>
       <c r="W96">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15993,7 +15993,7 @@
         <v>1.16</v>
       </c>
       <c r="Z96">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="AA96">
         <v>1.65</v>
@@ -16002,13 +16002,13 @@
         <v>2.11</v>
       </c>
       <c r="AC96">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AD96">
         <v>1.39</v>
       </c>
       <c r="AE96">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF96">
         <v>1.85</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK96">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="O97">
         <v>3.8</v>
@@ -16129,55 +16129,55 @@
         <v>1.75</v>
       </c>
       <c r="Q97">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="R97">
         <v>2.23</v>
       </c>
       <c r="S97">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T97">
         <v>3.25</v>
       </c>
       <c r="U97">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="V97">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W97">
         <v>1.09</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y97">
         <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA97">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB97">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC97">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="AD97">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE97">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF97">
         <v>1.68</v>
       </c>
       <c r="AG97">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.21</v>
       </c>
       <c r="AK97">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="P98">
         <v>7.5</v>
       </c>
       <c r="Q98">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R98">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S98">
         <v>1.24</v>
@@ -16319,13 +16319,13 @@
         <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA98">
         <v>1.49</v>
       </c>
       <c r="AB98">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC98">
         <v>2.38</v>
@@ -16334,13 +16334,13 @@
         <v>1.58</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF98">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG98">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O99">
         <v>3.3</v>
       </c>
       <c r="P99">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q99">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R99">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S99">
         <v>1.33</v>
@@ -16467,7 +16467,7 @@
         <v>3.04</v>
       </c>
       <c r="U99">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V99">
         <v>1.45</v>
@@ -16482,7 +16482,7 @@
         <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.62</v>
+        <v>3.97</v>
       </c>
       <c r="AA99">
         <v>1.76</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK99">
         <v>1.45</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O100">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P100">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="Q100">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R100">
         <v>2.5</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U100">
         <v>2.2</v>
       </c>
       <c r="V100">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z100">
         <v>4.4</v>
       </c>
       <c r="AA100">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB100">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AC100">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AD100">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE100">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF100">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG100">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O101">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
         <v>3.6</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16941,49 +16941,49 @@
         <v>3.3</v>
       </c>
       <c r="P102">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q102">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="R102">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S102">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
         <v>3.18</v>
       </c>
       <c r="U102">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V102">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z102">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA102">
         <v>1.66</v>
       </c>
       <c r="AB102">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC102">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD102">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE102">
         <v>1.17</v>
@@ -16992,7 +16992,7 @@
         <v>1.58</v>
       </c>
       <c r="AG102">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,37 +17098,37 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="O103">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P103">
-        <v>6.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q103">
         <v>1.93</v>
       </c>
       <c r="R103">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S103">
         <v>1.28</v>
       </c>
       <c r="T103">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U103">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V103">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W103">
         <v>1.14</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
         <v>1.2</v>
@@ -17146,13 +17146,13 @@
         <v>2.28</v>
       </c>
       <c r="AD103">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE103">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF103">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG103">
         <v>1.95</v>
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="O104">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="P104">
         <v>8.550000000000001</v>
@@ -17285,53 +17285,53 @@
         <v>1.93</v>
       </c>
       <c r="V104">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W104">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
+        <v>1.08</v>
+      </c>
+      <c r="Z104">
+        <v>5.6</v>
+      </c>
+      <c r="AA104">
+        <v>1.36</v>
+      </c>
+      <c r="AB104">
+        <v>2.7</v>
+      </c>
+      <c r="AC104">
+        <v>1.99</v>
+      </c>
+      <c r="AD104">
+        <v>1.75</v>
+      </c>
+      <c r="AE104">
+        <v>1.28</v>
+      </c>
+      <c r="AF104">
+        <v>1.64</v>
+      </c>
+      <c r="AG104">
+        <v>1.97</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.09</v>
-      </c>
-      <c r="Z104">
-        <v>5.3</v>
-      </c>
-      <c r="AA104">
-        <v>1.38</v>
-      </c>
-      <c r="AB104">
-        <v>2.59</v>
-      </c>
-      <c r="AC104">
-        <v>2.06</v>
-      </c>
-      <c r="AD104">
-        <v>1.68</v>
-      </c>
-      <c r="AE104">
-        <v>1.26</v>
-      </c>
-      <c r="AF104">
-        <v>1.75</v>
-      </c>
-      <c r="AG104">
-        <v>1.92</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.15</v>
       </c>
       <c r="AK104">
         <v>3.6</v>
@@ -17427,19 +17427,19 @@
         <v>2.3</v>
       </c>
       <c r="O105">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q105">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="R105">
         <v>2.11</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
         <v>2.91</v>
@@ -17451,7 +17451,7 @@
         <v>1.39</v>
       </c>
       <c r="W105">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
         <v>1.01</v>
@@ -17463,22 +17463,22 @@
         <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC105">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AD105">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG105">
         <v>2.1</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="O109">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P109">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Q109">
         <v>5.49</v>
@@ -18106,7 +18106,7 @@
         <v>1.11</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y109">
         <v>1.18</v>
@@ -18115,7 +18115,7 @@
         <v>4.2</v>
       </c>
       <c r="AA109">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB109">
         <v>2.23</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AG109">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="O110">
         <v>3.4</v>
@@ -18248,13 +18248,13 @@
         <v>2.15</v>
       </c>
       <c r="Q110">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R110">
         <v>2.2</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T110">
         <v>3.15</v>
@@ -18278,10 +18278,10 @@
         <v>3.94</v>
       </c>
       <c r="AA110">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB110">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AC110">
         <v>2.72</v>
@@ -18290,13 +18290,13 @@
         <v>1.38</v>
       </c>
       <c r="AE110">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG110">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18565,16 +18565,16 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q112">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R112">
         <v>2.05</v>
@@ -18583,16 +18583,16 @@
         <v>1.36</v>
       </c>
       <c r="T112">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="U112">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="V112">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X112">
         <v>1.02</v>
@@ -18604,13 +18604,13 @@
         <v>3.47</v>
       </c>
       <c r="AA112">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB112">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC112">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AD112">
         <v>1.29</v>
@@ -18619,7 +18619,7 @@
         <v>1.06</v>
       </c>
       <c r="AF112">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG112">
         <v>2</v>
@@ -18638,7 +18638,7 @@
         <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19543,19 +19543,19 @@
         </is>
       </c>
       <c r="N118">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O118">
         <v>5.25</v>
       </c>
       <c r="P118">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q118">
         <v>8</v>
       </c>
       <c r="R118">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="S118">
         <v>1.21</v>
@@ -19564,7 +19564,7 @@
         <v>3.75</v>
       </c>
       <c r="U118">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V118">
         <v>1.62</v>
@@ -19576,31 +19576,31 @@
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z118">
-        <v>5.15</v>
+        <v>4.7</v>
       </c>
       <c r="AA118">
         <v>1.44</v>
       </c>
       <c r="AB118">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC118">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD118">
         <v>1.66</v>
       </c>
       <c r="AE118">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF118">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG118">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O119">
         <v>3.48</v>
@@ -19715,13 +19715,13 @@
         <v>2.26</v>
       </c>
       <c r="Q119">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="R119">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S119">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T119">
         <v>3.02</v>
@@ -19730,28 +19730,28 @@
         <v>2.65</v>
       </c>
       <c r="V119">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
         <v>1.23</v>
       </c>
       <c r="Z119">
-        <v>3.64</v>
+        <v>4.08</v>
       </c>
       <c r="AA119">
         <v>1.85</v>
       </c>
       <c r="AB119">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC119">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD119">
         <v>1.35</v>
@@ -20032,19 +20032,19 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O121">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P121">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
       </c>
       <c r="R121">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S121">
         <v>1.38</v>
@@ -20056,19 +20056,19 @@
         <v>2.96</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W121">
         <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z121">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA121">
         <v>2</v>
@@ -20077,13 +20077,13 @@
         <v>1.8</v>
       </c>
       <c r="AC121">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="AD121">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE121">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
         <v>1.97</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20198,13 +20198,13 @@
         <v>2.6</v>
       </c>
       <c r="O122">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
         <v>2.45</v>
       </c>
       <c r="Q122">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R122">
         <v>2.31</v>
@@ -20213,13 +20213,13 @@
         <v>1.3</v>
       </c>
       <c r="T122">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U122">
         <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W122">
         <v>1.11</v>
@@ -20228,7 +20228,7 @@
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
         <v>3.7</v>
@@ -20240,10 +20240,10 @@
         <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD122">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE122">
         <v>1.1</v>
@@ -20252,7 +20252,7 @@
         <v>1.57</v>
       </c>
       <c r="AG122">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK122">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20361,28 +20361,28 @@
         <v>1.8</v>
       </c>
       <c r="O123">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q123">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S123">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T123">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U123">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="V123">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W123">
         <v>1.05</v>
@@ -20394,25 +20394,25 @@
         <v>1.35</v>
       </c>
       <c r="Z123">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AA123">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AB123">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC123">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD123">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE123">
         <v>1.01</v>
       </c>
       <c r="AF123">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AG123">
         <v>1.73</v>
@@ -20431,7 +20431,7 @@
         <v>1.3</v>
       </c>
       <c r="AK123">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.1</v>
+        <v>1.81</v>
       </c>
       <c r="O124">
-        <v>1.9</v>
+        <v>3.78</v>
       </c>
       <c r="P124">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="O125">
         <v>3.6</v>
       </c>
       <c r="P125">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20847,25 +20847,25 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P126">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q126">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="R126">
         <v>1.92</v>
       </c>
       <c r="S126">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T126">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U126">
         <v>3.1</v>
@@ -20880,10 +20880,10 @@
         <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z126">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA126">
         <v>2.17</v>
@@ -20892,7 +20892,7 @@
         <v>1.65</v>
       </c>
       <c r="AC126">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD126">
         <v>1.18</v>
@@ -21013,16 +21013,16 @@
         <v>1.67</v>
       </c>
       <c r="O127">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P127">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q127">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S127">
         <v>1.46</v>
@@ -21031,34 +21031,34 @@
         <v>2.5</v>
       </c>
       <c r="U127">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
         <v>1.04</v>
       </c>
       <c r="X127">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
         <v>1.29</v>
       </c>
       <c r="Z127">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA127">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB127">
         <v>1.7</v>
       </c>
       <c r="AC127">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="AD127">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE127">
         <v>1.05</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK127">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q133">
+        <v>1.91</v>
+      </c>
+      <c r="R133">
+        <v>2.29</v>
+      </c>
+      <c r="S133">
+        <v>1.31</v>
+      </c>
+      <c r="T133">
+        <v>2.97</v>
+      </c>
+      <c r="U133">
+        <v>2.57</v>
+      </c>
+      <c r="V133">
+        <v>1.43</v>
+      </c>
+      <c r="W133">
+        <v>1.05</v>
+      </c>
+      <c r="X133">
+        <v>1.01</v>
+      </c>
+      <c r="Y133">
+        <v>1.21</v>
+      </c>
+      <c r="Z133">
         <v>2.9</v>
       </c>
-      <c r="R133">
-        <v>1.91</v>
-      </c>
-      <c r="S133">
-        <v>1.53</v>
-      </c>
-      <c r="T133">
-        <v>2.5</v>
-      </c>
-      <c r="U133">
-        <v>3.25</v>
-      </c>
-      <c r="V133">
-        <v>1.22</v>
-      </c>
-      <c r="W133">
-        <v>1.04</v>
-      </c>
-      <c r="X133">
-        <v>1.06</v>
-      </c>
-      <c r="Y133">
-        <v>1.46</v>
-      </c>
-      <c r="Z133">
-        <v>2.46</v>
-      </c>
       <c r="AA133">
-        <v>2.55</v>
+        <v>1.59</v>
       </c>
       <c r="AB133">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AC133">
-        <v>4.67</v>
+        <v>2.92</v>
       </c>
       <c r="AD133">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AE133">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK133">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G134">
@@ -22160,55 +22160,55 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="R134">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S134">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T134">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U134">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V134">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X134">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z134">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB134">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC134">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD134">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE134">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF134">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG134">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK134">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22267,27 +22267,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-28 21:00:00</t>
+          <t>2026-08-28 22:00:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q136">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="R136">
-        <v>1.87</v>
+        <v>2.41</v>
       </c>
       <c r="S136">
+        <v>1.25</v>
+      </c>
+      <c r="T136">
+        <v>3.5</v>
+      </c>
+      <c r="U136">
+        <v>2.22</v>
+      </c>
+      <c r="V136">
         <v>1.57</v>
       </c>
-      <c r="T136">
-        <v>2.24</v>
-      </c>
-      <c r="U136">
-        <v>3.58</v>
-      </c>
-      <c r="V136">
-        <v>1.21</v>
-      </c>
       <c r="W136">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X136">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="Z136">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="AA136">
-        <v>2.56</v>
+        <v>1.51</v>
       </c>
       <c r="AB136">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC136">
-        <v>5.39</v>
+        <v>2.34</v>
       </c>
       <c r="AD136">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="AE136">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF136">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AG136">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK136">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22580,169 +22580,6 @@
         <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-08-28 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>1.99</v>
-      </c>
-      <c r="R137">
-        <v>2.45</v>
-      </c>
-      <c r="S137">
-        <v>1.25</v>
-      </c>
-      <c r="T137">
-        <v>3.8</v>
-      </c>
-      <c r="U137">
-        <v>2.22</v>
-      </c>
-      <c r="V137">
-        <v>1.58</v>
-      </c>
-      <c r="W137">
-        <v>1.14</v>
-      </c>
-      <c r="X137">
-        <v>1.02</v>
-      </c>
-      <c r="Y137">
-        <v>1.14</v>
-      </c>
-      <c r="Z137">
-        <v>4.8</v>
-      </c>
-      <c r="AA137">
-        <v>1.51</v>
-      </c>
-      <c r="AB137">
-        <v>2.26</v>
-      </c>
-      <c r="AC137">
-        <v>2.2</v>
-      </c>
-      <c r="AD137">
-        <v>1.54</v>
-      </c>
-      <c r="AE137">
-        <v>1.18</v>
-      </c>
-      <c r="AF137">
-        <v>1.6</v>
-      </c>
-      <c r="AG137">
-        <v>2.09</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.07</v>
-      </c>
-      <c r="AK137">
-        <v>2.27</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
         <is>
           <t>2026-08-28 23:00:00</t>
         </is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.33</v>
+        <v>9.4</v>
       </c>
       <c r="O60">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="P60">
-        <v>8.199999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="Q60">
-        <v>1.67</v>
+        <v>6.5</v>
       </c>
       <c r="R60">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V60">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W60">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z60">
-        <v>5.7</v>
+        <v>5.46</v>
       </c>
       <c r="AA60">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AC60">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD60">
         <v>1.69</v>
       </c>
       <c r="AE60">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF60">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG60">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.08</v>
+        <v>3.7</v>
       </c>
       <c r="AK60">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>9.4</v>
+        <v>1.33</v>
       </c>
       <c r="O61">
-        <v>5.5</v>
+        <v>5.86</v>
       </c>
       <c r="P61">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q61">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="R61">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>5.46</v>
+        <v>5.7</v>
       </c>
       <c r="AA61">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB61">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="AC61">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD61">
         <v>1.69</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>3.7</v>
+        <v>1.08</v>
       </c>
       <c r="AK61">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="AL61">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -2111,40 +2111,40 @@
         <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="S11">
         <v>1.62</v>
       </c>
       <c r="T11">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="V11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
         <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y11">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z11">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AA11">
         <v>2.7</v>
       </c>
       <c r="AB11">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -2156,10 +2156,10 @@
         <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P13">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="S13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
         <v>1.14</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5.75</v>
+        <v>5.57</v>
       </c>
       <c r="AA13">
         <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AD13">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG13">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="O15">
         <v>3.95</v>
@@ -2811,7 +2811,7 @@
         <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -2938,10 +2938,10 @@
         <v>2.8</v>
       </c>
       <c r="U16">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="V16">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2956,10 +2956,10 @@
         <v>3.21</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
         <v>3.48</v>
@@ -2971,10 +2971,10 @@
         <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="O18">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="P18">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>2.66</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,58 +4384,58 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="P25">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q25">
-        <v>4.34</v>
+        <v>3.75</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V25">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB25">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
         <v>1.6</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
         <v>3.4</v>
@@ -4559,7 +4559,7 @@
         <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
         <v>1.2</v>
@@ -4568,7 +4568,7 @@
         <v>4</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="V26">
         <v>1.64</v>
@@ -4592,19 +4592,19 @@
         <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD26">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE26">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF26">
         <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,46 +4873,46 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S28">
         <v>1.36</v>
       </c>
       <c r="T28">
+        <v>2.87</v>
+      </c>
+      <c r="U28">
         <v>2.8</v>
-      </c>
-      <c r="U28">
-        <v>2.95</v>
       </c>
       <c r="V28">
         <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z28">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB28">
         <v>1.8</v>
@@ -4921,7 +4921,7 @@
         <v>3.55</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
@@ -4930,7 +4930,7 @@
         <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
         <v>1.4</v>
@@ -5045,25 +5045,25 @@
         <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T29">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5075,7 +5075,7 @@
         <v>3.05</v>
       </c>
       <c r="AA29">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AB29">
         <v>1.75</v>
@@ -5093,7 +5093,7 @@
         <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
         <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
+        <v>2.74</v>
+      </c>
+      <c r="U30">
         <v>2.7</v>
       </c>
-      <c r="U30">
-        <v>2.74</v>
-      </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5235,29 +5235,29 @@
         <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AB30">
         <v>1.85</v>
       </c>
       <c r="AC30">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
         <v>1.11</v>
       </c>
       <c r="AF30">
+        <v>1.84</v>
+      </c>
+      <c r="AG30">
         <v>1.85</v>
       </c>
-      <c r="AG30">
-        <v>1.84</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
         <v>2.05</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,28 +5694,28 @@
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="Q33">
         <v>2.46</v>
       </c>
       <c r="R33">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
         <v>1.45</v>
       </c>
       <c r="T33">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U33">
-        <v>3.16</v>
+        <v>2.87</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1.02</v>
@@ -5727,16 +5727,16 @@
         <v>3</v>
       </c>
       <c r="AA33">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
         <v>1.67</v>
       </c>
       <c r="AC33">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="AD33">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
         <v>1.02</v>
@@ -5745,7 +5745,7 @@
         <v>1.94</v>
       </c>
       <c r="AG33">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6017,61 +6017,61 @@
         <v>2.55</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
         <v>2.35</v>
       </c>
       <c r="Q35">
-        <v>2.91</v>
+        <v>3.22</v>
       </c>
       <c r="R35">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T35">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U35">
         <v>2.5</v>
       </c>
       <c r="V35">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AC35">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD35">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE35">
         <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="O36">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="P36">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q36">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R36">
         <v>1.86</v>
@@ -6216,10 +6216,10 @@
         <v>2.49</v>
       </c>
       <c r="AA36">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="AB36">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AC36">
         <v>4.7</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK36">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O37">
+        <v>3.4</v>
+      </c>
+      <c r="P37">
         <v>3.5</v>
-      </c>
-      <c r="P37">
-        <v>3.7</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,10 +6669,10 @@
         <v>2.25</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q39">
         <v>2.74</v>
@@ -6681,19 +6681,19 @@
         <v>2.23</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="U39">
         <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1.04</v>
@@ -6702,16 +6702,16 @@
         <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA39">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC39">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="AD39">
         <v>1.43</v>
@@ -6720,10 +6720,10 @@
         <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q41">
         <v>2.17</v>
       </c>
       <c r="R41">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.3</v>
@@ -7013,28 +7013,28 @@
         <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V41">
         <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
         <v>4.1</v>
       </c>
       <c r="AA41">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC41">
         <v>2.68</v>
@@ -7043,13 +7043,13 @@
         <v>1.37</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>2.5</v>
       </c>
       <c r="O42">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="Q42">
         <v>3.14</v>
@@ -7176,40 +7176,40 @@
         <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="V42">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
         <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AA42">
         <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC42">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
         <v>2.3</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,25 +7327,25 @@
         <v>2.03</v>
       </c>
       <c r="Q43">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S43">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U43">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V43">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7354,28 +7354,28 @@
         <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>4.6</v>
+        <v>4.98</v>
       </c>
       <c r="AA43">
         <v>1.49</v>
       </c>
       <c r="AB43">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AC43">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AD43">
         <v>1.57</v>
       </c>
       <c r="AE43">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF43">
         <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK43">
         <v>1.33</v>
@@ -7490,10 +7490,10 @@
         <v>1.4</v>
       </c>
       <c r="Q44">
-        <v>5.67</v>
+        <v>5.25</v>
       </c>
       <c r="R44">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="S44">
         <v>1.16</v>
@@ -7502,10 +7502,10 @@
         <v>4.5</v>
       </c>
       <c r="U44">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V44">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W44">
         <v>1.2</v>
@@ -7517,7 +7517,7 @@
         <v>1.06</v>
       </c>
       <c r="Z44">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA44">
         <v>1.33</v>
@@ -7532,7 +7532,7 @@
         <v>1.93</v>
       </c>
       <c r="AE44">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF44">
         <v>1.45</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK44">
         <v>1.07</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,52 +7807,52 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O46">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P46">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="R46">
         <v>1.72</v>
       </c>
       <c r="S46">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="T46">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U46">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="V46">
         <v>1.2</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y46">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z46">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA46">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB46">
         <v>1.36</v>
       </c>
       <c r="AC46">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="AD46">
         <v>1.12</v>
@@ -7970,25 +7970,25 @@
         </is>
       </c>
       <c r="N47">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="O47">
         <v>3.94</v>
       </c>
       <c r="P47">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q47">
-        <v>6.85</v>
+        <v>6.25</v>
       </c>
       <c r="R47">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
         <v>1.38</v>
       </c>
       <c r="T47">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U47">
         <v>2.67</v>
@@ -8003,19 +8003,19 @@
         <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
         <v>3.28</v>
       </c>
       <c r="AA47">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AB47">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC47">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD47">
         <v>1.3</v>
@@ -8043,7 +8043,7 @@
         <v>2.6</v>
       </c>
       <c r="AK47">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P48">
+        <v>2.9</v>
+      </c>
+      <c r="Q48">
+        <v>2.9</v>
+      </c>
+      <c r="R48">
+        <v>2.06</v>
+      </c>
+      <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
         <v>2.75</v>
       </c>
-      <c r="Q48">
-        <v>3.05</v>
-      </c>
-      <c r="R48">
-        <v>2.03</v>
-      </c>
-      <c r="S48">
-        <v>1.36</v>
-      </c>
-      <c r="T48">
-        <v>2.88</v>
-      </c>
       <c r="U48">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V48">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z48">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA48">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB48">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC48">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF48">
         <v>1.77</v>
       </c>
       <c r="AG48">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="O49">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R49">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T49">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="V49">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>5.4</v>
+        <v>5.15</v>
       </c>
       <c r="AA49">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB49">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AC49">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AD49">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AE49">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG49">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK49">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>2.12</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
         <v>2.93</v>
@@ -8634,25 +8634,25 @@
         <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S51">
         <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U51">
         <v>2.6</v>
       </c>
       <c r="V51">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
@@ -8661,25 +8661,25 @@
         <v>3.74</v>
       </c>
       <c r="AA51">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC51">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE51">
         <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,52 +8785,52 @@
         </is>
       </c>
       <c r="N52">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="O52">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="P52">
         <v>1.7</v>
       </c>
       <c r="Q52">
-        <v>4.72</v>
+        <v>3.95</v>
       </c>
       <c r="R52">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
         <v>3.34</v>
       </c>
       <c r="U52">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AB52">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC52">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="AD52">
         <v>1.42</v>
@@ -8839,10 +8839,10 @@
         <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="AK52">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8963,16 +8963,16 @@
         <v>2.07</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U53">
         <v>2.81</v>
       </c>
       <c r="V53">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W53">
         <v>1.07</v>
@@ -8987,10 +8987,10 @@
         <v>3.14</v>
       </c>
       <c r="AA53">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB53">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
         <v>3.28</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,61 +9111,61 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O54">
         <v>3.45</v>
       </c>
       <c r="P54">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q54">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R54">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S54">
         <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z54">
         <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC54">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="AD54">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG54">
         <v>2.3</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK54">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="O57">
         <v>4</v>
       </c>
       <c r="P57">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="Q57">
         <v>2.05</v>
       </c>
       <c r="R57">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="S57">
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V57">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9636,10 +9636,10 @@
         <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>5.13</v>
+        <v>4.95</v>
       </c>
       <c r="AA57">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB57">
         <v>2.5</v>
@@ -9651,13 +9651,13 @@
         <v>1.61</v>
       </c>
       <c r="AE57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
         <v>1.5</v>
       </c>
       <c r="AG57">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK57">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10261,46 +10261,46 @@
         <v>1.27</v>
       </c>
       <c r="Q61">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R61">
         <v>2.7</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U61">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>5.46</v>
+        <v>5.3</v>
       </c>
       <c r="AA61">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
         <v>2.59</v>
       </c>
       <c r="AC61">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD61">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE61">
         <v>1.28</v>
@@ -10309,7 +10309,7 @@
         <v>1.76</v>
       </c>
       <c r="AG61">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="O62">
-        <v>5.86</v>
+        <v>5.25</v>
       </c>
       <c r="P62">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="Q62">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R62">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="S62">
         <v>1.2</v>
@@ -10439,19 +10439,19 @@
         <v>2.05</v>
       </c>
       <c r="V62">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA62">
         <v>1.45</v>
@@ -10463,7 +10463,7 @@
         <v>2.08</v>
       </c>
       <c r="AD62">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE62">
         <v>1.24</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK62">
         <v>3.35</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="R63">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S63">
         <v>1.55</v>
@@ -10602,10 +10602,10 @@
         <v>3.58</v>
       </c>
       <c r="V63">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W63">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
         <v>1.05</v>
@@ -10617,13 +10617,13 @@
         <v>2.44</v>
       </c>
       <c r="AA63">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AB63">
         <v>1.5</v>
       </c>
       <c r="AC63">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD63">
         <v>1.1</v>
@@ -10632,10 +10632,10 @@
         <v>1.01</v>
       </c>
       <c r="AF63">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG63">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="AK63">
         <v>1.12</v>
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R64">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S64">
         <v>1.5</v>
@@ -10762,43 +10762,43 @@
         <v>2.5</v>
       </c>
       <c r="U64">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V64">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W64">
         <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y64">
         <v>1.44</v>
       </c>
       <c r="Z64">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AA64">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB64">
         <v>1.5</v>
       </c>
       <c r="AC64">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD64">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE64">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG64">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK64">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q65">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="R65">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S65">
+        <v>1.24</v>
+      </c>
+      <c r="T65">
+        <v>3.34</v>
+      </c>
+      <c r="U65">
+        <v>2.25</v>
+      </c>
+      <c r="V65">
+        <v>1.5</v>
+      </c>
+      <c r="W65">
+        <v>1.1</v>
+      </c>
+      <c r="X65">
+        <v>1.02</v>
+      </c>
+      <c r="Y65">
+        <v>1.16</v>
+      </c>
+      <c r="Z65">
+        <v>4.89</v>
+      </c>
+      <c r="AA65">
+        <v>1.56</v>
+      </c>
+      <c r="AB65">
+        <v>2.55</v>
+      </c>
+      <c r="AC65">
+        <v>2.38</v>
+      </c>
+      <c r="AD65">
+        <v>1.53</v>
+      </c>
+      <c r="AE65">
+        <v>1.17</v>
+      </c>
+      <c r="AF65">
+        <v>1.53</v>
+      </c>
+      <c r="AG65">
+        <v>2.28</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.22</v>
       </c>
-      <c r="T65">
-        <v>3.5</v>
-      </c>
-      <c r="U65">
-        <v>2.2</v>
-      </c>
-      <c r="V65">
+      <c r="AK65">
         <v>1.59</v>
-      </c>
-      <c r="W65">
-        <v>1.11</v>
-      </c>
-      <c r="X65">
-        <v>1.01</v>
-      </c>
-      <c r="Y65">
-        <v>1.1</v>
-      </c>
-      <c r="Z65">
-        <v>5.05</v>
-      </c>
-      <c r="AA65">
-        <v>1.6</v>
-      </c>
-      <c r="AB65">
-        <v>2.15</v>
-      </c>
-      <c r="AC65">
-        <v>2.45</v>
-      </c>
-      <c r="AD65">
-        <v>1.46</v>
-      </c>
-      <c r="AE65">
-        <v>1.19</v>
-      </c>
-      <c r="AF65">
-        <v>1.44</v>
-      </c>
-      <c r="AG65">
-        <v>2.56</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.2</v>
-      </c>
-      <c r="AK65">
-        <v>1.72</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,37 +11070,37 @@
         <v>1.75</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q66">
         <v>2.29</v>
       </c>
       <c r="R66">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
         <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U66">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V66">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W66">
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
         <v>3.78</v>
@@ -11109,7 +11109,7 @@
         <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC66">
         <v>2.76</v>
@@ -11121,7 +11121,7 @@
         <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG66">
         <v>2.1</v>
@@ -11140,7 +11140,7 @@
         <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O67">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11393,28 +11393,28 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O68">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="P68">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q68">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="R68">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="S68">
         <v>1.46</v>
       </c>
       <c r="T68">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="U68">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="V68">
         <v>1.28</v>
@@ -11423,28 +11423,28 @@
         <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
         <v>1.37</v>
       </c>
       <c r="Z68">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA68">
         <v>2.25</v>
       </c>
       <c r="AB68">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC68">
         <v>4.2</v>
       </c>
       <c r="AD68">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF68">
         <v>1.89</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AK68">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O69">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P69">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="Q69">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R69">
         <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T69">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U69">
         <v>2.75</v>
@@ -11586,7 +11586,7 @@
         <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
         <v>1.25</v>
@@ -11595,25 +11595,25 @@
         <v>3.3</v>
       </c>
       <c r="AA69">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC69">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE69">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
         <v>1.84</v>
       </c>
       <c r="AG69">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK69">
         <v>2.05</v>
@@ -11719,28 +11719,28 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="O70">
         <v>3</v>
       </c>
       <c r="P70">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q70">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R70">
         <v>2.03</v>
       </c>
       <c r="S70">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T70">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U70">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="V70">
         <v>1.32</v>
@@ -11752,31 +11752,31 @@
         <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z70">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="AA70">
         <v>2.07</v>
       </c>
       <c r="AB70">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC70">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD70">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF70">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG70">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.29</v>
       </c>
       <c r="AK70">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
         <v>4.2</v>
       </c>
       <c r="Q73">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="R73">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S73">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T73">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U73">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="V73">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z73">
         <v>3.3</v>
       </c>
       <c r="AA73">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC73">
-        <v>3.57</v>
+        <v>3.35</v>
       </c>
       <c r="AD73">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE73">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF73">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG73">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,34 +12371,34 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="O74">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="P74">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q74">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R74">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="S74">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T74">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="U74">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V74">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W74">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12407,7 +12407,7 @@
         <v>1.08</v>
       </c>
       <c r="Z74">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AA74">
         <v>1.43</v>
@@ -12419,16 +12419,16 @@
         <v>2</v>
       </c>
       <c r="AD74">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE74">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF74">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AK74">
         <v>2.53</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O76">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="P76">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="Q76">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U76">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="V76">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X76">
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z76">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA76">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB76">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC76">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD76">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE76">
         <v>1.18</v>
       </c>
       <c r="AF76">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG76">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="O77">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P77">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="Q77">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R77">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S77">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U77">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="V77">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W77">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z77">
-        <v>5.75</v>
+        <v>5.84</v>
       </c>
       <c r="AA77">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB77">
         <v>2.7</v>
       </c>
       <c r="AC77">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD77">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE77">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF77">
         <v>1.42</v>
       </c>
       <c r="AG77">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK77">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P78">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="Q78">
         <v>2.15</v>
       </c>
       <c r="R78">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T78">
         <v>4.2</v>
       </c>
       <c r="U78">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V78">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W78">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z78">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA78">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB78">
         <v>3</v>
       </c>
       <c r="AC78">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE78">
         <v>1.27</v>
       </c>
       <c r="AF78">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG78">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,25 +13186,25 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="P79">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q79">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R79">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="S79">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T79">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U79">
         <v>2.08</v>
@@ -13213,19 +13213,19 @@
         <v>1.69</v>
       </c>
       <c r="W79">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z79">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA79">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB79">
         <v>2.8</v>
@@ -13234,16 +13234,16 @@
         <v>2.1</v>
       </c>
       <c r="AD79">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE79">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF79">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG79">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13352,16 +13352,16 @@
         <v>2.1</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P80">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="Q80">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R80">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="S80">
         <v>1.24</v>
@@ -13376,13 +13376,13 @@
         <v>1.59</v>
       </c>
       <c r="W80">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X80">
         <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z80">
         <v>4.65</v>
@@ -13391,19 +13391,19 @@
         <v>1.53</v>
       </c>
       <c r="AB80">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC80">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD80">
         <v>1.57</v>
       </c>
       <c r="AE80">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF80">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG80">
         <v>2.53</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O81">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
         <v>3.6</v>
@@ -13527,49 +13527,49 @@
         <v>2.49</v>
       </c>
       <c r="S81">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
         <v>3.44</v>
       </c>
       <c r="U81">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="V81">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W81">
         <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z81">
         <v>4.85</v>
       </c>
       <c r="AA81">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB81">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AC81">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD81">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE81">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG81">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
         <v>1.93</v>
@@ -13675,52 +13675,52 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O82">
+        <v>3.5</v>
+      </c>
+      <c r="P82">
+        <v>2.2</v>
+      </c>
+      <c r="Q82">
+        <v>3.3</v>
+      </c>
+      <c r="R82">
+        <v>2.25</v>
+      </c>
+      <c r="S82">
+        <v>1.25</v>
+      </c>
+      <c r="T82">
         <v>3.6</v>
       </c>
-      <c r="P82">
-        <v>2.25</v>
-      </c>
-      <c r="Q82">
-        <v>3.44</v>
-      </c>
-      <c r="R82">
-        <v>2.26</v>
-      </c>
-      <c r="S82">
-        <v>1.27</v>
-      </c>
-      <c r="T82">
-        <v>3.35</v>
-      </c>
       <c r="U82">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="V82">
         <v>1.51</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="AA82">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB82">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC82">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AD82">
         <v>1.43</v>
@@ -13729,7 +13729,7 @@
         <v>1.2</v>
       </c>
       <c r="AF82">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG82">
         <v>2.45</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14010,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R84">
         <v>2.28</v>
@@ -14019,10 +14019,10 @@
         <v>1.23</v>
       </c>
       <c r="T84">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U84">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V84">
         <v>1.56</v>
@@ -14046,7 +14046,7 @@
         <v>2.45</v>
       </c>
       <c r="AC84">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AD84">
         <v>1.54</v>
@@ -14055,10 +14055,10 @@
         <v>1.19</v>
       </c>
       <c r="AF84">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG84">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.83</v>
+        <v>1.19</v>
       </c>
       <c r="AK84">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="O85">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q85">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R85">
         <v>2.56</v>
@@ -14188,7 +14188,7 @@
         <v>2.1</v>
       </c>
       <c r="V85">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W85">
         <v>1.14</v>
@@ -14200,22 +14200,22 @@
         <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA85">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB85">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC85">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD85">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE85">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF85">
         <v>1.42</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK85">
         <v>1.8</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O86">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P86">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q86">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R86">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T86">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="U86">
         <v>2.05</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W86">
         <v>1.14</v>
@@ -14360,31 +14360,31 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA86">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB86">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AC86">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AD86">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE86">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
         <v>1.79</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P87">
         <v>5.75</v>
       </c>
       <c r="Q87">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="R87">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T87">
         <v>2.88</v>
       </c>
       <c r="U87">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V87">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W87">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA87">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB87">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC87">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD87">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE87">
         <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG87">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14659,19 +14659,19 @@
         <v>3.42</v>
       </c>
       <c r="P88">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="R88">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S88">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T88">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="U88">
         <v>3.22</v>
@@ -14680,19 +14680,19 @@
         <v>1.3</v>
       </c>
       <c r="W88">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X88">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y88">
         <v>1.37</v>
       </c>
       <c r="Z88">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AA88">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AB88">
         <v>1.57</v>
@@ -14704,13 +14704,13 @@
         <v>1.2</v>
       </c>
       <c r="AE88">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF88">
         <v>2.05</v>
       </c>
       <c r="AG88">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK88">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14828,7 +14828,7 @@
         <v>2.6</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
         <v>1.36</v>
@@ -14840,31 +14840,31 @@
         <v>2.69</v>
       </c>
       <c r="V89">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W89">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z89">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA89">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB89">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC89">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AD89">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE89">
         <v>1.09</v>
@@ -14873,7 +14873,7 @@
         <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,40 +14979,40 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O90">
         <v>3.3</v>
       </c>
       <c r="P90">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q90">
         <v>3</v>
       </c>
       <c r="R90">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="S90">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T90">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U90">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="V90">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W90">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z90">
         <v>3.34</v>
@@ -15021,22 +15021,22 @@
         <v>1.85</v>
       </c>
       <c r="AB90">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC90">
         <v>2.9</v>
       </c>
       <c r="AD90">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE90">
         <v>1.07</v>
       </c>
       <c r="AF90">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
         <v>1.44</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB91">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15308,25 +15308,25 @@
         <v>1.5</v>
       </c>
       <c r="O92">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="P92">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="Q92">
         <v>1.98</v>
       </c>
       <c r="R92">
-        <v>2.53</v>
+        <v>2.21</v>
       </c>
       <c r="S92">
         <v>1.28</v>
       </c>
       <c r="T92">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U92">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="V92">
         <v>1.5</v>
@@ -15335,13 +15335,13 @@
         <v>1.09</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
         <v>1.21</v>
       </c>
       <c r="Z92">
-        <v>4.31</v>
+        <v>4.05</v>
       </c>
       <c r="AA92">
         <v>1.66</v>
@@ -15356,10 +15356,10 @@
         <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF92">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG92">
         <v>1.97</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK92">
         <v>2.32</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15797,37 +15797,37 @@
         <v>1.28</v>
       </c>
       <c r="O95">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="P95">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q95">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R95">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="S95">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T95">
         <v>5.5</v>
       </c>
       <c r="U95">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V95">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="W95">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z95">
         <v>10</v>
@@ -15836,16 +15836,16 @@
         <v>1.18</v>
       </c>
       <c r="AB95">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC95">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD95">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AE95">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AF95">
         <v>1.44</v>
@@ -15957,34 +15957,34 @@
         </is>
       </c>
       <c r="N96">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O96">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q96">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R96">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="S96">
         <v>1.38</v>
       </c>
       <c r="T96">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U96">
         <v>2.9</v>
       </c>
       <c r="V96">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W96">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15996,7 +15996,7 @@
         <v>3.06</v>
       </c>
       <c r="AA96">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AB96">
         <v>1.71</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,16 +16120,16 @@
         </is>
       </c>
       <c r="N97">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="O97">
-        <v>5.05</v>
+        <v>4.5</v>
       </c>
       <c r="P97">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q97">
-        <v>7.74</v>
+        <v>7</v>
       </c>
       <c r="R97">
         <v>2.43</v>
@@ -16147,7 +16147,7 @@
         <v>1.5</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X97">
         <v>1.02</v>
@@ -16165,16 +16165,16 @@
         <v>2.11</v>
       </c>
       <c r="AC97">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AD97">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE97">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF97">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG97">
         <v>1.85</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK97">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16286,28 +16286,28 @@
         <v>4.33</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P98">
         <v>1.75</v>
       </c>
       <c r="Q98">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="R98">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S98">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T98">
         <v>3.25</v>
       </c>
       <c r="U98">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="V98">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W98">
         <v>1.09</v>
@@ -16322,25 +16322,25 @@
         <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB98">
+        <v>2.14</v>
+      </c>
+      <c r="AC98">
+        <v>2.8</v>
+      </c>
+      <c r="AD98">
+        <v>1.42</v>
+      </c>
+      <c r="AE98">
+        <v>1.13</v>
+      </c>
+      <c r="AF98">
+        <v>1.65</v>
+      </c>
+      <c r="AG98">
         <v>2.1</v>
-      </c>
-      <c r="AC98">
-        <v>2.87</v>
-      </c>
-      <c r="AD98">
-        <v>1.44</v>
-      </c>
-      <c r="AE98">
-        <v>1.14</v>
-      </c>
-      <c r="AF98">
-        <v>1.68</v>
-      </c>
-      <c r="AG98">
-        <v>2.08</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.21</v>
       </c>
       <c r="AK98">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17753,61 +17753,61 @@
         <v>1.36</v>
       </c>
       <c r="O107">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P107">
         <v>8</v>
       </c>
       <c r="Q107">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R107">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U107">
         <v>2.68</v>
       </c>
       <c r="V107">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z107">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="AA107">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB107">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AC107">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="AD107">
         <v>1.35</v>
       </c>
       <c r="AE107">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG107">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK107">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O108">
-        <v>4.1</v>
+        <v>4.58</v>
       </c>
       <c r="P108">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB108">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18239,19 +18239,19 @@
         </is>
       </c>
       <c r="N110">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="O110">
         <v>4.15</v>
       </c>
       <c r="P110">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q110">
-        <v>5.49</v>
+        <v>5.44</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S110">
         <v>1.29</v>
@@ -18266,25 +18266,25 @@
         <v>1.53</v>
       </c>
       <c r="W110">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
         <v>1.18</v>
       </c>
       <c r="Z110">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA110">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB110">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC110">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD110">
         <v>1.44</v>
@@ -18293,10 +18293,10 @@
         <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG110">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AK110">
         <v>1.18</v>
@@ -18565,58 +18565,58 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O112">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="P112">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q112">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R112">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S112">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
         <v>2.75</v>
       </c>
       <c r="U112">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V112">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X112">
         <v>1.05</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z112">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AA112">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AB112">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC112">
-        <v>3.85</v>
+        <v>4.36</v>
       </c>
       <c r="AD112">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE112">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF112">
         <v>1.91</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,16 +18728,16 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P113">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q113">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="R113">
         <v>2.05</v>
@@ -18746,7 +18746,7 @@
         <v>1.36</v>
       </c>
       <c r="T113">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U113">
         <v>2.85</v>
@@ -18761,31 +18761,31 @@
         <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="AA113">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB113">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC113">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="AD113">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE113">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,55 +19389,55 @@
         <v>0</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,55 +19552,55 @@
         <v>0</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,19 +19706,19 @@
         </is>
       </c>
       <c r="N119">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O119">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P119">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q119">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="R119">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="S119">
         <v>1.21</v>
@@ -19730,10 +19730,10 @@
         <v>2.2</v>
       </c>
       <c r="V119">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W119">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X119">
         <v>1.02</v>
@@ -19745,25 +19745,25 @@
         <v>4.7</v>
       </c>
       <c r="AA119">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB119">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AC119">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD119">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE119">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF119">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AG119">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK119">
         <v>1.05</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O120">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="P120">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q120">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="R120">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S120">
         <v>1.38</v>
@@ -19893,40 +19893,40 @@
         <v>2.65</v>
       </c>
       <c r="V120">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W120">
         <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z120">
-        <v>4.08</v>
+        <v>3.64</v>
       </c>
       <c r="AA120">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB120">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC120">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AD120">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE120">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF120">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AG120">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AK120">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="R121">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T121">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="U121">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V121">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W121">
         <v>1.04</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z121">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA121">
         <v>2.38</v>
       </c>
       <c r="AB121">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC121">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD121">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE121">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF121">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG121">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK121">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20361,16 +20361,16 @@
         <v>2.6</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P123">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
       </c>
       <c r="R123">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
         <v>1.3</v>
@@ -20379,7 +20379,7 @@
         <v>3.2</v>
       </c>
       <c r="U123">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="V123">
         <v>1.45</v>
@@ -20391,16 +20391,16 @@
         <v>1.03</v>
       </c>
       <c r="Y123">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z123">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA123">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB123">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC123">
         <v>2.8</v>
@@ -20409,10 +20409,10 @@
         <v>1.37</v>
       </c>
       <c r="AE123">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG123">
         <v>2.17</v>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,43 +20521,43 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P124">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q124">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R124">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T124">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U124">
         <v>3.16</v>
       </c>
       <c r="V124">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W124">
+        <v>1.01</v>
+      </c>
+      <c r="X124">
         <v>1.05</v>
       </c>
-      <c r="X124">
-        <v>1.02</v>
-      </c>
       <c r="Y124">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z124">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AA124">
         <v>2.23</v>
@@ -20572,7 +20572,7 @@
         <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
         <v>1.93</v>
@@ -20594,7 +20594,7 @@
         <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21013,25 +21013,25 @@
         <v>2</v>
       </c>
       <c r="O127">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P127">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q127">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R127">
         <v>1.92</v>
       </c>
       <c r="S127">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T127">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U127">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V127">
         <v>1.31</v>
@@ -21049,22 +21049,22 @@
         <v>2.83</v>
       </c>
       <c r="AA127">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB127">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC127">
-        <v>3.84</v>
+        <v>4.26</v>
       </c>
       <c r="AD127">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE127">
         <v>1.04</v>
       </c>
       <c r="AF127">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG127">
         <v>1.81</v>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK127">
         <v>1.7</v>
@@ -21182,22 +21182,22 @@
         <v>4.4</v>
       </c>
       <c r="Q128">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R128">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S128">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T128">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="U128">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="V128">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W128">
         <v>1.04</v>
@@ -21206,19 +21206,19 @@
         <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z128">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA128">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB128">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC128">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="AD128">
         <v>1.23</v>
@@ -21227,10 +21227,10 @@
         <v>1.05</v>
       </c>
       <c r="AF128">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG128">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK128">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.16</v>
+        <v>5.75</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P2">
-        <v>2.46</v>
+        <v>1.4</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>6.21</v>
       </c>
       <c r="R2">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W2">
+        <v>1.15</v>
+      </c>
+      <c r="X2">
+        <v>1.01</v>
+      </c>
+      <c r="Y2">
+        <v>1.16</v>
+      </c>
+      <c r="Z2">
+        <v>5.15</v>
+      </c>
+      <c r="AA2">
+        <v>1.49</v>
+      </c>
+      <c r="AB2">
+        <v>2.55</v>
+      </c>
+      <c r="AC2">
+        <v>2.28</v>
+      </c>
+      <c r="AD2">
+        <v>1.58</v>
+      </c>
+      <c r="AE2">
+        <v>1.19</v>
+      </c>
+      <c r="AF2">
+        <v>1.62</v>
+      </c>
+      <c r="AG2">
+        <v>2.15</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.14</v>
+      </c>
+      <c r="AK2">
         <v>1.11</v>
-      </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
-      <c r="Y2">
-        <v>1.18</v>
-      </c>
-      <c r="Z2">
-        <v>3.95</v>
-      </c>
-      <c r="AA2">
-        <v>1.7</v>
-      </c>
-      <c r="AB2">
-        <v>2.03</v>
-      </c>
-      <c r="AC2">
-        <v>2.66</v>
-      </c>
-      <c r="AD2">
-        <v>1.37</v>
-      </c>
-      <c r="AE2">
-        <v>1.12</v>
-      </c>
-      <c r="AF2">
-        <v>1.57</v>
-      </c>
-      <c r="AG2">
-        <v>2.3</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.36</v>
-      </c>
-      <c r="AK2">
-        <v>1.48</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>5.75</v>
+        <v>2.17</v>
       </c>
       <c r="O3">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S3">
+        <v>1.3</v>
+      </c>
+      <c r="T3">
+        <v>3.08</v>
+      </c>
+      <c r="U3">
+        <v>2.47</v>
+      </c>
+      <c r="V3">
+        <v>1.48</v>
+      </c>
+      <c r="W3">
+        <v>1.11</v>
+      </c>
+      <c r="X3">
+        <v>1.04</v>
+      </c>
+      <c r="Y3">
+        <v>1.19</v>
+      </c>
+      <c r="Z3">
+        <v>3.8</v>
+      </c>
+      <c r="AA3">
+        <v>1.73</v>
+      </c>
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>2.48</v>
+      </c>
+      <c r="AD3">
+        <v>1.43</v>
+      </c>
+      <c r="AE3">
+        <v>1.12</v>
+      </c>
+      <c r="AF3">
+        <v>1.57</v>
+      </c>
+      <c r="AG3">
+        <v>2.2</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.22</v>
       </c>
-      <c r="T3">
-        <v>3.6</v>
-      </c>
-      <c r="U3">
-        <v>2.1</v>
-      </c>
-      <c r="V3">
-        <v>1.65</v>
-      </c>
-      <c r="W3">
-        <v>1.14</v>
-      </c>
-      <c r="X3">
-        <v>1.02</v>
-      </c>
-      <c r="Y3">
-        <v>1.16</v>
-      </c>
-      <c r="Z3">
-        <v>5.01</v>
-      </c>
-      <c r="AA3">
-        <v>1.5</v>
-      </c>
-      <c r="AB3">
-        <v>2.55</v>
-      </c>
-      <c r="AC3">
-        <v>2.28</v>
-      </c>
-      <c r="AD3">
-        <v>1.61</v>
-      </c>
-      <c r="AE3">
-        <v>1.23</v>
-      </c>
-      <c r="AF3">
-        <v>1.64</v>
-      </c>
-      <c r="AG3">
-        <v>2.1</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.12</v>
-      </c>
       <c r="AK3">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="O5">
         <v>3.9</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q5">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="U5">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
         <v>1.68</v>
@@ -1157,31 +1157,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA5">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB5">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AE5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG5">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,43 +1287,43 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="O6">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="Q6">
         <v>2.06</v>
       </c>
       <c r="R6">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S6">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T6">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="W6">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z6">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA6">
         <v>1.21</v>
@@ -1335,16 +1335,16 @@
         <v>1.68</v>
       </c>
       <c r="AD6">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AE6">
         <v>1.44</v>
       </c>
       <c r="AF6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AG6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q7">
         <v>3.54</v>
@@ -1468,16 +1468,16 @@
         <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V7">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1486,28 +1486,28 @@
         <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA7">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AC7">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AD7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE7">
         <v>1.21</v>
       </c>
       <c r="AF7">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="AK7">
         <v>1.21</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="O25">
         <v>3.55</v>
@@ -4399,28 +4399,28 @@
         <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U25">
         <v>2.44</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA25">
         <v>1.7</v>
@@ -4441,7 +4441,7 @@
         <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
+        <v>2.3</v>
+      </c>
+      <c r="O27">
+        <v>3.25</v>
+      </c>
+      <c r="P27">
+        <v>3.2</v>
+      </c>
+      <c r="Q27">
+        <v>2.7</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>1.4</v>
+      </c>
+      <c r="T27">
+        <v>2.75</v>
+      </c>
+      <c r="U27">
+        <v>3.07</v>
+      </c>
+      <c r="V27">
+        <v>1.33</v>
+      </c>
+      <c r="W27">
+        <v>1.05</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.33</v>
+      </c>
+      <c r="Z27">
+        <v>3.1</v>
+      </c>
+      <c r="AA27">
         <v>2.09</v>
       </c>
-      <c r="O27">
-        <v>3.4</v>
-      </c>
-      <c r="P27">
-        <v>3.6</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -8643,10 +8643,10 @@
         <v>3</v>
       </c>
       <c r="U51">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
         <v>1.08</v>
@@ -8664,22 +8664,22 @@
         <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="AD51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
         <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
         <v>1.7</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>9.4</v>
+        <v>1.27</v>
       </c>
       <c r="O61">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P61">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q61">
-        <v>7</v>
+        <v>1.62</v>
       </c>
       <c r="R61">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="S61">
         <v>1.17</v>
       </c>
       <c r="T61">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="AC61">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AD61">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG61">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="AK61">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>8</v>
+      </c>
+      <c r="O62">
+        <v>5.5</v>
+      </c>
+      <c r="P62">
         <v>1.27</v>
       </c>
-      <c r="O62">
-        <v>5.25</v>
-      </c>
-      <c r="P62">
-        <v>7.5</v>
-      </c>
       <c r="Q62">
-        <v>1.66</v>
+        <v>7</v>
       </c>
       <c r="R62">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T62">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="U62">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V62">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA62">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AC62">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE62">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG62">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="AK62">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q81">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="R81">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="S81">
         <v>1.25</v>
       </c>
       <c r="T81">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="V81">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W81">
         <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z81">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AA81">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB81">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AD81">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE81">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF81">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q82">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="S82">
         <v>1.25</v>
       </c>
       <c r="T82">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U82">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V82">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W82">
         <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="AA82">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB82">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AC82">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD82">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AE82">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF82">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.38</v>
+        <v>1.93</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G85">
@@ -14167,28 +14167,28 @@
         <v>1.93</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P85">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q85">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R85">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T85">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
         <v>1.14</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA85">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AB85">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AC85">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD85">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE85">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G86">
@@ -14330,28 +14330,28 @@
         <v>1.93</v>
       </c>
       <c r="O86">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q86">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S86">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W86">
         <v>1.14</v>
@@ -14360,31 +14360,31 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA86">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AB86">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC86">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD86">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE86">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG86">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK86">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O99">
         <v>5.3</v>
       </c>
       <c r="P99">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q99">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R99">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="S99">
         <v>1.24</v>
@@ -16467,10 +16467,10 @@
         <v>3.5</v>
       </c>
       <c r="U99">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V99">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W99">
         <v>1.13</v>
@@ -16482,7 +16482,7 @@
         <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA99">
         <v>1.49</v>
@@ -16491,7 +16491,7 @@
         <v>2.4</v>
       </c>
       <c r="AC99">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD99">
         <v>1.58</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK99">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16612,49 +16612,49 @@
         <v>2.55</v>
       </c>
       <c r="O100">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
         <v>2.4</v>
       </c>
       <c r="Q100">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R100">
         <v>2.12</v>
       </c>
       <c r="S100">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T100">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="U100">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V100">
         <v>1.45</v>
       </c>
       <c r="W100">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="AA100">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB100">
         <v>2.03</v>
       </c>
       <c r="AC100">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AD100">
         <v>1.36</v>
@@ -16663,10 +16663,10 @@
         <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG100">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK100">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,10 +16781,10 @@
         <v>6.5</v>
       </c>
       <c r="Q101">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R101">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
         <v>1.25</v>
@@ -16793,43 +16793,43 @@
         <v>3.5</v>
       </c>
       <c r="U101">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V101">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W101">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA101">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AB101">
+        <v>2.4</v>
+      </c>
+      <c r="AC101">
         <v>2.35</v>
-      </c>
-      <c r="AC101">
-        <v>2.38</v>
       </c>
       <c r="AD101">
         <v>1.56</v>
       </c>
       <c r="AE101">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF101">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG101">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK101">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="O102">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17104,10 +17104,10 @@
         <v>3.3</v>
       </c>
       <c r="P103">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q103">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R103">
         <v>2.25</v>
@@ -17125,16 +17125,16 @@
         <v>1.46</v>
       </c>
       <c r="W103">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X103">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z103">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="AA103">
         <v>1.66</v>
@@ -17143,19 +17143,19 @@
         <v>2.16</v>
       </c>
       <c r="AC103">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD103">
         <v>1.45</v>
       </c>
       <c r="AE103">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF103">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.22</v>
       </c>
       <c r="AK103">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="O104">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="P104">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="Q104">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="R104">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="S104">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U104">
         <v>2.2</v>
       </c>
       <c r="V104">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W104">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z104">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA104">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
         <v>2.3</v>
       </c>
       <c r="AC104">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD104">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE104">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF104">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK104">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="O105">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
-        <v>8.550000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="Q105">
-        <v>1.65</v>
+        <v>2.77</v>
       </c>
       <c r="R105">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="U105">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="V105">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AB105">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="AC105">
-        <v>1.99</v>
+        <v>2.8</v>
       </c>
       <c r="AD105">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="P106">
-        <v>2.62</v>
+        <v>7.8</v>
       </c>
       <c r="Q106">
-        <v>2.92</v>
+        <v>1.62</v>
       </c>
       <c r="R106">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T106">
-        <v>2.91</v>
+        <v>3.88</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="V106">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA106">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AB106">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="AC106">
-        <v>3.04</v>
+        <v>1.96</v>
       </c>
       <c r="AD106">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AE106">
+        <v>1.33</v>
+      </c>
+      <c r="AF106">
+        <v>1.75</v>
+      </c>
+      <c r="AG106">
+        <v>1.95</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.07</v>
       </c>
-      <c r="AF106">
-        <v>1.64</v>
-      </c>
-      <c r="AG106">
-        <v>2.1</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.24</v>
-      </c>
       <c r="AK106">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O111">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P111">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q111">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="R111">
         <v>2.2</v>
       </c>
       <c r="S111">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T111">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U111">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V111">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z111">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="AA111">
         <v>1.75</v>
       </c>
       <c r="AB111">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC111">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AD111">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE111">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF111">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG111">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -19878,19 +19878,19 @@
         <v>2.18</v>
       </c>
       <c r="Q120">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="R120">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
         <v>1.38</v>
       </c>
       <c r="T120">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U120">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V120">
         <v>1.41</v>
@@ -19902,7 +19902,7 @@
         <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
         <v>3.64</v>
@@ -19914,7 +19914,7 @@
         <v>2</v>
       </c>
       <c r="AC120">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AD120">
         <v>1.38</v>
@@ -19942,7 +19942,7 @@
         <v>1.62</v>
       </c>
       <c r="AK120">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20198,7 +20198,7 @@
         <v>1.53</v>
       </c>
       <c r="O122">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P122">
         <v>5.25</v>
@@ -20237,7 +20237,7 @@
         <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC122">
         <v>3.47</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O125">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P125">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20853,7 +20853,7 @@
         <v>3.6</v>
       </c>
       <c r="P126">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O129">
         <v>2.87</v>
       </c>
       <c r="P129">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q129">
         <v>2.9</v>
       </c>
       <c r="R129">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="S129">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T129">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U129">
         <v>3.48</v>
       </c>
       <c r="V129">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W129">
         <v>1.04</v>
       </c>
       <c r="X129">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y129">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z129">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AA129">
         <v>2.55</v>
       </c>
       <c r="AB129">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC129">
-        <v>4.68</v>
+        <v>4.75</v>
       </c>
       <c r="AD129">
         <v>1.13</v>
       </c>
       <c r="AE129">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF129">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AG129">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>1.36</v>
       </c>
       <c r="AK129">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,25 +21508,25 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R130">
         <v>2.29</v>
       </c>
       <c r="S130">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T130">
         <v>2.97</v>
       </c>
       <c r="U130">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="V130">
         <v>1.43</v>
       </c>
       <c r="W130">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
         <v>1.01</v>
@@ -21535,28 +21535,28 @@
         <v>1.21</v>
       </c>
       <c r="Z130">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA130">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB130">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC130">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AD130">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE130">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF130">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK130">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21843,7 +21843,7 @@
         <v>1.57</v>
       </c>
       <c r="T132">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U132">
         <v>3.58</v>
@@ -21855,22 +21855,22 @@
         <v>1.03</v>
       </c>
       <c r="X132">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y132">
         <v>1.5</v>
       </c>
       <c r="Z132">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AA132">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AB132">
         <v>1.44</v>
       </c>
       <c r="AC132">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AD132">
         <v>1.13</v>
@@ -21898,7 +21898,7 @@
         <v>1.18</v>
       </c>
       <c r="AK132">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22003,19 +22003,19 @@
         <v>2.41</v>
       </c>
       <c r="S133">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T133">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U133">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V133">
         <v>1.57</v>
       </c>
       <c r="W133">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X133">
         <v>1.02</v>
@@ -22039,13 +22039,13 @@
         <v>1.52</v>
       </c>
       <c r="AE133">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF133">
         <v>1.6</v>
       </c>
       <c r="AG133">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK133">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL133">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>6.7</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>1.31</v>
+        <v>2.62</v>
       </c>
       <c r="Q38">
-        <v>5.42</v>
+        <v>2.74</v>
       </c>
       <c r="R38">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="U38">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA38">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
+        <v>2.15</v>
+      </c>
+      <c r="AC38">
         <v>2.62</v>
       </c>
-      <c r="AC38">
-        <v>2.19</v>
-      </c>
       <c r="AD38">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="Q39">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="AA39">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AC39">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AD39">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AF39">
+        <v>1.42</v>
+      </c>
+      <c r="AG39">
+        <v>2.66</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.19</v>
+      </c>
+      <c r="AK39">
         <v>1.6</v>
-      </c>
-      <c r="AG39">
-        <v>2.28</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.26</v>
-      </c>
-      <c r="AK39">
-        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.05</v>
+        <v>6.7</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P40">
-        <v>2.87</v>
+        <v>1.31</v>
       </c>
       <c r="Q40">
-        <v>2.35</v>
+        <v>5.42</v>
       </c>
       <c r="R40">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z40">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AB40">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AC40">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD40">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE40">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AK40">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>8</v>
+      </c>
+      <c r="O61">
+        <v>5.5</v>
+      </c>
+      <c r="P61">
         <v>1.27</v>
       </c>
-      <c r="O61">
-        <v>5.3</v>
-      </c>
-      <c r="P61">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Q61">
-        <v>1.62</v>
+        <v>7</v>
       </c>
       <c r="R61">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="S61">
         <v>1.17</v>
       </c>
       <c r="T61">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="U61">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V61">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AC61">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE61">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG61">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="AK61">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>8</v>
+        <v>1.27</v>
       </c>
       <c r="O62">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P62">
-        <v>1.27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q62">
-        <v>7</v>
+        <v>1.62</v>
       </c>
       <c r="R62">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="S62">
         <v>1.17</v>
       </c>
       <c r="T62">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="U62">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V62">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
+        <v>1.13</v>
+      </c>
+      <c r="Z62">
+        <v>5.9</v>
+      </c>
+      <c r="AA62">
+        <v>1.36</v>
+      </c>
+      <c r="AB62">
+        <v>2.72</v>
+      </c>
+      <c r="AC62">
+        <v>2.03</v>
+      </c>
+      <c r="AD62">
+        <v>1.74</v>
+      </c>
+      <c r="AE62">
+        <v>1.25</v>
+      </c>
+      <c r="AF62">
+        <v>1.73</v>
+      </c>
+      <c r="AG62">
+        <v>2.1</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.1</v>
       </c>
-      <c r="Z62">
-        <v>6.5</v>
-      </c>
-      <c r="AA62">
-        <v>1.4</v>
-      </c>
-      <c r="AB62">
-        <v>2.59</v>
-      </c>
-      <c r="AC62">
-        <v>2.09</v>
-      </c>
-      <c r="AD62">
-        <v>1.67</v>
-      </c>
-      <c r="AE62">
-        <v>1.29</v>
-      </c>
-      <c r="AF62">
-        <v>1.77</v>
-      </c>
-      <c r="AG62">
-        <v>1.92</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>3.7</v>
-      </c>
       <c r="AK62">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q81">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="S81">
         <v>1.25</v>
       </c>
       <c r="T81">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U81">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V81">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W81">
         <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z81">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="AA81">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB81">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AC81">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD81">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG81">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.38</v>
+        <v>1.93</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q82">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="R82">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
         <v>1.25</v>
       </c>
       <c r="T82">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U82">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="V82">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W82">
         <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="AA82">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB82">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AC82">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AD82">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE82">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF82">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG82">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.93</v>
+        <v>1.38</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.35</v>
+        <v>1.23</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="P105">
-        <v>2.62</v>
+        <v>7.8</v>
       </c>
       <c r="Q105">
-        <v>2.77</v>
+        <v>1.62</v>
       </c>
       <c r="R105">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T105">
-        <v>2.91</v>
+        <v>3.88</v>
       </c>
       <c r="U105">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="V105">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA105">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AB105">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="AC105">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE105">
+        <v>1.33</v>
+      </c>
+      <c r="AF105">
+        <v>1.75</v>
+      </c>
+      <c r="AG105">
+        <v>1.95</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.07</v>
       </c>
-      <c r="AF105">
-        <v>1.65</v>
-      </c>
-      <c r="AG105">
-        <v>2.05</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.24</v>
-      </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="O106">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="P106">
-        <v>7.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q106">
-        <v>1.62</v>
+        <v>2.77</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="S106">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>3.88</v>
+        <v>2.91</v>
       </c>
       <c r="U106">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="V106">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z106">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AB106">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC106">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="AD106">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>3.75</v>
+        <v>1.47</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -20524,19 +20524,19 @@
         <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P124">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q124">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="R124">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S124">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
         <v>2.65</v>
@@ -20551,34 +20551,34 @@
         <v>1.01</v>
       </c>
       <c r="X124">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
         <v>1.36</v>
       </c>
       <c r="Z124">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AA124">
         <v>2.23</v>
       </c>
       <c r="AB124">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC124">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AD124">
         <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF124">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG124">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK124">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O127">
         <v>3.2</v>
       </c>
       <c r="P127">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q127">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="R127">
         <v>1.92</v>
       </c>
       <c r="S127">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T127">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U127">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="V127">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W127">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y127">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z127">
         <v>2.83</v>
       </c>
       <c r="AA127">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB127">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC127">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="AD127">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE127">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF127">
         <v>1.85</v>
       </c>
       <c r="AG127">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O128">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P128">
         <v>4.4</v>
@@ -21191,22 +21191,22 @@
         <v>1.38</v>
       </c>
       <c r="T128">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="U128">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="V128">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W128">
         <v>1.04</v>
       </c>
       <c r="X128">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y128">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z128">
         <v>2.88</v>
@@ -21230,7 +21230,7 @@
         <v>1.95</v>
       </c>
       <c r="AG128">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.28</v>
       </c>
       <c r="AK128">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="O18">
         <v>2.6</v>
       </c>
       <c r="P18">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="Q18">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="R18">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="S18">
         <v>1.75</v>
@@ -3273,7 +3273,7 @@
         <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Y18">
         <v>1.83</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AK18">
         <v>1.43</v>
@@ -3415,22 +3415,22 @@
         <v>1.77</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -3439,31 +3439,31 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="Q24">
         <v>3.18</v>
@@ -5371,22 +5371,22 @@
         <v>4.39</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5395,31 +5395,31 @@
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>2.04</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -9959,31 +9959,31 @@
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE59">
         <v>0</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="O105">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
-        <v>7.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q105">
-        <v>1.62</v>
+        <v>2.77</v>
       </c>
       <c r="R105">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>3.88</v>
+        <v>2.91</v>
       </c>
       <c r="U105">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="V105">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AB105">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC105">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="AD105">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>3.75</v>
+        <v>1.47</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.35</v>
+        <v>1.23</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="P106">
-        <v>2.62</v>
+        <v>7.8</v>
       </c>
       <c r="Q106">
-        <v>2.77</v>
+        <v>1.62</v>
       </c>
       <c r="R106">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T106">
-        <v>2.91</v>
+        <v>3.88</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="V106">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA106">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AB106">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="AC106">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AD106">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE106">
+        <v>1.33</v>
+      </c>
+      <c r="AF106">
+        <v>1.75</v>
+      </c>
+      <c r="AG106">
+        <v>1.95</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.07</v>
       </c>
-      <c r="AF106">
-        <v>1.65</v>
-      </c>
-      <c r="AG106">
-        <v>2.05</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.24</v>
-      </c>
       <c r="AK106">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O123">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -20373,49 +20373,49 @@
         <v>2.25</v>
       </c>
       <c r="S123">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T123">
         <v>3.2</v>
       </c>
       <c r="U123">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
       <c r="V123">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W123">
         <v>1.11</v>
       </c>
       <c r="X123">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z123">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AA123">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB123">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC123">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD123">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE123">
         <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG123">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21508,7 +21508,7 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R130">
         <v>2.29</v>
@@ -21520,7 +21520,7 @@
         <v>2.97</v>
       </c>
       <c r="U130">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V130">
         <v>1.43</v>
@@ -21535,19 +21535,19 @@
         <v>1.21</v>
       </c>
       <c r="Z130">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA130">
         <v>1.75</v>
       </c>
       <c r="AB130">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AC130">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="AD130">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE130">
         <v>1.08</v>
@@ -21556,7 +21556,7 @@
         <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK130">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21879,10 +21879,10 @@
         <v>1.01</v>
       </c>
       <c r="AF132">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG132">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK132">
         <v>1.81</v>
@@ -22009,7 +22009,7 @@
         <v>3.6</v>
       </c>
       <c r="U133">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V133">
         <v>1.57</v>
@@ -22039,13 +22039,13 @@
         <v>1.52</v>
       </c>
       <c r="AE133">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF133">
         <v>1.6</v>
       </c>
       <c r="AG133">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -641,22 +641,22 @@
         <v>4.33</v>
       </c>
       <c r="P2">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q2">
-        <v>6.21</v>
+        <v>6.07</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S2">
         <v>1.25</v>
       </c>
       <c r="T2">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U2">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V2">
         <v>1.62</v>
@@ -665,7 +665,7 @@
         <v>1.15</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.16</v>
@@ -674,19 +674,19 @@
         <v>5.15</v>
       </c>
       <c r="AA2">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AB2">
         <v>2.55</v>
       </c>
       <c r="AC2">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD2">
         <v>1.58</v>
       </c>
       <c r="AE2">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF2">
         <v>1.62</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -822,16 +822,16 @@
         <v>2.47</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
         <v>3.8</v>
@@ -852,10 +852,10 @@
         <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG3">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -2120,16 +2120,16 @@
         <v>1.62</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U11">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
         <v>1.12</v>
@@ -2138,13 +2138,13 @@
         <v>1.53</v>
       </c>
       <c r="Z11">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="AA11">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AB11">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -2153,13 +2153,13 @@
         <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
         <v>1.44</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="O13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>4.95</v>
       </c>
       <c r="Q13">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="R13">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="S13">
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V13">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB13">
         <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE13">
         <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>4.1</v>
       </c>
       <c r="O15">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P15">
         <v>1.66</v>
@@ -2775,7 +2775,7 @@
         <v>3.45</v>
       </c>
       <c r="U15">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V15">
         <v>1.58</v>
@@ -2790,10 +2790,10 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AA15">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB15">
         <v>2.38</v>
@@ -2805,7 +2805,7 @@
         <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF15">
         <v>1.58</v>
@@ -2938,10 +2938,10 @@
         <v>2.8</v>
       </c>
       <c r="U16">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2962,13 +2962,13 @@
         <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
         <v>1.8</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AK16">
         <v>1.5</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>4.27</v>
+      </c>
+      <c r="O18">
+        <v>3.22</v>
+      </c>
+      <c r="P18">
+        <v>1.77</v>
+      </c>
+      <c r="Q18">
+        <v>4.75</v>
+      </c>
+      <c r="R18">
+        <v>1.95</v>
+      </c>
+      <c r="S18">
+        <v>1.5</v>
+      </c>
+      <c r="T18">
+        <v>2.38</v>
+      </c>
+      <c r="U18">
+        <v>3.35</v>
+      </c>
+      <c r="V18">
+        <v>1.25</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>1.45</v>
+      </c>
+      <c r="Z18">
+        <v>2.6</v>
+      </c>
+      <c r="AA18">
         <v>2.45</v>
       </c>
-      <c r="O18">
-        <v>2.6</v>
-      </c>
-      <c r="P18">
-        <v>3.2</v>
-      </c>
-      <c r="Q18">
-        <v>3.45</v>
-      </c>
-      <c r="R18">
-        <v>1.73</v>
-      </c>
-      <c r="S18">
-        <v>1.75</v>
-      </c>
-      <c r="T18">
-        <v>1.95</v>
-      </c>
-      <c r="U18">
-        <v>4.7</v>
-      </c>
-      <c r="V18">
-        <v>1.12</v>
-      </c>
-      <c r="W18">
-        <v>1.02</v>
-      </c>
-      <c r="X18">
-        <v>1.18</v>
-      </c>
-      <c r="Y18">
-        <v>1.83</v>
-      </c>
-      <c r="Z18">
-        <v>1.87</v>
-      </c>
-      <c r="AA18">
-        <v>3.5</v>
-      </c>
       <c r="AB18">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AC18">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD18">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.27</v>
+        <v>2.45</v>
       </c>
       <c r="O19">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="P19">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="Q19">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="R19">
+        <v>1.73</v>
+      </c>
+      <c r="S19">
+        <v>1.75</v>
+      </c>
+      <c r="T19">
         <v>1.95</v>
       </c>
-      <c r="S19">
-        <v>1.5</v>
-      </c>
-      <c r="T19">
-        <v>2.38</v>
-      </c>
       <c r="U19">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="V19">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y19">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AA19">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AC19">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD19">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK19">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
         <v>3.55</v>
@@ -4393,13 +4393,13 @@
         <v>2.05</v>
       </c>
       <c r="Q25">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
         <v>3.15</v>
@@ -4420,7 +4420,7 @@
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA25">
         <v>1.7</v>
@@ -4429,7 +4429,7 @@
         <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
         <v>1.43</v>
@@ -4438,10 +4438,10 @@
         <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O26">
         <v>3.5</v>
@@ -4556,10 +4556,10 @@
         <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S26">
         <v>1.2</v>
@@ -4580,22 +4580,22 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z26">
         <v>5.3</v>
       </c>
       <c r="AA26">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC26">
         <v>2.2</v>
       </c>
       <c r="AD26">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AE26">
         <v>1.19</v>
@@ -4604,7 +4604,7 @@
         <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q27">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
         <v>1.4</v>
@@ -4740,25 +4740,25 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27">
         <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA27">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
         <v>3.7</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE27">
         <v>1.03</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="R28">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4900,10 +4900,10 @@
         <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
         <v>1.32</v>
@@ -4930,7 +4930,7 @@
         <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O29">
         <v>3.1</v>
@@ -5051,10 +5051,10 @@
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="U29">
         <v>2.97</v>
@@ -5063,10 +5063,10 @@
         <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
         <v>1.28</v>
@@ -5075,10 +5075,10 @@
         <v>3.05</v>
       </c>
       <c r="AA29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
         <v>3.28</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
         <v>1.67</v>
@@ -5208,71 +5208,71 @@
         <v>4.6</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
         <v>2.74</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC30">
         <v>3.08</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE30">
+        <v>1.07</v>
+      </c>
+      <c r="AF30">
+        <v>1.85</v>
+      </c>
+      <c r="AG30">
+        <v>1.83</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.11</v>
       </c>
-      <c r="AF30">
-        <v>1.84</v>
-      </c>
-      <c r="AG30">
-        <v>1.85</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.21</v>
-      </c>
       <c r="AK30">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,31 +5525,31 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
         <v>1.06</v>
@@ -5558,22 +5558,22 @@
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="AA32">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
         <v>1.09</v>
@@ -5598,7 +5598,7 @@
         <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,37 +5694,37 @@
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q33">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U33">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
@@ -5733,10 +5733,10 @@
         <v>1.67</v>
       </c>
       <c r="AC33">
-        <v>3.35</v>
+        <v>3.76</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
         <v>1.02</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
         <v>2.35</v>
       </c>
       <c r="Q35">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S35">
         <v>1.28</v>
@@ -6035,7 +6035,7 @@
         <v>3.18</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V35">
         <v>1.5</v>
@@ -6047,31 +6047,31 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB35">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AD35">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
         <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG35">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         <v>3.3</v>
       </c>
       <c r="R36">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="S36">
         <v>1.52</v>
@@ -6222,13 +6222,13 @@
         <v>1.51</v>
       </c>
       <c r="AC36">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="AD36">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
         <v>2.02</v>
@@ -6343,10 +6343,10 @@
         <v>1.75</v>
       </c>
       <c r="O37">
+        <v>3.5</v>
+      </c>
+      <c r="P37">
         <v>3.4</v>
-      </c>
-      <c r="P37">
-        <v>3.5</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q38">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="R38">
         <v>2.23</v>
@@ -6521,7 +6521,7 @@
         <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="U38">
         <v>2.4</v>
@@ -6530,10 +6530,10 @@
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
         <v>1.18</v>
@@ -6542,10 +6542,10 @@
         <v>3.9</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC38">
         <v>2.62</v>
@@ -6554,10 +6554,10 @@
         <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG38">
         <v>2.28</v>
@@ -6576,7 +6576,7 @@
         <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,34 +6669,34 @@
         <v>2.05</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
         <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.1</v>
@@ -6708,38 +6708,38 @@
         <v>1.43</v>
       </c>
       <c r="AB39">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
         <v>2.2</v>
       </c>
       <c r="AD39">
+        <v>1.65</v>
+      </c>
+      <c r="AE39">
+        <v>1.22</v>
+      </c>
+      <c r="AF39">
+        <v>1.41</v>
+      </c>
+      <c r="AG39">
+        <v>2.69</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.38</v>
+      </c>
+      <c r="AK39">
         <v>1.64</v>
-      </c>
-      <c r="AE39">
-        <v>1.27</v>
-      </c>
-      <c r="AF39">
-        <v>1.42</v>
-      </c>
-      <c r="AG39">
-        <v>2.66</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.19</v>
-      </c>
-      <c r="AK39">
-        <v>1.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="O40">
         <v>4.8</v>
@@ -6841,13 +6841,13 @@
         <v>5.42</v>
       </c>
       <c r="R40">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="S40">
         <v>1.2</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U40">
         <v>2.14</v>
@@ -6862,16 +6862,16 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
         <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB40">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AC40">
         <v>2.19</v>
@@ -6880,7 +6880,7 @@
         <v>1.65</v>
       </c>
       <c r="AE40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
         <v>1.73</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7007,22 +7007,22 @@
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
         <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
         <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
         <v>1.2</v>
@@ -7034,7 +7034,7 @@
         <v>1.73</v>
       </c>
       <c r="AB41">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AC41">
         <v>2.68</v>
@@ -7043,13 +7043,13 @@
         <v>1.37</v>
       </c>
       <c r="AE41">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Q42">
         <v>3.14</v>
@@ -7176,43 +7176,43 @@
         <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V42">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
         <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
         <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB42">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q43">
         <v>3.42</v>
@@ -7333,7 +7333,7 @@
         <v>2.35</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T43">
         <v>3.7</v>
@@ -7342,40 +7342,40 @@
         <v>2.2</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AB43">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC43">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AD43">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
         <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.21</v>
       </c>
       <c r="AK43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O44">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q44">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R44">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S44">
         <v>1.16</v>
@@ -7514,10 +7514,10 @@
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z44">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA44">
         <v>1.33</v>
@@ -7532,10 +7532,10 @@
         <v>1.93</v>
       </c>
       <c r="AE44">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF44">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
         <v>2.53</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK44">
         <v>1.07</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="R45">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T45">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U45">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="V45">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W45">
         <v>1.03</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z45">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA45">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AB45">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC45">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD45">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,61 +7810,61 @@
         <v>3.1</v>
       </c>
       <c r="O46">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q46">
         <v>3.85</v>
       </c>
       <c r="R46">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="S46">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T46">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U46">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y46">
         <v>1.59</v>
       </c>
       <c r="Z46">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AA46">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB46">
         <v>1.36</v>
       </c>
       <c r="AC46">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AD46">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE46">
         <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AG46">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>1.41</v>
       </c>
       <c r="Q47">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="R47">
         <v>2.3</v>
@@ -7994,7 +7994,7 @@
         <v>2.67</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W47">
         <v>1.03</v>
@@ -8003,13 +8003,13 @@
         <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AA47">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB47">
         <v>1.83</v>
@@ -8021,13 +8021,13 @@
         <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG47">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
         <v>1.05</v>
@@ -8133,37 +8133,37 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O48">
         <v>3.2</v>
       </c>
       <c r="P48">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q48">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R48">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="V48">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
         <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
         <v>1.27</v>
@@ -8175,22 +8175,22 @@
         <v>1.95</v>
       </c>
       <c r="AB48">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC48">
         <v>3.42</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE48">
         <v>1.04</v>
       </c>
       <c r="AF48">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG48">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O49">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
       </c>
       <c r="R49">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V49">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W49">
         <v>1.13</v>
@@ -8338,19 +8338,19 @@
         <v>1.43</v>
       </c>
       <c r="AB49">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AC49">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD49">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE49">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF49">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG49">
         <v>2.4</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8625,7 +8625,7 @@
         <v>2.12</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
         <v>2.93</v>
@@ -8634,34 +8634,34 @@
         <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U51">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB51">
         <v>2.05</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,28 +8785,28 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="O52">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="P52">
         <v>1.7</v>
       </c>
       <c r="Q52">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="R52">
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
         <v>3.34</v>
       </c>
       <c r="U52">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V52">
         <v>1.5</v>
@@ -8824,25 +8824,25 @@
         <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC52">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AD52">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE52">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
         <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>2.1</v>
       </c>
       <c r="AK52">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P53">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="Q53">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R53">
         <v>2.07</v>
@@ -8969,10 +8969,10 @@
         <v>2.77</v>
       </c>
       <c r="U53">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
         <v>1.07</v>
@@ -9005,7 +9005,7 @@
         <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O54">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q54">
         <v>2.9</v>
@@ -9141,7 +9141,7 @@
         <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.2</v>
@@ -9150,10 +9150,10 @@
         <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB54">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
         <v>2.61</v>
@@ -9162,7 +9162,7 @@
         <v>1.42</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF54">
         <v>1.55</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q55">
         <v>2.35</v>
@@ -9289,10 +9289,10 @@
         <v>2.33</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U55">
         <v>2.3</v>
@@ -9301,19 +9301,19 @@
         <v>1.47</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
         <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="AA55">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
         <v>2.05</v>
@@ -9325,7 +9325,7 @@
         <v>1.41</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF55">
         <v>1.58</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O56">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q56">
         <v>2.04</v>
@@ -9452,19 +9452,19 @@
         <v>2.63</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V56">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.02</v>
@@ -9476,10 +9476,10 @@
         <v>5.49</v>
       </c>
       <c r="AA56">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
         <v>2.16</v>
@@ -9488,13 +9488,13 @@
         <v>1.62</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q57">
         <v>2.05</v>
@@ -9615,10 +9615,10 @@
         <v>2.36</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T57">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U57">
         <v>2.18</v>
@@ -9630,7 +9630,7 @@
         <v>1.15</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
         <v>1.11</v>
@@ -9639,25 +9639,25 @@
         <v>4.95</v>
       </c>
       <c r="AA57">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB57">
         <v>2.5</v>
       </c>
       <c r="AC57">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
         <v>1.5</v>
       </c>
       <c r="AG57">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O58">
         <v>3.4</v>
       </c>
       <c r="P58">
+        <v>2.45</v>
+      </c>
+      <c r="Q58">
+        <v>2.72</v>
+      </c>
+      <c r="R58">
         <v>2.4</v>
       </c>
-      <c r="Q58">
-        <v>3.14</v>
-      </c>
-      <c r="R58">
-        <v>2.38</v>
-      </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U58">
         <v>2.18</v>
       </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9799,22 +9799,22 @@
         <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="AA58">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AB58">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="AC58">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AD58">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
         <v>1.4</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>8</v>
+        <v>1.19</v>
       </c>
       <c r="O61">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="P61">
-        <v>1.27</v>
+        <v>11</v>
       </c>
       <c r="Q61">
-        <v>7</v>
+        <v>1.56</v>
       </c>
       <c r="R61">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="S61">
+        <v>1.16</v>
+      </c>
+      <c r="T61">
+        <v>4.1</v>
+      </c>
+      <c r="U61">
+        <v>2</v>
+      </c>
+      <c r="V61">
+        <v>1.73</v>
+      </c>
+      <c r="W61">
         <v>1.17</v>
-      </c>
-      <c r="T61">
-        <v>3.96</v>
-      </c>
-      <c r="U61">
-        <v>2.04</v>
-      </c>
-      <c r="V61">
-        <v>1.69</v>
-      </c>
-      <c r="W61">
-        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AC61">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD61">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AE61">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF61">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="AK61">
-        <v>1.06</v>
+        <v>3.65</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,34 +10415,34 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.27</v>
+        <v>8.1</v>
       </c>
       <c r="O62">
-        <v>5.3</v>
+        <v>6.05</v>
       </c>
       <c r="P62">
-        <v>8.199999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="Q62">
-        <v>1.62</v>
+        <v>7</v>
       </c>
       <c r="R62">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="S62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U62">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W62">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10451,28 +10451,28 @@
         <v>1.13</v>
       </c>
       <c r="Z62">
-        <v>5.9</v>
+        <v>5.49</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB62">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AC62">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG62">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="AK62">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q63">
         <v>5</v>
@@ -10593,10 +10593,10 @@
         <v>2</v>
       </c>
       <c r="S63">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T63">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U63">
         <v>3.58</v>
@@ -10611,31 +10611,31 @@
         <v>1.05</v>
       </c>
       <c r="Y63">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z63">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AA63">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB63">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC63">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AD63">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG63">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,31 +10741,31 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q64">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R64">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S64">
         <v>1.5</v>
       </c>
       <c r="T64">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U64">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="V64">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W64">
         <v>1.04</v>
@@ -10774,19 +10774,19 @@
         <v>1.06</v>
       </c>
       <c r="Y64">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z64">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AA64">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AB64">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC64">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD64">
         <v>1.14</v>
@@ -10795,7 +10795,7 @@
         <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AG64">
         <v>1.66</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10910,49 +10910,49 @@
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q65">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="R65">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="S65">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="AA65">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
         <v>2.55</v>
       </c>
       <c r="AC65">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
         <v>1.17</v>
@@ -10977,7 +10977,7 @@
         <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="Q66">
         <v>2.29</v>
@@ -11082,25 +11082,25 @@
         <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T66">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
         <v>2.56</v>
       </c>
       <c r="V66">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W66">
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
         <v>3.78</v>
@@ -11112,19 +11112,19 @@
         <v>2.04</v>
       </c>
       <c r="AC66">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE66">
         <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG66">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O67">
         <v>3.52</v>
       </c>
       <c r="P67">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O68">
         <v>2.9</v>
       </c>
       <c r="P68">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q68">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="R68">
         <v>1.96</v>
@@ -11411,10 +11411,10 @@
         <v>1.46</v>
       </c>
       <c r="T68">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U68">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="V68">
         <v>1.28</v>
@@ -11423,13 +11423,13 @@
         <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y68">
         <v>1.37</v>
       </c>
       <c r="Z68">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA68">
         <v>2.25</v>
@@ -11441,10 +11441,10 @@
         <v>4.2</v>
       </c>
       <c r="AD68">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
         <v>1.89</v>
@@ -11466,7 +11466,7 @@
         <v>1.36</v>
       </c>
       <c r="AK68">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="O69">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P69">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="Q69">
         <v>2.22</v>
@@ -11583,19 +11583,19 @@
         <v>1.39</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA69">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB69">
         <v>1.88</v>
@@ -11604,7 +11604,7 @@
         <v>3.28</v>
       </c>
       <c r="AD69">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE69">
         <v>1.06</v>
@@ -11613,7 +11613,7 @@
         <v>1.84</v>
       </c>
       <c r="AG69">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="O70">
         <v>3</v>
@@ -11734,40 +11734,40 @@
         <v>2.03</v>
       </c>
       <c r="S70">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
         <v>2.77</v>
       </c>
       <c r="U70">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V70">
         <v>1.32</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y70">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z70">
         <v>2.95</v>
       </c>
       <c r="AA70">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB70">
         <v>1.67</v>
       </c>
       <c r="AC70">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD70">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE70">
         <v>1.02</v>
@@ -11776,7 +11776,7 @@
         <v>1.87</v>
       </c>
       <c r="AG70">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -12217,22 +12217,22 @@
         <v>4.2</v>
       </c>
       <c r="Q73">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R73">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T73">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="U73">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W73">
         <v>1.03</v>
@@ -12244,28 +12244,28 @@
         <v>1.31</v>
       </c>
       <c r="Z73">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA73">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB73">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC73">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD73">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE73">
         <v>1.06</v>
       </c>
       <c r="AF73">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG73">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12392,7 +12392,7 @@
         <v>3.92</v>
       </c>
       <c r="U74">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V74">
         <v>1.71</v>
@@ -12410,16 +12410,16 @@
         <v>5.65</v>
       </c>
       <c r="AA74">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="AC74">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD74">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE74">
         <v>1.27</v>
@@ -12428,7 +12428,7 @@
         <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="O76">
         <v>3.55</v>
@@ -12715,10 +12715,10 @@
         <v>1.22</v>
       </c>
       <c r="T76">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U76">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V76">
         <v>1.58</v>
@@ -12751,10 +12751,10 @@
         <v>1.18</v>
       </c>
       <c r="AF76">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG76">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O77">
         <v>4</v>
       </c>
       <c r="P77">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q77">
         <v>2.16</v>
@@ -12875,49 +12875,49 @@
         <v>2.6</v>
       </c>
       <c r="S77">
+        <v>1.19</v>
+      </c>
+      <c r="T77">
+        <v>4</v>
+      </c>
+      <c r="U77">
+        <v>2.07</v>
+      </c>
+      <c r="V77">
+        <v>1.71</v>
+      </c>
+      <c r="W77">
         <v>1.2</v>
-      </c>
-      <c r="T77">
-        <v>4.1</v>
-      </c>
-      <c r="U77">
-        <v>1.99</v>
-      </c>
-      <c r="V77">
-        <v>1.7</v>
-      </c>
-      <c r="W77">
-        <v>1.18</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z77">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="AA77">
         <v>1.36</v>
       </c>
       <c r="AB77">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC77">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD77">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE77">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF77">
         <v>1.42</v>
       </c>
       <c r="AG77">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,34 +13023,34 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="O78">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="P78">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q78">
         <v>2.15</v>
       </c>
       <c r="R78">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S78">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U78">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V78">
         <v>1.75</v>
       </c>
       <c r="W78">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X78">
         <v>1.01</v>
@@ -13059,13 +13059,13 @@
         <v>1.06</v>
       </c>
       <c r="Z78">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA78">
         <v>1.33</v>
       </c>
       <c r="AB78">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC78">
         <v>1.96</v>
@@ -13080,7 +13080,7 @@
         <v>1.4</v>
       </c>
       <c r="AG78">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,31 +13186,31 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O79">
         <v>3.82</v>
       </c>
       <c r="P79">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q79">
         <v>2.85</v>
       </c>
       <c r="R79">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="S79">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T79">
         <v>3.9</v>
       </c>
       <c r="U79">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="V79">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W79">
         <v>1.2</v>
@@ -13219,31 +13219,31 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z79">
         <v>5.3</v>
       </c>
       <c r="AA79">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB79">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AC79">
         <v>2.1</v>
       </c>
       <c r="AD79">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE79">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF79">
         <v>1.38</v>
       </c>
       <c r="AG79">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>2.5</v>
       </c>
       <c r="R80">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="S80">
         <v>1.24</v>
@@ -13370,13 +13370,13 @@
         <v>3.44</v>
       </c>
       <c r="U80">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V80">
         <v>1.59</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X80">
         <v>1.02</v>
@@ -13388,22 +13388,22 @@
         <v>4.65</v>
       </c>
       <c r="AA80">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB80">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AC80">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD80">
         <v>1.57</v>
       </c>
       <c r="AE80">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG80">
         <v>2.53</v>
@@ -13524,28 +13524,28 @@
         <v>2.32</v>
       </c>
       <c r="R81">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="S81">
         <v>1.25</v>
       </c>
       <c r="T81">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V81">
         <v>1.57</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z81">
         <v>4.85</v>
@@ -13560,16 +13560,16 @@
         <v>2.55</v>
       </c>
       <c r="AD81">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE81">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF81">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG81">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
         <v>2.2</v>
@@ -13690,49 +13690,49 @@
         <v>2.25</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U82">
         <v>2.18</v>
       </c>
       <c r="V82">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z82">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA82">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB82">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC82">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AD82">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE82">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
         <v>1.47</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="R84">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T84">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="U84">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V84">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z84">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA84">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB84">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="AC84">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AD84">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AE84">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF84">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG84">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AK84">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O85">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P85">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q85">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R85">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="S85">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>4.85</v>
+        <v>5.42</v>
       </c>
       <c r="AA85">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB85">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC85">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD85">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE85">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
         <v>1.79</v>
@@ -14327,28 +14327,28 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O86">
         <v>3.7</v>
       </c>
       <c r="P86">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="Q86">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="R86">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U86">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V86">
         <v>1.66</v>
@@ -14357,31 +14357,31 @@
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
         <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA86">
         <v>1.43</v>
       </c>
       <c r="AB86">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AC86">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD86">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF86">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
         <v>2.57</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O87">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
         <v>5.75</v>
       </c>
       <c r="Q87">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R87">
         <v>2.09</v>
@@ -14517,13 +14517,13 @@
         <v>1.37</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z87">
         <v>3.08</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK87">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="O88">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
       </c>
       <c r="R88">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S88">
         <v>1.48</v>
       </c>
       <c r="T88">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="U88">
         <v>3.22</v>
@@ -14689,13 +14689,13 @@
         <v>1.37</v>
       </c>
       <c r="Z88">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA88">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB88">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC88">
         <v>4.5</v>
@@ -14707,10 +14707,10 @@
         <v>1.05</v>
       </c>
       <c r="AF88">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG88">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.28</v>
       </c>
       <c r="AK88">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14828,37 +14828,37 @@
         <v>2.6</v>
       </c>
       <c r="R89">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S89">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T89">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="U89">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V89">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AA89">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC89">
         <v>3</v>
@@ -14870,10 +14870,10 @@
         <v>1.09</v>
       </c>
       <c r="AF89">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14991,7 +14991,7 @@
         <v>3</v>
       </c>
       <c r="R90">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
         <v>1.36</v>
@@ -15000,25 +15000,25 @@
         <v>2.9</v>
       </c>
       <c r="U90">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="V90">
         <v>1.42</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z90">
         <v>3.34</v>
       </c>
       <c r="AA90">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB90">
         <v>1.9</v>
@@ -15036,7 +15036,7 @@
         <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15314,16 +15314,16 @@
         <v>5</v>
       </c>
       <c r="Q92">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="R92">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="S92">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
         <v>2.46</v>
@@ -15338,25 +15338,25 @@
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z92">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA92">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB92">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC92">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD92">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE92">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF92">
         <v>1.73</v>
@@ -15378,7 +15378,7 @@
         <v>1.2</v>
       </c>
       <c r="AK92">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="O93">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P93">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q93">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="R93">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="U93">
         <v>2.77</v>
       </c>
       <c r="V93">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W93">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z93">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="AA93">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB93">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AC93">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
         <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG93">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK93">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,25 +15631,25 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O94">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q94">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R94">
         <v>2.1</v>
       </c>
       <c r="S94">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="U94">
         <v>2.92</v>
@@ -15658,7 +15658,7 @@
         <v>1.38</v>
       </c>
       <c r="W94">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X94">
         <v>1.03</v>
@@ -15670,25 +15670,25 @@
         <v>3.3</v>
       </c>
       <c r="AA94">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AB94">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC94">
         <v>3.35</v>
       </c>
       <c r="AD94">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE94">
         <v>1.07</v>
       </c>
       <c r="AF94">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG94">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R95">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="S95">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T95">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="U95">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V95">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="W95">
         <v>1.3</v>
       </c>
       <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
         <v>1.01</v>
       </c>
-      <c r="Y95">
-        <v>1.04</v>
-      </c>
       <c r="Z95">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA95">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AB95">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC95">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD95">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AE95">
         <v>1.58</v>
       </c>
       <c r="AF95">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK95">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,22 +15957,22 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O96">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q96">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="R96">
         <v>2.09</v>
       </c>
       <c r="S96">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T96">
         <v>2.75</v>
@@ -15984,7 +15984,7 @@
         <v>1.34</v>
       </c>
       <c r="W96">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15996,7 +15996,7 @@
         <v>3.06</v>
       </c>
       <c r="AA96">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB96">
         <v>1.71</v>
@@ -16005,10 +16005,10 @@
         <v>3.58</v>
       </c>
       <c r="AD96">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE96">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF96">
         <v>1.71</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="O97">
         <v>4.5</v>
@@ -16132,7 +16132,7 @@
         <v>7</v>
       </c>
       <c r="R97">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="S97">
         <v>1.28</v>
@@ -16141,10 +16141,10 @@
         <v>3.18</v>
       </c>
       <c r="U97">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V97">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W97">
         <v>1.1</v>
@@ -16153,16 +16153,16 @@
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z97">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="AA97">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AB97">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC97">
         <v>2.69</v>
@@ -16171,13 +16171,13 @@
         <v>1.43</v>
       </c>
       <c r="AE97">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF97">
         <v>1.97</v>
       </c>
       <c r="AG97">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK97">
         <v>1.01</v>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O98">
         <v>3.9</v>
@@ -16292,28 +16292,28 @@
         <v>1.75</v>
       </c>
       <c r="Q98">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="R98">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S98">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T98">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U98">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V98">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W98">
         <v>1.09</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y98">
         <v>1.2</v>
@@ -16322,7 +16322,7 @@
         <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB98">
         <v>2.14</v>
@@ -16334,7 +16334,7 @@
         <v>1.42</v>
       </c>
       <c r="AE98">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF98">
         <v>1.65</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="O102">
         <v>3.3</v>
       </c>
       <c r="P102">
-        <v>3.65</v>
+        <v>2.25</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA102">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB102">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="O103">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P103">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q103">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S103">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="U103">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="V103">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W103">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z103">
-        <v>4.26</v>
+        <v>3.5</v>
       </c>
       <c r="AA103">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB103">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="AC103">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD103">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF103">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG103">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O104">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="P104">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="Q104">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="R104">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T104">
-        <v>3.55</v>
+        <v>3.88</v>
       </c>
       <c r="U104">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="V104">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W104">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z104">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AB104">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AC104">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AD104">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AE104">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF104">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG104">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK104">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="P105">
-        <v>2.62</v>
+        <v>6.7</v>
       </c>
       <c r="Q105">
-        <v>2.77</v>
+        <v>1.8</v>
       </c>
       <c r="R105">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>2.91</v>
+        <v>3.55</v>
       </c>
       <c r="U105">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="V105">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA105">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AB105">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AC105">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF105">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>2.88</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="O106">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>7.8</v>
+        <v>3.58</v>
       </c>
       <c r="Q106">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T106">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V106">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA106">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB106">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC106">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG106">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK106">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17753,7 +17753,7 @@
         <v>1.36</v>
       </c>
       <c r="O107">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="P107">
         <v>8</v>
@@ -17771,25 +17771,25 @@
         <v>3.1</v>
       </c>
       <c r="U107">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z107">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="AA107">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB107">
         <v>1.92</v>
@@ -17804,10 +17804,10 @@
         <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG107">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK107">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O108">
-        <v>4.58</v>
+        <v>4.35</v>
       </c>
       <c r="P108">
         <v>5.5</v>
@@ -18239,46 +18239,46 @@
         </is>
       </c>
       <c r="N110">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O110">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q110">
         <v>5.44</v>
       </c>
       <c r="R110">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S110">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T110">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U110">
         <v>2.4</v>
       </c>
       <c r="V110">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z110">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA110">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AB110">
         <v>2.25</v>
@@ -18287,13 +18287,13 @@
         <v>2.48</v>
       </c>
       <c r="AD110">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE110">
         <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG110">
         <v>2.2</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AK110">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>2.15</v>
       </c>
       <c r="O112">
-        <v>3.28</v>
+        <v>3.03</v>
       </c>
       <c r="P112">
         <v>3.3</v>
@@ -18580,46 +18580,46 @@
         <v>1.97</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T112">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U112">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V112">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W112">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X112">
         <v>1.05</v>
       </c>
       <c r="Y112">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z112">
         <v>2.87</v>
       </c>
       <c r="AA112">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB112">
         <v>1.65</v>
       </c>
       <c r="AC112">
-        <v>4.36</v>
+        <v>3.95</v>
       </c>
       <c r="AD112">
         <v>1.18</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF112">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG112">
         <v>1.8</v>
@@ -18638,7 +18638,7 @@
         <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,16 +18728,16 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O113">
         <v>3.27</v>
       </c>
       <c r="P113">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="Q113">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="R113">
         <v>2.05</v>
@@ -18758,34 +18758,34 @@
         <v>1.05</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y113">
         <v>1.32</v>
       </c>
       <c r="Z113">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA113">
         <v>1.91</v>
       </c>
       <c r="AB113">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC113">
         <v>3.44</v>
       </c>
       <c r="AD113">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE113">
         <v>1.07</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG113">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19075,13 +19075,13 @@
         <v>2.63</v>
       </c>
       <c r="U115">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V115">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19389,7 +19389,7 @@
         <v>0</v>
       </c>
       <c r="Q117">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="R117">
         <v>2.03</v>
@@ -19453,7 +19453,7 @@
         <v>1.26</v>
       </c>
       <c r="AK117">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,28 +19543,28 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q118">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S118">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T118">
         <v>2.7</v>
       </c>
       <c r="U118">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
         <v>1.35</v>
@@ -19576,22 +19576,22 @@
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z118">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB118">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC118">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD118">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE118">
         <v>1.05</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK118">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,37 +19706,37 @@
         </is>
       </c>
       <c r="N119">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O119">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="P119">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Q119">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="R119">
         <v>2.62</v>
       </c>
       <c r="S119">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T119">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U119">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V119">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W119">
         <v>1.13</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
         <v>1.14</v>
@@ -19745,25 +19745,25 @@
         <v>4.7</v>
       </c>
       <c r="AA119">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB119">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AC119">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD119">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE119">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF119">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG119">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.12</v>
       </c>
       <c r="AK119">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19872,28 +19872,28 @@
         <v>3.1</v>
       </c>
       <c r="O120">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="P120">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="Q120">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="R120">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S120">
         <v>1.38</v>
       </c>
       <c r="T120">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U120">
         <v>2.7</v>
       </c>
       <c r="V120">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W120">
         <v>1.07</v>
@@ -19902,7 +19902,7 @@
         <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z120">
         <v>3.64</v>
@@ -19914,19 +19914,19 @@
         <v>2</v>
       </c>
       <c r="AC120">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AD120">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE120">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF120">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG120">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
         <v>1.35</v>
@@ -20032,25 +20032,25 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q121">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="R121">
         <v>1.9</v>
       </c>
       <c r="S121">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U121">
         <v>3.32</v>
@@ -20065,10 +20065,10 @@
         <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z121">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA121">
         <v>2.38</v>
@@ -20077,19 +20077,19 @@
         <v>1.57</v>
       </c>
       <c r="AC121">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD121">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE121">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG121">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK121">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O122">
         <v>3.7</v>
@@ -20207,52 +20207,52 @@
         <v>2.1</v>
       </c>
       <c r="R122">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
         <v>1.38</v>
       </c>
       <c r="T122">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U122">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="V122">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W122">
         <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z122">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA122">
         <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC122">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="AD122">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE122">
         <v>1.05</v>
       </c>
       <c r="AF122">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG122">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK122">
         <v>2.33</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="O123">
         <v>3.3</v>
@@ -20376,10 +20376,10 @@
         <v>1.35</v>
       </c>
       <c r="T123">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U123">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="V123">
         <v>1.47</v>
@@ -20403,10 +20403,10 @@
         <v>1.98</v>
       </c>
       <c r="AC123">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AD123">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE123">
         <v>1.15</v>
@@ -20524,10 +20524,10 @@
         <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P124">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q124">
         <v>2.52</v>
@@ -20560,7 +20560,7 @@
         <v>2.91</v>
       </c>
       <c r="AA124">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AB124">
         <v>1.66</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="O125">
+        <v>3.7</v>
+      </c>
+      <c r="P125">
+        <v>3.4</v>
+      </c>
+      <c r="Q125">
+        <v>2.4</v>
+      </c>
+      <c r="R125">
+        <v>2.38</v>
+      </c>
+      <c r="S125">
+        <v>1.22</v>
+      </c>
+      <c r="T125">
         <v>3.8</v>
       </c>
-      <c r="P125">
-        <v>3.75</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125">
-        <v>0</v>
-      </c>
       <c r="U125">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.77</v>
+        <v>3.2</v>
       </c>
       <c r="O126">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P126">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA126">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB126">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21188,16 +21188,16 @@
         <v>2.1</v>
       </c>
       <c r="S128">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T128">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U128">
         <v>2.95</v>
       </c>
       <c r="V128">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W128">
         <v>1.04</v>
@@ -21212,7 +21212,7 @@
         <v>2.88</v>
       </c>
       <c r="AA128">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB128">
         <v>1.73</v>
@@ -21230,7 +21230,7 @@
         <v>1.95</v>
       </c>
       <c r="AG128">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21339,10 +21339,10 @@
         <v>2.35</v>
       </c>
       <c r="O129">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P129">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q129">
         <v>2.9</v>
@@ -21351,7 +21351,7 @@
         <v>2.04</v>
       </c>
       <c r="S129">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T129">
         <v>2.4</v>
@@ -21360,25 +21360,25 @@
         <v>3.48</v>
       </c>
       <c r="V129">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W129">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X129">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y129">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z129">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AA129">
         <v>2.55</v>
       </c>
       <c r="AB129">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC129">
         <v>4.75</v>
@@ -21387,7 +21387,7 @@
         <v>1.13</v>
       </c>
       <c r="AE129">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF129">
         <v>1.92</v>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK129">
         <v>1.5</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
         <v>2.07</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S5">
         <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W5">
         <v>1.16</v>
@@ -1157,7 +1157,7 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
         <v>5.5</v>
@@ -1169,13 +1169,13 @@
         <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD5">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
         <v>1.38</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.38</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="P6">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="Q6">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="R6">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="S6">
         <v>1.15</v>
@@ -1314,37 +1314,37 @@
         <v>1.9</v>
       </c>
       <c r="W6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Z6">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AB6">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AC6">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AD6">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE6">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG6">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>3.1</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q7">
         <v>3.54</v>
@@ -1468,7 +1468,7 @@
         <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="U7">
         <v>2.18</v>
@@ -1477,10 +1477,10 @@
         <v>1.62</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.13</v>
@@ -1489,22 +1489,22 @@
         <v>5.4</v>
       </c>
       <c r="AA7">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AB7">
         <v>2.43</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD7">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE7">
         <v>1.21</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG7">
         <v>2.43</v>
@@ -1523,7 +1523,7 @@
         <v>1.77</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="P11">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
         <v>3.32</v>
@@ -2132,7 +2132,7 @@
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y11">
         <v>1.53</v>
@@ -2153,7 +2153,7 @@
         <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
         <v>2.1</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
         <v>2.75</v>
@@ -2938,7 +2938,7 @@
         <v>2.8</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V16">
         <v>1.34</v>
@@ -2953,7 +2953,7 @@
         <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AA16">
         <v>2.05</v>
@@ -2962,7 +2962,7 @@
         <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="AD16">
         <v>1.25</v>
@@ -5531,7 +5531,7 @@
         <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
         <v>2.3</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O36">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="P36">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q36">
         <v>3.3</v>
@@ -6219,16 +6219,16 @@
         <v>2.47</v>
       </c>
       <c r="AB36">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AC36">
-        <v>4.76</v>
+        <v>4.81</v>
       </c>
       <c r="AD36">
         <v>1.12</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
         <v>2.02</v>
@@ -7810,10 +7810,10 @@
         <v>3.1</v>
       </c>
       <c r="O46">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P46">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
         <v>3.85</v>
@@ -7825,7 +7825,7 @@
         <v>1.6</v>
       </c>
       <c r="T46">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U46">
         <v>3.7</v>
@@ -7837,10 +7837,10 @@
         <v>1.01</v>
       </c>
       <c r="X46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y46">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Z46">
         <v>2.45</v>
@@ -7849,13 +7849,13 @@
         <v>2.88</v>
       </c>
       <c r="AB46">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC46">
         <v>5.25</v>
       </c>
       <c r="AD46">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE46">
         <v>1.03</v>
@@ -7973,7 +7973,7 @@
         <v>6</v>
       </c>
       <c r="O47">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="P47">
         <v>1.41</v>
@@ -7997,31 +7997,31 @@
         <v>1.37</v>
       </c>
       <c r="W47">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA47">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC47">
         <v>3.2</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
         <v>2.15</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>2.53</v>
       </c>
       <c r="AK47">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>3.2</v>
       </c>
       <c r="P53">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q53">
         <v>2.65</v>
@@ -8969,10 +8969,10 @@
         <v>2.77</v>
       </c>
       <c r="U53">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W53">
         <v>1.07</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="O55">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>2.85</v>
+        <v>3.51</v>
       </c>
       <c r="Q55">
         <v>2.35</v>
@@ -9289,10 +9289,10 @@
         <v>2.33</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T55">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U55">
         <v>2.3</v>
@@ -9304,16 +9304,16 @@
         <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
         <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB55">
         <v>2.05</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.19</v>
+        <v>8.1</v>
       </c>
       <c r="O61">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="P61">
-        <v>11</v>
+        <v>1.24</v>
       </c>
       <c r="Q61">
-        <v>1.56</v>
+        <v>7</v>
       </c>
       <c r="R61">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="S61">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
         <v>2</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>6.15</v>
+        <v>5.49</v>
       </c>
       <c r="AA61">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AB61">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AC61">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE61">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG61">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="AK61">
-        <v>3.65</v>
+        <v>1.06</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>8.1</v>
+        <v>1.19</v>
       </c>
       <c r="O62">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="P62">
-        <v>1.24</v>
+        <v>11</v>
       </c>
       <c r="Q62">
-        <v>7</v>
+        <v>1.56</v>
       </c>
       <c r="R62">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T62">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U62">
         <v>2</v>
       </c>
       <c r="V62">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>5.49</v>
+        <v>6.15</v>
       </c>
       <c r="AA62">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD62">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF62">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG62">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="AK62">
-        <v>1.06</v>
+        <v>3.65</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -12244,19 +12244,19 @@
         <v>1.31</v>
       </c>
       <c r="Z73">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AA73">
         <v>2.02</v>
       </c>
       <c r="AB73">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC73">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD73">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
         <v>1.06</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,16 +12371,16 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O74">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P74">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="Q74">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R74">
         <v>2.62</v>
@@ -12416,13 +12416,13 @@
         <v>2.82</v>
       </c>
       <c r="AC74">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD74">
         <v>1.78</v>
       </c>
       <c r="AE74">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF74">
         <v>1.5</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,55 +14164,55 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O85">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q85">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R85">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U85">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.42</v>
+        <v>5.05</v>
       </c>
       <c r="AA85">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB85">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AC85">
         <v>2.2</v>
       </c>
       <c r="AD85">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
         <v>1.25</v>
@@ -14221,7 +14221,7 @@
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,55 +14327,55 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P86">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q86">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="S86">
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V86">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>5.05</v>
+        <v>5.42</v>
       </c>
       <c r="AA86">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB86">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AC86">
         <v>2.2</v>
       </c>
       <c r="AD86">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE86">
         <v>1.25</v>
@@ -14384,7 +14384,7 @@
         <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O99">
         <v>5.3</v>
@@ -16470,28 +16470,28 @@
         <v>2.3</v>
       </c>
       <c r="V99">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W99">
         <v>1.13</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
         <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA99">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AB99">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC99">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD99">
         <v>1.58</v>
@@ -16500,10 +16500,10 @@
         <v>1.19</v>
       </c>
       <c r="AF99">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG99">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>2.55</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P100">
         <v>2.4</v>
@@ -16621,16 +16621,16 @@
         <v>3.2</v>
       </c>
       <c r="R100">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="S100">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T100">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V100">
         <v>1.45</v>
@@ -16639,22 +16639,22 @@
         <v>1.08</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
         <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA100">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB100">
         <v>2.03</v>
       </c>
       <c r="AC100">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD100">
         <v>1.36</v>
@@ -16663,10 +16663,10 @@
         <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,25 +16772,25 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="O101">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="P101">
         <v>6.5</v>
       </c>
       <c r="Q101">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R101">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T101">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U101">
         <v>2.17</v>
@@ -16805,10 +16805,10 @@
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z101">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA101">
         <v>1.55</v>
@@ -16823,7 +16823,7 @@
         <v>1.56</v>
       </c>
       <c r="AE101">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF101">
         <v>1.78</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK101">
         <v>3.1</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.23</v>
+        <v>1.25</v>
       </c>
       <c r="O103">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="P103">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="Q103">
+        <v>1.62</v>
+      </c>
+      <c r="R103">
         <v>2.88</v>
       </c>
-      <c r="R103">
-        <v>2.12</v>
-      </c>
       <c r="S103">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T103">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="U103">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="V103">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z103">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA103">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AB103">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="AC103">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD103">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE103">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF103">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK103">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
+        <v>1.39</v>
+      </c>
+      <c r="O104">
+        <v>4.35</v>
+      </c>
+      <c r="P104">
+        <v>6.7</v>
+      </c>
+      <c r="Q104">
+        <v>1.8</v>
+      </c>
+      <c r="R104">
+        <v>2.5</v>
+      </c>
+      <c r="S104">
         <v>1.25</v>
       </c>
-      <c r="O104">
-        <v>5.5</v>
-      </c>
-      <c r="P104">
-        <v>7.5</v>
-      </c>
-      <c r="Q104">
-        <v>1.62</v>
-      </c>
-      <c r="R104">
-        <v>2.88</v>
-      </c>
-      <c r="S104">
-        <v>1.17</v>
-      </c>
       <c r="T104">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="U104">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="V104">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W104">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z104">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA104">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AC104">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AD104">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE104">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF104">
         <v>1.67</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK104">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="O105">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>6.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q105">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB105">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC105">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD105">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK105">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P106">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB106">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18402,19 +18402,19 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O111">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P111">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q111">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R111">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S111">
         <v>1.32</v>
@@ -18426,40 +18426,40 @@
         <v>2.59</v>
       </c>
       <c r="V111">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W111">
         <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z111">
         <v>3.75</v>
       </c>
       <c r="AA111">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB111">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC111">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD111">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE111">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF111">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG111">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -20524,10 +20524,10 @@
         <v>1.83</v>
       </c>
       <c r="O124">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>3.8</v>
+        <v>4.46</v>
       </c>
       <c r="Q124">
         <v>2.52</v>
@@ -20539,7 +20539,7 @@
         <v>1.44</v>
       </c>
       <c r="T124">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U124">
         <v>3.16</v>
@@ -20554,13 +20554,13 @@
         <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z124">
         <v>2.91</v>
       </c>
       <c r="AA124">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AB124">
         <v>1.66</v>
@@ -20572,13 +20572,13 @@
         <v>1.22</v>
       </c>
       <c r="AE124">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF124">
         <v>1.91</v>
       </c>
       <c r="AG124">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>2.49</v>
       </c>
       <c r="R127">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S127">
         <v>1.47</v>
@@ -21031,7 +21031,7 @@
         <v>2.75</v>
       </c>
       <c r="U127">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="V127">
         <v>1.3</v>
@@ -21040,7 +21040,7 @@
         <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
         <v>1.4</v>
@@ -21049,16 +21049,16 @@
         <v>2.83</v>
       </c>
       <c r="AA127">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AB127">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC127">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AD127">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE127">
         <v>1.07</v>
@@ -21182,10 +21182,10 @@
         <v>4.4</v>
       </c>
       <c r="Q128">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="R128">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S128">
         <v>1.41</v>
@@ -21246,7 +21246,7 @@
         <v>1.28</v>
       </c>
       <c r="AK128">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="Q2">
-        <v>6.07</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="U2">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V2">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z2">
-        <v>5.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA2">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AB2">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC2">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="AD2">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AE2">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P3">
-        <v>2.62</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>6.07</v>
       </c>
       <c r="R3">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.08</v>
+        <v>3.58</v>
       </c>
       <c r="U3">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
+        <v>1.62</v>
+      </c>
+      <c r="W3">
+        <v>1.15</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.16</v>
+      </c>
+      <c r="Z3">
+        <v>5.15</v>
+      </c>
+      <c r="AA3">
         <v>1.44</v>
       </c>
-      <c r="W3">
-        <v>1.08</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
+      <c r="AB3">
+        <v>2.55</v>
+      </c>
+      <c r="AC3">
+        <v>2.29</v>
+      </c>
+      <c r="AD3">
+        <v>1.58</v>
+      </c>
+      <c r="AE3">
         <v>1.23</v>
       </c>
-      <c r="Z3">
-        <v>3.8</v>
-      </c>
-      <c r="AA3">
-        <v>1.73</v>
-      </c>
-      <c r="AB3">
-        <v>2.05</v>
-      </c>
-      <c r="AC3">
-        <v>2.48</v>
-      </c>
-      <c r="AD3">
-        <v>1.43</v>
-      </c>
-      <c r="AE3">
-        <v>1.12</v>
-      </c>
       <c r="AF3">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
+        <v>1.39</v>
+      </c>
+      <c r="O103">
+        <v>4.35</v>
+      </c>
+      <c r="P103">
+        <v>6.7</v>
+      </c>
+      <c r="Q103">
+        <v>1.8</v>
+      </c>
+      <c r="R103">
+        <v>2.5</v>
+      </c>
+      <c r="S103">
         <v>1.25</v>
       </c>
-      <c r="O103">
-        <v>5.5</v>
-      </c>
-      <c r="P103">
-        <v>7.5</v>
-      </c>
-      <c r="Q103">
-        <v>1.62</v>
-      </c>
-      <c r="R103">
-        <v>2.88</v>
-      </c>
-      <c r="S103">
-        <v>1.17</v>
-      </c>
       <c r="T103">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="U103">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="V103">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W103">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z103">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA103">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AC103">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AD103">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE103">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF103">
         <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK103">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="O104">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="P104">
-        <v>6.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AB104">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="O105">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P105">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB105">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.23</v>
+        <v>1.25</v>
       </c>
       <c r="O106">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="P106">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="Q106">
+        <v>1.62</v>
+      </c>
+      <c r="R106">
         <v>2.88</v>
       </c>
-      <c r="R106">
-        <v>2.12</v>
-      </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T106">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA106">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AB106">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="AC106">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD106">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE106">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF106">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK106">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AL106">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O11">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
         <v>3.32</v>
@@ -2117,49 +2117,49 @@
         <v>1.76</v>
       </c>
       <c r="S11">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T11">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="V11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1.13</v>
       </c>
       <c r="Y11">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z11">
         <v>2.39</v>
       </c>
       <c r="AA11">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AB11">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AD11">
         <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG11">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P13">
-        <v>4.95</v>
+        <v>4.65</v>
       </c>
       <c r="Q13">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="R13">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="S13">
         <v>1.2</v>
@@ -2449,22 +2449,22 @@
         <v>4</v>
       </c>
       <c r="U13">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W13">
         <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5.55</v>
+        <v>5.74</v>
       </c>
       <c r="AA13">
         <v>1.42</v>
@@ -2473,7 +2473,7 @@
         <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD13">
         <v>1.7</v>
@@ -2482,7 +2482,7 @@
         <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG13">
         <v>2.45</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -2938,10 +2938,10 @@
         <v>2.8</v>
       </c>
       <c r="U16">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="V16">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2950,19 +2950,19 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z16">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB16">
         <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="AD16">
         <v>1.25</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.27</v>
+        <v>4.66</v>
       </c>
       <c r="O18">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="P18">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q18">
         <v>4.75</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O19">
         <v>2.6</v>
       </c>
       <c r="P19">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="R19">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="S19">
         <v>1.75</v>
@@ -3436,7 +3436,7 @@
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Y19">
         <v>1.83</v>
@@ -3448,7 +3448,7 @@
         <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC19">
         <v>7.8</v>
@@ -3457,13 +3457,13 @@
         <v>1.02</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>2.67</v>
       </c>
       <c r="AG19">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4224,13 +4224,13 @@
         <v>2.3</v>
       </c>
       <c r="O24">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P24">
         <v>3</v>
       </c>
       <c r="Q24">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R24">
         <v>1.82</v>
@@ -4251,7 +4251,7 @@
         <v>1.03</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y24">
         <v>1.58</v>
@@ -4272,13 +4272,13 @@
         <v>1.07</v>
       </c>
       <c r="AE24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
         <v>2.23</v>
       </c>
       <c r="AG24">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="O31">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>4.39</v>
+        <v>4.74</v>
       </c>
       <c r="Q31">
         <v>2.5</v>
@@ -5860,55 +5860,55 @@
         <v>4.09</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O43">
         <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q43">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R43">
         <v>2.35</v>
@@ -7348,35 +7348,35 @@
         <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA43">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
+        <v>2.41</v>
+      </c>
+      <c r="AC43">
+        <v>2.35</v>
+      </c>
+      <c r="AD43">
+        <v>1.55</v>
+      </c>
+      <c r="AE43">
+        <v>1.22</v>
+      </c>
+      <c r="AF43">
+        <v>1.44</v>
+      </c>
+      <c r="AG43">
         <v>2.55</v>
       </c>
-      <c r="AC43">
-        <v>2.24</v>
-      </c>
-      <c r="AD43">
-        <v>1.56</v>
-      </c>
-      <c r="AE43">
-        <v>1.2</v>
-      </c>
-      <c r="AF43">
-        <v>1.5</v>
-      </c>
-      <c r="AG43">
-        <v>2.45</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
         <v>1.36</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P44">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="R44">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S44">
         <v>1.16</v>
@@ -7502,13 +7502,13 @@
         <v>4.5</v>
       </c>
       <c r="U44">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V44">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7517,28 +7517,28 @@
         <v>1.09</v>
       </c>
       <c r="Z44">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="AA44">
         <v>1.33</v>
       </c>
       <c r="AB44">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AC44">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD44">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AE44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF44">
         <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="O46">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P46">
         <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="R46">
         <v>1.86</v>
@@ -7840,10 +7840,10 @@
         <v>1.12</v>
       </c>
       <c r="Y46">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z46">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AA46">
         <v>2.88</v>
@@ -7852,16 +7852,16 @@
         <v>1.4</v>
       </c>
       <c r="AC46">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AD46">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE46">
         <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AG46">
         <v>1.57</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="O47">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q47">
         <v>6.5</v>
@@ -7988,22 +7988,22 @@
         <v>1.38</v>
       </c>
       <c r="T47">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U47">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="V47">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
         <v>3.5</v>
@@ -8012,22 +8012,22 @@
         <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC47">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD47">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
         <v>2.15</v>
       </c>
       <c r="AG47">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>2.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
         <v>1.08</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O53">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
         <v>3</v>
       </c>
       <c r="Q53">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="R53">
         <v>2.07</v>
@@ -8969,10 +8969,10 @@
         <v>2.77</v>
       </c>
       <c r="U53">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V53">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
         <v>1.07</v>
@@ -8987,16 +8987,16 @@
         <v>3.14</v>
       </c>
       <c r="AA53">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC53">
         <v>3.28</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
@@ -9926,28 +9926,28 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.43</v>
+        <v>3.94</v>
       </c>
       <c r="O59">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="P59">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q59">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="R59">
         <v>1.95</v>
       </c>
       <c r="S59">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T59">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U59">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V59">
         <v>1.28</v>
@@ -9962,7 +9962,7 @@
         <v>1.45</v>
       </c>
       <c r="Z59">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AA59">
         <v>2.45</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="AF59">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG59">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P63">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q63">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R63">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S63">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="T63">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U63">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="V63">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W63">
         <v>1.03</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Z63">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AA63">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AB63">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC63">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AD63">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF63">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG63">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AK63">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,37 +10741,37 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O64">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P64">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q64">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="R64">
         <v>1.93</v>
       </c>
       <c r="S64">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T64">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="U64">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="V64">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
         <v>1.45</v>
@@ -10780,25 +10780,25 @@
         <v>2.55</v>
       </c>
       <c r="AA64">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB64">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC64">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD64">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF64">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AG64">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -12208,34 +12208,34 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>4.2</v>
+        <v>4.63</v>
       </c>
       <c r="Q73">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="R73">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T73">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="U73">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V73">
         <v>1.35</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -12244,16 +12244,16 @@
         <v>1.31</v>
       </c>
       <c r="Z73">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AA73">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AB73">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC73">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD73">
         <v>1.25</v>
@@ -12262,7 +12262,7 @@
         <v>1.06</v>
       </c>
       <c r="AF73">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG73">
         <v>1.91</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
         <v>2.11</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.23</v>
+        <v>1.25</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="P105">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="Q105">
+        <v>1.62</v>
+      </c>
+      <c r="R105">
         <v>2.88</v>
       </c>
-      <c r="R105">
-        <v>2.12</v>
-      </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T105">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="U105">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="V105">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="W105">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA105">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AB105">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="AC105">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF105">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG105">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.25</v>
+        <v>2.23</v>
       </c>
       <c r="O106">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="P106">
-        <v>7.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q106">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="R106">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="S106">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="U106">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="V106">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="W106">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="Z106">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB106">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC106">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AD106">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AK106">
-        <v>3.75</v>
+        <v>1.47</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,34 +19054,34 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q115">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="R115">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S115">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U115">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V115">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19099,10 +19099,10 @@
         <v>1.68</v>
       </c>
       <c r="AC115">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD115">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE115">
         <v>1.03</v>
@@ -19127,7 +19127,7 @@
         <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q117">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="R117">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="S117">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T117">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U117">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="V117">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W117">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z117">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA117">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AB117">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC117">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD117">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE117">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG117">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -20032,58 +20032,58 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="O121">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P121">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q121">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="R121">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T121">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="U121">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="V121">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W121">
         <v>1.04</v>
       </c>
       <c r="X121">
+        <v>1.05</v>
+      </c>
+      <c r="Y121">
+        <v>1.41</v>
+      </c>
+      <c r="Z121">
+        <v>2.52</v>
+      </c>
+      <c r="AA121">
+        <v>2.39</v>
+      </c>
+      <c r="AB121">
+        <v>1.51</v>
+      </c>
+      <c r="AC121">
+        <v>4.4</v>
+      </c>
+      <c r="AD121">
+        <v>1.18</v>
+      </c>
+      <c r="AE121">
         <v>1.03</v>
-      </c>
-      <c r="Y121">
-        <v>1.44</v>
-      </c>
-      <c r="Z121">
-        <v>2.7</v>
-      </c>
-      <c r="AA121">
-        <v>2.38</v>
-      </c>
-      <c r="AB121">
-        <v>1.57</v>
-      </c>
-      <c r="AC121">
-        <v>4.5</v>
-      </c>
-      <c r="AD121">
-        <v>1.2</v>
-      </c>
-      <c r="AE121">
-        <v>1.05</v>
       </c>
       <c r="AF121">
         <v>2.1</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK121">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -638,43 +638,43 @@
         <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA2">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB2">
         <v>2.05</v>
@@ -686,7 +686,7 @@
         <v>1.43</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
         <v>1.52</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>6.07</v>
+        <v>5.8</v>
       </c>
       <c r="R3">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S3">
         <v>1.25</v>
@@ -819,7 +819,7 @@
         <v>3.58</v>
       </c>
       <c r="U3">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V3">
         <v>1.62</v>
@@ -831,19 +831,19 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA3">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB3">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC3">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AD3">
         <v>1.58</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
         <v>1.11</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
         <v>1.2</v>
@@ -1157,25 +1157,25 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA5">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB5">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC5">
         <v>2.09</v>
       </c>
       <c r="AD5">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF5">
         <v>1.38</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK5">
         <v>1.38</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O6">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="Q6">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="R6">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="S6">
         <v>1.15</v>
@@ -1311,19 +1311,19 @@
         <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W6">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="AA6">
         <v>1.22</v>
@@ -1332,10 +1332,10 @@
         <v>3.5</v>
       </c>
       <c r="AC6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD6">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AE6">
         <v>1.43</v>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>3.1</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>3.54</v>
+        <v>3.36</v>
       </c>
       <c r="R7">
         <v>2.32</v>
@@ -1468,13 +1468,13 @@
         <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
         <v>1.13</v>
@@ -1489,22 +1489,22 @@
         <v>5.4</v>
       </c>
       <c r="AA7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
         <v>2.43</v>
       </c>
       <c r="AC7">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD7">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE7">
         <v>1.21</v>
       </c>
       <c r="AF7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG7">
         <v>2.43</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.1</v>
+        <v>4.68</v>
       </c>
       <c r="O15">
         <v>4.2</v>
@@ -2775,7 +2775,7 @@
         <v>3.45</v>
       </c>
       <c r="U15">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="V15">
         <v>1.58</v>
@@ -2787,22 +2787,22 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="AA15">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AB15">
+        <v>2.39</v>
+      </c>
+      <c r="AC15">
         <v>2.38</v>
       </c>
-      <c r="AC15">
-        <v>2.36</v>
-      </c>
       <c r="AD15">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE15">
         <v>1.16</v>
@@ -2811,7 +2811,7 @@
         <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4384,34 +4384,34 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O25">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>3.15</v>
       </c>
       <c r="U25">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.02</v>
@@ -4420,28 +4420,28 @@
         <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA25">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB25">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC25">
         <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE25">
         <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P26">
         <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
         <v>2.33</v>
@@ -4568,10 +4568,10 @@
         <v>4</v>
       </c>
       <c r="U26">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W26">
         <v>1.17</v>
@@ -4580,19 +4580,19 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA26">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB26">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD26">
         <v>1.5</v>
@@ -4604,7 +4604,7 @@
         <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.85</v>
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="O27">
         <v>3.3</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U27">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
         <v>1.05</v>
@@ -4743,31 +4743,31 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z27">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB27">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC27">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD27">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG27">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="Q28">
         <v>3.02</v>
       </c>
       <c r="R28">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
         <v>2.8</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1.05</v>
@@ -4909,7 +4909,7 @@
         <v>1.32</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AA28">
         <v>2</v>
@@ -4927,10 +4927,10 @@
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R29">
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q30">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA30">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB30">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK30">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q32">
         <v>2.3</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S32">
         <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
         <v>1.4</v>
@@ -5555,34 +5555,34 @@
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AA32">
         <v>1.85</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC32">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
         <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK32">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="P33">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q33">
         <v>2.23</v>
@@ -5706,22 +5706,22 @@
         <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U33">
         <v>2.85</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
         <v>3.1</v>
@@ -5739,10 +5739,10 @@
         <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG33">
         <v>1.77</v>
@@ -5761,7 +5761,7 @@
         <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6017,31 +6017,31 @@
         <v>2.6</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P35">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
         <v>3</v>
       </c>
       <c r="R35">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6053,7 +6053,7 @@
         <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB35">
         <v>2.15</v>
@@ -6062,16 +6062,16 @@
         <v>2.6</v>
       </c>
       <c r="AD35">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O36">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P36">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="S36">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T36">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U36">
         <v>3.5</v>
@@ -6216,7 +6216,7 @@
         <v>2.49</v>
       </c>
       <c r="AA36">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AB36">
         <v>1.54</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK36">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P37">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6509,10 +6509,10 @@
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q38">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="R38">
         <v>2.23</v>
@@ -6533,34 +6533,34 @@
         <v>1.13</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA38">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
         <v>2.62</v>
       </c>
       <c r="AD38">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE38">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF38">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,46 +6666,46 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q39">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U39">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
         <v>2.5</v>
@@ -6717,13 +6717,13 @@
         <v>1.65</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,28 +6829,28 @@
         </is>
       </c>
       <c r="N40">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="O40">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="P40">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q40">
         <v>5.42</v>
       </c>
       <c r="R40">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U40">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
         <v>1.65</v>
@@ -6862,28 +6862,28 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AA40">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC40">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AD40">
         <v>1.65</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG40">
         <v>2</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK40">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,22 +6992,22 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P41">
-        <v>4.45</v>
+        <v>4.81</v>
       </c>
       <c r="Q41">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R41">
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
         <v>3.3</v>
@@ -7016,7 +7016,7 @@
         <v>2.3</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
         <v>1.12</v>
@@ -7031,19 +7031,19 @@
         <v>4.1</v>
       </c>
       <c r="AA41">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB41">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AC41">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AD41">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
         <v>1.67</v>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="O42">
         <v>3.5</v>
       </c>
       <c r="P42">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q42">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="R42">
         <v>2.38</v>
@@ -7176,10 +7176,10 @@
         <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W42">
         <v>1.08</v>
@@ -7188,7 +7188,7 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
         <v>3.96</v>
@@ -7197,22 +7197,22 @@
         <v>1.68</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC42">
         <v>2.54</v>
       </c>
       <c r="AD42">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
         <v>1.54</v>
       </c>
       <c r="AG42">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>2.6</v>
       </c>
       <c r="O45">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
         <v>2.5</v>
@@ -7656,13 +7656,13 @@
         <v>3.2</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S45">
         <v>1.44</v>
       </c>
       <c r="T45">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U45">
         <v>3.18</v>
@@ -7680,16 +7680,16 @@
         <v>1.4</v>
       </c>
       <c r="Z45">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA45">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AB45">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC45">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD45">
         <v>1.2</v>
@@ -7698,10 +7698,10 @@
         <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK45">
         <v>1.44</v>
@@ -8139,31 +8139,31 @@
         <v>3.2</v>
       </c>
       <c r="P48">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="Q48">
         <v>2.7</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S48">
         <v>1.39</v>
       </c>
       <c r="T48">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U48">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V48">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.27</v>
@@ -8178,10 +8178,10 @@
         <v>1.77</v>
       </c>
       <c r="AC48">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AD48">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE48">
         <v>1.04</v>
@@ -8206,7 +8206,7 @@
         <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="Q49">
         <v>2.1</v>
@@ -8311,16 +8311,16 @@
         <v>2.45</v>
       </c>
       <c r="S49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U49">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V49">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
         <v>1.13</v>
@@ -8332,16 +8332,16 @@
         <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA49">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC49">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD49">
         <v>1.65</v>
@@ -8350,10 +8350,10 @@
         <v>1.26</v>
       </c>
       <c r="AF49">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O51">
         <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U51">
         <v>2.65</v>
@@ -8649,37 +8649,37 @@
         <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AA51">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AB51">
         <v>2.05</v>
       </c>
       <c r="AC51">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE51">
         <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK51">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,28 +8785,28 @@
         </is>
       </c>
       <c r="N52">
+        <v>4.36</v>
+      </c>
+      <c r="O52">
         <v>4</v>
       </c>
-      <c r="O52">
-        <v>4.05</v>
-      </c>
       <c r="P52">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q52">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="R52">
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
         <v>3.34</v>
       </c>
       <c r="U52">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
         <v>1.5</v>
@@ -8818,16 +8818,16 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z52">
         <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB52">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
         <v>2.54</v>
@@ -8842,7 +8842,7 @@
         <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9114,19 +9114,19 @@
         <v>2.25</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="Q54">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R54">
         <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
         <v>3.25</v>
@@ -9138,7 +9138,7 @@
         <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9150,7 +9150,7 @@
         <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB54">
         <v>2.1</v>
@@ -9165,10 +9165,10 @@
         <v>1.17</v>
       </c>
       <c r="AF54">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG54">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
         <v>1.49</v>
@@ -9452,13 +9452,13 @@
         <v>2.63</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U56">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="V56">
         <v>1.63</v>
@@ -9470,10 +9470,10 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>5.49</v>
+        <v>5.4</v>
       </c>
       <c r="AA56">
         <v>1.5</v>
@@ -9482,19 +9482,19 @@
         <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD56">
         <v>1.62</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9606,13 +9606,13 @@
         <v>3.75</v>
       </c>
       <c r="P57">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="Q57">
         <v>2.05</v>
       </c>
       <c r="R57">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="S57">
         <v>1.23</v>
@@ -9621,34 +9621,34 @@
         <v>3.42</v>
       </c>
       <c r="U57">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W57">
         <v>1.15</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
         <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="AA57">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC57">
         <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE57">
         <v>1.25</v>
@@ -9673,7 +9673,7 @@
         <v>1.14</v>
       </c>
       <c r="AK57">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,25 +9769,25 @@
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q58">
         <v>2.72</v>
       </c>
       <c r="R58">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U58">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
         <v>1.18</v>
@@ -9799,28 +9799,28 @@
         <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="AA58">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AC58">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD58">
         <v>1.62</v>
       </c>
       <c r="AE58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG58">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
         <v>1.41</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="O60">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P60">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>8.1</v>
+        <v>9.25</v>
       </c>
       <c r="O61">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="P61">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q61">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="R61">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -10285,19 +10285,19 @@
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AC61">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD61">
         <v>1.73</v>
@@ -10306,10 +10306,10 @@
         <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>3.7</v>
+        <v>4.12</v>
       </c>
       <c r="AK61">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="O62">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="P62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q62">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R62">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="S62">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T62">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U62">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AA62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB62">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD62">
         <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.11</v>
       </c>
       <c r="AK62">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N64">
@@ -10904,43 +10904,43 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="Q65">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="R65">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T65">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="U65">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V65">
         <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA65">
         <v>1.5</v>
@@ -10961,7 +10961,7 @@
         <v>1.53</v>
       </c>
       <c r="AG65">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,40 +11067,40 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O66">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>3.47</v>
+        <v>3.85</v>
       </c>
       <c r="Q66">
         <v>2.29</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S66">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U66">
         <v>2.56</v>
       </c>
       <c r="V66">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
         <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
         <v>3.78</v>
@@ -11112,7 +11112,7 @@
         <v>2.04</v>
       </c>
       <c r="AC66">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD66">
         <v>1.42</v>
@@ -11121,7 +11121,7 @@
         <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG66">
         <v>2.15</v>
@@ -11140,7 +11140,7 @@
         <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O67">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="P67">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="O68">
         <v>2.9</v>
       </c>
       <c r="P68">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q68">
         <v>3.48</v>
@@ -11411,10 +11411,10 @@
         <v>1.46</v>
       </c>
       <c r="T68">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="U68">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="V68">
         <v>1.28</v>
@@ -11423,34 +11423,34 @@
         <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
         <v>1.37</v>
       </c>
       <c r="Z68">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA68">
         <v>2.25</v>
       </c>
       <c r="AB68">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC68">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD68">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF68">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG68">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,65 +11556,65 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="O69">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="Q69">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S69">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="U69">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="V69">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z69">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA69">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AB69">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC69">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="AD69">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF69">
+        <v>1.86</v>
+      </c>
+      <c r="AG69">
         <v>1.84</v>
       </c>
-      <c r="AG69">
-        <v>1.9</v>
-      </c>
       <c r="AH69" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK69">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="O70">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P70">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="Q70">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="R70">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S70">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
         <v>2.77</v>
       </c>
       <c r="U70">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V70">
+        <v>1.36</v>
+      </c>
+      <c r="W70">
+        <v>1.06</v>
+      </c>
+      <c r="X70">
+        <v>1.03</v>
+      </c>
+      <c r="Y70">
         <v>1.32</v>
       </c>
-      <c r="W70">
-        <v>1.02</v>
-      </c>
-      <c r="X70">
-        <v>1.06</v>
-      </c>
-      <c r="Y70">
-        <v>1.36</v>
-      </c>
       <c r="Z70">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA70">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AB70">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC70">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD70">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
+        <v>1.89</v>
+      </c>
+      <c r="AG70">
         <v>1.87</v>
       </c>
-      <c r="AG70">
-        <v>1.86</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,55 +11891,55 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,55 +12054,55 @@
         <v>0</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12374,61 +12374,61 @@
         <v>1.53</v>
       </c>
       <c r="O74">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="P74">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="Q74">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R74">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T74">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="U74">
         <v>2</v>
       </c>
       <c r="V74">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W74">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z74">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AA74">
         <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="AC74">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD74">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE74">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF74">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG74">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK74">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="O76">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -12712,7 +12712,7 @@
         <v>2.3</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
         <v>3.45</v>
@@ -12721,25 +12721,25 @@
         <v>2.16</v>
       </c>
       <c r="V76">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W76">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA76">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB76">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC76">
         <v>2.31</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK76">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,22 +12860,22 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O77">
         <v>4</v>
       </c>
       <c r="P77">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q77">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R77">
         <v>2.6</v>
       </c>
       <c r="S77">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T77">
         <v>4</v>
@@ -12893,7 +12893,7 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z77">
         <v>5.75</v>
@@ -12902,16 +12902,16 @@
         <v>1.36</v>
       </c>
       <c r="AB77">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC77">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD77">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE77">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF77">
         <v>1.42</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="O78">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="R78">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T78">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U78">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V78">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W78">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z78">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA78">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB78">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AC78">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AD78">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE78">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF78">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG78">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AK78">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="O79">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q79">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="R79">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T79">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="U79">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="V79">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W79">
+        <v>1.15</v>
+      </c>
+      <c r="X79">
+        <v>1.02</v>
+      </c>
+      <c r="Y79">
+        <v>1.17</v>
+      </c>
+      <c r="Z79">
+        <v>4.65</v>
+      </c>
+      <c r="AA79">
+        <v>1.49</v>
+      </c>
+      <c r="AB79">
+        <v>2.29</v>
+      </c>
+      <c r="AC79">
+        <v>2.38</v>
+      </c>
+      <c r="AD79">
+        <v>1.58</v>
+      </c>
+      <c r="AE79">
         <v>1.2</v>
       </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.1</v>
-      </c>
-      <c r="Z79">
-        <v>5.3</v>
-      </c>
-      <c r="AA79">
-        <v>1.41</v>
-      </c>
-      <c r="AB79">
-        <v>2.65</v>
-      </c>
-      <c r="AC79">
-        <v>2.1</v>
-      </c>
-      <c r="AD79">
-        <v>1.71</v>
-      </c>
-      <c r="AE79">
-        <v>1.28</v>
-      </c>
       <c r="AF79">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AG79">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="O80">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P80">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q80">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R80">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U80">
         <v>2.2</v>
       </c>
       <c r="V80">
+        <v>1.57</v>
+      </c>
+      <c r="W80">
+        <v>1.13</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.14</v>
+      </c>
+      <c r="Z80">
+        <v>4.74</v>
+      </c>
+      <c r="AA80">
         <v>1.59</v>
       </c>
-      <c r="W80">
-        <v>1.15</v>
-      </c>
-      <c r="X80">
-        <v>1.02</v>
-      </c>
-      <c r="Y80">
-        <v>1.17</v>
-      </c>
-      <c r="Z80">
-        <v>4.65</v>
-      </c>
-      <c r="AA80">
-        <v>1.49</v>
-      </c>
       <c r="AB80">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="AC80">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD80">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE80">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF80">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AG80">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q81">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U81">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="V81">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA81">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AB81">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="AC81">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD81">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AE81">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.93</v>
+        <v>1.39</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>2.2</v>
+        <v>4.26</v>
       </c>
       <c r="Q82">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="U82">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="V82">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="Z82">
-        <v>4.45</v>
+        <v>5.3</v>
       </c>
       <c r="AA82">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.21</v>
+        <v>3.1</v>
       </c>
       <c r="AC82">
-        <v>2.49</v>
+        <v>1.96</v>
       </c>
       <c r="AD82">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AE82">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AF82">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG82">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <v>3.82</v>
+        <v>4.09</v>
       </c>
       <c r="R84">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="S84">
         <v>1.31</v>
       </c>
       <c r="T84">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="U84">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W84">
         <v>1.11</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y84">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
         <v>4.1</v>
       </c>
       <c r="AA84">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB84">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC84">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD84">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE84">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
         <v>1.57</v>
       </c>
       <c r="AG84">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AK84">
         <v>1.3</v>
@@ -14167,7 +14167,7 @@
         <v>1.91</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
         <v>3.3</v>
@@ -14176,7 +14176,7 @@
         <v>2.32</v>
       </c>
       <c r="R85">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S85">
         <v>1.22</v>
@@ -14185,7 +14185,7 @@
         <v>3.7</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V85">
         <v>1.66</v>
@@ -14194,34 +14194,34 @@
         <v>1.14</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AA85">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AB85">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AC85">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD85">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE85">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF85">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG85">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O86">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q86">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R86">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S86">
         <v>1.22</v>
@@ -14348,7 +14348,7 @@
         <v>3.75</v>
       </c>
       <c r="U86">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="V86">
         <v>1.7</v>
@@ -14363,28 +14363,28 @@
         <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>5.42</v>
+        <v>5.17</v>
       </c>
       <c r="AA86">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB86">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AC86">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD86">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF86">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG86">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P87">
-        <v>5.75</v>
+        <v>6.55</v>
       </c>
       <c r="Q87">
         <v>2</v>
@@ -14517,7 +14517,7 @@
         <v>1.37</v>
       </c>
       <c r="W87">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14535,7 +14535,7 @@
         <v>1.8</v>
       </c>
       <c r="AC87">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD87">
         <v>1.26</v>
@@ -14547,7 +14547,7 @@
         <v>2.03</v>
       </c>
       <c r="AG87">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O88">
         <v>3.2</v>
       </c>
       <c r="P88">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="Q88">
         <v>2.5</v>
       </c>
       <c r="R88">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S88">
         <v>1.48</v>
       </c>
       <c r="T88">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U88">
         <v>3.22</v>
@@ -14689,25 +14689,25 @@
         <v>1.37</v>
       </c>
       <c r="Z88">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AA88">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB88">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC88">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE88">
         <v>1.05</v>
       </c>
       <c r="AF88">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG88">
         <v>1.67</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK88">
         <v>1.91</v>
@@ -14825,19 +14825,19 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="R89">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V89">
         <v>1.44</v>
@@ -14849,31 +14849,31 @@
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z89">
         <v>3.54</v>
       </c>
       <c r="AA89">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB89">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AC89">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AD89">
         <v>1.34</v>
       </c>
       <c r="AE89">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF89">
         <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,49 +14979,49 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O90">
         <v>3.3</v>
       </c>
       <c r="P90">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q90">
         <v>3</v>
       </c>
       <c r="R90">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S90">
         <v>1.36</v>
       </c>
       <c r="T90">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="U90">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V90">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z90">
         <v>3.34</v>
       </c>
       <c r="AA90">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB90">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC90">
         <v>2.9</v>
@@ -15036,7 +15036,7 @@
         <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA91">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB91">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O92">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P92">
-        <v>5</v>
+        <v>5.79</v>
       </c>
       <c r="Q92">
         <v>1.89</v>
@@ -15323,25 +15323,25 @@
         <v>1.3</v>
       </c>
       <c r="T92">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U92">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W92">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA92">
         <v>1.62</v>
@@ -15359,10 +15359,10 @@
         <v>1.16</v>
       </c>
       <c r="AF92">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG92">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15468,34 +15468,34 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O93">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P93">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q93">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S93">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T93">
-        <v>3.01</v>
+        <v>2.76</v>
       </c>
       <c r="U93">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="V93">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -15504,13 +15504,13 @@
         <v>1.28</v>
       </c>
       <c r="Z93">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA93">
         <v>1.85</v>
       </c>
       <c r="AB93">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
         <v>3.2</v>
@@ -15519,10 +15519,10 @@
         <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG93">
         <v>1.75</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK93">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,31 +15631,31 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O94">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P94">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q94">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R94">
         <v>2.1</v>
       </c>
       <c r="S94">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T94">
         <v>2.66</v>
       </c>
       <c r="U94">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V94">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W94">
         <v>1.07</v>
@@ -15664,25 +15664,25 @@
         <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA94">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB94">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC94">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE94">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF94">
         <v>1.75</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK94">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,43 +15794,43 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="O95">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="P95">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="Q95">
         <v>1.57</v>
       </c>
       <c r="R95">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S95">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="T95">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="U95">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V95">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="W95">
         <v>1.3</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
         <v>1.01</v>
       </c>
       <c r="Z95">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA95">
         <v>1.17</v>
@@ -15845,13 +15845,13 @@
         <v>2.4</v>
       </c>
       <c r="AE95">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AF95">
         <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.06</v>
       </c>
       <c r="AK95">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O96">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P96">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q96">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R96">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S96">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T96">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="U96">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V96">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W96">
         <v>1.06</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="AA96">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB96">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC96">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD96">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE96">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF96">
         <v>1.71</v>
       </c>
       <c r="AG96">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="O97">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P97">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q97">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R97">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
         <v>1.28</v>
@@ -16141,43 +16141,43 @@
         <v>3.18</v>
       </c>
       <c r="U97">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="V97">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W97">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X97">
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z97">
-        <v>4.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA97">
         <v>1.52</v>
       </c>
       <c r="AB97">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC97">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AD97">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE97">
         <v>1.12</v>
       </c>
       <c r="AF97">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AG97">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK97">
         <v>1.01</v>
@@ -16283,58 +16283,58 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O98">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="P98">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
       </c>
       <c r="R98">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U98">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V98">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W98">
         <v>1.09</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z98">
         <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB98">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC98">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD98">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE98">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF98">
         <v>1.65</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
         <v>1.22</v>
@@ -16938,16 +16938,16 @@
         <v>2.7</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q102">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="R102">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S102">
         <v>1.28</v>
@@ -16959,7 +16959,7 @@
         <v>2.3</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W102">
         <v>1.07</v>
@@ -16968,10 +16968,10 @@
         <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z102">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA102">
         <v>1.65</v>
@@ -16980,19 +16980,19 @@
         <v>2.11</v>
       </c>
       <c r="AC102">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD102">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE102">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF102">
         <v>1.53</v>
       </c>
       <c r="AG102">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O103">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="P103">
-        <v>6.7</v>
+        <v>6.15</v>
       </c>
       <c r="Q103">
         <v>1.8</v>
       </c>
       <c r="R103">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T103">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="U103">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V103">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W103">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z103">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA103">
         <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AC103">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD103">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE103">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF103">
         <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK103">
         <v>2.88</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O104">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P104">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA104">
         <v>1.95</v>
       </c>
       <c r="AB104">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17430,25 +17430,25 @@
         <v>5.5</v>
       </c>
       <c r="P105">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R105">
         <v>2.88</v>
       </c>
       <c r="S105">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T105">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="U105">
         <v>1.93</v>
       </c>
       <c r="V105">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W105">
         <v>1.17</v>
@@ -17466,23 +17466,23 @@
         <v>1.35</v>
       </c>
       <c r="AB105">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC105">
+        <v>1.95</v>
+      </c>
+      <c r="AD105">
+        <v>1.76</v>
+      </c>
+      <c r="AE105">
+        <v>1.3</v>
+      </c>
+      <c r="AF105">
+        <v>1.75</v>
+      </c>
+      <c r="AG105">
         <v>2</v>
       </c>
-      <c r="AD105">
-        <v>1.8</v>
-      </c>
-      <c r="AE105">
-        <v>1.33</v>
-      </c>
-      <c r="AF105">
-        <v>1.67</v>
-      </c>
-      <c r="AG105">
-        <v>2.1</v>
-      </c>
       <c r="AH105" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK105">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O106">
         <v>3.25</v>
@@ -17602,37 +17602,37 @@
         <v>2.12</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T106">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U106">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V106">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W106">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y106">
         <v>1.23</v>
       </c>
       <c r="Z106">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA106">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB106">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC106">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="AD106">
         <v>1.3</v>
@@ -17644,7 +17644,7 @@
         <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17753,61 +17753,61 @@
         <v>1.36</v>
       </c>
       <c r="O107">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="P107">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q107">
         <v>1.8</v>
       </c>
       <c r="R107">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T107">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U107">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V107">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z107">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="AA107">
         <v>1.8</v>
       </c>
       <c r="AB107">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC107">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD107">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF107">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG107">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK107">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O108">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P108">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18239,22 +18239,22 @@
         </is>
       </c>
       <c r="N110">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="O110">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P110">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q110">
-        <v>5.44</v>
+        <v>5.25</v>
       </c>
       <c r="R110">
         <v>2.4</v>
       </c>
       <c r="S110">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T110">
         <v>3.25</v>
@@ -18263,40 +18263,40 @@
         <v>2.4</v>
       </c>
       <c r="V110">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W110">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
         <v>1.21</v>
       </c>
       <c r="Z110">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA110">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB110">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC110">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AD110">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE110">
         <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG110">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AK110">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18568,28 +18568,28 @@
         <v>2.15</v>
       </c>
       <c r="O112">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="P112">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q112">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="R112">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S112">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T112">
         <v>2.63</v>
       </c>
       <c r="U112">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V112">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W112">
         <v>1.05</v>
@@ -18601,16 +18601,16 @@
         <v>1.42</v>
       </c>
       <c r="Z112">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AA112">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AB112">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC112">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AD112">
         <v>1.18</v>
@@ -18619,7 +18619,7 @@
         <v>1.02</v>
       </c>
       <c r="AF112">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG112">
         <v>1.8</v>
@@ -18638,7 +18638,7 @@
         <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,16 +18728,16 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="O113">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q113">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="R113">
         <v>2.05</v>
@@ -18749,43 +18749,43 @@
         <v>2.9</v>
       </c>
       <c r="U113">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V113">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W113">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z113">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AA113">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB113">
         <v>1.8</v>
       </c>
       <c r="AC113">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="AD113">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE113">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG113">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
         <v>1.53</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,43 +18891,43 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O114">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q114">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="R114">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S114">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U114">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="V114">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W114">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z114">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA114">
         <v>2.04</v>
@@ -18936,19 +18936,19 @@
         <v>1.68</v>
       </c>
       <c r="AC114">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD114">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE114">
         <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG114">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q115">
-        <v>2.69</v>
+        <v>3.48</v>
       </c>
       <c r="R115">
         <v>1.99</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T115">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U115">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="V115">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W115">
         <v>1.02</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z115">
         <v>2.97</v>
       </c>
       <c r="AA115">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AB115">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC115">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD115">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE115">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK115">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
+        <v>2.15</v>
+      </c>
+      <c r="O117">
         <v>3</v>
       </c>
-      <c r="O117">
-        <v>3.1</v>
-      </c>
       <c r="P117">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q117">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="R117">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S117">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T117">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="U117">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V117">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W117">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z117">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA117">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB117">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC117">
         <v>3.5</v>
       </c>
       <c r="AD117">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE117">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF117">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG117">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK117">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O118">
         <v>3.15</v>
@@ -19552,19 +19552,19 @@
         <v>2.25</v>
       </c>
       <c r="Q118">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R118">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T118">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U118">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V118">
         <v>1.35</v>
@@ -19573,22 +19573,22 @@
         <v>1.04</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z118">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA118">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB118">
         <v>1.77</v>
       </c>
       <c r="AC118">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD118">
         <v>1.28</v>
@@ -19597,10 +19597,10 @@
         <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG118">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AK118">
         <v>1.36</v>
@@ -19712,7 +19712,7 @@
         <v>4.9</v>
       </c>
       <c r="P119">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q119">
         <v>7.5</v>
@@ -19721,19 +19721,19 @@
         <v>2.62</v>
       </c>
       <c r="S119">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T119">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U119">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V119">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W119">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X119">
         <v>1.01</v>
@@ -19745,25 +19745,25 @@
         <v>4.7</v>
       </c>
       <c r="AA119">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB119">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AC119">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD119">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AE119">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF119">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG119">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK119">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19875,13 +19875,13 @@
         <v>3.15</v>
       </c>
       <c r="P120">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q120">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="R120">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S120">
         <v>1.38</v>
@@ -19893,40 +19893,40 @@
         <v>2.7</v>
       </c>
       <c r="V120">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W120">
         <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="AA120">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AB120">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC120">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="AD120">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE120">
         <v>1.1</v>
       </c>
       <c r="AF120">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG120">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="O122">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P122">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="Q122">
         <v>2.1</v>
@@ -20213,10 +20213,10 @@
         <v>1.38</v>
       </c>
       <c r="T122">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U122">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V122">
         <v>1.34</v>
@@ -20237,7 +20237,7 @@
         <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC122">
         <v>3.5</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O124">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P124">
         <v>4.46</v>
@@ -20533,7 +20533,7 @@
         <v>2.52</v>
       </c>
       <c r="R124">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S124">
         <v>1.44</v>
@@ -20542,7 +20542,7 @@
         <v>2.62</v>
       </c>
       <c r="U124">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="V124">
         <v>1.33</v>
@@ -20557,19 +20557,19 @@
         <v>1.35</v>
       </c>
       <c r="Z124">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="AA124">
         <v>2.23</v>
       </c>
       <c r="AB124">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC124">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AD124">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE124">
         <v>1.01</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O125">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P125">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q125">
+        <v>2.3</v>
+      </c>
+      <c r="R125">
         <v>2.4</v>
       </c>
-      <c r="R125">
-        <v>2.38</v>
-      </c>
       <c r="S125">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T125">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U125">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="V125">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W125">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X125">
         <v>1.01</v>
       </c>
       <c r="Y125">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z125">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA125">
         <v>1.44</v>
       </c>
       <c r="AB125">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC125">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD125">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE125">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF125">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AG125">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK125">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="O126">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P126">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q126">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="R126">
         <v>2.15</v>
       </c>
       <c r="S126">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="U126">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="V126">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W126">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X126">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z126">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA126">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB126">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC126">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AD126">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE126">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG126">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,19 +21010,19 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O127">
         <v>3.2</v>
       </c>
       <c r="P127">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q127">
         <v>2.49</v>
       </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S127">
         <v>1.47</v>
@@ -21034,34 +21034,34 @@
         <v>3.2</v>
       </c>
       <c r="V127">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W127">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y127">
         <v>1.4</v>
       </c>
       <c r="Z127">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA127">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB127">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC127">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AD127">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE127">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF127">
         <v>1.85</v>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK127">
         <v>1.7</v>
@@ -21173,16 +21173,16 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="O128">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P128">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q128">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R128">
         <v>2.02</v>
@@ -21194,7 +21194,7 @@
         <v>2.7</v>
       </c>
       <c r="U128">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V128">
         <v>1.35</v>
@@ -21206,25 +21206,25 @@
         <v>1.04</v>
       </c>
       <c r="Y128">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z128">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA128">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB128">
         <v>1.73</v>
       </c>
       <c r="AC128">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AD128">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE128">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF128">
         <v>1.95</v>
@@ -21246,7 +21246,7 @@
         <v>1.28</v>
       </c>
       <c r="AK128">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O129">
         <v>2.9</v>
       </c>
       <c r="P129">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q129">
         <v>2.9</v>
       </c>
       <c r="R129">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="S129">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T129">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U129">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="V129">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W129">
         <v>1.01</v>
       </c>
       <c r="X129">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y129">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z129">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA129">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AB129">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC129">
         <v>4.75</v>
       </c>
       <c r="AD129">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE129">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF129">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AG129">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>1.29</v>
       </c>
       <c r="AK129">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21514,19 +21514,19 @@
         <v>2.29</v>
       </c>
       <c r="S130">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T130">
         <v>2.97</v>
       </c>
       <c r="U130">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V130">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W130">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X130">
         <v>1.01</v>
@@ -21535,28 +21535,28 @@
         <v>1.21</v>
       </c>
       <c r="Z130">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA130">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB130">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC130">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AD130">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE130">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF130">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG130">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK130">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21825,10 +21825,10 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O132">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="P132">
         <v>4.5</v>
@@ -21843,10 +21843,10 @@
         <v>1.57</v>
       </c>
       <c r="T132">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U132">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="V132">
         <v>1.21</v>
@@ -21855,16 +21855,16 @@
         <v>1.03</v>
       </c>
       <c r="X132">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y132">
         <v>1.5</v>
       </c>
       <c r="Z132">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AA132">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AB132">
         <v>1.44</v>
@@ -21873,16 +21873,16 @@
         <v>5</v>
       </c>
       <c r="AD132">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE132">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF132">
         <v>2.3</v>
       </c>
       <c r="AG132">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK132">
         <v>1.81</v>
@@ -22009,7 +22009,7 @@
         <v>3.6</v>
       </c>
       <c r="U133">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V133">
         <v>1.57</v>
@@ -22027,25 +22027,25 @@
         <v>4.8</v>
       </c>
       <c r="AA133">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB133">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AC133">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD133">
         <v>1.52</v>
       </c>
       <c r="AE133">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF133">
         <v>1.6</v>
       </c>
       <c r="AG133">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.28</v>
+        <v>3.85</v>
       </c>
       <c r="Q65">
-        <v>3.48</v>
+        <v>2.29</v>
       </c>
       <c r="R65">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U65">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="V65">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="W65">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="AA65">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AC65">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="AD65">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AE65">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF65">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="O67">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="P67">
-        <v>2.71</v>
+        <v>2.28</v>
       </c>
       <c r="Q67">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S67">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="T67">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="U67">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z67">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB67">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC67">
-        <v>2.94</v>
+        <v>4.33</v>
       </c>
       <c r="AD67">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AG67">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,55 +11393,55 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P68">
-        <v>3.85</v>
+        <v>2.71</v>
       </c>
       <c r="Q68">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T68">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U68">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="V68">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="AA68">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB68">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AC68">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AD68">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE68">
         <v>1.1</v>
@@ -11450,7 +11450,7 @@
         <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="O97">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P97">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="Q97">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="R97">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="S97">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="U97">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="V97">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W97">
+        <v>1.13</v>
+      </c>
+      <c r="X97">
+        <v>1.01</v>
+      </c>
+      <c r="Y97">
+        <v>1.14</v>
+      </c>
+      <c r="Z97">
+        <v>5.5</v>
+      </c>
+      <c r="AA97">
+        <v>1.51</v>
+      </c>
+      <c r="AB97">
+        <v>2.27</v>
+      </c>
+      <c r="AC97">
+        <v>2.35</v>
+      </c>
+      <c r="AD97">
+        <v>1.57</v>
+      </c>
+      <c r="AE97">
+        <v>1.22</v>
+      </c>
+      <c r="AF97">
+        <v>1.81</v>
+      </c>
+      <c r="AG97">
+        <v>1.87</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
         <v>1.08</v>
       </c>
-      <c r="X97">
-        <v>1.02</v>
-      </c>
-      <c r="Y97">
-        <v>1.22</v>
-      </c>
-      <c r="Z97">
-        <v>4.1</v>
-      </c>
-      <c r="AA97">
-        <v>1.76</v>
-      </c>
-      <c r="AB97">
-        <v>2.03</v>
-      </c>
-      <c r="AC97">
-        <v>2.95</v>
-      </c>
-      <c r="AD97">
-        <v>1.36</v>
-      </c>
-      <c r="AE97">
-        <v>1.11</v>
-      </c>
-      <c r="AF97">
-        <v>1.6</v>
-      </c>
-      <c r="AG97">
-        <v>2.16</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.25</v>
-      </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="P98">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="Q98">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="R98">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="S98">
+        <v>1.33</v>
+      </c>
+      <c r="T98">
+        <v>3.25</v>
+      </c>
+      <c r="U98">
+        <v>2.56</v>
+      </c>
+      <c r="V98">
+        <v>1.45</v>
+      </c>
+      <c r="W98">
+        <v>1.08</v>
+      </c>
+      <c r="X98">
+        <v>1.02</v>
+      </c>
+      <c r="Y98">
         <v>1.22</v>
       </c>
-      <c r="T98">
-        <v>3.45</v>
-      </c>
-      <c r="U98">
-        <v>2.2</v>
-      </c>
-      <c r="V98">
+      <c r="Z98">
+        <v>4.1</v>
+      </c>
+      <c r="AA98">
+        <v>1.76</v>
+      </c>
+      <c r="AB98">
+        <v>2.03</v>
+      </c>
+      <c r="AC98">
+        <v>2.95</v>
+      </c>
+      <c r="AD98">
+        <v>1.36</v>
+      </c>
+      <c r="AE98">
+        <v>1.11</v>
+      </c>
+      <c r="AF98">
         <v>1.6</v>
       </c>
-      <c r="W98">
-        <v>1.13</v>
-      </c>
-      <c r="X98">
-        <v>1.01</v>
-      </c>
-      <c r="Y98">
-        <v>1.14</v>
-      </c>
-      <c r="Z98">
-        <v>5.5</v>
-      </c>
-      <c r="AA98">
-        <v>1.51</v>
-      </c>
-      <c r="AB98">
-        <v>2.27</v>
-      </c>
-      <c r="AC98">
-        <v>2.35</v>
-      </c>
-      <c r="AD98">
-        <v>1.57</v>
-      </c>
-      <c r="AE98">
-        <v>1.22</v>
-      </c>
-      <c r="AF98">
-        <v>1.81</v>
-      </c>
       <c r="AG98">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="O102">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="P102">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="Q102">
-        <v>1.64</v>
+        <v>2.49</v>
       </c>
       <c r="R102">
+        <v>2.11</v>
+      </c>
+      <c r="S102">
+        <v>1.36</v>
+      </c>
+      <c r="T102">
         <v>2.88</v>
       </c>
-      <c r="S102">
-        <v>1.18</v>
-      </c>
-      <c r="T102">
-        <v>3.9</v>
-      </c>
       <c r="U102">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="V102">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y102">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Z102">
-        <v>5.65</v>
+        <v>3.55</v>
       </c>
       <c r="AA102">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB102">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC102">
-        <v>1.95</v>
+        <v>3.14</v>
       </c>
       <c r="AD102">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AF102">
         <v>1.75</v>
       </c>
       <c r="AG102">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AK102">
-        <v>3.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.35</v>
+        <v>1.25</v>
       </c>
       <c r="O103">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="P103">
-        <v>2.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q103">
+        <v>1.64</v>
+      </c>
+      <c r="R103">
         <v>2.88</v>
       </c>
-      <c r="R103">
-        <v>2.12</v>
-      </c>
       <c r="S103">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="T103">
-        <v>3.13</v>
+        <v>3.9</v>
       </c>
       <c r="U103">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="V103">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Z103">
-        <v>3.72</v>
+        <v>5.65</v>
       </c>
       <c r="AA103">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AB103">
+        <v>2.75</v>
+      </c>
+      <c r="AC103">
         <v>1.95</v>
       </c>
-      <c r="AC103">
-        <v>2.97</v>
-      </c>
       <c r="AD103">
+        <v>1.76</v>
+      </c>
+      <c r="AE103">
         <v>1.3</v>
       </c>
-      <c r="AE103">
-        <v>1.13</v>
-      </c>
       <c r="AF103">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG103">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AK103">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="O104">
         <v>3.25</v>
       </c>
       <c r="P104">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q104">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S104">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T104">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U104">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V104">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z104">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="AA104">
+        <v>1.84</v>
+      </c>
+      <c r="AB104">
         <v>1.95</v>
       </c>
-      <c r="AB104">
-        <v>1.83</v>
-      </c>
       <c r="AC104">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD104">
         <v>1.3</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF104">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O120">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P120">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
       </c>
       <c r="R120">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S120">
         <v>1.3</v>
@@ -19911,10 +19911,10 @@
         <v>1.73</v>
       </c>
       <c r="AB120">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC120">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD120">
         <v>1.34</v>
@@ -19926,7 +19926,7 @@
         <v>1.61</v>
       </c>
       <c r="AG120">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
         <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q9">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U9">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
         <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB9">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AC9">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="O10">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="Q10">
         <v>3.55</v>
       </c>
       <c r="R10">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U10">
         <v>3.82</v>
@@ -1966,22 +1966,22 @@
         <v>1.19</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1.13</v>
       </c>
       <c r="Y10">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z10">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AA10">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="AB10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC10">
         <v>5.97</v>
@@ -2012,7 +2012,7 @@
         <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="O11">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P11">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U11">
         <v>3.8</v>
@@ -2135,16 +2135,16 @@
         <v>1.13</v>
       </c>
       <c r="Y11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z11">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AA11">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AB11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC11">
         <v>4.85</v>
@@ -2153,13 +2153,13 @@
         <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
         <v>2.07</v>
       </c>
       <c r="AG11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK11">
         <v>1.44</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="O13">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="Q13">
         <v>2.07</v>
       </c>
       <c r="R13">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="S13">
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="U13">
         <v>2</v>
@@ -2461,22 +2461,22 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>5.74</v>
+        <v>5.82</v>
       </c>
       <c r="AA13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
         <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AD13">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE13">
         <v>1.25</v>
@@ -2485,7 +2485,7 @@
         <v>1.45</v>
       </c>
       <c r="AG13">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK13">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.68</v>
+        <v>4.1</v>
       </c>
       <c r="O15">
         <v>4.2</v>
@@ -2763,7 +2763,7 @@
         <v>1.66</v>
       </c>
       <c r="Q15">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="R15">
         <v>2.39</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.84</v>
+        <v>4.75</v>
       </c>
       <c r="AA15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB15">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AC15">
         <v>2.38</v>
       </c>
       <c r="AD15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE15">
         <v>1.16</v>
       </c>
       <c r="AF15">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
         <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -2932,43 +2932,43 @@
         <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z16">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
         <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
         <v>1.8</v>
@@ -2990,7 +2990,7 @@
         <v>1.42</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="O17">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="P17">
-        <v>3.44</v>
+        <v>2.83</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="O18">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="P18">
         <v>1.69</v>
       </c>
       <c r="Q18">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>1.95</v>
@@ -3297,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG18">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O19">
         <v>2.6</v>
@@ -3415,7 +3415,7 @@
         <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="R19">
         <v>1.68</v>
@@ -3427,7 +3427,7 @@
         <v>1.95</v>
       </c>
       <c r="U19">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="V19">
         <v>1.12</v>
@@ -3439,7 +3439,7 @@
         <v>1.13</v>
       </c>
       <c r="Y19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z19">
         <v>1.87</v>
@@ -3448,7 +3448,7 @@
         <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC19">
         <v>7.8</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="O20">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>2.87</v>
       </c>
       <c r="P21">
-        <v>5.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>2.3</v>
       </c>
       <c r="O24">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -4236,7 +4236,7 @@
         <v>1.82</v>
       </c>
       <c r="S24">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T24">
         <v>2.22</v>
@@ -4257,7 +4257,7 @@
         <v>1.58</v>
       </c>
       <c r="Z24">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA24">
         <v>2.74</v>
@@ -4272,7 +4272,7 @@
         <v>1.07</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
         <v>2.23</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
         <v>1.47</v>
@@ -5045,10 +5045,10 @@
         <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S29">
         <v>1.35</v>
@@ -5057,7 +5057,7 @@
         <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="V29">
         <v>1.41</v>
@@ -5075,25 +5075,25 @@
         <v>3.28</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC29">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG29">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,37 +5199,37 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
         <v>4.8</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U30">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
         <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30">
         <v>1.3</v>
@@ -5238,7 +5238,7 @@
         <v>3.25</v>
       </c>
       <c r="AA30">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
         <v>1.8</v>
@@ -5250,13 +5250,13 @@
         <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         <v>4.74</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R31">
         <v>1.95</v>
@@ -5383,10 +5383,10 @@
         <v>2.38</v>
       </c>
       <c r="U31">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V31">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5398,7 +5398,7 @@
         <v>1.45</v>
       </c>
       <c r="Z31">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AA31">
         <v>2.45</v>
@@ -5435,7 +5435,7 @@
         <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q32">
         <v>2.3</v>
@@ -5540,10 +5540,10 @@
         <v>2.16</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
         <v>2.6</v>
@@ -5555,13 +5555,13 @@
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
         <v>1.85</v>
@@ -5573,7 +5573,7 @@
         <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
         <v>1.08</v>
@@ -5582,7 +5582,7 @@
         <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>4.09</v>
       </c>
       <c r="Q34">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R34">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
+        <v>1.07</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>1.22</v>
+      </c>
+      <c r="Z34">
+        <v>3.6</v>
+      </c>
+      <c r="AA34">
+        <v>1.75</v>
+      </c>
+      <c r="AB34">
+        <v>2.05</v>
+      </c>
+      <c r="AC34">
+        <v>2.74</v>
+      </c>
+      <c r="AD34">
+        <v>1.35</v>
+      </c>
+      <c r="AE34">
         <v>1.11</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.18</v>
-      </c>
-      <c r="Z34">
-        <v>3.86</v>
-      </c>
-      <c r="AA34">
-        <v>1.74</v>
-      </c>
-      <c r="AB34">
-        <v>2.04</v>
-      </c>
-      <c r="AC34">
-        <v>2.7</v>
-      </c>
-      <c r="AD34">
-        <v>1.36</v>
-      </c>
-      <c r="AE34">
-        <v>1.1</v>
       </c>
       <c r="AF34">
         <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q43">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R43">
         <v>2.35</v>
@@ -7336,46 +7336,46 @@
         <v>1.24</v>
       </c>
       <c r="T43">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V43">
         <v>1.58</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB43">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AC43">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AD43">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE43">
         <v>1.22</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG43">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="O44">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Q44">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="R44">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S44">
         <v>1.16</v>
       </c>
       <c r="T44">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U44">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V44">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W44">
         <v>1.22</v>
@@ -7514,31 +7514,31 @@
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z44">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="AA44">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB44">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AC44">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AD44">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AE44">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF44">
         <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P46">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q46">
-        <v>6.5</v>
+        <v>7.21</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="U46">
         <v>2.7</v>
@@ -7837,34 +7837,34 @@
         <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z46">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA46">
         <v>1.95</v>
       </c>
       <c r="AB46">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC46">
         <v>3.28</v>
       </c>
       <c r="AD46">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,28 +7970,28 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
         <v>2.6</v>
       </c>
       <c r="P47">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q47">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R47">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="S47">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="T47">
         <v>2.04</v>
       </c>
       <c r="U47">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="V47">
         <v>1.18</v>
@@ -8000,16 +8000,16 @@
         <v>1.01</v>
       </c>
       <c r="X47">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y47">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z47">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AA47">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AB47">
         <v>1.4</v>
@@ -8018,16 +8018,16 @@
         <v>5.3</v>
       </c>
       <c r="AD47">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE47">
         <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG47">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8948,31 +8948,31 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q53">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="R53">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T53">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U53">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W53">
         <v>1.07</v>
@@ -8990,13 +8990,13 @@
         <v>1.97</v>
       </c>
       <c r="AB53">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC53">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AD53">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O54">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q54">
         <v>2.88</v>
@@ -9126,43 +9126,43 @@
         <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
         <v>3.25</v>
       </c>
       <c r="U54">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V54">
         <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z54">
         <v>4.1</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC54">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="AD54">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF54">
         <v>1.52</v>
@@ -9184,7 +9184,7 @@
         <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="O56">
         <v>4</v>
       </c>
       <c r="P56">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q56">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T56">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U56">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W56">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>5.4</v>
+        <v>4.85</v>
       </c>
       <c r="AA56">
         <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC56">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AD56">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
         <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,46 +9600,46 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="O57">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q57">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="R57">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="S57">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T57">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U57">
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
         <v>4.85</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB57">
         <v>2.37</v>
@@ -9648,16 +9648,16 @@
         <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE57">
         <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG57">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AK57">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
+        <v>1.56</v>
+      </c>
+      <c r="O58">
+        <v>4.35</v>
+      </c>
+      <c r="P58">
+        <v>4.65</v>
+      </c>
+      <c r="Q58">
+        <v>2.05</v>
+      </c>
+      <c r="R58">
         <v>2.45</v>
       </c>
-      <c r="O58">
-        <v>3.4</v>
-      </c>
-      <c r="P58">
-        <v>2.37</v>
-      </c>
-      <c r="Q58">
-        <v>2.72</v>
-      </c>
-      <c r="R58">
-        <v>2.31</v>
-      </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U58">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9799,28 +9799,28 @@
         <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>4.85</v>
+        <v>5.53</v>
       </c>
       <c r="AA58">
         <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC58">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD58">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE58">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="O59">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q59">
         <v>4.5</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.15</v>
+        <v>9.25</v>
       </c>
       <c r="O61">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="P61">
-        <v>11</v>
+        <v>1.21</v>
       </c>
       <c r="Q61">
-        <v>1.57</v>
+        <v>6.75</v>
       </c>
       <c r="R61">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="S61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U61">
         <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AC61">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AD61">
+        <v>1.73</v>
+      </c>
+      <c r="AE61">
+        <v>1.28</v>
+      </c>
+      <c r="AF61">
         <v>1.82</v>
       </c>
-      <c r="AE61">
-        <v>1.31</v>
-      </c>
-      <c r="AF61">
-        <v>1.78</v>
-      </c>
       <c r="AG61">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>4.14</v>
       </c>
       <c r="AK61">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>9.25</v>
+        <v>1.15</v>
       </c>
       <c r="O62">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="P62">
-        <v>1.21</v>
+        <v>11</v>
       </c>
       <c r="Q62">
-        <v>6.75</v>
+        <v>1.57</v>
       </c>
       <c r="R62">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U62">
         <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB62">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AD62">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF62">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG62">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>4.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK62">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,65 +10741,65 @@
         </is>
       </c>
       <c r="N64">
+        <v>1.8</v>
+      </c>
+      <c r="O64">
+        <v>3.5</v>
+      </c>
+      <c r="P64">
+        <v>3.85</v>
+      </c>
+      <c r="Q64">
+        <v>2.29</v>
+      </c>
+      <c r="R64">
+        <v>2.25</v>
+      </c>
+      <c r="S64">
+        <v>1.35</v>
+      </c>
+      <c r="T64">
+        <v>3.1</v>
+      </c>
+      <c r="U64">
+        <v>2.56</v>
+      </c>
+      <c r="V64">
+        <v>1.47</v>
+      </c>
+      <c r="W64">
+        <v>1.11</v>
+      </c>
+      <c r="X64">
+        <v>1.04</v>
+      </c>
+      <c r="Y64">
+        <v>1.19</v>
+      </c>
+      <c r="Z64">
+        <v>3.78</v>
+      </c>
+      <c r="AA64">
+        <v>1.75</v>
+      </c>
+      <c r="AB64">
+        <v>2.04</v>
+      </c>
+      <c r="AC64">
+        <v>2.7</v>
+      </c>
+      <c r="AD64">
+        <v>1.42</v>
+      </c>
+      <c r="AE64">
+        <v>1.1</v>
+      </c>
+      <c r="AF64">
         <v>1.62</v>
       </c>
-      <c r="O64">
-        <v>3.7</v>
-      </c>
-      <c r="P64">
-        <v>4.6</v>
-      </c>
-      <c r="Q64">
-        <v>2.25</v>
-      </c>
-      <c r="R64">
+      <c r="AG64">
         <v>2.15</v>
       </c>
-      <c r="S64">
-        <v>1.39</v>
-      </c>
-      <c r="T64">
-        <v>2.77</v>
-      </c>
-      <c r="U64">
-        <v>2.88</v>
-      </c>
-      <c r="V64">
-        <v>1.36</v>
-      </c>
-      <c r="W64">
-        <v>1.06</v>
-      </c>
-      <c r="X64">
-        <v>1.03</v>
-      </c>
-      <c r="Y64">
-        <v>1.32</v>
-      </c>
-      <c r="Z64">
-        <v>3.2</v>
-      </c>
-      <c r="AA64">
-        <v>1.99</v>
-      </c>
-      <c r="AB64">
-        <v>1.83</v>
-      </c>
-      <c r="AC64">
-        <v>3.4</v>
-      </c>
-      <c r="AD64">
-        <v>1.25</v>
-      </c>
-      <c r="AE64">
-        <v>1.05</v>
-      </c>
-      <c r="AF64">
-        <v>1.89</v>
-      </c>
-      <c r="AG64">
-        <v>1.87</v>
-      </c>
       <c r="AH64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P65">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q65">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
+        <v>2.79</v>
+      </c>
+      <c r="U65">
+        <v>3.12</v>
+      </c>
+      <c r="V65">
+        <v>1.32</v>
+      </c>
+      <c r="W65">
+        <v>1.07</v>
+      </c>
+      <c r="X65">
+        <v>1.01</v>
+      </c>
+      <c r="Y65">
+        <v>1.33</v>
+      </c>
+      <c r="Z65">
         <v>3.1</v>
       </c>
-      <c r="U65">
-        <v>2.56</v>
-      </c>
-      <c r="V65">
-        <v>1.47</v>
-      </c>
-      <c r="W65">
-        <v>1.11</v>
-      </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
-      <c r="Y65">
-        <v>1.19</v>
-      </c>
-      <c r="Z65">
-        <v>3.78</v>
-      </c>
       <c r="AA65">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AB65">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD65">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AG65">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P66">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="Q66">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="S66">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T66">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="U66">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V66">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.37</v>
+      </c>
+      <c r="Z66">
+        <v>2.88</v>
+      </c>
+      <c r="AA66">
+        <v>2.25</v>
+      </c>
+      <c r="AB66">
+        <v>1.57</v>
+      </c>
+      <c r="AC66">
+        <v>4.33</v>
+      </c>
+      <c r="AD66">
+        <v>1.16</v>
+      </c>
+      <c r="AE66">
         <v>1.01</v>
       </c>
-      <c r="Y66">
-        <v>1.33</v>
-      </c>
-      <c r="Z66">
-        <v>3.1</v>
-      </c>
-      <c r="AA66">
-        <v>2.14</v>
-      </c>
-      <c r="AB66">
-        <v>1.72</v>
-      </c>
-      <c r="AC66">
-        <v>4.2</v>
-      </c>
-      <c r="AD66">
-        <v>1.22</v>
-      </c>
-      <c r="AE66">
-        <v>1.07</v>
-      </c>
       <c r="AF66">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG66">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK66">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.74</v>
+        <v>1.62</v>
       </c>
       <c r="O67">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="Q67">
-        <v>3.48</v>
+        <v>2.25</v>
       </c>
       <c r="R67">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T67">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="U67">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V67">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z67">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA67">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AB67">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AC67">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AD67">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG67">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK67">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11882,28 +11882,28 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>4.63</v>
+        <v>4.4</v>
       </c>
       <c r="Q71">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R71">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S71">
         <v>1.39</v>
       </c>
       <c r="T71">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U71">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V71">
         <v>1.35</v>
@@ -11921,13 +11921,13 @@
         <v>3.08</v>
       </c>
       <c r="AA71">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB71">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC71">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD71">
         <v>1.25</v>
@@ -11939,7 +11939,7 @@
         <v>1.89</v>
       </c>
       <c r="AG71">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
         <v>2.11</v>
@@ -13841,10 +13841,10 @@
         <v>1.9</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q83">
         <v>2.33</v>
@@ -13853,49 +13853,49 @@
         <v>2.32</v>
       </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T83">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U83">
         <v>2.05</v>
       </c>
       <c r="V83">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z83">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="AA83">
         <v>1.53</v>
       </c>
       <c r="AB83">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AC83">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD83">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE83">
         <v>1.24</v>
       </c>
       <c r="AF83">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14007,34 +14007,34 @@
         <v>3.6</v>
       </c>
       <c r="P84">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q84">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="R84">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U84">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="V84">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W84">
         <v>1.14</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z84">
         <v>4.95</v>
@@ -14043,7 +14043,7 @@
         <v>1.49</v>
       </c>
       <c r="AB84">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="AC84">
         <v>2.15</v>
@@ -14055,10 +14055,10 @@
         <v>1.27</v>
       </c>
       <c r="AF84">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG84">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15145,13 +15145,13 @@
         <v>1.48</v>
       </c>
       <c r="O91">
-        <v>4.15</v>
+        <v>3.63</v>
       </c>
       <c r="P91">
         <v>5.25</v>
       </c>
       <c r="Q91">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="R91">
         <v>2.22</v>
@@ -15160,19 +15160,19 @@
         <v>1.33</v>
       </c>
       <c r="T91">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="U91">
         <v>2.74</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
         <v>1.28</v>
@@ -15184,7 +15184,7 @@
         <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC91">
         <v>3.2</v>
@@ -15196,10 +15196,10 @@
         <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG91">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AK91">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,16 +15305,16 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O92">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P92">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q92">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R92">
         <v>2.1</v>
@@ -15326,22 +15326,22 @@
         <v>2.66</v>
       </c>
       <c r="U92">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V92">
         <v>1.4</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X92">
         <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z92">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AA92">
         <v>1.92</v>
@@ -15350,19 +15350,19 @@
         <v>1.79</v>
       </c>
       <c r="AC92">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE92">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,34 +15468,34 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O93">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="P93">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q93">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R93">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="S93">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T93">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="U93">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V93">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="W93">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15507,7 +15507,7 @@
         <v>11</v>
       </c>
       <c r="AA93">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AB93">
         <v>4.33</v>
@@ -15519,13 +15519,13 @@
         <v>2.4</v>
       </c>
       <c r="AE93">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AF93">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG93">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK93">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O98">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="P98">
+        <v>7.5</v>
+      </c>
+      <c r="Q98">
+        <v>1.69</v>
+      </c>
+      <c r="R98">
+        <v>2.81</v>
+      </c>
+      <c r="S98">
+        <v>1.24</v>
+      </c>
+      <c r="T98">
+        <v>3.5</v>
+      </c>
+      <c r="U98">
+        <v>2.31</v>
+      </c>
+      <c r="V98">
+        <v>1.59</v>
+      </c>
+      <c r="W98">
+        <v>1.13</v>
+      </c>
+      <c r="X98">
+        <v>1.01</v>
+      </c>
+      <c r="Y98">
+        <v>1.17</v>
+      </c>
+      <c r="Z98">
+        <v>4.75</v>
+      </c>
+      <c r="AA98">
+        <v>1.53</v>
+      </c>
+      <c r="AB98">
         <v>2.4</v>
       </c>
-      <c r="Q98">
-        <v>3.2</v>
-      </c>
-      <c r="R98">
-        <v>2.31</v>
-      </c>
-      <c r="S98">
-        <v>1.33</v>
-      </c>
-      <c r="T98">
-        <v>3.25</v>
-      </c>
-      <c r="U98">
-        <v>2.56</v>
-      </c>
-      <c r="V98">
-        <v>1.45</v>
-      </c>
-      <c r="W98">
-        <v>1.08</v>
-      </c>
-      <c r="X98">
-        <v>1.02</v>
-      </c>
-      <c r="Y98">
-        <v>1.22</v>
-      </c>
-      <c r="Z98">
-        <v>4.1</v>
-      </c>
-      <c r="AA98">
-        <v>1.76</v>
-      </c>
-      <c r="AB98">
-        <v>2.03</v>
-      </c>
       <c r="AC98">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="AD98">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AE98">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG98">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>3.45</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="O99">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q99">
-        <v>1.69</v>
+        <v>3.2</v>
       </c>
       <c r="R99">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="S99">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U99">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="V99">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="W99">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z99">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AB99">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC99">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="AD99">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AE99">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF99">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG99">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>3.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="O101">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P101">
-        <v>6.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q101">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="R101">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="S101">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="V101">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y101">
+        <v>1.26</v>
+      </c>
+      <c r="Z101">
+        <v>3.55</v>
+      </c>
+      <c r="AA101">
+        <v>1.95</v>
+      </c>
+      <c r="AB101">
+        <v>1.83</v>
+      </c>
+      <c r="AC101">
+        <v>3.14</v>
+      </c>
+      <c r="AD101">
+        <v>1.3</v>
+      </c>
+      <c r="AE101">
         <v>1.1</v>
       </c>
-      <c r="Z101">
-        <v>5.1</v>
-      </c>
-      <c r="AA101">
-        <v>1.5</v>
-      </c>
-      <c r="AB101">
-        <v>2.46</v>
-      </c>
-      <c r="AC101">
-        <v>2.28</v>
-      </c>
-      <c r="AD101">
-        <v>1.61</v>
-      </c>
-      <c r="AE101">
-        <v>1.22</v>
-      </c>
       <c r="AF101">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG101">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK101">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="O102">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="P102">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q102">
-        <v>2.49</v>
+        <v>1.64</v>
       </c>
       <c r="R102">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T102">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="U102">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X102">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="Z102">
-        <v>3.55</v>
+        <v>5.65</v>
       </c>
       <c r="AA102">
+        <v>1.35</v>
+      </c>
+      <c r="AB102">
+        <v>2.75</v>
+      </c>
+      <c r="AC102">
         <v>1.95</v>
       </c>
-      <c r="AB102">
-        <v>1.83</v>
-      </c>
-      <c r="AC102">
-        <v>3.14</v>
-      </c>
       <c r="AD102">
+        <v>1.76</v>
+      </c>
+      <c r="AE102">
         <v>1.3</v>
-      </c>
-      <c r="AE102">
-        <v>1.1</v>
       </c>
       <c r="AF102">
         <v>1.75</v>
       </c>
       <c r="AG102">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AK102">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O103">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="P103">
-        <v>8.800000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="Q103">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="R103">
+        <v>2.57</v>
+      </c>
+      <c r="S103">
+        <v>1.22</v>
+      </c>
+      <c r="T103">
+        <v>3.7</v>
+      </c>
+      <c r="U103">
+        <v>2.15</v>
+      </c>
+      <c r="V103">
+        <v>1.62</v>
+      </c>
+      <c r="W103">
+        <v>1.13</v>
+      </c>
+      <c r="X103">
+        <v>1.04</v>
+      </c>
+      <c r="Y103">
+        <v>1.1</v>
+      </c>
+      <c r="Z103">
+        <v>5.1</v>
+      </c>
+      <c r="AA103">
+        <v>1.5</v>
+      </c>
+      <c r="AB103">
+        <v>2.46</v>
+      </c>
+      <c r="AC103">
+        <v>2.28</v>
+      </c>
+      <c r="AD103">
+        <v>1.61</v>
+      </c>
+      <c r="AE103">
+        <v>1.22</v>
+      </c>
+      <c r="AF103">
+        <v>1.67</v>
+      </c>
+      <c r="AG103">
+        <v>2.07</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
+        <v>1.11</v>
+      </c>
+      <c r="AK103">
         <v>2.88</v>
-      </c>
-      <c r="S103">
-        <v>1.18</v>
-      </c>
-      <c r="T103">
-        <v>3.9</v>
-      </c>
-      <c r="U103">
-        <v>1.93</v>
-      </c>
-      <c r="V103">
-        <v>1.75</v>
-      </c>
-      <c r="W103">
-        <v>1.17</v>
-      </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
-        <v>1.08</v>
-      </c>
-      <c r="Z103">
-        <v>5.65</v>
-      </c>
-      <c r="AA103">
-        <v>1.35</v>
-      </c>
-      <c r="AB103">
-        <v>2.75</v>
-      </c>
-      <c r="AC103">
-        <v>1.95</v>
-      </c>
-      <c r="AD103">
-        <v>1.76</v>
-      </c>
-      <c r="AE103">
-        <v>1.3</v>
-      </c>
-      <c r="AF103">
-        <v>1.75</v>
-      </c>
-      <c r="AG103">
-        <v>2</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.07</v>
-      </c>
-      <c r="AK103">
-        <v>3.5</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17750,34 +17750,34 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O107">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P107">
         <v>3.1</v>
       </c>
       <c r="Q107">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R107">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S107">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T107">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="U107">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V107">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X107">
         <v>1.07</v>
@@ -17786,7 +17786,7 @@
         <v>1.44</v>
       </c>
       <c r="Z107">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AA107">
         <v>2.41</v>
@@ -17801,13 +17801,13 @@
         <v>1.14</v>
       </c>
       <c r="AE107">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF107">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG107">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18565,28 +18565,28 @@
         </is>
       </c>
       <c r="N112">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P112">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q112">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="R112">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T112">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U112">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="V112">
         <v>1.36</v>
@@ -18598,31 +18598,31 @@
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA112">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AB112">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC112">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD112">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE112">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG112">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,52 +18728,52 @@
         </is>
       </c>
       <c r="N113">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O113">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P113">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q113">
-        <v>3.48</v>
+        <v>3.71</v>
       </c>
       <c r="R113">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S113">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T113">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U113">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V113">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W113">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z113">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA113">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB113">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC113">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD113">
         <v>1.2</v>
@@ -18782,10 +18782,10 @@
         <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG113">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK113">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O114">
         <v>2.87</v>
@@ -18900,55 +18900,55 @@
         <v>2.7</v>
       </c>
       <c r="Q114">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="R114">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="S114">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="T114">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U114">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V114">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W114">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z114">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA114">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AB114">
         <v>1.51</v>
       </c>
       <c r="AC114">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD114">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE114">
         <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG114">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK114">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19057,61 +19057,61 @@
         <v>2.15</v>
       </c>
       <c r="O115">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P115">
         <v>3</v>
       </c>
       <c r="Q115">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S115">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T115">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U115">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="V115">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y115">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z115">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AA115">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AB115">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC115">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD115">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE115">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG115">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK115">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19383,28 +19383,28 @@
         <v>8</v>
       </c>
       <c r="O117">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="P117">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q117">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="R117">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S117">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T117">
         <v>3.55</v>
       </c>
       <c r="U117">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V117">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W117">
         <v>1.17</v>
@@ -19419,22 +19419,22 @@
         <v>4.7</v>
       </c>
       <c r="AA117">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB117">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AC117">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD117">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE117">
         <v>1.22</v>
       </c>
       <c r="AF117">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG117">
         <v>1.9</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK117">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -21025,7 +21025,7 @@
         <v>2.29</v>
       </c>
       <c r="S127">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
         <v>2.97</v>
@@ -21037,19 +21037,19 @@
         <v>1.44</v>
       </c>
       <c r="W127">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z127">
         <v>2.9</v>
       </c>
       <c r="AA127">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB127">
         <v>2</v>
@@ -21058,7 +21058,7 @@
         <v>2.9</v>
       </c>
       <c r="AD127">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE127">
         <v>1.11</v>
@@ -21508,46 +21508,46 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="R130">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="S130">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T130">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U130">
         <v>2.2</v>
       </c>
       <c r="V130">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W130">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z130">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA130">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB130">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AC130">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AD130">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE130">
         <v>1.22</v>
@@ -21556,7 +21556,7 @@
         <v>1.6</v>
       </c>
       <c r="AG130">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL130">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="O2">
         <v>4.5</v>
       </c>
       <c r="P2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q2">
-        <v>5.8</v>
+        <v>4.46</v>
       </c>
       <c r="R2">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
         <v>1.25</v>
@@ -656,7 +656,7 @@
         <v>3.58</v>
       </c>
       <c r="U2">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V2">
         <v>1.62</v>
@@ -671,7 +671,7 @@
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA2">
         <v>1.53</v>
@@ -680,19 +680,19 @@
         <v>2.4</v>
       </c>
       <c r="AC2">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
         <v>1.23</v>
       </c>
       <c r="AF2">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK2">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P3">
         <v>2.7</v>
@@ -810,52 +810,52 @@
         <v>3</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="AA3">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AB3">
         <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R4">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
         <v>1.32</v>
       </c>
       <c r="T4">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="U4">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
         <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>2.55</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="P5">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -1154,7 +1154,7 @@
         <v>1.16</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.09</v>
@@ -1169,13 +1169,13 @@
         <v>2.75</v>
       </c>
       <c r="AC5">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD5">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AE5">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF5">
         <v>1.38</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
         <v>1.38</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="S6">
         <v>1.15</v>
@@ -1308,40 +1308,40 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V6">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z6">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB6">
         <v>3.5</v>
       </c>
       <c r="AC6">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD6">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AE6">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AF6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG6">
         <v>3.27</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O7">
         <v>3.5</v>
@@ -1459,13 +1459,13 @@
         <v>2.05</v>
       </c>
       <c r="Q7">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="R7">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
         <v>3.55</v>
@@ -1474,10 +1474,10 @@
         <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1492,22 +1492,22 @@
         <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="AC7">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
         <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AK7">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O8">
         <v>3.6</v>
       </c>
       <c r="P8">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>4.36</v>
+        <v>3.85</v>
       </c>
       <c r="R8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
         <v>1.28</v>
@@ -1634,10 +1634,10 @@
         <v>3.15</v>
       </c>
       <c r="U8">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V8">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
         <v>1.13</v>
@@ -1646,10 +1646,10 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA8">
         <v>1.65</v>
@@ -1658,19 +1658,19 @@
         <v>2.14</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="O10">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P10">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="Q10">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R10">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="S10">
         <v>1.63</v>
       </c>
       <c r="T10">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U10">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1.13</v>
       </c>
       <c r="Y10">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Z10">
         <v>2.28</v>
       </c>
       <c r="AA10">
-        <v>2.93</v>
+        <v>2.52</v>
       </c>
       <c r="AB10">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AC10">
-        <v>5.97</v>
+        <v>4.85</v>
       </c>
       <c r="AD10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AG10">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK10">
         <v>1.44</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="O11">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P11">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R11">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="S11">
         <v>1.63</v>
       </c>
       <c r="T11">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U11">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="V11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
         <v>1.13</v>
       </c>
       <c r="Y11">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Z11">
         <v>2.28</v>
       </c>
       <c r="AA11">
-        <v>2.52</v>
+        <v>2.93</v>
       </c>
       <c r="AB11">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC11">
-        <v>4.85</v>
+        <v>5.97</v>
       </c>
       <c r="AD11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AG11">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
         <v>1.44</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="O12">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="P12">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2591,52 +2591,52 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>6.13</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V14">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
         <v>4</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC14">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD14">
         <v>1.33</v>
@@ -2645,10 +2645,10 @@
         <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q25">
         <v>3.75</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V25">
         <v>1.49</v>
@@ -4429,19 +4429,19 @@
         <v>2.1</v>
       </c>
       <c r="AC25">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD25">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O26">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
         <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
         <v>2.33</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="U26">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4583,19 +4583,19 @@
         <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC26">
         <v>2.21</v>
       </c>
       <c r="AD26">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AE26">
         <v>1.19</v>
@@ -4604,7 +4604,7 @@
         <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
         <v>1.85</v>
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R27">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
         <v>1.05</v>
@@ -4743,28 +4743,28 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA27">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
         <v>1.9</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="R28">
+        <v>2.02</v>
+      </c>
+      <c r="S28">
+        <v>1.43</v>
+      </c>
+      <c r="T28">
+        <v>2.9</v>
+      </c>
+      <c r="U28">
+        <v>2.95</v>
+      </c>
+      <c r="V28">
+        <v>1.34</v>
+      </c>
+      <c r="W28">
+        <v>1.06</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>1.28</v>
+      </c>
+      <c r="Z28">
+        <v>3.08</v>
+      </c>
+      <c r="AA28">
         <v>2.1</v>
       </c>
-      <c r="S28">
-        <v>1.4</v>
-      </c>
-      <c r="T28">
-        <v>2.88</v>
-      </c>
-      <c r="U28">
-        <v>2.8</v>
-      </c>
-      <c r="V28">
-        <v>1.37</v>
-      </c>
-      <c r="W28">
-        <v>1.02</v>
-      </c>
-      <c r="X28">
-        <v>1.05</v>
-      </c>
-      <c r="Y28">
-        <v>1.32</v>
-      </c>
-      <c r="Z28">
-        <v>3.36</v>
-      </c>
-      <c r="AA28">
-        <v>2</v>
-      </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC28">
         <v>3.55</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5697,71 +5697,71 @@
         <v>3.25</v>
       </c>
       <c r="Q33">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="R33">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="S33">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="U33">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.36</v>
+      </c>
+      <c r="Z33">
+        <v>3.15</v>
+      </c>
+      <c r="AA33">
+        <v>2.21</v>
+      </c>
+      <c r="AB33">
+        <v>1.62</v>
+      </c>
+      <c r="AC33">
+        <v>3.86</v>
+      </c>
+      <c r="AD33">
+        <v>1.23</v>
+      </c>
+      <c r="AE33">
         <v>1.02</v>
       </c>
-      <c r="Y33">
-        <v>1.32</v>
-      </c>
-      <c r="Z33">
-        <v>3.1</v>
-      </c>
-      <c r="AA33">
-        <v>2.15</v>
-      </c>
-      <c r="AB33">
-        <v>1.67</v>
-      </c>
-      <c r="AC33">
-        <v>3.76</v>
-      </c>
-      <c r="AD33">
-        <v>1.22</v>
-      </c>
-      <c r="AE33">
-        <v>1.05</v>
-      </c>
       <c r="AF33">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG33">
+        <v>1.78</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.33</v>
+      </c>
+      <c r="AK33">
         <v>1.77</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.19</v>
-      </c>
-      <c r="AK33">
-        <v>1.89</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O35">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q35">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
         <v>1.29</v>
@@ -6035,13 +6035,13 @@
         <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="V35">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6053,7 +6053,7 @@
         <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB35">
         <v>2.15</v>
@@ -6062,13 +6062,13 @@
         <v>2.6</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
         <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG35">
         <v>2.3</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
         <v>1.38</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O36">
         <v>3</v>
       </c>
       <c r="P36">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q36">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="R36">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="S36">
         <v>1.51</v>
@@ -6210,19 +6210,19 @@
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z36">
         <v>2.49</v>
       </c>
       <c r="AA36">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AB36">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AC36">
-        <v>4.81</v>
+        <v>4.87</v>
       </c>
       <c r="AD36">
         <v>1.12</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O37">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6503,46 +6503,46 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
         <v>2.8</v>
       </c>
       <c r="Q38">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R38">
         <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W38">
         <v>1.13</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB38">
         <v>2.1</v>
@@ -6551,16 +6551,16 @@
         <v>2.62</v>
       </c>
       <c r="AD38">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
         <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>2.8</v>
       </c>
       <c r="Q39">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
         <v>2.38</v>
@@ -6699,31 +6699,31 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC39">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD39">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AK39">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,28 +6829,28 @@
         </is>
       </c>
       <c r="N40">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="O40">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="P40">
         <v>1.32</v>
       </c>
       <c r="Q40">
-        <v>5.42</v>
+        <v>7.35</v>
       </c>
       <c r="R40">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="U40">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
         <v>1.65</v>
@@ -6859,34 +6859,34 @@
         <v>1.14</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB40">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC40">
         <v>2.23</v>
       </c>
       <c r="AD40">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE40">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF40">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.07</v>
       </c>
       <c r="AK40">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.65</v>
+        <v>2.61</v>
       </c>
       <c r="O41">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.81</v>
+        <v>2.43</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
         <v>1.3</v>
@@ -7013,43 +7013,43 @@
         <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
         <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="AA41">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB41">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AD41">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>2.09</v>
+        <v>1.49</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P42">
-        <v>2.43</v>
+        <v>4.47</v>
       </c>
       <c r="Q42">
-        <v>3.15</v>
+        <v>2.19</v>
       </c>
       <c r="R42">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.3</v>
@@ -7176,10 +7176,10 @@
         <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V42">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W42">
         <v>1.08</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AC42">
-        <v>2.54</v>
+        <v>2.79</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>1.49</v>
+        <v>2.17</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R45">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="S45">
         <v>1.44</v>
@@ -7665,10 +7665,10 @@
         <v>2.41</v>
       </c>
       <c r="U45">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V45">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W45">
         <v>1.03</v>
@@ -7677,31 +7677,31 @@
         <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z45">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA45">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB45">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC45">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="AD45">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE45">
         <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG45">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8133,37 +8133,37 @@
         </is>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
         <v>3.2</v>
       </c>
       <c r="P48">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="Q48">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="R48">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
         <v>1.39</v>
       </c>
       <c r="T48">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U48">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V48">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
         <v>1.27</v>
@@ -8172,10 +8172,10 @@
         <v>3.14</v>
       </c>
       <c r="AA48">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB48">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC48">
         <v>3.3</v>
@@ -8184,10 +8184,10 @@
         <v>1.23</v>
       </c>
       <c r="AE48">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
         <v>1.93</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O49">
+        <v>4.1</v>
+      </c>
+      <c r="P49">
         <v>4</v>
       </c>
-      <c r="P49">
-        <v>4.03</v>
-      </c>
       <c r="Q49">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R49">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
         <v>1.18</v>
@@ -8317,43 +8317,43 @@
         <v>2.8</v>
       </c>
       <c r="U49">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
         <v>5.1</v>
       </c>
       <c r="AA49">
+        <v>1.43</v>
+      </c>
+      <c r="AB49">
+        <v>2.58</v>
+      </c>
+      <c r="AC49">
+        <v>2.23</v>
+      </c>
+      <c r="AD49">
         <v>1.5</v>
-      </c>
-      <c r="AB49">
-        <v>2.5</v>
-      </c>
-      <c r="AC49">
-        <v>2.16</v>
-      </c>
-      <c r="AD49">
-        <v>1.65</v>
       </c>
       <c r="AE49">
         <v>1.26</v>
       </c>
       <c r="AF49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG49">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q50">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="R50">
         <v>3.3</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V50">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC50">
         <v>2.3</v>
@@ -8510,13 +8510,13 @@
         <v>1.55</v>
       </c>
       <c r="AE50">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AG50">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O51">
         <v>3.5</v>
       </c>
       <c r="P51">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q51">
         <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S51">
         <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U51">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W51">
         <v>1.07</v>
@@ -8661,25 +8661,25 @@
         <v>3.74</v>
       </c>
       <c r="AA51">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="AD51">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE51">
         <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="P52">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q52">
-        <v>4.83</v>
+        <v>4.5</v>
       </c>
       <c r="R52">
         <v>2.3</v>
@@ -8806,7 +8806,7 @@
         <v>3.34</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V52">
         <v>1.5</v>
@@ -8824,10 +8824,10 @@
         <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC52">
         <v>2.54</v>
@@ -8842,7 +8842,7 @@
         <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9280,58 +9280,58 @@
         <v>3.3</v>
       </c>
       <c r="P55">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Q55">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R55">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S55">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="V55">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA55">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB55">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC55">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AD55">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE55">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG55">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,40 +9437,40 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="O56">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q56">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="R56">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="S56">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T56">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U56">
         <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
         <v>4.85</v>
@@ -9482,19 +9482,19 @@
         <v>2.37</v>
       </c>
       <c r="AC56">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD56">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE56">
         <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG56">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK56">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
+        <v>1.56</v>
+      </c>
+      <c r="O57">
+        <v>4.35</v>
+      </c>
+      <c r="P57">
+        <v>4.65</v>
+      </c>
+      <c r="Q57">
+        <v>2.05</v>
+      </c>
+      <c r="R57">
         <v>2.45</v>
       </c>
-      <c r="O57">
+      <c r="S57">
+        <v>1.2</v>
+      </c>
+      <c r="T57">
         <v>3.5</v>
       </c>
-      <c r="P57">
-        <v>2.35</v>
-      </c>
-      <c r="Q57">
-        <v>2.73</v>
-      </c>
-      <c r="R57">
-        <v>2.29</v>
-      </c>
-      <c r="S57">
-        <v>1.26</v>
-      </c>
-      <c r="T57">
-        <v>3.2</v>
-      </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.85</v>
+        <v>5.53</v>
       </c>
       <c r="AA57">
         <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC57">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD57">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AG57">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,34 +9763,34 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="O58">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q58">
         <v>2.05</v>
       </c>
       <c r="R58">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T58">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U58">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V58">
         <v>1.62</v>
       </c>
       <c r="W58">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9799,28 +9799,28 @@
         <v>1.11</v>
       </c>
       <c r="Z58">
-        <v>5.53</v>
+        <v>4.85</v>
       </c>
       <c r="AA58">
         <v>1.5</v>
       </c>
       <c r="AB58">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC58">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AD58">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O60">
+        <v>2.95</v>
+      </c>
+      <c r="P60">
+        <v>2.7</v>
+      </c>
+      <c r="Q60">
+        <v>2.9</v>
+      </c>
+      <c r="R60">
+        <v>1.85</v>
+      </c>
+      <c r="S60">
+        <v>1.45</v>
+      </c>
+      <c r="T60">
+        <v>2.47</v>
+      </c>
+      <c r="U60">
         <v>3.15</v>
       </c>
-      <c r="P60">
-        <v>3.1</v>
-      </c>
-      <c r="Q60">
-        <v>2.71</v>
-      </c>
-      <c r="R60">
-        <v>2.06</v>
-      </c>
-      <c r="S60">
-        <v>1.39</v>
-      </c>
-      <c r="T60">
-        <v>2.66</v>
-      </c>
-      <c r="U60">
-        <v>2.82</v>
-      </c>
       <c r="V60">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W60">
         <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z60">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="AA60">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AB60">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AC60">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="AD60">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AG60">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK60">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>9.25</v>
+        <v>1.22</v>
       </c>
       <c r="O61">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="P61">
-        <v>1.21</v>
+        <v>11</v>
       </c>
       <c r="Q61">
-        <v>6.75</v>
+        <v>1.48</v>
       </c>
       <c r="R61">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U61">
         <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB61">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AC61">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD61">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF61">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG61">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>4.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK61">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,65 +10415,65 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.15</v>
+        <v>9.25</v>
       </c>
       <c r="O62">
-        <v>7</v>
+        <v>6.65</v>
       </c>
       <c r="P62">
-        <v>11</v>
+        <v>1.23</v>
       </c>
       <c r="Q62">
-        <v>1.57</v>
+        <v>6.95</v>
       </c>
       <c r="R62">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="S62">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T62">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB62">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC62">
+        <v>2.04</v>
+      </c>
+      <c r="AD62">
+        <v>1.73</v>
+      </c>
+      <c r="AE62">
+        <v>1.27</v>
+      </c>
+      <c r="AF62">
+        <v>1.81</v>
+      </c>
+      <c r="AG62">
         <v>1.88</v>
       </c>
-      <c r="AD62">
-        <v>1.82</v>
-      </c>
-      <c r="AE62">
-        <v>1.31</v>
-      </c>
-      <c r="AF62">
-        <v>1.78</v>
-      </c>
-      <c r="AG62">
-        <v>1.91</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="AK62">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P63">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q63">
         <v>2.69</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S63">
         <v>1.24</v>
@@ -10599,43 +10599,43 @@
         <v>3.34</v>
       </c>
       <c r="U63">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W63">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA63">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB63">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="AC63">
         <v>2.33</v>
       </c>
       <c r="AD63">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE63">
         <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P64">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q64">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T64">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="U64">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="V64">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z64">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="AA64">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AB64">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AC64">
-        <v>2.7</v>
+        <v>3.63</v>
       </c>
       <c r="AD64">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AE64">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AG64">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK64">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="P65">
+        <v>4.2</v>
+      </c>
+      <c r="Q65">
+        <v>2.22</v>
+      </c>
+      <c r="R65">
+        <v>2.33</v>
+      </c>
+      <c r="S65">
+        <v>1.3</v>
+      </c>
+      <c r="T65">
+        <v>3.22</v>
+      </c>
+      <c r="U65">
+        <v>2.44</v>
+      </c>
+      <c r="V65">
+        <v>1.45</v>
+      </c>
+      <c r="W65">
+        <v>1.08</v>
+      </c>
+      <c r="X65">
+        <v>1.04</v>
+      </c>
+      <c r="Y65">
+        <v>1.2</v>
+      </c>
+      <c r="Z65">
         <v>4</v>
       </c>
-      <c r="Q65">
-        <v>2.5</v>
-      </c>
-      <c r="R65">
-        <v>2.05</v>
-      </c>
-      <c r="S65">
-        <v>1.4</v>
-      </c>
-      <c r="T65">
-        <v>2.79</v>
-      </c>
-      <c r="U65">
-        <v>3.12</v>
-      </c>
-      <c r="V65">
-        <v>1.32</v>
-      </c>
-      <c r="W65">
-        <v>1.07</v>
-      </c>
-      <c r="X65">
-        <v>1.01</v>
-      </c>
-      <c r="Y65">
-        <v>1.33</v>
-      </c>
-      <c r="Z65">
-        <v>3.1</v>
-      </c>
       <c r="AA65">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AB65">
+        <v>2.11</v>
+      </c>
+      <c r="AC65">
+        <v>2.54</v>
+      </c>
+      <c r="AD65">
+        <v>1.41</v>
+      </c>
+      <c r="AE65">
+        <v>1.13</v>
+      </c>
+      <c r="AF65">
         <v>1.72</v>
       </c>
-      <c r="AC65">
-        <v>4.2</v>
-      </c>
-      <c r="AD65">
-        <v>1.22</v>
-      </c>
-      <c r="AE65">
-        <v>1.07</v>
-      </c>
-      <c r="AF65">
-        <v>1.86</v>
-      </c>
       <c r="AG65">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK65">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="O66">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q66">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="R66">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="S66">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T66">
         <v>2.65</v>
       </c>
       <c r="U66">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="V66">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
         <v>1.06</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA66">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB66">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AC66">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD66">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
         <v>1.9</v>
       </c>
       <c r="AG66">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK66">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q67">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S67">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.77</v>
+        <v>3.12</v>
       </c>
       <c r="U67">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
         <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z67">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA67">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD67">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AG67">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>2.09</v>
+        <v>1.43</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O68">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="P68">
-        <v>2.71</v>
+        <v>3.95</v>
       </c>
       <c r="Q68">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S68">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="T68">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="U68">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="V68">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z68">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="AA68">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AB68">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AC68">
-        <v>2.94</v>
+        <v>3.82</v>
       </c>
       <c r="AD68">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG68">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11571,22 +11571,22 @@
         <v>2.5</v>
       </c>
       <c r="S69">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="V69">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
         <v>1.13</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
         <v>1.17</v>
@@ -11595,25 +11595,25 @@
         <v>5</v>
       </c>
       <c r="AA69">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB69">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AC69">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AD69">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE69">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF69">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>1.7</v>
       </c>
       <c r="W70">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1.01</v>
@@ -11758,13 +11758,13 @@
         <v>5.35</v>
       </c>
       <c r="AA70">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AB70">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AC70">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD70">
         <v>1.62</v>
@@ -11776,7 +11776,7 @@
         <v>1.47</v>
       </c>
       <c r="AG70">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK70">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O72">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="P72">
-        <v>5.13</v>
+        <v>4.65</v>
       </c>
       <c r="Q72">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R72">
         <v>2.5</v>
@@ -12069,7 +12069,7 @@
         <v>2</v>
       </c>
       <c r="V72">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W72">
         <v>1.16</v>
@@ -12078,31 +12078,31 @@
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z72">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AA72">
         <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AC72">
         <v>2.12</v>
       </c>
       <c r="AD72">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE72">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF72">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG72">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,13 +12217,13 @@
         <v>4.38</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R73">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T73">
         <v>2.53</v>
@@ -12247,7 +12247,7 @@
         <v>2.97</v>
       </c>
       <c r="AA73">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AB73">
         <v>1.69</v>
@@ -12265,7 +12265,7 @@
         <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
         <v>2</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>3.5</v>
       </c>
       <c r="P74">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -12398,7 +12398,7 @@
         <v>1.6</v>
       </c>
       <c r="W74">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X74">
         <v>1.02</v>
@@ -12407,7 +12407,7 @@
         <v>1.16</v>
       </c>
       <c r="Z74">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AA74">
         <v>1.47</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK74">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,28 +12534,28 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P75">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q75">
         <v>2.08</v>
       </c>
       <c r="R75">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T75">
         <v>4</v>
       </c>
       <c r="U75">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V75">
         <v>1.71</v>
@@ -12570,10 +12570,10 @@
         <v>1.12</v>
       </c>
       <c r="Z75">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB75">
         <v>2.7</v>
@@ -12700,37 +12700,37 @@
         <v>2.45</v>
       </c>
       <c r="O76">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P76">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q76">
         <v>2.73</v>
       </c>
       <c r="R76">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="S76">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="U76">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V76">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="W76">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z76">
         <v>6.5</v>
@@ -12742,13 +12742,13 @@
         <v>2.7</v>
       </c>
       <c r="AC76">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD76">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE76">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF76">
         <v>1.38</v>
@@ -12770,7 +12770,7 @@
         <v>1.5</v>
       </c>
       <c r="AK76">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P77">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q77">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R77">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S77">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="U77">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V77">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W77">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA77">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AB77">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AC77">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD77">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AE77">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG77">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="P78">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q78">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="R78">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S78">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T78">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U78">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V78">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W78">
         <v>1.13</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
         <v>1.14</v>
       </c>
       <c r="Z78">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="AA78">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AB78">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC78">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD78">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE78">
         <v>1.16</v>
       </c>
       <c r="AF78">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG78">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P79">
-        <v>2.13</v>
+        <v>3.27</v>
       </c>
       <c r="Q79">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="R79">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="U79">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA79">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB79">
-        <v>2.21</v>
+        <v>3.1</v>
       </c>
       <c r="AC79">
-        <v>2.49</v>
+        <v>1.96</v>
       </c>
       <c r="AD79">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF79">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG79">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="P80">
-        <v>4.26</v>
+        <v>3.6</v>
       </c>
       <c r="Q80">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R80">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S80">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="U80">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="V80">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="W80">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z80">
-        <v>5.3</v>
+        <v>4.79</v>
       </c>
       <c r="AA80">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AB80">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="AC80">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="AD80">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AE80">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AF80">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AG80">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK80">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="R82">
         <v>2.12</v>
@@ -13696,10 +13696,10 @@
         <v>3.02</v>
       </c>
       <c r="U82">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V82">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13714,25 +13714,25 @@
         <v>4.1</v>
       </c>
       <c r="AA82">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB82">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC82">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="AD82">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE82">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF82">
         <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
+        <v>1.68</v>
+      </c>
+      <c r="AK82">
         <v>1.24</v>
-      </c>
-      <c r="AK82">
-        <v>1.3</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q83">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="R83">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S83">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U83">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="V83">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>5.24</v>
+        <v>4.95</v>
       </c>
       <c r="AA83">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB83">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="AC83">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="AD83">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE83">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF83">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG83">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
         <v>1.79</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O84">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q84">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U84">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V84">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W84">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z84">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="AA84">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="AC84">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AD84">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE84">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF84">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
         <v>1.79</v>
@@ -14164,28 +14164,28 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>6.55</v>
+        <v>5.78</v>
       </c>
       <c r="Q85">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="R85">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S85">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T85">
         <v>2.88</v>
       </c>
       <c r="U85">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="V85">
         <v>1.37</v>
@@ -14197,28 +14197,28 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z85">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB85">
         <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AD85">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE85">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF85">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG85">
         <v>1.69</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK85">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,25 +14327,25 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P86">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="Q86">
         <v>2.5</v>
       </c>
       <c r="R86">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S86">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T86">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U86">
         <v>3.22</v>
@@ -14360,31 +14360,31 @@
         <v>1.05</v>
       </c>
       <c r="Y86">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Z86">
         <v>2.53</v>
       </c>
       <c r="AA86">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="AB86">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC86">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD86">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE86">
         <v>1.05</v>
       </c>
       <c r="AF86">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG86">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK86">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,19 +14499,19 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="R87">
         <v>2.1</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T87">
         <v>3.2</v>
       </c>
       <c r="U87">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V87">
         <v>1.44</v>
@@ -14526,22 +14526,22 @@
         <v>1.25</v>
       </c>
       <c r="Z87">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="AA87">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB87">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC87">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AD87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
         <v>1.67</v>
@@ -14563,7 +14563,7 @@
         <v>1.28</v>
       </c>
       <c r="AK87">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,31 +14653,31 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="O88">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q88">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S88">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T88">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="U88">
         <v>2.7</v>
       </c>
       <c r="V88">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W88">
         <v>1.05</v>
@@ -14686,22 +14686,22 @@
         <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z88">
         <v>3.34</v>
       </c>
       <c r="AA88">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB88">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC88">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD88">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE88">
         <v>1.07</v>
@@ -14710,7 +14710,7 @@
         <v>1.67</v>
       </c>
       <c r="AG88">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AK88">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,22 +14825,22 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R89">
         <v>2.2</v>
       </c>
       <c r="S89">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
         <v>2.45</v>
       </c>
       <c r="V89">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W89">
         <v>1.11</v>
@@ -14858,13 +14858,13 @@
         <v>1.69</v>
       </c>
       <c r="AB89">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC89">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AD89">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE89">
         <v>1.15</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK89">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O90">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="P90">
-        <v>5.79</v>
+        <v>5.37</v>
       </c>
       <c r="Q90">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="R90">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="S90">
         <v>1.3</v>
       </c>
       <c r="T90">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U90">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V90">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA90">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB90">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC90">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD90">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE90">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15631,43 +15631,43 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="O94">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q94">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R94">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="S94">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T94">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U94">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V94">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W94">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.3</v>
       </c>
       <c r="Z94">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="AA94">
         <v>2</v>
@@ -15676,19 +15676,19 @@
         <v>1.72</v>
       </c>
       <c r="AC94">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD94">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE94">
         <v>1.05</v>
       </c>
       <c r="AF94">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG94">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.24</v>
       </c>
       <c r="AK94">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>7.2</v>
+        <v>7.75</v>
       </c>
       <c r="O95">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="P95">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Q95">
         <v>6.5</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S95">
         <v>1.28</v>
@@ -15815,37 +15815,37 @@
         <v>3.18</v>
       </c>
       <c r="U95">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="V95">
         <v>1.41</v>
       </c>
       <c r="W95">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA95">
         <v>1.52</v>
       </c>
       <c r="AB95">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC95">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="AD95">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF95">
         <v>1.75</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK95">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O96">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="P96">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q96">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R96">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="S96">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U96">
         <v>2.45</v>
       </c>
       <c r="V96">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W96">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X96">
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z96">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB96">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC96">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD96">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE96">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF96">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG96">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.19</v>
       </c>
       <c r="AK96">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,25 +16123,25 @@
         <v>1.32</v>
       </c>
       <c r="O97">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="P97">
         <v>7</v>
       </c>
       <c r="Q97">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="R97">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="S97">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T97">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V97">
         <v>1.6</v>
@@ -16159,25 +16159,25 @@
         <v>5.5</v>
       </c>
       <c r="AA97">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB97">
+        <v>2.29</v>
+      </c>
+      <c r="AC97">
         <v>2.27</v>
       </c>
-      <c r="AC97">
-        <v>2.35</v>
-      </c>
       <c r="AD97">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE97">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF97">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG97">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK97">
         <v>3.1</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.27</v>
+        <v>2.54</v>
       </c>
       <c r="O98">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="P98">
-        <v>7.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q98">
-        <v>1.69</v>
+        <v>3.2</v>
       </c>
       <c r="R98">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="S98">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U98">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="V98">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="W98">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z98">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC98">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="AD98">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AE98">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF98">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG98">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AK98">
-        <v>3.45</v>
+        <v>1.45</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.5</v>
+        <v>1.28</v>
       </c>
       <c r="O99">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="Q99">
-        <v>3.2</v>
+        <v>1.71</v>
       </c>
       <c r="R99">
-        <v>2.31</v>
+        <v>2.83</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T99">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U99">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="V99">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
+        <v>1.18</v>
+      </c>
+      <c r="Z99">
+        <v>5</v>
+      </c>
+      <c r="AA99">
+        <v>1.5</v>
+      </c>
+      <c r="AB99">
+        <v>2.3</v>
+      </c>
+      <c r="AC99">
+        <v>2.35</v>
+      </c>
+      <c r="AD99">
+        <v>1.57</v>
+      </c>
+      <c r="AE99">
         <v>1.22</v>
       </c>
-      <c r="Z99">
-        <v>4.1</v>
-      </c>
-      <c r="AA99">
-        <v>1.76</v>
-      </c>
-      <c r="AB99">
-        <v>2.03</v>
-      </c>
-      <c r="AC99">
-        <v>2.95</v>
-      </c>
-      <c r="AD99">
-        <v>1.36</v>
-      </c>
-      <c r="AE99">
-        <v>1.11</v>
-      </c>
       <c r="AF99">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG99">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK99">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P100">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q100">
-        <v>3.51</v>
+        <v>2.43</v>
       </c>
       <c r="R100">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T100">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="U100">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="V100">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="W100">
+        <v>1.05</v>
+      </c>
+      <c r="X100">
+        <v>1.01</v>
+      </c>
+      <c r="Y100">
+        <v>1.26</v>
+      </c>
+      <c r="Z100">
+        <v>3.2</v>
+      </c>
+      <c r="AA100">
+        <v>1.89</v>
+      </c>
+      <c r="AB100">
+        <v>1.81</v>
+      </c>
+      <c r="AC100">
+        <v>3.35</v>
+      </c>
+      <c r="AD100">
+        <v>1.27</v>
+      </c>
+      <c r="AE100">
         <v>1.07</v>
       </c>
-      <c r="X100">
-        <v>1.04</v>
-      </c>
-      <c r="Y100">
-        <v>1.21</v>
-      </c>
-      <c r="Z100">
-        <v>3.65</v>
-      </c>
-      <c r="AA100">
-        <v>1.65</v>
-      </c>
-      <c r="AB100">
-        <v>2.11</v>
-      </c>
-      <c r="AC100">
-        <v>2.59</v>
-      </c>
-      <c r="AD100">
-        <v>1.39</v>
-      </c>
-      <c r="AE100">
-        <v>1.12</v>
-      </c>
       <c r="AF100">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="O101">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="P101">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q101">
-        <v>2.49</v>
+        <v>1.58</v>
       </c>
       <c r="R101">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T101">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="U101">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="AA101">
+        <v>1.35</v>
+      </c>
+      <c r="AB101">
+        <v>2.75</v>
+      </c>
+      <c r="AC101">
         <v>1.95</v>
       </c>
-      <c r="AB101">
-        <v>1.83</v>
-      </c>
-      <c r="AC101">
-        <v>3.14</v>
-      </c>
       <c r="AD101">
+        <v>1.76</v>
+      </c>
+      <c r="AE101">
         <v>1.3</v>
-      </c>
-      <c r="AE101">
-        <v>1.1</v>
       </c>
       <c r="AF101">
         <v>1.75</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AK101">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O102">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>8.800000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="Q102">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="R102">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="S102">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T102">
-        <v>3.9</v>
+        <v>2.91</v>
       </c>
       <c r="U102">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="V102">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Z102">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA102">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB102">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC102">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AD102">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF102">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>3.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O103">
         <v>4.6</v>
@@ -17107,7 +17107,7 @@
         <v>6.15</v>
       </c>
       <c r="Q103">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R103">
         <v>2.57</v>
@@ -17128,10 +17128,10 @@
         <v>1.13</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z103">
         <v>5.1</v>
@@ -17140,22 +17140,22 @@
         <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC103">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AD103">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE103">
         <v>1.22</v>
       </c>
       <c r="AF103">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.11</v>
       </c>
       <c r="AK103">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="O104">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="R104">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="S104">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T104">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="U104">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="V104">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W104">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X104">
         <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z104">
-        <v>3.72</v>
+        <v>4.33</v>
       </c>
       <c r="AA104">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AB104">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC104">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="AD104">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE104">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF104">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG104">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK104">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,28 +17424,28 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O105">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="P105">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q105">
         <v>1.8</v>
       </c>
       <c r="R105">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S105">
         <v>1.35</v>
       </c>
       <c r="T105">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U105">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V105">
         <v>1.44</v>
@@ -17457,31 +17457,31 @@
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z105">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA105">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB105">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC105">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD105">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE105">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF105">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG105">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK105">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O106">
         <v>4.4</v>
@@ -17913,34 +17913,34 @@
         </is>
       </c>
       <c r="N108">
-        <v>4.65</v>
+        <v>9.5</v>
       </c>
       <c r="O108">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P108">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q108">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="R108">
         <v>2.4</v>
       </c>
       <c r="S108">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U108">
         <v>2.4</v>
       </c>
       <c r="V108">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W108">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X108">
         <v>1.01</v>
@@ -17949,10 +17949,10 @@
         <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA108">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB108">
         <v>2.2</v>
@@ -17964,13 +17964,13 @@
         <v>1.46</v>
       </c>
       <c r="AE108">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF108">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG108">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AK108">
         <v>1.2</v>
@@ -18076,52 +18076,52 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O109">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q109">
         <v>3.25</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S109">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
         <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W109">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X109">
         <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z109">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="AA109">
         <v>1.93</v>
       </c>
       <c r="AB109">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC109">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD109">
         <v>1.28</v>
@@ -18133,7 +18133,7 @@
         <v>1.67</v>
       </c>
       <c r="AG109">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>3</v>
       </c>
       <c r="P110">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q110">
         <v>2.81</v>
@@ -18254,7 +18254,7 @@
         <v>1.98</v>
       </c>
       <c r="S110">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T110">
         <v>2.63</v>
@@ -18263,37 +18263,37 @@
         <v>3.1</v>
       </c>
       <c r="V110">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
         <v>1.05</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y110">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z110">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AA110">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC110">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="AD110">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE110">
         <v>1.02</v>
       </c>
       <c r="AF110">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
         <v>1.8</v>
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="O111">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P111">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="Q111">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="R111">
         <v>2.05</v>
@@ -18420,7 +18420,7 @@
         <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U111">
         <v>2.88</v>
@@ -18429,37 +18429,37 @@
         <v>1.36</v>
       </c>
       <c r="W111">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
         <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>2.95</v>
+        <v>3.49</v>
       </c>
       <c r="AA111">
         <v>1.93</v>
       </c>
       <c r="AB111">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC111">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="AD111">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE111">
         <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG111">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="O114">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="P114">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q114">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="R114">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="S114">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="T114">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="U114">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="V114">
+        <v>1.33</v>
+      </c>
+      <c r="W114">
+        <v>1.05</v>
+      </c>
+      <c r="X114">
+        <v>1.05</v>
+      </c>
+      <c r="Y114">
+        <v>1.34</v>
+      </c>
+      <c r="Z114">
+        <v>2.78</v>
+      </c>
+      <c r="AA114">
+        <v>2.19</v>
+      </c>
+      <c r="AB114">
+        <v>1.65</v>
+      </c>
+      <c r="AC114">
+        <v>4.2</v>
+      </c>
+      <c r="AD114">
+        <v>1.19</v>
+      </c>
+      <c r="AE114">
+        <v>1.06</v>
+      </c>
+      <c r="AF114">
+        <v>1.87</v>
+      </c>
+      <c r="AG114">
+        <v>1.87</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.24</v>
       </c>
-      <c r="W114">
-        <v>1.03</v>
-      </c>
-      <c r="X114">
-        <v>1.07</v>
-      </c>
-      <c r="Y114">
-        <v>1.43</v>
-      </c>
-      <c r="Z114">
-        <v>2.46</v>
-      </c>
-      <c r="AA114">
-        <v>2.33</v>
-      </c>
-      <c r="AB114">
-        <v>1.51</v>
-      </c>
-      <c r="AC114">
-        <v>5</v>
-      </c>
-      <c r="AD114">
-        <v>1.17</v>
-      </c>
-      <c r="AE114">
-        <v>1.01</v>
-      </c>
-      <c r="AF114">
-        <v>1.96</v>
-      </c>
-      <c r="AG114">
-        <v>1.69</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.34</v>
-      </c>
       <c r="AK114">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,80 +19054,80 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="O115">
-        <v>3.15</v>
+        <v>2.87</v>
       </c>
       <c r="P115">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q115">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="R115">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="S115">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="T115">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="U115">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="V115">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X115">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y115">
+        <v>1.43</v>
+      </c>
+      <c r="Z115">
+        <v>2.46</v>
+      </c>
+      <c r="AA115">
+        <v>2.33</v>
+      </c>
+      <c r="AB115">
+        <v>1.51</v>
+      </c>
+      <c r="AC115">
+        <v>5</v>
+      </c>
+      <c r="AD115">
+        <v>1.17</v>
+      </c>
+      <c r="AE115">
+        <v>1.01</v>
+      </c>
+      <c r="AF115">
+        <v>1.96</v>
+      </c>
+      <c r="AG115">
+        <v>1.69</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ115">
         <v>1.34</v>
       </c>
-      <c r="Z115">
-        <v>2.78</v>
-      </c>
-      <c r="AA115">
-        <v>2.19</v>
-      </c>
-      <c r="AB115">
-        <v>1.65</v>
-      </c>
-      <c r="AC115">
-        <v>4.2</v>
-      </c>
-      <c r="AD115">
-        <v>1.19</v>
-      </c>
-      <c r="AE115">
-        <v>1.06</v>
-      </c>
-      <c r="AF115">
-        <v>1.87</v>
-      </c>
-      <c r="AG115">
-        <v>1.87</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.24</v>
-      </c>
       <c r="AK115">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19220,13 +19220,13 @@
         <v>2.76</v>
       </c>
       <c r="O116">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P116">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q116">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R116">
         <v>2.1</v>
@@ -19241,7 +19241,7 @@
         <v>2.82</v>
       </c>
       <c r="V116">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W116">
         <v>1.04</v>
@@ -19265,13 +19265,13 @@
         <v>3.28</v>
       </c>
       <c r="AD116">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE116">
         <v>1.05</v>
       </c>
       <c r="AF116">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG116">
         <v>2</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK116">
         <v>1.36</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="O118">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="P118">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -19567,25 +19567,25 @@
         <v>2.65</v>
       </c>
       <c r="V118">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W118">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
         <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="AA118">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB118">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC118">
         <v>2.94</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK118">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,34 +19706,34 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="O119">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P119">
-        <v>4.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q119">
         <v>2.1</v>
       </c>
       <c r="R119">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S119">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T119">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U119">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="V119">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
         <v>1.05</v>
@@ -19748,7 +19748,7 @@
         <v>2</v>
       </c>
       <c r="AB119">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC119">
         <v>3.5</v>
@@ -19757,13 +19757,13 @@
         <v>1.29</v>
       </c>
       <c r="AE119">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF119">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG119">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK119">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,19 +19869,19 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O120">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P120">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
       </c>
       <c r="R120">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
         <v>1.3</v>
@@ -19890,10 +19890,10 @@
         <v>3.05</v>
       </c>
       <c r="U120">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="V120">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W120">
         <v>1.11</v>
@@ -19902,31 +19902,31 @@
         <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z120">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="AA120">
         <v>1.73</v>
       </c>
       <c r="AB120">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC120">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD120">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE120">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF120">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG120">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20032,19 +20032,19 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>4.46</v>
+        <v>3.85</v>
       </c>
       <c r="Q121">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R121">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S121">
         <v>1.44</v>
@@ -20053,7 +20053,7 @@
         <v>2.62</v>
       </c>
       <c r="U121">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="V121">
         <v>1.33</v>
@@ -20062,34 +20062,34 @@
         <v>1.01</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
         <v>1.35</v>
       </c>
       <c r="Z121">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA121">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB121">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC121">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD121">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE121">
         <v>1.01</v>
       </c>
       <c r="AF121">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AG121">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK121">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20207,16 +20207,16 @@
         <v>2.3</v>
       </c>
       <c r="R122">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S122">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T122">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U122">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V122">
         <v>1.65</v>
@@ -20231,28 +20231,28 @@
         <v>1.11</v>
       </c>
       <c r="Z122">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA122">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB122">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC122">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AD122">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE122">
         <v>1.23</v>
       </c>
       <c r="AF122">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG122">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK122">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20364,58 +20364,58 @@
         <v>3.7</v>
       </c>
       <c r="P123">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q123">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S123">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="U123">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W123">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AA123">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AB123">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AC123">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AD123">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE123">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF123">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG123">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK123">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
+        <v>1.67</v>
+      </c>
+      <c r="O124">
+        <v>3.4</v>
+      </c>
+      <c r="P124">
+        <v>5.07</v>
+      </c>
+      <c r="Q124">
+        <v>2.31</v>
+      </c>
+      <c r="R124">
         <v>2.01</v>
       </c>
-      <c r="O124">
-        <v>3.2</v>
-      </c>
-      <c r="P124">
+      <c r="S124">
+        <v>1.44</v>
+      </c>
+      <c r="T124">
+        <v>2.53</v>
+      </c>
+      <c r="U124">
+        <v>2.9</v>
+      </c>
+      <c r="V124">
+        <v>1.35</v>
+      </c>
+      <c r="W124">
+        <v>1.05</v>
+      </c>
+      <c r="X124">
+        <v>1.04</v>
+      </c>
+      <c r="Y124">
+        <v>1.33</v>
+      </c>
+      <c r="Z124">
         <v>3.1</v>
       </c>
-      <c r="Q124">
-        <v>2.49</v>
-      </c>
-      <c r="R124">
-        <v>1.93</v>
-      </c>
-      <c r="S124">
-        <v>1.47</v>
-      </c>
-      <c r="T124">
-        <v>2.75</v>
-      </c>
-      <c r="U124">
-        <v>3.2</v>
-      </c>
-      <c r="V124">
-        <v>1.31</v>
-      </c>
-      <c r="W124">
-        <v>1.01</v>
-      </c>
-      <c r="X124">
-        <v>1.06</v>
-      </c>
-      <c r="Y124">
-        <v>1.4</v>
-      </c>
-      <c r="Z124">
-        <v>2.88</v>
-      </c>
       <c r="AA124">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AB124">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC124">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD124">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE124">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF124">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG124">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,80 +20684,80 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="O125">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="P125">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q125">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="R125">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="S125">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T125">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U125">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V125">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W125">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y125">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z125">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA125">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AB125">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC125">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="AD125">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE125">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG125">
+        <v>1.77</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
+        <v>1.3</v>
+      </c>
+      <c r="AK125">
         <v>1.79</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.28</v>
-      </c>
-      <c r="AK125">
-        <v>2.07</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.35</v>
+        <v>2.22</v>
       </c>
       <c r="O126">
         <v>2.9</v>
       </c>
       <c r="P126">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q126">
         <v>2.9</v>
@@ -20862,31 +20862,31 @@
         <v>1.83</v>
       </c>
       <c r="S126">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T126">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="U126">
         <v>3.42</v>
       </c>
       <c r="V126">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W126">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X126">
         <v>1.1</v>
       </c>
       <c r="Y126">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z126">
         <v>2.49</v>
       </c>
       <c r="AA126">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AB126">
         <v>1.52</v>
@@ -20895,10 +20895,10 @@
         <v>4.75</v>
       </c>
       <c r="AD126">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE126">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF126">
         <v>2.01</v>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
         <v>1.46</v>
@@ -21019,19 +21019,19 @@
         <v>0</v>
       </c>
       <c r="Q127">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="R127">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T127">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="U127">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V127">
         <v>1.44</v>
@@ -21043,31 +21043,31 @@
         <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z127">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA127">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB127">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AC127">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD127">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE127">
         <v>1.11</v>
       </c>
       <c r="AF127">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG127">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21342,22 +21342,22 @@
         <v>2.68</v>
       </c>
       <c r="P129">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
       <c r="Q129">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="R129">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="S129">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T129">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="U129">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V129">
         <v>1.21</v>
@@ -21369,13 +21369,13 @@
         <v>1.07</v>
       </c>
       <c r="Y129">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Z129">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AA129">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AB129">
         <v>1.44</v>
@@ -21384,16 +21384,16 @@
         <v>5</v>
       </c>
       <c r="AD129">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE129">
         <v>1.04</v>
       </c>
       <c r="AF129">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG129">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK129">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,55 +21508,55 @@
         <v>0</v>
       </c>
       <c r="Q130">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R130">
         <v>2.34</v>
       </c>
       <c r="S130">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T130">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U130">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V130">
         <v>1.54</v>
       </c>
       <c r="W130">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
         <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA130">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB130">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AC130">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="AD130">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AE130">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF130">
         <v>1.6</v>
       </c>
       <c r="AG130">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -603,16 +603,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,91 +624,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>5.35</v>
+        <v>2.37</v>
       </c>
       <c r="O2">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>4.46</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T2">
-        <v>3.58</v>
+        <v>3.02</v>
       </c>
       <c r="U2">
+        <v>2.67</v>
+      </c>
+      <c r="V2">
+        <v>1.44</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1.22</v>
+      </c>
+      <c r="Z2">
+        <v>3.7</v>
+      </c>
+      <c r="AA2">
+        <v>1.73</v>
+      </c>
+      <c r="AB2">
+        <v>2.12</v>
+      </c>
+      <c r="AC2">
+        <v>2.92</v>
+      </c>
+      <c r="AD2">
+        <v>1.36</v>
+      </c>
+      <c r="AE2">
+        <v>1.11</v>
+      </c>
+      <c r="AF2">
+        <v>1.52</v>
+      </c>
+      <c r="AG2">
         <v>2.25</v>
       </c>
-      <c r="V2">
-        <v>1.62</v>
-      </c>
-      <c r="W2">
-        <v>1.15</v>
-      </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
-        <v>1.17</v>
-      </c>
-      <c r="Z2">
-        <v>5.25</v>
-      </c>
-      <c r="AA2">
-        <v>1.53</v>
-      </c>
-      <c r="AB2">
-        <v>2.4</v>
-      </c>
-      <c r="AC2">
-        <v>2.2</v>
-      </c>
-      <c r="AD2">
-        <v>1.57</v>
-      </c>
-      <c r="AE2">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>["63"]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.23</v>
       </c>
-      <c r="AF2">
-        <v>1.65</v>
-      </c>
-      <c r="AG2">
-        <v>2.08</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.12</v>
-      </c>
       <c r="AK2">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -766,22 +766,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -790,115 +790,115 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>4.61</v>
       </c>
       <c r="R3">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="T3">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="U3">
         <v>2.25</v>
       </c>
       <c r="V3">
+        <v>1.57</v>
+      </c>
+      <c r="W3">
+        <v>1.14</v>
+      </c>
+      <c r="X3">
+        <v>1.01</v>
+      </c>
+      <c r="Y3">
+        <v>1.1</v>
+      </c>
+      <c r="Z3">
+        <v>5.5</v>
+      </c>
+      <c r="AA3">
         <v>1.44</v>
       </c>
-      <c r="W3">
-        <v>1.08</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1.22</v>
-      </c>
-      <c r="Z3">
-        <v>3.72</v>
-      </c>
-      <c r="AA3">
-        <v>1.68</v>
-      </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="AC3">
-        <v>2.92</v>
+        <v>2.19</v>
       </c>
       <c r="AD3">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF3">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "60"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK3">
-        <v>1.49</v>
+        <v>1.07</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>1.56</v>
+      </c>
+      <c r="O56">
+        <v>4.35</v>
+      </c>
+      <c r="P56">
+        <v>4.65</v>
+      </c>
+      <c r="Q56">
+        <v>2.05</v>
+      </c>
+      <c r="R56">
         <v>2.45</v>
       </c>
-      <c r="O56">
+      <c r="S56">
+        <v>1.2</v>
+      </c>
+      <c r="T56">
         <v>3.5</v>
       </c>
-      <c r="P56">
-        <v>2.35</v>
-      </c>
-      <c r="Q56">
-        <v>2.73</v>
-      </c>
-      <c r="R56">
-        <v>2.29</v>
-      </c>
-      <c r="S56">
-        <v>1.26</v>
-      </c>
-      <c r="T56">
-        <v>3.2</v>
-      </c>
       <c r="U56">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V56">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>4.85</v>
+        <v>5.53</v>
       </c>
       <c r="AA56">
         <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD56">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF56">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="O57">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P57">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q57">
         <v>2.05</v>
       </c>
       <c r="R57">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T57">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U57">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
         <v>1.62</v>
       </c>
       <c r="W57">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9636,28 +9636,28 @@
         <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>5.53</v>
+        <v>4.85</v>
       </c>
       <c r="AA57">
         <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC57">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AD57">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG57">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,40 +9763,40 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="O58">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q58">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="R58">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="S58">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T58">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
         <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
         <v>4.85</v>
@@ -9808,19 +9808,19 @@
         <v>2.37</v>
       </c>
       <c r="AC58">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD58">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE58">
         <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG58">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK58">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O64">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P64">
         <v>4.2</v>
       </c>
       <c r="Q64">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R64">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="S64">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="U64">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="V64">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="AA64">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AB64">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="AC64">
-        <v>3.63</v>
+        <v>2.54</v>
       </c>
       <c r="AD64">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE64">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AG64">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK64">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="O65">
+        <v>3</v>
+      </c>
+      <c r="P65">
         <v>3.95</v>
       </c>
-      <c r="P65">
-        <v>4.2</v>
-      </c>
       <c r="Q65">
-        <v>2.22</v>
+        <v>2.79</v>
       </c>
       <c r="R65">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T65">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="U65">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y65">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z65">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="AA65">
+        <v>2.11</v>
+      </c>
+      <c r="AB65">
         <v>1.7</v>
       </c>
-      <c r="AB65">
-        <v>2.11</v>
-      </c>
       <c r="AC65">
-        <v>2.54</v>
+        <v>3.82</v>
       </c>
       <c r="AD65">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG65">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P66">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q66">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="R66">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S66">
         <v>1.42</v>
       </c>
       <c r="T66">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U66">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y66">
         <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="AA66">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB66">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AC66">
-        <v>4.2</v>
+        <v>3.63</v>
       </c>
       <c r="AD66">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE66">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
         <v>1.9</v>
       </c>
       <c r="AG66">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK66">
-        <v>1.49</v>
+        <v>2.09</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R67">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T67">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="U67">
-        <v>2.53</v>
+        <v>2.96</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.3</v>
+      </c>
+      <c r="Z67">
+        <v>2.99</v>
+      </c>
+      <c r="AA67">
+        <v>2.1</v>
+      </c>
+      <c r="AB67">
+        <v>1.76</v>
+      </c>
+      <c r="AC67">
+        <v>4.2</v>
+      </c>
+      <c r="AD67">
+        <v>1.21</v>
+      </c>
+      <c r="AE67">
         <v>1.03</v>
       </c>
-      <c r="Y67">
-        <v>1.26</v>
-      </c>
-      <c r="Z67">
-        <v>3.35</v>
-      </c>
-      <c r="AA67">
-        <v>1.85</v>
-      </c>
-      <c r="AB67">
-        <v>1.95</v>
-      </c>
-      <c r="AC67">
-        <v>3.25</v>
-      </c>
-      <c r="AD67">
-        <v>1.33</v>
-      </c>
-      <c r="AE67">
-        <v>1.08</v>
-      </c>
       <c r="AF67">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG67">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK67">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
-        <v>3.95</v>
+        <v>2.58</v>
       </c>
       <c r="Q68">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="R68">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S68">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="U68">
-        <v>2.84</v>
+        <v>2.53</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z68">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="AA68">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AB68">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC68">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="AD68">
+        <v>1.33</v>
+      </c>
+      <c r="AE68">
+        <v>1.08</v>
+      </c>
+      <c r="AF68">
+        <v>1.65</v>
+      </c>
+      <c r="AG68">
+        <v>2.08</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.28</v>
       </c>
-      <c r="AE68">
-        <v>1.03</v>
-      </c>
-      <c r="AF68">
-        <v>1.87</v>
-      </c>
-      <c r="AG68">
-        <v>1.9</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.29</v>
-      </c>
       <c r="AK68">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O72">
+        <v>4.8</v>
+      </c>
+      <c r="P72">
+        <v>6.1</v>
+      </c>
+      <c r="Q72">
+        <v>2</v>
+      </c>
+      <c r="R72">
+        <v>2.49</v>
+      </c>
+      <c r="S72">
+        <v>1.22</v>
+      </c>
+      <c r="T72">
         <v>4.5</v>
       </c>
-      <c r="P72">
-        <v>4.65</v>
-      </c>
-      <c r="Q72">
-        <v>1.93</v>
-      </c>
-      <c r="R72">
-        <v>2.5</v>
-      </c>
-      <c r="S72">
-        <v>1.2</v>
-      </c>
-      <c r="T72">
-        <v>3.88</v>
-      </c>
       <c r="U72">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V72">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W72">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA72">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB72">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AC72">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AD72">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE72">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF72">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG72">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="O77">
-        <v>3.45</v>
+        <v>3.84</v>
       </c>
       <c r="P77">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="Q77">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R77">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="S77">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T77">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U77">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="V77">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z77">
-        <v>4.5</v>
+        <v>4.79</v>
       </c>
       <c r="AA77">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB77">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="AC77">
         <v>2.55</v>
       </c>
       <c r="AD77">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE77">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF77">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG77">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK77">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O78">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="P78">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q78">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="R78">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="S78">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="U78">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="V78">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA78">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AB78">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC78">
+        <v>2.55</v>
+      </c>
+      <c r="AD78">
+        <v>1.43</v>
+      </c>
+      <c r="AE78">
+        <v>1.13</v>
+      </c>
+      <c r="AF78">
+        <v>1.5</v>
+      </c>
+      <c r="AG78">
         <v>2.35</v>
-      </c>
-      <c r="AD78">
-        <v>1.57</v>
-      </c>
-      <c r="AE78">
-        <v>1.16</v>
-      </c>
-      <c r="AF78">
-        <v>1.47</v>
-      </c>
-      <c r="AG78">
-        <v>2.53</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="O80">
-        <v>3.84</v>
+        <v>3.67</v>
       </c>
       <c r="P80">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q80">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="R80">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T80">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U80">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="V80">
+        <v>1.61</v>
+      </c>
+      <c r="W80">
+        <v>1.13</v>
+      </c>
+      <c r="X80">
+        <v>1.02</v>
+      </c>
+      <c r="Y80">
+        <v>1.14</v>
+      </c>
+      <c r="Z80">
+        <v>4.65</v>
+      </c>
+      <c r="AA80">
+        <v>1.53</v>
+      </c>
+      <c r="AB80">
+        <v>2.3</v>
+      </c>
+      <c r="AC80">
+        <v>2.35</v>
+      </c>
+      <c r="AD80">
         <v>1.57</v>
-      </c>
-      <c r="W80">
-        <v>1.1</v>
-      </c>
-      <c r="X80">
-        <v>1.01</v>
-      </c>
-      <c r="Y80">
-        <v>1.18</v>
-      </c>
-      <c r="Z80">
-        <v>4.79</v>
-      </c>
-      <c r="AA80">
-        <v>1.6</v>
-      </c>
-      <c r="AB80">
-        <v>2.34</v>
-      </c>
-      <c r="AC80">
-        <v>2.55</v>
-      </c>
-      <c r="AD80">
-        <v>1.47</v>
       </c>
       <c r="AE80">
         <v>1.16</v>
       </c>
       <c r="AF80">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG80">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.54</v>
+        <v>1.28</v>
       </c>
       <c r="O98">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="P98">
-        <v>2.41</v>
+        <v>7</v>
       </c>
       <c r="Q98">
-        <v>3.2</v>
+        <v>1.71</v>
       </c>
       <c r="R98">
-        <v>2.13</v>
+        <v>2.83</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T98">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="U98">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="V98">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="W98">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
+        <v>1.18</v>
+      </c>
+      <c r="Z98">
+        <v>5</v>
+      </c>
+      <c r="AA98">
+        <v>1.5</v>
+      </c>
+      <c r="AB98">
+        <v>2.3</v>
+      </c>
+      <c r="AC98">
+        <v>2.35</v>
+      </c>
+      <c r="AD98">
+        <v>1.57</v>
+      </c>
+      <c r="AE98">
         <v>1.22</v>
       </c>
-      <c r="Z98">
-        <v>4.1</v>
-      </c>
-      <c r="AA98">
-        <v>1.75</v>
-      </c>
-      <c r="AB98">
-        <v>2.03</v>
-      </c>
-      <c r="AC98">
-        <v>2.95</v>
-      </c>
-      <c r="AD98">
-        <v>1.36</v>
-      </c>
-      <c r="AE98">
-        <v>1.15</v>
-      </c>
       <c r="AF98">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG98">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AK98">
-        <v>1.45</v>
+        <v>3.38</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.28</v>
+        <v>2.54</v>
       </c>
       <c r="O99">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>7</v>
+        <v>2.41</v>
       </c>
       <c r="Q99">
-        <v>1.71</v>
+        <v>3.2</v>
       </c>
       <c r="R99">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="S99">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="U99">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="V99">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="W99">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z99">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AA99">
+        <v>1.75</v>
+      </c>
+      <c r="AB99">
+        <v>2.03</v>
+      </c>
+      <c r="AC99">
+        <v>2.95</v>
+      </c>
+      <c r="AD99">
+        <v>1.36</v>
+      </c>
+      <c r="AE99">
+        <v>1.15</v>
+      </c>
+      <c r="AF99">
+        <v>1.6</v>
+      </c>
+      <c r="AG99">
+        <v>2.19</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.5</v>
       </c>
-      <c r="AB99">
-        <v>2.3</v>
-      </c>
-      <c r="AC99">
-        <v>2.35</v>
-      </c>
-      <c r="AD99">
-        <v>1.57</v>
-      </c>
-      <c r="AE99">
-        <v>1.22</v>
-      </c>
-      <c r="AF99">
-        <v>1.85</v>
-      </c>
-      <c r="AG99">
-        <v>1.83</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.13</v>
-      </c>
       <c r="AK99">
-        <v>3.38</v>
+        <v>1.45</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="O100">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="P100">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q100">
-        <v>2.43</v>
+        <v>1.58</v>
       </c>
       <c r="R100">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="S100">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="T100">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="U100">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="V100">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z100">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA100">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AB100">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="AC100">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AD100">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="AE100">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AF100">
         <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AK100">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O101">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>9.199999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="Q101">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="R101">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="S101">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
-        <v>4.5</v>
+        <v>2.91</v>
       </c>
       <c r="U101">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="V101">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z101">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA101">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB101">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC101">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AD101">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AE101">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF101">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG101">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AK101">
-        <v>3.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P102">
-        <v>2.62</v>
+        <v>6.15</v>
       </c>
       <c r="Q102">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="R102">
-        <v>2.11</v>
+        <v>2.57</v>
       </c>
       <c r="S102">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T102">
-        <v>2.91</v>
+        <v>3.7</v>
       </c>
       <c r="U102">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z102">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA102">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AB102">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="AC102">
-        <v>3.25</v>
+        <v>2.16</v>
       </c>
       <c r="AD102">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE102">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF102">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK102">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="O103">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>6.15</v>
+        <v>2.15</v>
       </c>
       <c r="Q103">
-        <v>1.84</v>
+        <v>3.42</v>
       </c>
       <c r="R103">
-        <v>2.57</v>
+        <v>2.21</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T103">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="U103">
+        <v>2.3</v>
+      </c>
+      <c r="V103">
+        <v>1.46</v>
+      </c>
+      <c r="W103">
+        <v>1.07</v>
+      </c>
+      <c r="X103">
+        <v>1.04</v>
+      </c>
+      <c r="Y103">
+        <v>1.2</v>
+      </c>
+      <c r="Z103">
+        <v>4.33</v>
+      </c>
+      <c r="AA103">
+        <v>1.65</v>
+      </c>
+      <c r="AB103">
         <v>2.15</v>
       </c>
-      <c r="V103">
-        <v>1.62</v>
-      </c>
-      <c r="W103">
-        <v>1.13</v>
-      </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
-        <v>1.14</v>
-      </c>
-      <c r="Z103">
-        <v>5.1</v>
-      </c>
-      <c r="AA103">
-        <v>1.5</v>
-      </c>
-      <c r="AB103">
-        <v>2.55</v>
-      </c>
       <c r="AC103">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AD103">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AE103">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="AK103">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O104">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P104">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q104">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="R104">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S104">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="U104">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="V104">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W104">
+        <v>1.05</v>
+      </c>
+      <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
+        <v>1.26</v>
+      </c>
+      <c r="Z104">
+        <v>3.2</v>
+      </c>
+      <c r="AA104">
+        <v>1.89</v>
+      </c>
+      <c r="AB104">
+        <v>1.81</v>
+      </c>
+      <c r="AC104">
+        <v>3.35</v>
+      </c>
+      <c r="AD104">
+        <v>1.27</v>
+      </c>
+      <c r="AE104">
         <v>1.07</v>
       </c>
-      <c r="X104">
-        <v>1.04</v>
-      </c>
-      <c r="Y104">
-        <v>1.2</v>
-      </c>
-      <c r="Z104">
-        <v>4.33</v>
-      </c>
-      <c r="AA104">
-        <v>1.65</v>
-      </c>
-      <c r="AB104">
-        <v>2.15</v>
-      </c>
-      <c r="AC104">
-        <v>2.59</v>
-      </c>
-      <c r="AD104">
-        <v>1.45</v>
-      </c>
-      <c r="AE104">
-        <v>1.17</v>
-      </c>
       <c r="AF104">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="AK104">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,80 +20521,80 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="O124">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P124">
-        <v>5.07</v>
+        <v>3.18</v>
       </c>
       <c r="Q124">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="R124">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S124">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T124">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U124">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V124">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W124">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X124">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y124">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z124">
         <v>3.1</v>
       </c>
       <c r="AA124">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="AB124">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC124">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="AD124">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE124">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG124">
+        <v>1.77</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
+        <v>1.3</v>
+      </c>
+      <c r="AK124">
         <v>1.79</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.28</v>
-      </c>
-      <c r="AK124">
-        <v>2.1</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="O125">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>3.18</v>
+        <v>5.07</v>
       </c>
       <c r="Q125">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="R125">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="S125">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T125">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="U125">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V125">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W125">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z125">
         <v>3.1</v>
       </c>
       <c r="AA125">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AB125">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC125">
-        <v>3.84</v>
+        <v>3.34</v>
       </c>
       <c r="AD125">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE125">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF125">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG125">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK125">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -938,75 +938,75 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="R4">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
         <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AD4">
         <v>1.39</v>
@@ -1015,14 +1015,14 @@
         <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
         <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "53"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,130 +1101,130 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
         <v>2.55</v>
       </c>
       <c r="O5">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
         <v>1.2</v>
       </c>
       <c r="T5">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA5">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
         <v>2.75</v>
       </c>
       <c r="AC5">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD5">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE5">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
         <v>1.38</v>
       </c>
       <c r="AG5">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AK5">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,42 +1264,42 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O6">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q6">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R6">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="S6">
         <v>1.15</v>
@@ -1308,86 +1308,86 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="W6">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.05</v>
       </c>
       <c r="Z6">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA6">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB6">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AC6">
         <v>1.7</v>
       </c>
       <c r="AD6">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="AE6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AF6">
         <v>1.29</v>
       </c>
       <c r="AG6">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "45+3"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "79", "83"]</t>
         </is>
       </c>
       <c r="AJ6">
         <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1442,63 +1442,63 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>3.38</v>
+        <v>3.17</v>
       </c>
       <c r="R7">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
         <v>3.55</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V7">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
         <v>1.14</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA7">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB7">
         <v>2.32</v>
       </c>
       <c r="AC7">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AD7">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE7">
         <v>1.22</v>
@@ -1507,7 +1507,7 @@
         <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1516,41 +1516,41 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1605,63 +1605,63 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q8">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
         <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC8">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD8">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
@@ -1670,7 +1670,7 @@
         <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1679,41 +1679,41 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "63", "90+2"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1765,14 +1765,14 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1785,22 +1785,22 @@
         <v>2.75</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
         <v>1.11</v>
@@ -1809,74 +1809,74 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA9">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
+        <v>1.17</v>
+      </c>
+      <c r="AF9">
+        <v>1.53</v>
+      </c>
+      <c r="AG9">
+        <v>2.38</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>["69", "72", "81", "90+3"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>["90+1"]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.22</v>
+      </c>
+      <c r="AK9">
+        <v>1.49</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>5</v>
+      </c>
+      <c r="AN9">
+        <v>5</v>
+      </c>
+      <c r="AO9">
+        <v>7</v>
+      </c>
+      <c r="AP9">
+        <v>15</v>
+      </c>
+      <c r="AQ9">
         <v>1.13</v>
       </c>
-      <c r="AF9">
-        <v>1.54</v>
-      </c>
-      <c r="AG9">
-        <v>2.29</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.23</v>
-      </c>
-      <c r="AK9">
-        <v>1.51</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-1</v>
-      </c>
-      <c r="AN9">
-        <v>-1</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>-1</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O10">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R10">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="S10">
         <v>1.63</v>
@@ -1960,43 +1960,43 @@
         <v>2.13</v>
       </c>
       <c r="U10">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z10">
         <v>2.28</v>
       </c>
       <c r="AA10">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AB10">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AC10">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AD10">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>2.07</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK10">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.65</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="P11">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="Q11">
-        <v>3.55</v>
+        <v>3.31</v>
       </c>
       <c r="R11">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="S11">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="T11">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="U11">
-        <v>3.82</v>
+        <v>4.8</v>
       </c>
       <c r="V11">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y11">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Z11">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="AA11">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="AB11">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AC11">
-        <v>5.97</v>
+        <v>6.65</v>
       </c>
       <c r="AD11">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="AG11">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,21 +2257,21 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "87"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,100 +2405,100 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="R13">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T13">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="V13">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z13">
-        <v>5.82</v>
+        <v>4.75</v>
       </c>
       <c r="AA13">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AB13">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="AC13">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
         <v>1.45</v>
       </c>
       <c r="AG13">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "51", "63"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "45", "90+2"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
         <v>2.08</v>
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q14">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U14">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB14">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AC14">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2894,36 +2894,36 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
         <v>3</v>
@@ -2932,43 +2932,43 @@
         <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
+        <v>2.9</v>
+      </c>
+      <c r="U16">
         <v>2.75</v>
       </c>
-      <c r="U16">
-        <v>3.14</v>
-      </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB16">
         <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3.77</v>
+        <v>3.62</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
         <v>1.8</v>
@@ -2978,46 +2978,46 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "14"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "72"]</t>
         </is>
       </c>
       <c r="AJ16">
         <v>1.42</v>
       </c>
       <c r="AK16">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3076,35 +3076,35 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="R17">
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
         <v>1.02</v>
@@ -3113,74 +3113,74 @@
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA17">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AB17">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC17">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "43"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3243,58 +3243,58 @@
         </is>
       </c>
       <c r="N18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S18">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T18">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="U18">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Z18">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AA18">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AB18">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AC18">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD18">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
         <v>2.15</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
         <v>1.13</v>
@@ -3415,19 +3415,19 @@
         <v>3.1</v>
       </c>
       <c r="Q19">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S19">
         <v>1.75</v>
       </c>
       <c r="T19">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U19">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="V19">
         <v>1.12</v>
@@ -3436,10 +3436,10 @@
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Y19">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z19">
         <v>1.87</v>
@@ -3448,7 +3448,7 @@
         <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC19">
         <v>7.8</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AG19">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AK19">
         <v>1.48</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q20">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="R20">
         <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -3608,7 +3608,7 @@
         <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB20">
         <v>1.79</v>
@@ -3623,7 +3623,7 @@
         <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG20">
         <v>1.82</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P21">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q21">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R21">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S21">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T21">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
         <v>1.07</v>
@@ -3768,16 +3768,16 @@
         <v>1.44</v>
       </c>
       <c r="Z21">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AA21">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AB21">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC21">
-        <v>4.55</v>
+        <v>5.25</v>
       </c>
       <c r="AD21">
         <v>1.13</v>
@@ -3786,10 +3786,10 @@
         <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,16 +3904,16 @@
         <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T22">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="U22">
         <v>3.14</v>
@@ -3922,19 +3922,19 @@
         <v>1.28</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z22">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AA22">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
         <v>1.6</v>
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W23">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>2.3</v>
       </c>
       <c r="O24">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -4236,7 +4236,7 @@
         <v>1.82</v>
       </c>
       <c r="S24">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="T24">
         <v>2.22</v>
@@ -4275,7 +4275,7 @@
         <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG24">
         <v>1.57</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK24">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
         <v>2.45</v>
@@ -5377,10 +5377,10 @@
         <v>1.95</v>
       </c>
       <c r="S31">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T31">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="U31">
         <v>3.3</v>
@@ -5389,22 +5389,22 @@
         <v>1.28</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Z31">
         <v>2.55</v>
       </c>
       <c r="AA31">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AB31">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC31">
         <v>4.5</v>
@@ -5413,13 +5413,13 @@
         <v>1.17</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AG31">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="O34">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>4.09</v>
+        <v>3.55</v>
       </c>
       <c r="Q34">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="R34">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5887,16 +5887,16 @@
         <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD34">
         <v>1.35</v>
@@ -5908,7 +5908,7 @@
         <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
         <v>1.83</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.61</v>
+        <v>1.69</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P41">
-        <v>2.43</v>
+        <v>4.47</v>
       </c>
       <c r="Q41">
-        <v>3.2</v>
+        <v>2.19</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.3</v>
@@ -7013,10 +7013,10 @@
         <v>3.3</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W41">
         <v>1.08</v>
@@ -7025,31 +7025,31 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA41">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AC41">
-        <v>2.54</v>
+        <v>2.79</v>
       </c>
       <c r="AD41">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>1.49</v>
+        <v>2.17</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="O42">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>4.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q42">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S42">
         <v>1.3</v>
@@ -7176,10 +7176,10 @@
         <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
         <v>1.08</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="AA42">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB42">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="AD42">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O43">
         <v>3.65</v>
@@ -7327,52 +7327,52 @@
         <v>2.11</v>
       </c>
       <c r="Q43">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R43">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="S43">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AA43">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AB43">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC43">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AD43">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE43">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG43">
         <v>2.45</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.25</v>
+        <v>4.73</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P44">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q44">
+        <v>5.31</v>
+      </c>
+      <c r="R44">
+        <v>2.71</v>
+      </c>
+      <c r="S44">
+        <v>1.14</v>
+      </c>
+      <c r="T44">
         <v>5</v>
       </c>
-      <c r="R44">
-        <v>2.8</v>
-      </c>
-      <c r="S44">
-        <v>1.16</v>
-      </c>
-      <c r="T44">
-        <v>4.1</v>
-      </c>
       <c r="U44">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="V44">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="W44">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7517,28 +7517,28 @@
         <v>1.1</v>
       </c>
       <c r="Z44">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="AA44">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AB44">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AC44">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AD44">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AE44">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="AK44">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="O46">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="P46">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Q46">
-        <v>7.21</v>
+        <v>9.68</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U46">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="V46">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
         <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z46">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA46">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AB46">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC46">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AG46">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O47">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P47">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="Q47">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="R47">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S47">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T47">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U47">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="V47">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W47">
         <v>1.01</v>
@@ -8003,19 +8003,19 @@
         <v>1.16</v>
       </c>
       <c r="Y47">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z47">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA47">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AB47">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC47">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AD47">
         <v>1.12</v>
@@ -8027,7 +8027,7 @@
         <v>2.2</v>
       </c>
       <c r="AG47">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AK47">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P53">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q53">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R53">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S53">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U53">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V53">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y53">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z53">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AA53">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB53">
         <v>1.78</v>
       </c>
       <c r="AC53">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE53">
         <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK53">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.56</v>
+        <v>2.45</v>
       </c>
       <c r="O56">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>4.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q56">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T56">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U56">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V56">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>5.53</v>
+        <v>4.85</v>
       </c>
       <c r="AA56">
         <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC56">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD56">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AK56">
-        <v>2.38</v>
+        <v>1.41</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="O57">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P57">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="Q57">
         <v>2.05</v>
       </c>
       <c r="R57">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S57">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V57">
         <v>1.62</v>
       </c>
       <c r="W57">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9636,28 +9636,28 @@
         <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.85</v>
+        <v>5.53</v>
       </c>
       <c r="AA57">
         <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC57">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AD57">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG57">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,40 +9763,40 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P58">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q58">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="R58">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="S58">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="U58">
         <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z58">
         <v>4.85</v>
@@ -9808,19 +9808,19 @@
         <v>2.37</v>
       </c>
       <c r="AC58">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD58">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE58">
         <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="O59">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q59">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="R59">
         <v>1.95</v>
@@ -9953,31 +9953,31 @@
         <v>1.28</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Z59">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AA59">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="AB59">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC59">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD59">
         <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
         <v>2.05</v>
@@ -9999,7 +9999,7 @@
         <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.22</v>
+        <v>9.25</v>
       </c>
       <c r="O61">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="P61">
-        <v>11</v>
+        <v>1.23</v>
       </c>
       <c r="Q61">
-        <v>1.48</v>
+        <v>6.95</v>
       </c>
       <c r="R61">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="S61">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T61">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC61">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD61">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE61">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG61">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
+        <v>4.1</v>
+      </c>
+      <c r="AK61">
         <v>1.04</v>
-      </c>
-      <c r="AK61">
-        <v>4.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>9.25</v>
+        <v>1.22</v>
       </c>
       <c r="O62">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="P62">
-        <v>1.23</v>
+        <v>11</v>
       </c>
       <c r="Q62">
-        <v>6.95</v>
+        <v>1.48</v>
       </c>
       <c r="R62">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="S62">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T62">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="U62">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z62">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA62">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AB62">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AD62">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE62">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF62">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG62">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="AK62">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>4.4</v>
+        <v>5.04</v>
       </c>
       <c r="Q71">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="R71">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S71">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
+        <v>3.29</v>
+      </c>
+      <c r="U71">
+        <v>2.56</v>
+      </c>
+      <c r="V71">
+        <v>1.48</v>
+      </c>
+      <c r="W71">
+        <v>1.06</v>
+      </c>
+      <c r="X71">
+        <v>1.02</v>
+      </c>
+      <c r="Y71">
+        <v>1.2</v>
+      </c>
+      <c r="Z71">
+        <v>3.7</v>
+      </c>
+      <c r="AA71">
+        <v>1.8</v>
+      </c>
+      <c r="AB71">
+        <v>2</v>
+      </c>
+      <c r="AC71">
         <v>2.81</v>
       </c>
-      <c r="U71">
-        <v>2.75</v>
-      </c>
-      <c r="V71">
-        <v>1.35</v>
-      </c>
-      <c r="W71">
-        <v>1.05</v>
-      </c>
-      <c r="X71">
-        <v>1.01</v>
-      </c>
-      <c r="Y71">
-        <v>1.31</v>
-      </c>
-      <c r="Z71">
-        <v>3.08</v>
-      </c>
-      <c r="AA71">
-        <v>1.93</v>
-      </c>
-      <c r="AB71">
-        <v>1.75</v>
-      </c>
-      <c r="AC71">
-        <v>3.42</v>
-      </c>
       <c r="AD71">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG71">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK71">
         <v>2.11</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="O78">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P78">
-        <v>2.15</v>
+        <v>3.27</v>
       </c>
       <c r="Q78">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="R78">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T78">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="U78">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="V78">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="Z78">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA78">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AB78">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="AC78">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="AD78">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AE78">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AF78">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AG78">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
-        <v>3.27</v>
+        <v>2.15</v>
       </c>
       <c r="Q79">
-        <v>2.17</v>
+        <v>3.4</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S79">
+        <v>1.29</v>
+      </c>
+      <c r="T79">
+        <v>3.4</v>
+      </c>
+      <c r="U79">
+        <v>2.45</v>
+      </c>
+      <c r="V79">
+        <v>1.53</v>
+      </c>
+      <c r="W79">
+        <v>1.11</v>
+      </c>
+      <c r="X79">
+        <v>1.02</v>
+      </c>
+      <c r="Y79">
         <v>1.2</v>
       </c>
-      <c r="T79">
-        <v>4.15</v>
-      </c>
-      <c r="U79">
-        <v>2.05</v>
-      </c>
-      <c r="V79">
-        <v>1.77</v>
-      </c>
-      <c r="W79">
-        <v>1.16</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.06</v>
-      </c>
       <c r="Z79">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA79">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AB79">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="AC79">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="AD79">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="AE79">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG79">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="O102">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>6.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q102">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="R102">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="S102">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T102">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="U102">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="V102">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="W102">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z102">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA102">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AB102">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="AC102">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="AD102">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AE102">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF102">
+        <v>1.75</v>
+      </c>
+      <c r="AG102">
+        <v>1.95</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.23</v>
+      </c>
+      <c r="AK102">
         <v>1.73</v>
-      </c>
-      <c r="AG102">
-        <v>2.08</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.11</v>
-      </c>
-      <c r="AK102">
-        <v>3</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="O104">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P104">
+        <v>6.15</v>
+      </c>
+      <c r="Q104">
+        <v>1.84</v>
+      </c>
+      <c r="R104">
+        <v>2.57</v>
+      </c>
+      <c r="S104">
+        <v>1.22</v>
+      </c>
+      <c r="T104">
         <v>3.7</v>
       </c>
-      <c r="Q104">
-        <v>2.43</v>
-      </c>
-      <c r="R104">
-        <v>2.25</v>
-      </c>
-      <c r="S104">
-        <v>1.35</v>
-      </c>
-      <c r="T104">
-        <v>2.9</v>
-      </c>
       <c r="U104">
-        <v>2.74</v>
+        <v>2.15</v>
       </c>
       <c r="V104">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z104">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA104">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="AC104">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="AD104">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AE104">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF104">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK104">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O107">
         <v>2.95</v>
@@ -17759,22 +17759,22 @@
         <v>3.1</v>
       </c>
       <c r="Q107">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R107">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="S107">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="T107">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="U107">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="V107">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W107">
         <v>1.02</v>
@@ -17783,31 +17783,31 @@
         <v>1.07</v>
       </c>
       <c r="Y107">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="Z107">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AA107">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AB107">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC107">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD107">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE107">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG107">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK107">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18565,52 +18565,52 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O112">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
         <v>3.35</v>
       </c>
       <c r="Q112">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R112">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S112">
+        <v>1.39</v>
+      </c>
+      <c r="T112">
+        <v>2.88</v>
+      </c>
+      <c r="U112">
+        <v>2.63</v>
+      </c>
+      <c r="V112">
         <v>1.41</v>
       </c>
-      <c r="T112">
-        <v>2.56</v>
-      </c>
-      <c r="U112">
-        <v>2.92</v>
-      </c>
-      <c r="V112">
-        <v>1.36</v>
-      </c>
       <c r="W112">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA112">
         <v>1.98</v>
       </c>
       <c r="AB112">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC112">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD112">
         <v>1.24</v>
@@ -18619,10 +18619,10 @@
         <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AG112">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="O113">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P113">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q113">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="R113">
         <v>2</v>
       </c>
       <c r="S113">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T113">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U113">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="V113">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W113">
         <v>1.04</v>
       </c>
       <c r="X113">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y113">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z113">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA113">
         <v>2.12</v>
       </c>
       <c r="AB113">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC113">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD113">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF113">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG113">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AK113">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,61 +18891,61 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O114">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P114">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q114">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="R114">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S114">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T114">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="U114">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="V114">
         <v>1.33</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X114">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z114">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA114">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AB114">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC114">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD114">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE114">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF114">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG114">
         <v>1.87</v>
@@ -18964,7 +18964,7 @@
         <v>1.24</v>
       </c>
       <c r="AK114">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O115">
         <v>2.87</v>
       </c>
       <c r="P115">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q115">
         <v>3.5</v>
       </c>
       <c r="R115">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S115">
         <v>1.54</v>
       </c>
       <c r="T115">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U115">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V115">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W115">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X115">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y115">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z115">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AA115">
         <v>2.33</v>
       </c>
       <c r="AB115">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC115">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD115">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE115">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AG115">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AK115">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL115">
         <v>0</v>

--- a/jogos_2026-08-28.xlsx
+++ b/jogos_2026-08-28.xlsx
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -7636,11 +7636,11 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c